--- a/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B81BFB6-692A-4587-96BA-A5FD94766F63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{460DC738-4CE5-4F09-9F5B-069026BAD2DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57495" yWindow="5085" windowWidth="31395" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-3250" yWindow="3200" windowWidth="38610" windowHeight="16040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -87,9 +87,6 @@
     <t>InventoryUI</t>
   </si>
   <si>
-    <t>CrashSprintPanel</t>
-  </si>
-  <si>
     <t>GameSettlePanel</t>
   </si>
   <si>
@@ -106,9 +103,6 @@
   </si>
   <si>
     <t>KitchenPanel</t>
-  </si>
-  <si>
-    <t>WitchPoisonPanel</t>
   </si>
   <si>
     <t>PhotoGamePanel</t>
@@ -324,6 +318,14 @@
   </si>
   <si>
     <t>UIDialogue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CrashSprintPanel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WitchPoisonPanel</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -429,7 +431,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -458,31 +460,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -787,19 +765,19 @@
         <v>3</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="F1" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>66</v>
-      </c>
-      <c r="G1" s="15" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -810,18 +788,18 @@
         <v>4</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="F2" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="G2" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>4</v>
       </c>
     </row>
@@ -830,22 +808,22 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F3" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -853,19 +831,19 @@
         <v>5</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="F4" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="G4" s="17" t="s">
-        <v>70</v>
+        <v>57</v>
+      </c>
+      <c r="F4" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -873,19 +851,19 @@
         <v>6</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="F5" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="G5" s="17" t="s">
-        <v>71</v>
+        <v>92</v>
+      </c>
+      <c r="F5" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -893,19 +871,19 @@
         <v>7</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="F6" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="G6" s="17" t="s">
-        <v>72</v>
+        <v>57</v>
+      </c>
+      <c r="F6" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -913,19 +891,19 @@
         <v>8</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="F7" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="G7" s="17" t="s">
-        <v>73</v>
+        <v>57</v>
+      </c>
+      <c r="F7" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -933,19 +911,19 @@
         <v>9</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="F8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="G8" s="17" t="s">
-        <v>74</v>
+        <v>57</v>
+      </c>
+      <c r="F8" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -953,19 +931,19 @@
         <v>10</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="F9" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="G9" s="17" t="s">
-        <v>75</v>
+        <v>92</v>
+      </c>
+      <c r="F9" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -973,19 +951,19 @@
         <v>11</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="F10" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="G10" s="17" t="s">
-        <v>76</v>
+        <v>92</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="F10" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -993,19 +971,19 @@
         <v>12</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="F11" s="18" t="b">
+        <v>57</v>
+      </c>
+      <c r="F11" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="G11" s="17" t="s">
-        <v>77</v>
+      <c r="G11" s="4" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -1013,19 +991,19 @@
         <v>13</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="F12" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="G12" s="17" t="s">
-        <v>78</v>
+        <v>57</v>
+      </c>
+      <c r="F12" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -1033,19 +1011,19 @@
         <v>14</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="F13" s="18" t="b">
+        <v>92</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="F13" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="G13" s="17" t="s">
-        <v>79</v>
+      <c r="G13" s="4" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -1053,19 +1031,19 @@
         <v>15</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="F14" s="18" t="b">
+        <v>57</v>
+      </c>
+      <c r="F14" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="G14" s="17" t="s">
-        <v>80</v>
+      <c r="G14" s="4" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -1073,19 +1051,19 @@
         <v>16</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="F15" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="G15" s="17" t="s">
-        <v>81</v>
+        <v>92</v>
+      </c>
+      <c r="F15" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -1093,19 +1071,19 @@
         <v>17</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="F16" s="18" t="b">
+        <v>57</v>
+      </c>
+      <c r="F16" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="G16" s="17" t="s">
-        <v>82</v>
+      <c r="G16" s="4" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.3">
@@ -1113,219 +1091,219 @@
         <v>18</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="F17" s="18" t="b">
+        <v>92</v>
+      </c>
+      <c r="F17" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="G17" s="17" t="s">
-        <v>83</v>
+      <c r="G17" s="4" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B18" s="2" t="s">
-        <v>19</v>
+        <v>94</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="F18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="G18" s="17" t="s">
-        <v>84</v>
+        <v>57</v>
+      </c>
+      <c r="F18" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B19" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="F19" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="G19" s="17" t="s">
-        <v>85</v>
+        <v>57</v>
+      </c>
+      <c r="F19" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B20" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="F20" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="G20" s="17" t="s">
-        <v>86</v>
+        <v>57</v>
+      </c>
+      <c r="F20" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B21" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="F21" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="G21" s="17" t="s">
-        <v>87</v>
+        <v>57</v>
+      </c>
+      <c r="F21" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B22" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="F22" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="G22" s="17" t="s">
-        <v>88</v>
+        <v>57</v>
+      </c>
+      <c r="F22" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B23" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="F23" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="G23" s="17" t="s">
-        <v>89</v>
+        <v>57</v>
+      </c>
+      <c r="F23" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B24" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="F24" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="G24" s="17" t="s">
-        <v>90</v>
+        <v>57</v>
+      </c>
+      <c r="F24" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B25" s="2" t="s">
-        <v>26</v>
+        <v>95</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="F25" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="G25" s="17" t="s">
-        <v>91</v>
+        <v>57</v>
+      </c>
+      <c r="F25" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B26" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="F26" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="17" t="s">
-        <v>92</v>
+        <v>57</v>
+      </c>
+      <c r="F26" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B27" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="F27" s="18" t="b">
+        <v>57</v>
+      </c>
+      <c r="F27" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="G27" s="17" t="s">
-        <v>93</v>
+      <c r="G27" s="4" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.3">
@@ -1346,5 +1324,6 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{460DC738-4CE5-4F09-9F5B-069026BAD2DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D523AA2-1A76-4ECC-9B9F-475E00418FDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-3250" yWindow="3200" windowWidth="38610" windowHeight="16040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="4840" windowWidth="38610" windowHeight="16040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="99">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -327,6 +327,17 @@
   <si>
     <t>WitchPoisonPanel</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>超市商店</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SuperMarketUI</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/SupermarketUI/SuperMarketUI.prefab</t>
   </si>
 </sst>
 </file>
@@ -1307,7 +1318,24 @@
       </c>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B28" s="2"/>
+      <c r="B28" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="F28" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B29" s="2"/>

--- a/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D523AA2-1A76-4ECC-9B9F-475E00418FDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F1C3F36-8505-4C97-A33F-FF7AD9CA8BA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="4840" windowWidth="38610" windowHeight="16040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8590" yWindow="2120" windowWidth="42470" windowHeight="16040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="102">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -338,6 +338,16 @@
   </si>
   <si>
     <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/SupermarketUI/SuperMarketUI.prefab</t>
+  </si>
+  <si>
+    <t>FruitShopUI</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/FruitShopUI/FruitShopUI.prefab</t>
+  </si>
+  <si>
+    <t>果蔬店商店</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1338,7 +1348,24 @@
       </c>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B29" s="2"/>
+      <c r="B29" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="F29" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B30" s="2"/>

--- a/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F1C3F36-8505-4C97-A33F-FF7AD9CA8BA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A0FEEBA-51B5-423E-B2BC-E626650A1CEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8590" yWindow="2120" windowWidth="42470" windowHeight="16040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6640" yWindow="2540" windowWidth="42470" windowHeight="16040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="105">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -347,6 +347,16 @@
   </si>
   <si>
     <t>果蔬店商店</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SexToyStoreUI</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/SexToyStoreUI/SexToyStoreUI.prefab</t>
+  </si>
+  <si>
+    <t>情趣用品店</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1368,7 +1378,24 @@
       </c>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B30" s="2"/>
+      <c r="B30" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="F30" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B31" s="2"/>

--- a/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A0FEEBA-51B5-423E-B2BC-E626650A1CEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA65B57A-6ABC-4AED-BA1E-195E6FBEA67E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6640" yWindow="2540" windowWidth="42470" windowHeight="16040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3900" yWindow="3880" windowWidth="42470" windowHeight="16040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="108">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -357,6 +357,16 @@
   </si>
   <si>
     <t>情趣用品店</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FishShopUI</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/FishShopUI/FishShopUI.prefab</t>
+  </si>
+  <si>
+    <t>钓鱼商店</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1398,7 +1408,24 @@
       </c>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B31" s="2"/>
+      <c r="B31" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="F31" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B32" s="2"/>

--- a/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA65B57A-6ABC-4AED-BA1E-195E6FBEA67E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79BA06E4-4C24-402F-A430-68FCD19F0165}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3900" yWindow="3880" windowWidth="42470" windowHeight="16040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5500" yWindow="3720" windowWidth="38610" windowHeight="19220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="111">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -368,6 +368,16 @@
   <si>
     <t>钓鱼商店</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PopClawMachineTipUI</t>
+  </si>
+  <si>
+    <t>娃娃机启动UI</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/PopClawMachineTipUI/PopClawMachineTipUI.prefab</t>
   </si>
 </sst>
 </file>
@@ -1428,7 +1438,24 @@
       </c>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B32" s="2"/>
+      <c r="B32" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="F32" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>109</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60516735-855F-4F47-9299-40318F2B7696}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView xWindow="0" yWindow="1660" windowWidth="38610" windowHeight="19220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="113">
   <si>
     <t>##var</t>
   </si>
@@ -357,19 +363,24 @@
   </si>
   <si>
     <t>娃娃机启动UI</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/ClawMachineUI/ClawMachineUI.prefab</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>ClawMachineUI</t>
+  </si>
+  <si>
+    <t>娃娃机主UI</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="25">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -381,27 +392,30 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF1F2329"/>
       <name val="等线"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -409,155 +423,12 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="35">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -566,7 +437,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.599993896298105"/>
+        <fgColor theme="3" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -576,194 +447,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -786,273 +471,31 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1064,66 +507,25 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="50">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="常规 2" xfId="49"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1381,26 +783,26 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:G32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G33"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.66666666666667" style="1"/>
-    <col min="2" max="2" width="28.5833333333333" style="1" customWidth="1"/>
-    <col min="3" max="3" width="100.083333333333" style="1" customWidth="1"/>
-    <col min="4" max="4" width="25.1666666666667" style="1" customWidth="1"/>
-    <col min="5" max="5" width="23.6666666666667" style="1" customWidth="1"/>
-    <col min="6" max="6" width="17.6666666666667" style="1" customWidth="1"/>
-    <col min="7" max="7" width="24.1666666666667" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.66666666666667" style="1"/>
+    <col min="1" max="1" width="8.6640625" style="1"/>
+    <col min="2" max="2" width="28.58203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="100.08203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="25.1640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="23.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="24.1640625" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1423,7 +825,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -1446,7 +848,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -1469,7 +871,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
         <v>19</v>
       </c>
@@ -1489,7 +891,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" ht="19.5" customHeight="1" spans="1:7">
+    <row r="5" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
         <v>24</v>
       </c>
@@ -1509,7 +911,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
         <v>28</v>
       </c>
@@ -1529,7 +931,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
         <v>31</v>
       </c>
@@ -1549,7 +951,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B8" s="2" t="s">
         <v>34</v>
       </c>
@@ -1569,7 +971,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
         <v>37</v>
       </c>
@@ -1589,7 +991,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B10" s="2" t="s">
         <v>40</v>
       </c>
@@ -1609,7 +1011,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B11" s="2" t="s">
         <v>44</v>
       </c>
@@ -1629,7 +1031,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B12" s="2" t="s">
         <v>47</v>
       </c>
@@ -1649,7 +1051,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
         <v>50</v>
       </c>
@@ -1669,7 +1071,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B14" s="2" t="s">
         <v>53</v>
       </c>
@@ -1689,7 +1091,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B15" s="2" t="s">
         <v>56</v>
       </c>
@@ -1709,7 +1111,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B16" s="2" t="s">
         <v>59</v>
       </c>
@@ -1729,7 +1131,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="17" spans="2:7">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B17" s="2" t="s">
         <v>62</v>
       </c>
@@ -1749,7 +1151,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="18" spans="2:7">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B18" s="2" t="s">
         <v>65</v>
       </c>
@@ -1769,7 +1171,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="2:7">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B19" s="2" t="s">
         <v>68</v>
       </c>
@@ -1789,7 +1191,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="20" spans="2:7">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B20" s="2" t="s">
         <v>71</v>
       </c>
@@ -1809,7 +1211,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="21" spans="2:7">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B21" s="2" t="s">
         <v>74</v>
       </c>
@@ -1829,7 +1231,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="22" spans="2:7">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B22" s="2" t="s">
         <v>77</v>
       </c>
@@ -1849,7 +1251,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="23" spans="2:7">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B23" s="2" t="s">
         <v>80</v>
       </c>
@@ -1869,7 +1271,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="24" spans="2:7">
+    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B24" s="2" t="s">
         <v>83</v>
       </c>
@@ -1889,7 +1291,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="25" spans="2:7">
+    <row r="25" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B25" s="2" t="s">
         <v>86</v>
       </c>
@@ -1909,7 +1311,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="26" spans="2:7">
+    <row r="26" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B26" s="2" t="s">
         <v>89</v>
       </c>
@@ -1929,7 +1331,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="27" spans="2:7">
+    <row r="27" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B27" s="2" t="s">
         <v>92</v>
       </c>
@@ -1949,7 +1351,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="28" spans="2:7">
+    <row r="28" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B28" s="2" t="s">
         <v>95</v>
       </c>
@@ -1969,7 +1371,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="29" spans="2:7">
+    <row r="29" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B29" s="2" t="s">
         <v>98</v>
       </c>
@@ -1989,7 +1391,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="2:7">
+    <row r="30" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B30" s="2" t="s">
         <v>101</v>
       </c>
@@ -2009,7 +1411,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="31" spans="2:7">
+    <row r="31" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B31" s="2" t="s">
         <v>104</v>
       </c>
@@ -2029,7 +1431,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="32" spans="2:7">
+    <row r="32" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B32" s="2" t="s">
         <v>107</v>
       </c>
@@ -2049,9 +1451,29 @@
         <v>109</v>
       </c>
     </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B33" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F33" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G33" s="11" t="s">
+        <v>112</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
@@ -1,39 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
+  <fileSharing readOnlyRecommended="0" userName="Lumino Game 03"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60516735-855F-4F47-9299-40318F2B7696}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1660" windowWidth="38610" windowHeight="19220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView activeTab="0" xWindow="240" yWindow="60" windowWidth="38610" windowHeight="19220" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
+    <ext uri="smNativeData">
+      <pm:revision xmlns:pm="smNativeData" day="1783044432" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
+      <pm:docPrefs xmlns:pm="smNativeData" id="1783044432" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
+      <pm:compatibility xmlns:pm="smNativeData" id="1783044432" overlapCells="1"/>
+      <pm:defCurrency xmlns:pm="smNativeData" id="1783044432"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="122">
   <si>
     <t>##var</t>
   </si>
@@ -251,7 +241,7 @@
     <t>FactoryMaterialSelectPanel</t>
   </si>
   <si>
-    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/Factory/FactoryMaterialSelectPanel.prefab</t>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/FactoryUI/FactoryMaterialSelectPanel.prefab</t>
   </si>
   <si>
     <t>工厂材料选择面板</t>
@@ -260,7 +250,7 @@
     <t>FactoryProductSelectPanel</t>
   </si>
   <si>
-    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/Factory/FactoryProductSelectPanel.prefab</t>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/FactoryUI/FactoryProductSelectPanel.prefab</t>
   </si>
   <si>
     <t>工厂产品选择面板</t>
@@ -269,7 +259,7 @@
     <t>FactoryMainPanel</t>
   </si>
   <si>
-    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/Factory/FactoryMainPanel.prefab</t>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/FactoryUI/FactoryMainPanel.prefab</t>
   </si>
   <si>
     <t>工厂主面板</t>
@@ -365,70 +355,119 @@
     <t>娃娃机启动UI</t>
   </si>
   <si>
+    <t>ClawMachineUI</t>
+  </si>
+  <si>
     <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/ClawMachineUI/ClawMachineUI.prefab</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>ClawMachineUI</t>
   </si>
   <si>
     <t>娃娃机主UI</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>FactoryMoldSettlePanel</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/FactoryUI/FactoryMoldSettlePanel.prefab</t>
+  </si>
+  <si>
+    <t>工厂模具结算面板</t>
+  </si>
+  <si>
+    <t>FactoryMoldMgPanel</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/FactoryUI/FactoryMoldMgPanel.prefab</t>
+  </si>
+  <si>
+    <t>工厂模具管理面板</t>
+  </si>
+  <si>
+    <t>FactorySettlePanel</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/FactoryUI/FactorySettlePanel.prefab</t>
+  </si>
+  <si>
+    <t>工厂结算面板</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="8">
+    <numFmt numFmtId="5" formatCode="#,##0\ &quot;¥&quot;;\-#,##0\ &quot;¥&quot;"/>
+    <numFmt numFmtId="6" formatCode="#,##0\ &quot;¥&quot;;[Red]\-#,##0\ &quot;¥&quot;"/>
+    <numFmt numFmtId="7" formatCode="#,##0.00\ &quot;¥&quot;;\-#,##0.00\ &quot;¥&quot;"/>
+    <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;¥&quot;;[Red]\-#,##0.00\ &quot;¥&quot;"/>
+    <numFmt numFmtId="42" formatCode="_-* #,##0\ &quot;¥&quot;_-;\-* #,##0\ &quot;¥&quot;_-;_-* &quot;-&quot;\ &quot;¥&quot;_-;_-@_-"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0\ _¥_-;\-* #,##0\ _¥_-;_-* &quot;-&quot;\ _¥_-;_-@_-"/>
+    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;¥&quot;_-;\-* #,##0.00\ &quot;¥&quot;_-;_-* &quot;-&quot;??\ &quot;¥&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _¥_-;\-* #,##0.00\ _¥_-;_-* &quot;-&quot;??\ _¥_-;_-@_-"/>
+  </numFmts>
+  <fonts count="4">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1783044432" ulstyle="none" kern="1">
+            <pm:latin face="等线" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <scheme val="minor"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1783044432" ulstyle="none" kern="1">
+            <pm:latin face="Arial" sz="200" lang="default"/>
+            <pm:cs face="Times New Roman" sz="200" lang="default"/>
+            <pm:ea face="SimSun" sz="200" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <color rgb="FF000000"/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
-      <scheme val="minor"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1783044432" ulstyle="none" kern="1">
+            <pm:latin face="等线" sz="200" lang="default"/>
+            <pm:cs face="Times New Roman" sz="200" lang="default"/>
+            <pm:ea face="SimSun" sz="200" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <color rgb="FF1F2329"/>
       <sz val="11"/>
-      <color rgb="FF1F2329"/>
-      <name val="等线"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1783044432" fgClr="1F2329" ulstyle="none" kern="1">
+            <pm:latin face="等线" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -436,25 +475,61 @@
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFACB9CA"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1783044432" type="1" fgLvl="100" fgClr="00ACB9CA" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FF5B9BD5"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1783044432" type="1" fgLvl="100" fgClr="005B9BD5" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1783044432" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783044432"/>
+        </ext>
+      </extLst>
     </border>
     <border>
       <left style="thin">
@@ -469,21 +544,90 @@
       <bottom style="thin">
         <color rgb="FFDEE0E3"/>
       </bottom>
-      <diagonal/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783044432">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783044432"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783044432"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783044432"/>
+        </ext>
+      </extLst>
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -492,40 +636,36 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
+    <cellStyle name="常规 2" xfId="1"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="smNativeData">
+      <pm:charStyles xmlns:pm="smNativeData" id="1783044432" count="1">
+        <pm:charStyle name="普通" fontId="0" Id="1"/>
+      </pm:charStyles>
+      <pm:colors xmlns:pm="smNativeData" id="1783044432" count="5">
+        <pm:color name="颜色 24" rgb="1F2329"/>
+        <pm:color name="颜色 25" rgb="ACB9CA"/>
+        <pm:color name="20% 灰色" rgb="000000"/>
+        <pm:color name="颜色 27" rgb="5B9BD5"/>
+        <pm:color name="颜色 28" rgb="DEE0E3"/>
+      </pm:colors>
     </ext>
   </extLst>
 </styleSheet>
@@ -542,106 +682,46 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="EEECE1"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="1F497D"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:latin typeface="等线"/>
+        <a:ea typeface="SimSun"/>
+        <a:cs typeface="Times New Roman"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -653,827 +733,969 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr>
+        <a:prstTxWarp prst="textNoShape">
+          <a:avLst/>
+        </a:prstTxWarp>
+        <a:noAutofit/>
+      </a:bodyPr>
+      <a:lstStyle>
+        <a:defPPr>
+          <a:defRPr/>
+        </a:defPPr>
+      </a:lstStyle>
+      <a:style>
+        <a:lnRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G33"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <dimension ref="A1:G36"/>
+  <sheetFormatPr defaultRowHeight="13.45"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" style="1"/>
-    <col min="2" max="2" width="28.58203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="100.08203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="25.1640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="23.6640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="17.6640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="24.1640625" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.6640625" style="1"/>
+    <col min="1" max="1" width="8.663793" customWidth="1" style="2"/>
+    <col min="2" max="2" width="28.577586" customWidth="1" style="2"/>
+    <col min="3" max="3" width="100.077586" customWidth="1" style="2"/>
+    <col min="4" max="4" width="25.163793" customWidth="1" style="2"/>
+    <col min="5" max="5" width="23.663793" customWidth="1" style="2"/>
+    <col min="6" max="6" width="17.663793" customWidth="1" style="2"/>
+    <col min="7" max="7" width="24.163793" customWidth="1" style="2"/>
+    <col min="8" max="16384" width="8.663793" customWidth="1" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
+    <row r="1" spans="1:7">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:7">
+      <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:7">
+      <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B4" s="2" t="s">
+    <row r="4" spans="2:7">
+      <c r="B4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="6" t="s">
         <v>21</v>
       </c>
       <c r="E4" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G4" s="4" t="s">
+      <c r="F4" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="2" t="s">
+    <row r="5" spans="2:7" ht="19.50" customHeight="1">
+      <c r="B5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="6" t="s">
         <v>21</v>
       </c>
       <c r="E5" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G5" s="4" t="s">
+      <c r="F5" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B6" s="2" t="s">
+    <row r="6" spans="2:7">
+      <c r="B6" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="6" t="s">
         <v>21</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G6" s="4" t="s">
+      <c r="F6" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B7" s="2" t="s">
+    <row r="7" spans="2:7">
+      <c r="B7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="6" t="s">
         <v>21</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F7" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G7" s="4" t="s">
+      <c r="F7" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B8" s="2" t="s">
+    <row r="8" spans="2:7">
+      <c r="B8" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="6" t="s">
         <v>21</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F8" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G8" s="4" t="s">
+      <c r="F8" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B9" s="2" t="s">
+    <row r="9" spans="2:7">
+      <c r="B9" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="F9" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G9" s="4" t="s">
+      <c r="F9" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" s="5" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B10" s="2" t="s">
+    <row r="10" spans="2:7">
+      <c r="B10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="E10" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="F10" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G10" s="4" t="s">
+      <c r="F10" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B11" s="2" t="s">
+    <row r="11" spans="2:7">
+      <c r="B11" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="6" t="s">
         <v>21</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F11" s="4" t="b">
+      <c r="F11" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="5" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B12" s="2" t="s">
+    <row r="12" spans="2:7">
+      <c r="B12" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="6" t="s">
         <v>21</v>
       </c>
       <c r="E12" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F12" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G12" s="4" t="s">
+      <c r="F12" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12" s="5" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B13" s="2" t="s">
+    <row r="13" spans="2:7">
+      <c r="B13" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="E13" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="F13" s="4" t="b">
+      <c r="F13" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G13" s="5" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B14" s="2" t="s">
+    <row r="14" spans="2:7">
+      <c r="B14" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="6" t="s">
         <v>26</v>
       </c>
       <c r="E14" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F14" s="4" t="b">
+      <c r="F14" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="5" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B15" s="2" t="s">
+    <row r="15" spans="2:7">
+      <c r="B15" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="6" t="s">
         <v>21</v>
       </c>
       <c r="E15" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="F15" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G15" s="4" t="s">
+      <c r="F15" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15" s="5" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B16" s="2" t="s">
+    <row r="16" spans="2:7">
+      <c r="B16" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="6" t="s">
         <v>21</v>
       </c>
       <c r="E16" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F16" s="4" t="b">
+      <c r="F16" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="5" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B17" s="2" t="s">
+    <row r="17" spans="2:7">
+      <c r="B17" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="6" t="s">
         <v>21</v>
       </c>
       <c r="E17" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="F17" s="4" t="b">
+      <c r="F17" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="G17" s="5" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B18" s="2" t="s">
+    <row r="18" spans="2:7">
+      <c r="B18" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="6" t="s">
         <v>21</v>
       </c>
       <c r="E18" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F18" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G18" s="4" t="s">
+      <c r="F18" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18" s="5" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B19" s="2" t="s">
+    <row r="19" spans="2:7">
+      <c r="B19" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="6" t="s">
         <v>21</v>
       </c>
       <c r="E19" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F19" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G19" s="4" t="s">
+      <c r="F19" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" s="5" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B20" s="2" t="s">
+    <row r="20" spans="2:7">
+      <c r="B20" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="6" t="s">
         <v>21</v>
       </c>
       <c r="E20" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F20" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G20" s="4" t="s">
+      <c r="F20" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" s="5" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B21" s="2" t="s">
+    <row r="21" spans="2:7">
+      <c r="B21" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C21" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D21" s="6" t="s">
         <v>21</v>
       </c>
       <c r="E21" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F21" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G21" s="4" t="s">
+      <c r="F21" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" s="5" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B22" s="2" t="s">
+    <row r="22" spans="2:7">
+      <c r="B22" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C22" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D22" s="6" t="s">
         <v>21</v>
       </c>
       <c r="E22" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F22" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G22" s="4" t="s">
+      <c r="F22" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" s="5" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B23" s="2" t="s">
+    <row r="23" spans="2:7">
+      <c r="B23" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="C23" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="D23" s="6" t="s">
         <v>21</v>
       </c>
       <c r="E23" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F23" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G23" s="4" t="s">
+      <c r="F23" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" s="5" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B24" s="2" t="s">
+    <row r="24" spans="2:7">
+      <c r="B24" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C24" s="10" t="s">
+      <c r="C24" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="D24" s="7" t="s">
+      <c r="D24" s="6" t="s">
         <v>21</v>
       </c>
       <c r="E24" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F24" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G24" s="4" t="s">
+      <c r="F24" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" s="5" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B25" s="2" t="s">
+    <row r="25" spans="2:7">
+      <c r="B25" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="C25" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="D25" s="6" t="s">
         <v>21</v>
       </c>
       <c r="E25" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F25" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G25" s="4" t="s">
+      <c r="F25" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" s="5" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B26" s="2" t="s">
+    <row r="26" spans="2:7">
+      <c r="B26" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C26" s="10" t="s">
+      <c r="C26" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="D26" s="7" t="s">
+      <c r="D26" s="6" t="s">
         <v>21</v>
       </c>
       <c r="E26" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F26" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="4" t="s">
+      <c r="F26" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26" s="5" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B27" s="2" t="s">
+    <row r="27" spans="2:7">
+      <c r="B27" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="C27" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="D27" s="7" t="s">
+      <c r="D27" s="6" t="s">
         <v>21</v>
       </c>
       <c r="E27" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F27" s="4" t="b">
+      <c r="F27" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="G27" s="4" t="s">
+      <c r="G27" s="5" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B28" s="2" t="s">
+    <row r="28" spans="2:7">
+      <c r="B28" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D28" s="7" t="s">
+      <c r="D28" s="6" t="s">
         <v>21</v>
       </c>
       <c r="E28" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F28" s="4" t="b">
+      <c r="F28" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="G28" s="1" t="s">
+      <c r="G28" s="2" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B29" s="2" t="s">
+    <row r="29" spans="2:7">
+      <c r="B29" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="D29" s="6" t="s">
         <v>21</v>
       </c>
       <c r="E29" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F29" s="4" t="b">
+      <c r="F29" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="G29" s="1" t="s">
+      <c r="G29" s="2" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B30" s="2" t="s">
+    <row r="30" spans="2:7">
+      <c r="B30" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D30" s="7" t="s">
+      <c r="D30" s="6" t="s">
         <v>21</v>
       </c>
       <c r="E30" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F30" s="4" t="b">
+      <c r="F30" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="G30" s="1" t="s">
+      <c r="G30" s="2" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B31" s="2" t="s">
+    <row r="31" spans="2:7">
+      <c r="B31" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="D31" s="7" t="s">
+      <c r="D31" s="6" t="s">
         <v>21</v>
       </c>
       <c r="E31" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F31" s="4" t="b">
+      <c r="F31" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="G31" s="1" t="s">
+      <c r="G31" s="2" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B32" s="2" t="s">
+    <row r="32" spans="2:7">
+      <c r="B32" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="D32" s="7" t="s">
+      <c r="D32" s="6" t="s">
         <v>21</v>
       </c>
       <c r="E32" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F32" s="4" t="b">
+      <c r="F32" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="G32" s="1" t="s">
+      <c r="G32" s="2" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B33" s="1" t="s">
+    <row r="33" spans="2:7">
+      <c r="B33" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C33" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C33" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="D33" s="7" t="s">
+      <c r="D33" s="6" t="s">
         <v>21</v>
       </c>
       <c r="E33" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F33" s="4" t="b">
+      <c r="F33" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="G33" s="11" t="s">
+      <c r="G33" s="2" t="s">
         <v>112</v>
       </c>
     </row>
+    <row r="34" spans="2:7">
+      <c r="B34" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F34" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7">
+      <c r="B35" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F35" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7">
+      <c r="B36" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F36" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <printOptions>
+    <extLst>
+      <ext uri="smNativeData">
+        <pm:pageFlags xmlns:pm="smNativeData" id="1783044432" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+      </ext>
+    </extLst>
+  </printOptions>
+  <pageMargins left="0.700000" right="0.700000" top="0.750000" bottom="0.750000" header="0.300000" footer="0.300000"/>
+  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="1"/>
+  <headerFooter>
+    <extLst>
+      <ext uri="smNativeData">
+        <pm:header xmlns:pm="smNativeData" id="1783044432" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1783044432" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1783044432" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1783044432" Id="1" type="0" value="0"/>
+      </ext>
+    </extLst>
+  </headerFooter>
+  <extLst>
+    <ext uri="smNativeData">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1783044432" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+        <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
+        <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
+      </pm:sheetPrefs>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
--- a/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
@@ -13,17 +13,17 @@
   <calcPr/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:revision xmlns:pm="smNativeData" day="1783044432" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
-      <pm:docPrefs xmlns:pm="smNativeData" id="1783044432" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
-      <pm:compatibility xmlns:pm="smNativeData" id="1783044432" overlapCells="1"/>
-      <pm:defCurrency xmlns:pm="smNativeData" id="1783044432"/>
+      <pm:revision xmlns:pm="smNativeData" day="1783065970" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
+      <pm:docPrefs xmlns:pm="smNativeData" id="1783065970" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
+      <pm:compatibility xmlns:pm="smNativeData" id="1783065970" overlapCells="1"/>
+      <pm:defCurrency xmlns:pm="smNativeData" id="1783065970"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="125">
   <si>
     <t>##var</t>
   </si>
@@ -389,6 +389,15 @@
   </si>
   <si>
     <t>工厂结算面板</t>
+  </si>
+  <si>
+    <t>TestPanel</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/TestPanel/TestPanel.prefab</t>
+  </si>
+  <si>
+    <t>测试面板</t>
   </si>
 </sst>
 </file>
@@ -413,7 +422,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1783044432" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1783065970" ulstyle="none" kern="1">
             <pm:latin face="等线" sz="220" lang="default"/>
             <pm:cs face="Times New Roman" sz="220" lang="default"/>
             <pm:ea face="SimSun" sz="220" lang="default"/>
@@ -428,7 +437,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1783044432" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1783065970" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="200" lang="default"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -443,7 +452,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1783044432" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1783065970" ulstyle="none" kern="1">
             <pm:latin face="等线" sz="200" lang="default"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -458,7 +467,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1783044432" fgClr="1F2329" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1783065970" fgClr="1F2329" ulstyle="none" kern="1">
             <pm:latin face="等线" sz="220" lang="default"/>
             <pm:cs face="Times New Roman" sz="220" lang="default"/>
             <pm:ea face="SimSun" sz="220" lang="default"/>
@@ -483,7 +492,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783044432" type="1" fgLvl="100" fgClr="00ACB9CA" bgLvl="0" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1783065970" type="1" fgLvl="100" fgClr="00ACB9CA" bgLvl="0" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -494,7 +503,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783044432" type="1" fgLvl="100" fgClr="005B9BD5" bgLvl="0" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1783065970" type="1" fgLvl="100" fgClr="005B9BD5" bgLvl="0" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -505,7 +514,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783044432" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1783065970" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -527,7 +536,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783044432"/>
+          <pm:border xmlns:pm="smNativeData" id="1783065970"/>
         </ext>
       </extLst>
     </border>
@@ -546,7 +555,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783044432">
+          <pm:border xmlns:pm="smNativeData" id="1783065970">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
@@ -570,7 +579,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783044432"/>
+          <pm:border xmlns:pm="smNativeData" id="1783065970"/>
         </ext>
       </extLst>
     </border>
@@ -589,7 +598,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783044432"/>
+          <pm:border xmlns:pm="smNativeData" id="1783065970"/>
         </ext>
       </extLst>
     </border>
@@ -608,7 +617,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783044432"/>
+          <pm:border xmlns:pm="smNativeData" id="1783065970"/>
         </ext>
       </extLst>
     </border>
@@ -656,10 +665,10 @@
   <tableStyles count="0"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:charStyles xmlns:pm="smNativeData" id="1783044432" count="1">
+      <pm:charStyles xmlns:pm="smNativeData" id="1783065970" count="1">
         <pm:charStyle name="普通" fontId="0" Id="1"/>
       </pm:charStyles>
-      <pm:colors xmlns:pm="smNativeData" id="1783044432" count="5">
+      <pm:colors xmlns:pm="smNativeData" id="1783065970" count="5">
         <pm:color name="颜色 24" rgb="1F2329"/>
         <pm:color name="颜色 25" rgb="ACB9CA"/>
         <pm:color name="20% 灰色" rgb="000000"/>
@@ -927,7 +936,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultRowHeight="13.45"/>
   <cols>
     <col min="1" max="1" width="8.663793" customWidth="1" style="2"/>
@@ -1669,11 +1678,31 @@
         <v>121</v>
       </c>
     </row>
+    <row r="37" spans="2:7">
+      <c r="B37" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F37" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1783044432" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1783065970" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -1682,16 +1711,16 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1783044432" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1783044432" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1783044432" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1783044432" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1783065970" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1783065970" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1783065970" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1783065970" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1783044432" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1783065970" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>

--- a/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
@@ -13,17 +13,17 @@
   <calcPr/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:revision xmlns:pm="smNativeData" day="1783065970" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
-      <pm:docPrefs xmlns:pm="smNativeData" id="1783065970" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
-      <pm:compatibility xmlns:pm="smNativeData" id="1783065970" overlapCells="1"/>
-      <pm:defCurrency xmlns:pm="smNativeData" id="1783065970"/>
+      <pm:revision xmlns:pm="smNativeData" day="1783066630" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
+      <pm:docPrefs xmlns:pm="smNativeData" id="1783066630" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
+      <pm:compatibility xmlns:pm="smNativeData" id="1783066630" overlapCells="1"/>
+      <pm:defCurrency xmlns:pm="smNativeData" id="1783066630"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="128">
   <si>
     <t>##var</t>
   </si>
@@ -398,6 +398,15 @@
   </si>
   <si>
     <t>测试面板</t>
+  </si>
+  <si>
+    <t>FactoryProcessPanel</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/FactoryUI/FactoryProcessPanel.prefab</t>
+  </si>
+  <si>
+    <t>工厂处理面板</t>
   </si>
 </sst>
 </file>
@@ -422,7 +431,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1783065970" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1783066630" ulstyle="none" kern="1">
             <pm:latin face="等线" sz="220" lang="default"/>
             <pm:cs face="Times New Roman" sz="220" lang="default"/>
             <pm:ea face="SimSun" sz="220" lang="default"/>
@@ -437,7 +446,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1783065970" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1783066630" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="200" lang="default"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -452,7 +461,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1783065970" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1783066630" ulstyle="none" kern="1">
             <pm:latin face="等线" sz="200" lang="default"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -467,7 +476,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1783065970" fgClr="1F2329" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1783066630" fgClr="1F2329" ulstyle="none" kern="1">
             <pm:latin face="等线" sz="220" lang="default"/>
             <pm:cs face="Times New Roman" sz="220" lang="default"/>
             <pm:ea face="SimSun" sz="220" lang="default"/>
@@ -492,7 +501,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783065970" type="1" fgLvl="100" fgClr="00ACB9CA" bgLvl="0" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1783066630" type="1" fgLvl="100" fgClr="00ACB9CA" bgLvl="0" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -503,7 +512,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783065970" type="1" fgLvl="100" fgClr="005B9BD5" bgLvl="0" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1783066630" type="1" fgLvl="100" fgClr="005B9BD5" bgLvl="0" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -514,7 +523,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783065970" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1783066630" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -536,7 +545,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783065970"/>
+          <pm:border xmlns:pm="smNativeData" id="1783066630"/>
         </ext>
       </extLst>
     </border>
@@ -555,7 +564,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783065970">
+          <pm:border xmlns:pm="smNativeData" id="1783066630">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
@@ -579,7 +588,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783065970"/>
+          <pm:border xmlns:pm="smNativeData" id="1783066630"/>
         </ext>
       </extLst>
     </border>
@@ -598,7 +607,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783065970"/>
+          <pm:border xmlns:pm="smNativeData" id="1783066630"/>
         </ext>
       </extLst>
     </border>
@@ -617,7 +626,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783065970"/>
+          <pm:border xmlns:pm="smNativeData" id="1783066630"/>
         </ext>
       </extLst>
     </border>
@@ -665,10 +674,10 @@
   <tableStyles count="0"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:charStyles xmlns:pm="smNativeData" id="1783065970" count="1">
+      <pm:charStyles xmlns:pm="smNativeData" id="1783066630" count="1">
         <pm:charStyle name="普通" fontId="0" Id="1"/>
       </pm:charStyles>
-      <pm:colors xmlns:pm="smNativeData" id="1783065970" count="5">
+      <pm:colors xmlns:pm="smNativeData" id="1783066630" count="5">
         <pm:color name="颜色 24" rgb="1F2329"/>
         <pm:color name="颜色 25" rgb="ACB9CA"/>
         <pm:color name="20% 灰色" rgb="000000"/>
@@ -936,7 +945,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr defaultRowHeight="13.45"/>
   <cols>
     <col min="1" max="1" width="8.663793" customWidth="1" style="2"/>
@@ -1698,11 +1707,31 @@
         <v>124</v>
       </c>
     </row>
+    <row r="38" spans="2:7">
+      <c r="B38" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F38" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1783065970" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1783066630" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -1711,16 +1740,16 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1783065970" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1783065970" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1783065970" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1783065970" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1783066630" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1783066630" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1783066630" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1783066630" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1783065970" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1783066630" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>

--- a/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
@@ -1,16 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
-  <fileSharing readOnlyRecommended="0" userName="Lumino Game 03"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{675A94B6-97E9-45FA-A883-8BC4B14B8B99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0" xWindow="240" yWindow="60" windowWidth="38610" windowHeight="19220" tabRatio="500"/>
+    <workbookView xWindow="8120" yWindow="3450" windowWidth="24990" windowHeight="19220" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext uri="smNativeData">
       <pm:revision xmlns:pm="smNativeData" day="1783044432" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
@@ -23,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="125">
   <si>
     <t>##var</t>
   </si>
@@ -389,85 +394,60 @@
   </si>
   <si>
     <t>工厂结算面板</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/ClawMachineGuideUI/ClawMachineGuideUI.prefab</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ClawMachineGuideUI</t>
+  </si>
+  <si>
+    <t>抓娃娃机UI</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
-    <numFmt numFmtId="5" formatCode="#,##0\ &quot;¥&quot;;\-#,##0\ &quot;¥&quot;"/>
-    <numFmt numFmtId="6" formatCode="#,##0\ &quot;¥&quot;;[Red]\-#,##0\ &quot;¥&quot;"/>
-    <numFmt numFmtId="7" formatCode="#,##0.00\ &quot;¥&quot;;\-#,##0.00\ &quot;¥&quot;"/>
-    <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;¥&quot;;[Red]\-#,##0.00\ &quot;¥&quot;"/>
-    <numFmt numFmtId="42" formatCode="_-* #,##0\ &quot;¥&quot;_-;\-* #,##0\ &quot;¥&quot;_-;_-* &quot;-&quot;\ &quot;¥&quot;_-;_-@_-"/>
-    <numFmt numFmtId="41" formatCode="_-* #,##0\ _¥_-;\-* #,##0\ _¥_-;_-* &quot;-&quot;\ _¥_-;_-@_-"/>
-    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;¥&quot;_-;\-* #,##0.00\ &quot;¥&quot;_-;_-* &quot;-&quot;??\ &quot;¥&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _¥_-;\-* #,##0.00\ _¥_-;_-* &quot;-&quot;??\ _¥_-;_-@_-"/>
-  </numFmts>
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="等线"/>
       <charset val="134"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1783044432" ulstyle="none" kern="1">
-            <pm:latin face="等线" sz="220" lang="default"/>
-            <pm:cs face="Times New Roman" sz="220" lang="default"/>
-            <pm:ea face="SimSun" sz="220" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
-      <name val="Arial"/>
-      <family val="2"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
-      <sz val="10"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1783044432" ulstyle="none" kern="1">
-            <pm:latin face="Arial" sz="200" lang="default"/>
-            <pm:cs face="Times New Roman" sz="200" lang="default"/>
-            <pm:ea face="SimSun" sz="200" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
+      <name val="等线"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF1F2329"/>
       <name val="等线"/>
-      <charset val="134"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1783044432" ulstyle="none" kern="1">
-            <pm:latin face="等线" sz="200" lang="default"/>
-            <pm:cs face="Times New Roman" sz="200" lang="default"/>
-            <pm:ea face="SimSun" sz="200" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="等线"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
-      <color rgb="FF1F2329"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1783044432" fgClr="1F2329" ulstyle="none" kern="1">
-            <pm:latin face="等线" sz="220" lang="default"/>
-            <pm:cs face="Times New Roman" sz="220" lang="default"/>
-            <pm:ea face="SimSun" sz="220" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -475,61 +455,25 @@
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
-      <patternFill patternType="none"/>
-    </fill>
-    <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFACB9CA"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783044432" type="1" fgLvl="100" fgClr="00ACB9CA" bgLvl="0" bgClr="00000000"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF5B9BD5"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783044432" type="1" fgLvl="100" fgClr="005B9BD5" bgLvl="0" bgClr="00000000"/>
-          </ext>
-        </extLst>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783044432" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="4">
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783044432"/>
-        </ext>
-      </extLst>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -544,117 +488,72 @@
       <bottom style="thin">
         <color rgb="FFDEE0E3"/>
       </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783044432">
-            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-          </pm:border>
-        </ext>
-      </extLst>
+      <diagonal/>
     </border>
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783044432"/>
-        </ext>
-      </extLst>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783044432"/>
-        </ext>
-      </extLst>
-    </border>
-    <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783044432"/>
-        </ext>
-      </extLst>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
-    <cellStyle name="常规 2" xfId="1"/>
+    <cellStyle name="常规" xfId="0" builtinId="0" customBuiltin="1"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0"/>
   <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
     <ext uri="smNativeData">
       <pm:charStyles xmlns:pm="smNativeData" id="1783044432" count="1">
         <pm:charStyle name="普通" fontId="0" Id="1"/>
@@ -926,769 +825,774 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:G36"/>
-  <sheetFormatPr defaultRowHeight="13.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G37"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.663793" customWidth="1" style="2"/>
-    <col min="2" max="2" width="28.577586" customWidth="1" style="2"/>
-    <col min="3" max="3" width="100.077586" customWidth="1" style="2"/>
-    <col min="4" max="4" width="25.163793" customWidth="1" style="2"/>
-    <col min="5" max="5" width="23.663793" customWidth="1" style="2"/>
-    <col min="6" max="6" width="17.663793" customWidth="1" style="2"/>
-    <col min="7" max="7" width="24.163793" customWidth="1" style="2"/>
-    <col min="8" max="16384" width="8.663793" customWidth="1" style="2"/>
+    <col min="1" max="1" width="8.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="28.58203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="100.08203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="25.1640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="23.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="24.1640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="8.6640625" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="2:7">
-      <c r="B4" s="3" t="s">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G4" s="5" t="s">
+      <c r="D4" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="2:7" ht="19.50" customHeight="1">
-      <c r="B5" s="3" t="s">
+    <row r="5" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="8" t="s">
+      <c r="D5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G5" s="5" t="s">
+      <c r="F5" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="2:7">
-      <c r="B6" s="3" t="s">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G6" s="5" t="s">
+      <c r="D6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="2:7">
-      <c r="B7" s="3" t="s">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B7" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G7" s="5" t="s">
+      <c r="D7" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="2:7">
-      <c r="B8" s="3" t="s">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G8" s="5" t="s">
+      <c r="D8" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="2:7">
-      <c r="B9" s="3" t="s">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B9" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="F9" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G9" s="5" t="s">
+      <c r="F9" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="2:7">
-      <c r="B10" s="3" t="s">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B10" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="F10" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G10" s="5" t="s">
+      <c r="F10" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="2:7">
-      <c r="B11" s="3" t="s">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B11" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D11" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F11" s="5" t="b">
+      <c r="D11" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="G11" s="4" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="2:7">
-      <c r="B12" s="3" t="s">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B12" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F12" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G12" s="5" t="s">
+      <c r="D12" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="13" spans="2:7">
-      <c r="B13" s="3" t="s">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B13" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="F13" s="5" t="b">
+      <c r="F13" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="G13" s="5" t="s">
+      <c r="G13" s="4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="14" spans="2:7">
-      <c r="B14" s="3" t="s">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B14" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E14" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F14" s="5" t="b">
+      <c r="E14" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="G14" s="5" t="s">
+      <c r="G14" s="4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="15" spans="2:7">
-      <c r="B15" s="3" t="s">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B15" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D15" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E15" s="8" t="s">
+      <c r="D15" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="F15" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G15" s="5" t="s">
+      <c r="F15" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15" s="4" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="16" spans="2:7">
-      <c r="B16" s="3" t="s">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B16" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D16" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F16" s="5" t="b">
+      <c r="D16" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F16" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="G16" s="5" t="s">
+      <c r="G16" s="4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="17" spans="2:7">
-      <c r="B17" s="3" t="s">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B17" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D17" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E17" s="8" t="s">
+      <c r="D17" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="F17" s="5" t="b">
+      <c r="F17" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="G17" s="5" t="s">
+      <c r="G17" s="4" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="18" spans="2:7">
-      <c r="B18" s="3" t="s">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B18" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D18" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F18" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G18" s="5" t="s">
+      <c r="D18" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F18" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18" s="4" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="2:7">
-      <c r="B19" s="3" t="s">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B19" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D19" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F19" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G19" s="5" t="s">
+      <c r="D19" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F19" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="20" spans="2:7">
-      <c r="B20" s="3" t="s">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B20" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C20" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="D20" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F20" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G20" s="5" t="s">
+      <c r="D20" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F20" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" s="4" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="21" spans="2:7">
-      <c r="B21" s="3" t="s">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B21" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="D21" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F21" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G21" s="5" t="s">
+      <c r="D21" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F21" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="22" spans="2:7">
-      <c r="B22" s="3" t="s">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B22" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C22" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="D22" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F22" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G22" s="5" t="s">
+      <c r="D22" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F22" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="23" spans="2:7">
-      <c r="B23" s="3" t="s">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B23" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="D23" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F23" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G23" s="5" t="s">
+      <c r="D23" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F23" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" s="4" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="24" spans="2:7">
-      <c r="B24" s="3" t="s">
+    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B24" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D24" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F24" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G24" s="5" t="s">
+      <c r="D24" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F24" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" s="4" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="25" spans="2:7">
-      <c r="B25" s="3" t="s">
+    <row r="25" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B25" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="D25" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F25" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G25" s="5" t="s">
+      <c r="D25" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F25" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="26" spans="2:7">
-      <c r="B26" s="3" t="s">
+    <row r="26" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B26" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="C26" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="D26" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F26" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="5" t="s">
+      <c r="D26" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F26" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26" s="4" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="27" spans="2:7">
-      <c r="B27" s="3" t="s">
+    <row r="27" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B27" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="C27" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="D27" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F27" s="5" t="b">
+      <c r="D27" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F27" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="G27" s="5" t="s">
+      <c r="G27" s="4" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="28" spans="2:7">
-      <c r="B28" s="3" t="s">
+    <row r="28" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B28" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D28" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F28" s="5" t="b">
+      <c r="D28" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F28" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="G28" s="2" t="s">
+      <c r="G28" s="1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="29" spans="2:7">
-      <c r="B29" s="3" t="s">
+    <row r="29" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B29" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="D29" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F29" s="5" t="b">
+      <c r="D29" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F29" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="G29" s="2" t="s">
+      <c r="G29" s="1" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="2:7">
-      <c r="B30" s="3" t="s">
+    <row r="30" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B30" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="D30" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F30" s="5" t="b">
+      <c r="D30" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F30" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="G30" s="2" t="s">
+      <c r="G30" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="31" spans="2:7">
-      <c r="B31" s="3" t="s">
+    <row r="31" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B31" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="D31" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F31" s="5" t="b">
+      <c r="D31" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F31" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="G31" s="2" t="s">
+      <c r="G31" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="32" spans="2:7">
-      <c r="B32" s="3" t="s">
+    <row r="32" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B32" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="D32" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F32" s="5" t="b">
+      <c r="D32" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F32" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="G32" s="2" t="s">
+      <c r="G32" s="1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="33" spans="2:7">
-      <c r="B33" s="2" t="s">
+    <row r="33" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B33" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="D33" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F33" s="5" t="b">
+      <c r="D33" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F33" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="G33" s="2" t="s">
+      <c r="G33" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="34" spans="2:7">
-      <c r="B34" s="2" t="s">
+    <row r="34" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B34" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D34" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F34" s="5" t="b">
+      <c r="D34" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F34" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="G34" s="2" t="s">
+      <c r="G34" s="1" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="35" spans="2:7">
-      <c r="B35" s="2" t="s">
+    <row r="35" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B35" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="D35" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E35" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F35" s="5" t="b">
+      <c r="D35" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F35" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="G35" s="2" t="s">
+      <c r="G35" s="1" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="36" spans="2:7">
-      <c r="B36" s="2" t="s">
+    <row r="36" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B36" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="D36" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F36" s="5" t="b">
+      <c r="D36" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F36" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="G36" s="2" t="s">
+      <c r="G36" s="1" t="s">
         <v>121</v>
       </c>
     </row>
+    <row r="37" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B37" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F37" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G37" s="9" t="s">
+        <v>124</v>
+      </c>
+    </row>
   </sheetData>
-  <printOptions>
-    <extLst>
-      <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1783044432" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
-      </ext>
-    </extLst>
-  </printOptions>
-  <pageMargins left="0.700000" right="0.700000" top="0.750000" bottom="0.750000" header="0.300000" footer="0.300000"/>
-  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="1"/>
-  <headerFooter>
-    <extLst>
-      <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1783044432" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1783044432" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1783044432" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1783044432" Id="1" type="0" value="0"/>
-      </ext>
-    </extLst>
-  </headerFooter>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" fitToWidth="0"/>
   <extLst>
     <ext uri="smNativeData">
       <pm:sheetPrefs xmlns:pm="smNativeData" day="1783044432" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">

--- a/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
@@ -1,34 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
+  <fileSharing readOnlyRecommended="0" userName="Lumino Game 03"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{675A94B6-97E9-45FA-A883-8BC4B14B8B99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8120" yWindow="3450" windowWidth="24990" windowHeight="19220" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView activeTab="0" xWindow="240" yWindow="60" windowWidth="24990" windowHeight="19220" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:revision xmlns:pm="smNativeData" day="1783044432" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
-      <pm:docPrefs xmlns:pm="smNativeData" id="1783044432" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
-      <pm:compatibility xmlns:pm="smNativeData" id="1783044432" overlapCells="1"/>
-      <pm:defCurrency xmlns:pm="smNativeData" id="1783044432"/>
+      <pm:revision xmlns:pm="smNativeData" day="1783073298" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
+      <pm:docPrefs xmlns:pm="smNativeData" id="1783073298" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
+      <pm:compatibility xmlns:pm="smNativeData" id="1783073298" overlapCells="1"/>
+      <pm:defCurrency xmlns:pm="smNativeData" id="1783073298"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="131">
   <si>
     <t>##var</t>
   </si>
@@ -396,58 +391,110 @@
     <t>工厂结算面板</t>
   </si>
   <si>
+    <t>ClawMachineGuideUI</t>
+  </si>
+  <si>
     <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/ClawMachineGuideUI/ClawMachineGuideUI.prefab</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>ClawMachineGuideUI</t>
   </si>
   <si>
     <t>抓娃娃机UI</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>FactoryProcessPanel</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/FactoryUI/FactoryProcessPanel.prefab</t>
+  </si>
+  <si>
+    <t>工厂处理面板</t>
+  </si>
+  <si>
+    <t>TestPanel</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/TestPanel/TestPanel.prefab</t>
+  </si>
+  <si>
+    <t>测试面板</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="8">
+    <numFmt numFmtId="5" formatCode="#,##0\ &quot;¥&quot;;\-#,##0\ &quot;¥&quot;"/>
+    <numFmt numFmtId="6" formatCode="#,##0\ &quot;¥&quot;;[Red]\-#,##0\ &quot;¥&quot;"/>
+    <numFmt numFmtId="7" formatCode="#,##0.00\ &quot;¥&quot;;\-#,##0.00\ &quot;¥&quot;"/>
+    <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;¥&quot;;[Red]\-#,##0.00\ &quot;¥&quot;"/>
+    <numFmt numFmtId="42" formatCode="_-* #,##0\ &quot;¥&quot;_-;\-* #,##0\ &quot;¥&quot;_-;_-* &quot;-&quot;\ &quot;¥&quot;_-;_-@_-"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0\ _¥_-;\-* #,##0\ _¥_-;_-* &quot;-&quot;\ _¥_-;_-@_-"/>
+    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;¥&quot;_-;\-* #,##0.00\ &quot;¥&quot;_-;_-* &quot;-&quot;??\ &quot;¥&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _¥_-;\-* #,##0.00\ _¥_-;_-* &quot;-&quot;??\ _¥_-;_-@_-"/>
+  </numFmts>
+  <fonts count="4">
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="等线"/>
       <charset val="134"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1783073298" ulstyle="none" kern="1">
+            <pm:latin face="等线" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1783073298" ulstyle="none" kern="1">
+            <pm:latin face="Arial" sz="200" lang="default"/>
+            <pm:cs face="Times New Roman" sz="200" lang="default"/>
+            <pm:ea face="SimSun" sz="200" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF1F2329"/>
       <name val="等线"/>
+      <charset val="134"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1783073298" ulstyle="none" kern="1">
+            <pm:latin face="等线" sz="200" lang="default"/>
+            <pm:cs face="Times New Roman" sz="200" lang="default"/>
+            <pm:ea face="SimSun" sz="200" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <color rgb="FF1F2329"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1783073298" fgClr="1F2329" ulstyle="none" kern="1">
+            <pm:latin face="等线" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -455,25 +502,61 @@
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFACB9CA"/>
         <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1783073298" type="1" fgLvl="100" fgClr="00ACB9CA" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF5B9BD5"/>
         <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1783073298" type="1" fgLvl="100" fgClr="005B9BD5" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1783073298" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783073298"/>
+        </ext>
+      </extLst>
     </border>
     <border>
       <left style="thin">
@@ -488,82 +571,129 @@
       <bottom style="thin">
         <color rgb="FFDEE0E3"/>
       </bottom>
-      <diagonal/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783073298">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+          </pm:border>
+        </ext>
+      </extLst>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783073298"/>
+        </ext>
+      </extLst>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783073298"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783073298"/>
+        </ext>
+      </extLst>
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="常规" xfId="0" builtinId="0" customBuiltin="1"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
+    <cellStyle name="常规 2" xfId="1"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
     <ext uri="smNativeData">
-      <pm:charStyles xmlns:pm="smNativeData" id="1783044432" count="1">
+      <pm:charStyles xmlns:pm="smNativeData" id="1783073298" count="1">
         <pm:charStyle name="普通" fontId="0" Id="1"/>
       </pm:charStyles>
-      <pm:colors xmlns:pm="smNativeData" id="1783044432" count="5">
+      <pm:colors xmlns:pm="smNativeData" id="1783073298" count="4">
         <pm:color name="颜色 24" rgb="1F2329"/>
         <pm:color name="颜色 25" rgb="ACB9CA"/>
-        <pm:color name="20% 灰色" rgb="000000"/>
-        <pm:color name="颜色 27" rgb="5B9BD5"/>
-        <pm:color name="颜色 28" rgb="DEE0E3"/>
+        <pm:color name="颜色 26" rgb="5B9BD5"/>
+        <pm:color name="颜色 27" rgb="DEE0E3"/>
       </pm:colors>
     </ext>
   </extLst>
@@ -825,777 +955,832 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G37"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <dimension ref="A1:G39"/>
+  <sheetFormatPr defaultRowHeight="13.45"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="28.58203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="100.08203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="25.1640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="23.6640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="17.6640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="24.1640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="8.6640625" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.6640625" style="1"/>
+    <col min="1" max="1" width="8.663793" customWidth="1" style="2"/>
+    <col min="2" max="2" width="28.577586" customWidth="1" style="2"/>
+    <col min="3" max="3" width="100.077586" customWidth="1" style="2"/>
+    <col min="4" max="4" width="25.163793" customWidth="1" style="2"/>
+    <col min="5" max="5" width="23.663793" customWidth="1" style="2"/>
+    <col min="6" max="6" width="17.663793" customWidth="1" style="2"/>
+    <col min="7" max="7" width="24.163793" customWidth="1" style="2"/>
+    <col min="8" max="16384" width="8.663793" customWidth="1" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
+    <row r="1" spans="1:7">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:7">
+      <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:7">
+      <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B4" s="2" t="s">
+    <row r="4" spans="2:7">
+      <c r="B4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G4" s="4" t="s">
+      <c r="D4" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="2" t="s">
+    <row r="5" spans="2:7" ht="19.50" customHeight="1">
+      <c r="B5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="7" t="s">
+      <c r="D5" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G5" s="4" t="s">
+      <c r="F5" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B6" s="2" t="s">
+    <row r="6" spans="2:7">
+      <c r="B6" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G6" s="4" t="s">
+      <c r="D6" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B7" s="2" t="s">
+    <row r="7" spans="2:7">
+      <c r="B7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G7" s="4" t="s">
+      <c r="D7" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B8" s="2" t="s">
+    <row r="8" spans="2:7">
+      <c r="B8" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G8" s="4" t="s">
+      <c r="D8" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B9" s="2" t="s">
+    <row r="9" spans="2:7">
+      <c r="B9" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="F9" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G9" s="4" t="s">
+      <c r="F9" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" s="5" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B10" s="2" t="s">
+    <row r="10" spans="2:7">
+      <c r="B10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="F10" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G10" s="4" t="s">
+      <c r="F10" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B11" s="2" t="s">
+    <row r="11" spans="2:7">
+      <c r="B11" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D11" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F11" s="4" t="b">
+      <c r="D11" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="5" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B12" s="2" t="s">
+    <row r="12" spans="2:7">
+      <c r="B12" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F12" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G12" s="4" t="s">
+      <c r="D12" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12" s="5" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B13" s="2" t="s">
+    <row r="13" spans="2:7">
+      <c r="B13" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="F13" s="4" t="b">
+      <c r="F13" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G13" s="5" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B14" s="2" t="s">
+    <row r="14" spans="2:7">
+      <c r="B14" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E14" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F14" s="4" t="b">
+      <c r="E14" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="5" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B15" s="2" t="s">
+    <row r="15" spans="2:7">
+      <c r="B15" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D15" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E15" s="7" t="s">
+      <c r="D15" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="F15" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G15" s="4" t="s">
+      <c r="F15" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15" s="5" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B16" s="2" t="s">
+    <row r="16" spans="2:7">
+      <c r="B16" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="D16" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F16" s="4" t="b">
+      <c r="D16" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F16" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="5" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B17" s="2" t="s">
+    <row r="17" spans="2:7">
+      <c r="B17" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="D17" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E17" s="7" t="s">
+      <c r="D17" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="F17" s="4" t="b">
+      <c r="F17" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="G17" s="5" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B18" s="2" t="s">
+    <row r="18" spans="2:7">
+      <c r="B18" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="D18" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F18" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G18" s="4" t="s">
+      <c r="D18" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F18" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18" s="5" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B19" s="2" t="s">
+    <row r="19" spans="2:7">
+      <c r="B19" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="D19" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F19" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G19" s="4" t="s">
+      <c r="D19" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F19" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" s="5" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B20" s="2" t="s">
+    <row r="20" spans="2:7">
+      <c r="B20" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="D20" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F20" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G20" s="4" t="s">
+      <c r="D20" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F20" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" s="5" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B21" s="2" t="s">
+    <row r="21" spans="2:7">
+      <c r="B21" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="D21" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F21" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G21" s="4" t="s">
+      <c r="D21" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F21" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" s="5" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B22" s="2" t="s">
+    <row r="22" spans="2:7">
+      <c r="B22" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="D22" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F22" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G22" s="4" t="s">
+      <c r="D22" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F22" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" s="5" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B23" s="2" t="s">
+    <row r="23" spans="2:7">
+      <c r="B23" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="D23" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F23" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G23" s="4" t="s">
+      <c r="D23" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F23" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" s="5" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B24" s="2" t="s">
+    <row r="24" spans="2:7">
+      <c r="B24" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="D24" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F24" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G24" s="4" t="s">
+      <c r="D24" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F24" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" s="5" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B25" s="2" t="s">
+    <row r="25" spans="2:7">
+      <c r="B25" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="D25" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F25" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G25" s="4" t="s">
+      <c r="D25" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F25" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" s="5" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B26" s="2" t="s">
+    <row r="26" spans="2:7">
+      <c r="B26" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C26" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="D26" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F26" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="4" t="s">
+      <c r="D26" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F26" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26" s="5" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B27" s="2" t="s">
+    <row r="27" spans="2:7">
+      <c r="B27" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="D27" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F27" s="4" t="b">
+      <c r="D27" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F27" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="G27" s="4" t="s">
+      <c r="G27" s="5" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B28" s="2" t="s">
+    <row r="28" spans="2:7">
+      <c r="B28" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D28" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F28" s="4" t="b">
+      <c r="D28" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F28" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="G28" s="1" t="s">
+      <c r="G28" s="2" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B29" s="2" t="s">
+    <row r="29" spans="2:7">
+      <c r="B29" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="D29" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F29" s="4" t="b">
+      <c r="D29" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F29" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="G29" s="1" t="s">
+      <c r="G29" s="2" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B30" s="2" t="s">
+    <row r="30" spans="2:7">
+      <c r="B30" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D30" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F30" s="4" t="b">
+      <c r="D30" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F30" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="G30" s="1" t="s">
+      <c r="G30" s="2" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B31" s="2" t="s">
+    <row r="31" spans="2:7">
+      <c r="B31" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="D31" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F31" s="4" t="b">
+      <c r="D31" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F31" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="G31" s="1" t="s">
+      <c r="G31" s="2" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B32" s="2" t="s">
+    <row r="32" spans="2:7">
+      <c r="B32" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="D32" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F32" s="4" t="b">
+      <c r="D32" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F32" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="G32" s="1" t="s">
+      <c r="G32" s="2" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B33" s="1" t="s">
+    <row r="33" spans="2:7">
+      <c r="B33" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="D33" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F33" s="4" t="b">
+      <c r="D33" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F33" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="G33" s="1" t="s">
+      <c r="G33" s="2" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B34" s="1" t="s">
+    <row r="34" spans="2:7">
+      <c r="B34" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D34" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E34" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F34" s="4" t="b">
+      <c r="D34" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F34" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="G34" s="1" t="s">
+      <c r="G34" s="2" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B35" s="1" t="s">
+    <row r="35" spans="2:7">
+      <c r="B35" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="D35" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F35" s="4" t="b">
+      <c r="D35" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F35" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="G35" s="1" t="s">
+      <c r="G35" s="2" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B36" s="1" t="s">
+    <row r="36" spans="2:7">
+      <c r="B36" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="D36" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F36" s="4" t="b">
+      <c r="D36" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F36" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="G36" s="1" t="s">
+      <c r="G36" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B37" s="1" t="s">
+    <row r="37" spans="2:7">
+      <c r="B37" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C37" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="C37" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F37" s="4" t="b">
+      <c r="D37" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F37" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="G37" s="9" t="s">
+      <c r="G37" s="10" t="s">
         <v>124</v>
       </c>
     </row>
+    <row r="38" spans="2:7">
+      <c r="B38" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F38" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7">
+      <c r="B39" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F39" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" fitToWidth="0"/>
+  <printOptions>
+    <extLst>
+      <ext uri="smNativeData">
+        <pm:pageFlags xmlns:pm="smNativeData" id="1783073298" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+      </ext>
+    </extLst>
+  </printOptions>
+  <pageMargins left="0.700000" right="0.700000" top="0.750000" bottom="0.750000" header="0.300000" footer="0.300000"/>
+  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="1"/>
+  <headerFooter>
+    <extLst>
+      <ext uri="smNativeData">
+        <pm:header xmlns:pm="smNativeData" id="1783073298" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1783073298" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1783073298" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1783073298" Id="1" type="0" value="0"/>
+      </ext>
+    </extLst>
+  </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1783044432" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1783073298" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>

--- a/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
@@ -1,16 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
-  <fileSharing readOnlyRecommended="0" userName="Lumino Game 03"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EF048BD-BED5-4625-A859-E620B1915AF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0" xWindow="240" yWindow="60" windowWidth="24990" windowHeight="19220" tabRatio="500"/>
+    <workbookView xWindow="6680" yWindow="3710" windowWidth="24990" windowHeight="19220" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext uri="smNativeData">
       <pm:revision xmlns:pm="smNativeData" day="1783073298" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
@@ -23,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="134">
   <si>
     <t>##var</t>
   </si>
@@ -416,85 +421,60 @@
   </si>
   <si>
     <t>测试面板</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/PopUnlockDollWindowsUI/PopUnlockDollWindowsUI.prefab</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>PopUnlockDollWindowsUI</t>
+  </si>
+  <si>
+    <t>解锁娃娃机展示界面</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
-    <numFmt numFmtId="5" formatCode="#,##0\ &quot;¥&quot;;\-#,##0\ &quot;¥&quot;"/>
-    <numFmt numFmtId="6" formatCode="#,##0\ &quot;¥&quot;;[Red]\-#,##0\ &quot;¥&quot;"/>
-    <numFmt numFmtId="7" formatCode="#,##0.00\ &quot;¥&quot;;\-#,##0.00\ &quot;¥&quot;"/>
-    <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;¥&quot;;[Red]\-#,##0.00\ &quot;¥&quot;"/>
-    <numFmt numFmtId="42" formatCode="_-* #,##0\ &quot;¥&quot;_-;\-* #,##0\ &quot;¥&quot;_-;_-* &quot;-&quot;\ &quot;¥&quot;_-;_-@_-"/>
-    <numFmt numFmtId="41" formatCode="_-* #,##0\ _¥_-;\-* #,##0\ _¥_-;_-* &quot;-&quot;\ _¥_-;_-@_-"/>
-    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;¥&quot;_-;\-* #,##0.00\ &quot;¥&quot;_-;_-* &quot;-&quot;??\ &quot;¥&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _¥_-;\-* #,##0.00\ _¥_-;_-* &quot;-&quot;??\ _¥_-;_-@_-"/>
-  </numFmts>
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="等线"/>
       <charset val="134"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1783073298" ulstyle="none" kern="1">
-            <pm:latin face="等线" sz="220" lang="default"/>
-            <pm:cs face="Times New Roman" sz="220" lang="default"/>
-            <pm:ea face="SimSun" sz="220" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
-      <name val="Arial"/>
-      <family val="2"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
-      <sz val="10"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1783073298" ulstyle="none" kern="1">
-            <pm:latin face="Arial" sz="200" lang="default"/>
-            <pm:cs face="Times New Roman" sz="200" lang="default"/>
-            <pm:ea face="SimSun" sz="200" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
+      <name val="等线"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF1F2329"/>
       <name val="等线"/>
-      <charset val="134"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1783073298" ulstyle="none" kern="1">
-            <pm:latin face="等线" sz="200" lang="default"/>
-            <pm:cs face="Times New Roman" sz="200" lang="default"/>
-            <pm:ea face="SimSun" sz="200" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="等线"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
-      <color rgb="FF1F2329"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1783073298" fgClr="1F2329" ulstyle="none" kern="1">
-            <pm:latin face="等线" sz="220" lang="default"/>
-            <pm:cs face="Times New Roman" sz="220" lang="default"/>
-            <pm:ea face="SimSun" sz="220" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -502,61 +482,25 @@
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
-      <patternFill patternType="none"/>
-    </fill>
-    <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFACB9CA"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783073298" type="1" fgLvl="100" fgClr="00ACB9CA" bgLvl="0" bgClr="00FFFFFF"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF5B9BD5"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783073298" type="1" fgLvl="100" fgClr="005B9BD5" bgLvl="0" bgClr="00FFFFFF"/>
-          </ext>
-        </extLst>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783073298" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="4">
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783073298"/>
-        </ext>
-      </extLst>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -571,120 +515,72 @@
       <bottom style="thin">
         <color rgb="FFDEE0E3"/>
       </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783073298">
-            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-          </pm:border>
-        </ext>
-      </extLst>
+      <diagonal/>
     </border>
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783073298"/>
-        </ext>
-      </extLst>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783073298"/>
-        </ext>
-      </extLst>
-    </border>
-    <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783073298"/>
-        </ext>
-      </extLst>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
-    <cellStyle name="常规 2" xfId="1"/>
+    <cellStyle name="常规" xfId="0" builtinId="0" customBuiltin="1"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0"/>
   <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
     <ext uri="smNativeData">
       <pm:charStyles xmlns:pm="smNativeData" id="1783073298" count="1">
         <pm:charStyle name="普通" fontId="0" Id="1"/>
@@ -955,829 +851,834 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultRowHeight="13.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G40"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.663793" customWidth="1" style="2"/>
-    <col min="2" max="2" width="28.577586" customWidth="1" style="2"/>
-    <col min="3" max="3" width="100.077586" customWidth="1" style="2"/>
-    <col min="4" max="4" width="25.163793" customWidth="1" style="2"/>
-    <col min="5" max="5" width="23.663793" customWidth="1" style="2"/>
-    <col min="6" max="6" width="17.663793" customWidth="1" style="2"/>
-    <col min="7" max="7" width="24.163793" customWidth="1" style="2"/>
-    <col min="8" max="16384" width="8.663793" customWidth="1" style="2"/>
+    <col min="1" max="1" width="8.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="28.58203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="100.08203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="25.1640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="23.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="24.1640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="8.6640625" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="4" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="2:7">
-      <c r="B4" s="3" t="s">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G4" s="5" t="s">
+      <c r="D4" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="2:7" ht="19.50" customHeight="1">
-      <c r="B5" s="3" t="s">
+    <row r="5" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="8" t="s">
+      <c r="D5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G5" s="5" t="s">
+      <c r="F5" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="2:7">
-      <c r="B6" s="3" t="s">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G6" s="5" t="s">
+      <c r="D6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="2:7">
-      <c r="B7" s="3" t="s">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B7" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G7" s="5" t="s">
+      <c r="D7" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="2:7">
-      <c r="B8" s="3" t="s">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G8" s="5" t="s">
+      <c r="D8" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="2:7">
-      <c r="B9" s="3" t="s">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B9" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="F9" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G9" s="5" t="s">
+      <c r="F9" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="2:7">
-      <c r="B10" s="3" t="s">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B10" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="F10" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G10" s="5" t="s">
+      <c r="F10" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="2:7">
-      <c r="B11" s="3" t="s">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B11" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D11" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F11" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G11" s="5" t="s">
+      <c r="D11" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="2:7">
-      <c r="B12" s="3" t="s">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B12" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F12" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G12" s="5" t="s">
+      <c r="D12" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="13" spans="2:7">
-      <c r="B13" s="3" t="s">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B13" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="F13" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G13" s="5" t="s">
+      <c r="F13" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G13" s="4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="14" spans="2:7">
-      <c r="B14" s="3" t="s">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B14" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E14" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F14" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G14" s="5" t="s">
+      <c r="E14" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G14" s="4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="15" spans="2:7">
-      <c r="B15" s="3" t="s">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B15" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D15" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E15" s="8" t="s">
+      <c r="D15" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="F15" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G15" s="5" t="s">
+      <c r="F15" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15" s="4" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="16" spans="2:7">
-      <c r="B16" s="3" t="s">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B16" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D16" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F16" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G16" s="5" t="s">
+      <c r="D16" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F16" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G16" s="4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="17" spans="2:7">
-      <c r="B17" s="3" t="s">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B17" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D17" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E17" s="8" t="s">
+      <c r="D17" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="F17" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G17" s="5" t="s">
+      <c r="F17" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G17" s="4" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="18" spans="2:7">
-      <c r="B18" s="3" t="s">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B18" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D18" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F18" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G18" s="5" t="s">
+      <c r="D18" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F18" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18" s="4" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="2:7">
-      <c r="B19" s="3" t="s">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B19" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D19" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F19" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G19" s="5" t="s">
+      <c r="D19" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F19" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="20" spans="2:7">
-      <c r="B20" s="3" t="s">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B20" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C20" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="D20" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F20" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G20" s="5" t="s">
+      <c r="D20" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F20" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" s="4" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="21" spans="2:7">
-      <c r="B21" s="3" t="s">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B21" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="D21" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F21" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G21" s="5" t="s">
+      <c r="D21" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F21" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="22" spans="2:7">
-      <c r="B22" s="3" t="s">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B22" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C22" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="D22" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F22" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G22" s="5" t="s">
+      <c r="D22" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F22" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="23" spans="2:7">
-      <c r="B23" s="3" t="s">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B23" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="D23" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F23" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G23" s="5" t="s">
+      <c r="D23" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F23" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" s="4" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="24" spans="2:7">
-      <c r="B24" s="3" t="s">
+    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B24" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D24" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F24" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G24" s="5" t="s">
+      <c r="D24" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F24" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" s="4" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="25" spans="2:7">
-      <c r="B25" s="3" t="s">
+    <row r="25" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B25" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="D25" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F25" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G25" s="5" t="s">
+      <c r="D25" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F25" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="26" spans="2:7">
-      <c r="B26" s="3" t="s">
+    <row r="26" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B26" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="C26" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="D26" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F26" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="5" t="s">
+      <c r="D26" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F26" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26" s="4" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="27" spans="2:7">
-      <c r="B27" s="3" t="s">
+    <row r="27" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B27" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="C27" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="D27" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F27" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G27" s="5" t="s">
+      <c r="D27" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F27" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G27" s="4" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="28" spans="2:7">
-      <c r="B28" s="3" t="s">
+    <row r="28" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B28" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D28" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F28" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G28" s="2" t="s">
+      <c r="D28" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F28" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G28" s="1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="29" spans="2:7">
-      <c r="B29" s="3" t="s">
+    <row r="29" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B29" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="D29" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F29" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G29" s="2" t="s">
+      <c r="D29" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F29" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G29" s="1" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="2:7">
-      <c r="B30" s="3" t="s">
+    <row r="30" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B30" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="D30" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F30" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G30" s="2" t="s">
+      <c r="D30" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F30" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G30" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="31" spans="2:7">
-      <c r="B31" s="3" t="s">
+    <row r="31" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B31" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="D31" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F31" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G31" s="2" t="s">
+      <c r="D31" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F31" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G31" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="32" spans="2:7">
-      <c r="B32" s="3" t="s">
+    <row r="32" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B32" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="D32" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F32" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G32" s="2" t="s">
+      <c r="D32" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F32" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G32" s="1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="33" spans="2:7">
-      <c r="B33" s="2" t="s">
+    <row r="33" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B33" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="D33" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F33" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G33" s="2" t="s">
+      <c r="D33" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F33" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G33" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="34" spans="2:7">
-      <c r="B34" s="2" t="s">
+    <row r="34" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B34" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D34" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F34" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G34" s="2" t="s">
+      <c r="D34" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F34" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G34" s="1" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="35" spans="2:7">
-      <c r="B35" s="2" t="s">
+    <row r="35" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B35" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="D35" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E35" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F35" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G35" s="2" t="s">
+      <c r="D35" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F35" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G35" s="1" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="36" spans="2:7">
-      <c r="B36" s="2" t="s">
+    <row r="36" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B36" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="D36" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F36" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G36" s="2" t="s">
+      <c r="D36" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F36" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G36" s="1" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="37" spans="2:7">
-      <c r="B37" s="2" t="s">
+    <row r="37" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B37" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C37" s="10" t="s">
+      <c r="C37" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D37" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E37" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F37" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G37" s="10" t="s">
+      <c r="D37" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F37" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G37" s="1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="38" spans="2:7">
-      <c r="B38" s="2" t="s">
+    <row r="38" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B38" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="D38" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E38" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F38" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G38" s="2" t="s">
+      <c r="D38" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F38" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G38" s="1" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="39" spans="2:7">
-      <c r="B39" s="2" t="s">
+    <row r="39" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B39" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="D39" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E39" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F39" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G39" s="2" t="s">
+      <c r="D39" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F39" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G39" s="1" t="s">
         <v>130</v>
       </c>
     </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B40" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F40" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G40" s="9" t="s">
+        <v>133</v>
+      </c>
+    </row>
   </sheetData>
-  <printOptions>
-    <extLst>
-      <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1783073298" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
-      </ext>
-    </extLst>
-  </printOptions>
-  <pageMargins left="0.700000" right="0.700000" top="0.750000" bottom="0.750000" header="0.300000" footer="0.300000"/>
-  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="1"/>
-  <headerFooter>
-    <extLst>
-      <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1783073298" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1783073298" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1783073298" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1783073298" Id="1" type="0" value="0"/>
-      </ext>
-    </extLst>
-  </headerFooter>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" fitToWidth="0"/>
   <extLst>
     <ext uri="smNativeData">
       <pm:sheetPrefs xmlns:pm="smNativeData" day="1783073298" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">

--- a/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
@@ -1,34 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
+  <fileSharing readOnlyRecommended="0" userName="Lumino Game 03"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EF048BD-BED5-4625-A859-E620B1915AF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6680" yWindow="3710" windowWidth="24990" windowHeight="19220" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView activeTab="0" xWindow="240" yWindow="60" windowWidth="24990" windowHeight="19220" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:revision xmlns:pm="smNativeData" day="1783073298" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
-      <pm:docPrefs xmlns:pm="smNativeData" id="1783073298" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
-      <pm:compatibility xmlns:pm="smNativeData" id="1783073298" overlapCells="1"/>
-      <pm:defCurrency xmlns:pm="smNativeData" id="1783073298"/>
+      <pm:revision xmlns:pm="smNativeData" day="1783587489" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
+      <pm:docPrefs xmlns:pm="smNativeData" id="1783587489" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
+      <pm:compatibility xmlns:pm="smNativeData" id="1783587489" overlapCells="1"/>
+      <pm:defCurrency xmlns:pm="smNativeData" id="1783587489"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="137">
   <si>
     <t>##var</t>
   </si>
@@ -423,58 +418,101 @@
     <t>测试面板</t>
   </si>
   <si>
+    <t>PopUnlockDollWindowsUI</t>
+  </si>
+  <si>
     <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/PopUnlockDollWindowsUI/PopUnlockDollWindowsUI.prefab</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>PopUnlockDollWindowsUI</t>
   </si>
   <si>
     <t>解锁娃娃机展示界面</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>FactoryProcessGamePanel</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/FactoryUI/FactoryProcessGamePanel.prefab</t>
+  </si>
+  <si>
+    <t>工厂处理游戏面板</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="8">
+    <numFmt numFmtId="5" formatCode="#,##0\ &quot;¥&quot;;\-#,##0\ &quot;¥&quot;"/>
+    <numFmt numFmtId="6" formatCode="#,##0\ &quot;¥&quot;;[Red]\-#,##0\ &quot;¥&quot;"/>
+    <numFmt numFmtId="7" formatCode="#,##0.00\ &quot;¥&quot;;\-#,##0.00\ &quot;¥&quot;"/>
+    <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;¥&quot;;[Red]\-#,##0.00\ &quot;¥&quot;"/>
+    <numFmt numFmtId="42" formatCode="_-* #,##0\ &quot;¥&quot;_-;\-* #,##0\ &quot;¥&quot;_-;_-* &quot;-&quot;\ &quot;¥&quot;_-;_-@_-"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0\ _¥_-;\-* #,##0\ _¥_-;_-* &quot;-&quot;\ _¥_-;_-@_-"/>
+    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;¥&quot;_-;\-* #,##0.00\ &quot;¥&quot;_-;_-* &quot;-&quot;??\ &quot;¥&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _¥_-;\-* #,##0.00\ _¥_-;_-* &quot;-&quot;??\ _¥_-;_-@_-"/>
+  </numFmts>
+  <fonts count="4">
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="等线"/>
       <charset val="134"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1783587489" ulstyle="none" kern="1">
+            <pm:latin face="等线" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1783587489" ulstyle="none" kern="1">
+            <pm:latin face="Arial" sz="200" lang="default"/>
+            <pm:cs face="Times New Roman" sz="200" lang="default"/>
+            <pm:ea face="SimSun" sz="200" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF1F2329"/>
       <name val="等线"/>
+      <charset val="134"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1783587489" ulstyle="none" kern="1">
+            <pm:latin face="等线" sz="200" lang="default"/>
+            <pm:cs face="Times New Roman" sz="200" lang="default"/>
+            <pm:ea face="SimSun" sz="200" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <color rgb="FF1F2329"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1783587489" fgClr="1F2329" ulstyle="none" kern="1">
+            <pm:latin face="等线" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -482,25 +520,61 @@
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFACB9CA"/>
         <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1783587489" type="1" fgLvl="100" fgClr="00ACB9CA" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF5B9BD5"/>
         <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1783587489" type="1" fgLvl="100" fgClr="005B9BD5" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1783587489" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783587489"/>
+        </ext>
+      </extLst>
     </border>
     <border>
       <left style="thin">
@@ -515,77 +589,125 @@
       <bottom style="thin">
         <color rgb="FFDEE0E3"/>
       </bottom>
-      <diagonal/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783587489">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+          </pm:border>
+        </ext>
+      </extLst>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783587489"/>
+        </ext>
+      </extLst>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783587489"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783587489"/>
+        </ext>
+      </extLst>
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="常规" xfId="0" builtinId="0" customBuiltin="1"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
+    <cellStyle name="常规 2" xfId="1"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
     <ext uri="smNativeData">
-      <pm:charStyles xmlns:pm="smNativeData" id="1783073298" count="1">
+      <pm:charStyles xmlns:pm="smNativeData" id="1783587489" count="1">
         <pm:charStyle name="普通" fontId="0" Id="1"/>
       </pm:charStyles>
-      <pm:colors xmlns:pm="smNativeData" id="1783073298" count="4">
+      <pm:colors xmlns:pm="smNativeData" id="1783587489" count="4">
         <pm:color name="颜色 24" rgb="1F2329"/>
         <pm:color name="颜色 25" rgb="ACB9CA"/>
         <pm:color name="颜色 26" rgb="5B9BD5"/>
@@ -851,837 +973,872 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G40"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <dimension ref="A1:G41"/>
+  <sheetFormatPr defaultRowHeight="13.45"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="28.58203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="100.08203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="25.1640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="23.6640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="17.6640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="24.1640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="8.6640625" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.6640625" style="1"/>
+    <col min="1" max="1" width="8.663793" customWidth="1" style="2"/>
+    <col min="2" max="2" width="28.577586" customWidth="1" style="2"/>
+    <col min="3" max="3" width="100.077586" customWidth="1" style="2"/>
+    <col min="4" max="4" width="25.163793" customWidth="1" style="2"/>
+    <col min="5" max="5" width="23.663793" customWidth="1" style="2"/>
+    <col min="6" max="6" width="17.663793" customWidth="1" style="2"/>
+    <col min="7" max="7" width="24.163793" customWidth="1" style="2"/>
+    <col min="8" max="16384" width="8.663793" customWidth="1" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
+    <row r="1" spans="1:7">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:7">
+      <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:7">
+      <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B4" s="2" t="s">
+    <row r="4" spans="2:7">
+      <c r="B4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G4" s="4" t="s">
+      <c r="D4" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="2" t="s">
+    <row r="5" spans="2:7" ht="19.50" customHeight="1">
+      <c r="B5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="7" t="s">
+      <c r="D5" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G5" s="4" t="s">
+      <c r="F5" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B6" s="2" t="s">
+    <row r="6" spans="2:7">
+      <c r="B6" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G6" s="4" t="s">
+      <c r="D6" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B7" s="2" t="s">
+    <row r="7" spans="2:7">
+      <c r="B7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G7" s="4" t="s">
+      <c r="D7" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B8" s="2" t="s">
+    <row r="8" spans="2:7">
+      <c r="B8" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G8" s="4" t="s">
+      <c r="D8" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B9" s="2" t="s">
+    <row r="9" spans="2:7">
+      <c r="B9" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="F9" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G9" s="4" t="s">
+      <c r="F9" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" s="5" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B10" s="2" t="s">
+    <row r="10" spans="2:7">
+      <c r="B10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="F10" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G10" s="4" t="s">
+      <c r="F10" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B11" s="2" t="s">
+    <row r="11" spans="2:7">
+      <c r="B11" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D11" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F11" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G11" s="4" t="s">
+      <c r="D11" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G11" s="5" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B12" s="2" t="s">
+    <row r="12" spans="2:7">
+      <c r="B12" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F12" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G12" s="4" t="s">
+      <c r="D12" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12" s="5" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B13" s="2" t="s">
+    <row r="13" spans="2:7">
+      <c r="B13" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="F13" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G13" s="4" t="s">
+      <c r="F13" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G13" s="5" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B14" s="2" t="s">
+    <row r="14" spans="2:7">
+      <c r="B14" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E14" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F14" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G14" s="4" t="s">
+      <c r="E14" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G14" s="5" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B15" s="2" t="s">
+    <row r="15" spans="2:7">
+      <c r="B15" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D15" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E15" s="7" t="s">
+      <c r="D15" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="F15" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G15" s="4" t="s">
+      <c r="F15" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15" s="5" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B16" s="2" t="s">
+    <row r="16" spans="2:7">
+      <c r="B16" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="D16" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F16" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G16" s="4" t="s">
+      <c r="D16" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F16" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G16" s="5" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B17" s="2" t="s">
+    <row r="17" spans="2:7">
+      <c r="B17" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="D17" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E17" s="7" t="s">
+      <c r="D17" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="F17" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G17" s="4" t="s">
+      <c r="F17" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G17" s="5" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B18" s="2" t="s">
+    <row r="18" spans="2:7">
+      <c r="B18" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="D18" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F18" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G18" s="4" t="s">
+      <c r="D18" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F18" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18" s="5" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B19" s="2" t="s">
+    <row r="19" spans="2:7">
+      <c r="B19" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="D19" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F19" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G19" s="4" t="s">
+      <c r="D19" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F19" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" s="5" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B20" s="2" t="s">
+    <row r="20" spans="2:7">
+      <c r="B20" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="D20" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F20" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G20" s="4" t="s">
+      <c r="D20" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F20" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" s="5" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B21" s="2" t="s">
+    <row r="21" spans="2:7">
+      <c r="B21" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="D21" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F21" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G21" s="4" t="s">
+      <c r="D21" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F21" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" s="5" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B22" s="2" t="s">
+    <row r="22" spans="2:7">
+      <c r="B22" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="D22" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F22" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G22" s="4" t="s">
+      <c r="D22" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F22" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" s="5" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B23" s="2" t="s">
+    <row r="23" spans="2:7">
+      <c r="B23" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="D23" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F23" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G23" s="4" t="s">
+      <c r="D23" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F23" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" s="5" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B24" s="2" t="s">
+    <row r="24" spans="2:7">
+      <c r="B24" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="D24" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F24" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G24" s="4" t="s">
+      <c r="D24" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F24" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" s="5" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B25" s="2" t="s">
+    <row r="25" spans="2:7">
+      <c r="B25" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="D25" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F25" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G25" s="4" t="s">
+      <c r="D25" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F25" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" s="5" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B26" s="2" t="s">
+    <row r="26" spans="2:7">
+      <c r="B26" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C26" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="D26" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F26" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="4" t="s">
+      <c r="D26" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F26" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26" s="5" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B27" s="2" t="s">
+    <row r="27" spans="2:7">
+      <c r="B27" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="D27" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F27" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G27" s="4" t="s">
+      <c r="D27" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F27" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G27" s="5" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B28" s="2" t="s">
+    <row r="28" spans="2:7">
+      <c r="B28" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D28" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F28" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G28" s="1" t="s">
+      <c r="D28" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F28" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G28" s="2" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B29" s="2" t="s">
+    <row r="29" spans="2:7">
+      <c r="B29" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="D29" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F29" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G29" s="1" t="s">
+      <c r="D29" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F29" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G29" s="2" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B30" s="2" t="s">
+    <row r="30" spans="2:7">
+      <c r="B30" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D30" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F30" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G30" s="1" t="s">
+      <c r="D30" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F30" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G30" s="2" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B31" s="2" t="s">
+    <row r="31" spans="2:7">
+      <c r="B31" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="D31" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F31" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G31" s="1" t="s">
+      <c r="D31" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F31" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G31" s="2" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B32" s="2" t="s">
+    <row r="32" spans="2:7">
+      <c r="B32" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="D32" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F32" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G32" s="1" t="s">
+      <c r="D32" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F32" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G32" s="2" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B33" s="1" t="s">
+    <row r="33" spans="2:7">
+      <c r="B33" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="D33" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F33" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G33" s="1" t="s">
+      <c r="D33" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F33" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G33" s="2" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B34" s="1" t="s">
+    <row r="34" spans="2:7">
+      <c r="B34" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D34" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E34" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F34" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G34" s="1" t="s">
+      <c r="D34" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F34" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G34" s="2" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B35" s="1" t="s">
+    <row r="35" spans="2:7">
+      <c r="B35" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="D35" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F35" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G35" s="1" t="s">
+      <c r="D35" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F35" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G35" s="2" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B36" s="1" t="s">
+    <row r="36" spans="2:7">
+      <c r="B36" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="D36" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F36" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G36" s="1" t="s">
+      <c r="D36" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F36" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G36" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B37" s="1" t="s">
+    <row r="37" spans="2:7">
+      <c r="B37" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="D37" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F37" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G37" s="1" t="s">
+      <c r="D37" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F37" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G37" s="2" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="38" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B38" s="1" t="s">
+    <row r="38" spans="2:7">
+      <c r="B38" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="D38" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E38" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F38" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G38" s="1" t="s">
+      <c r="D38" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F38" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G38" s="2" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B39" s="1" t="s">
+    <row r="39" spans="2:7">
+      <c r="B39" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="D39" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E39" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F39" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G39" s="1" t="s">
+      <c r="D39" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F39" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G39" s="2" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B40" s="1" t="s">
+    <row r="40" spans="2:7">
+      <c r="B40" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C40" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="C40" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E40" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F40" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G40" s="9" t="s">
+      <c r="D40" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F40" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G40" s="10" t="s">
         <v>133</v>
       </c>
     </row>
+    <row r="41" spans="2:7">
+      <c r="B41" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C41" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F41" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G41" s="10" t="s">
+        <v>136</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" fitToWidth="0"/>
+  <printOptions>
+    <extLst>
+      <ext uri="smNativeData">
+        <pm:pageFlags xmlns:pm="smNativeData" id="1783587489" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+      </ext>
+    </extLst>
+  </printOptions>
+  <pageMargins left="0.700000" right="0.700000" top="0.750000" bottom="0.750000" header="0.300000" footer="0.300000"/>
+  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="1"/>
+  <headerFooter>
+    <extLst>
+      <ext uri="smNativeData">
+        <pm:header xmlns:pm="smNativeData" id="1783587489" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1783587489" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1783587489" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1783587489" Id="1" type="0" value="0"/>
+      </ext>
+    </extLst>
+  </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1783073298" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1783587489" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>

--- a/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
@@ -1,16 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
-  <fileSharing readOnlyRecommended="0" userName="Lumino Game 03"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F16A6324-F4FB-40DA-8FFB-7E8994BFD58D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0" xWindow="240" yWindow="60" windowWidth="24990" windowHeight="19220" tabRatio="500"/>
+    <workbookView xWindow="2280" yWindow="2200" windowWidth="30580" windowHeight="18680" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext uri="smNativeData">
       <pm:revision xmlns:pm="smNativeData" day="1783587489" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
@@ -23,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="140">
   <si>
     <t>##var</t>
   </si>
@@ -434,85 +439,60 @@
   </si>
   <si>
     <t>工厂处理游戏面板</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/PopRewardUI/PopRewardUI.prefab</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>通用获得道具界面</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>PopRewardUI</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
-    <numFmt numFmtId="5" formatCode="#,##0\ &quot;¥&quot;;\-#,##0\ &quot;¥&quot;"/>
-    <numFmt numFmtId="6" formatCode="#,##0\ &quot;¥&quot;;[Red]\-#,##0\ &quot;¥&quot;"/>
-    <numFmt numFmtId="7" formatCode="#,##0.00\ &quot;¥&quot;;\-#,##0.00\ &quot;¥&quot;"/>
-    <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;¥&quot;;[Red]\-#,##0.00\ &quot;¥&quot;"/>
-    <numFmt numFmtId="42" formatCode="_-* #,##0\ &quot;¥&quot;_-;\-* #,##0\ &quot;¥&quot;_-;_-* &quot;-&quot;\ &quot;¥&quot;_-;_-@_-"/>
-    <numFmt numFmtId="41" formatCode="_-* #,##0\ _¥_-;\-* #,##0\ _¥_-;_-* &quot;-&quot;\ _¥_-;_-@_-"/>
-    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;¥&quot;_-;\-* #,##0.00\ &quot;¥&quot;_-;_-* &quot;-&quot;??\ &quot;¥&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _¥_-;\-* #,##0.00\ _¥_-;_-* &quot;-&quot;??\ _¥_-;_-@_-"/>
-  </numFmts>
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="等线"/>
       <charset val="134"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1783587489" ulstyle="none" kern="1">
-            <pm:latin face="等线" sz="220" lang="default"/>
-            <pm:cs face="Times New Roman" sz="220" lang="default"/>
-            <pm:ea face="SimSun" sz="220" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
-      <name val="Arial"/>
-      <family val="2"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
-      <sz val="10"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1783587489" ulstyle="none" kern="1">
-            <pm:latin face="Arial" sz="200" lang="default"/>
-            <pm:cs face="Times New Roman" sz="200" lang="default"/>
-            <pm:ea face="SimSun" sz="200" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
+      <name val="等线"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF1F2329"/>
       <name val="等线"/>
-      <charset val="134"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1783587489" ulstyle="none" kern="1">
-            <pm:latin face="等线" sz="200" lang="default"/>
-            <pm:cs face="Times New Roman" sz="200" lang="default"/>
-            <pm:ea face="SimSun" sz="200" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="等线"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
-      <color rgb="FF1F2329"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1783587489" fgClr="1F2329" ulstyle="none" kern="1">
-            <pm:latin face="等线" sz="220" lang="default"/>
-            <pm:cs face="Times New Roman" sz="220" lang="default"/>
-            <pm:ea face="SimSun" sz="220" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -520,61 +500,25 @@
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
-      <patternFill patternType="none"/>
-    </fill>
-    <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFACB9CA"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783587489" type="1" fgLvl="100" fgClr="00ACB9CA" bgLvl="0" bgClr="00FFFFFF"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF5B9BD5"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783587489" type="1" fgLvl="100" fgClr="005B9BD5" bgLvl="0" bgClr="00FFFFFF"/>
-          </ext>
-        </extLst>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783587489" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="4">
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783587489"/>
-        </ext>
-      </extLst>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -589,120 +533,72 @@
       <bottom style="thin">
         <color rgb="FFDEE0E3"/>
       </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783587489">
-            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-          </pm:border>
-        </ext>
-      </extLst>
+      <diagonal/>
     </border>
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783587489"/>
-        </ext>
-      </extLst>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783587489"/>
-        </ext>
-      </extLst>
-    </border>
-    <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783587489"/>
-        </ext>
-      </extLst>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
-    <cellStyle name="常规 2" xfId="1"/>
+    <cellStyle name="常规" xfId="0" builtinId="0" customBuiltin="1"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0"/>
   <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
     <ext uri="smNativeData">
       <pm:charStyles xmlns:pm="smNativeData" id="1783587489" count="1">
         <pm:charStyle name="普通" fontId="0" Id="1"/>
@@ -973,869 +869,874 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:G41"/>
-  <sheetFormatPr defaultRowHeight="13.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G42"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.663793" customWidth="1" style="2"/>
-    <col min="2" max="2" width="28.577586" customWidth="1" style="2"/>
-    <col min="3" max="3" width="100.077586" customWidth="1" style="2"/>
-    <col min="4" max="4" width="25.163793" customWidth="1" style="2"/>
-    <col min="5" max="5" width="23.663793" customWidth="1" style="2"/>
-    <col min="6" max="6" width="17.663793" customWidth="1" style="2"/>
-    <col min="7" max="7" width="24.163793" customWidth="1" style="2"/>
-    <col min="8" max="16384" width="8.663793" customWidth="1" style="2"/>
+    <col min="1" max="1" width="8.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="28.58203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="100.08203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="25.1640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="23.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="24.1640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="8.6640625" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="4" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="2:7">
-      <c r="B4" s="3" t="s">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G4" s="5" t="s">
+      <c r="D4" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="2:7" ht="19.50" customHeight="1">
-      <c r="B5" s="3" t="s">
+    <row r="5" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="8" t="s">
+      <c r="D5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G5" s="5" t="s">
+      <c r="F5" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="2:7">
-      <c r="B6" s="3" t="s">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G6" s="5" t="s">
+      <c r="D6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="2:7">
-      <c r="B7" s="3" t="s">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B7" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G7" s="5" t="s">
+      <c r="D7" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="2:7">
-      <c r="B8" s="3" t="s">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G8" s="5" t="s">
+      <c r="D8" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="2:7">
-      <c r="B9" s="3" t="s">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B9" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="F9" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G9" s="5" t="s">
+      <c r="F9" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="2:7">
-      <c r="B10" s="3" t="s">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B10" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="F10" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G10" s="5" t="s">
+      <c r="F10" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="2:7">
-      <c r="B11" s="3" t="s">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B11" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D11" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F11" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G11" s="5" t="s">
+      <c r="D11" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="2:7">
-      <c r="B12" s="3" t="s">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B12" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F12" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G12" s="5" t="s">
+      <c r="D12" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="13" spans="2:7">
-      <c r="B13" s="3" t="s">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B13" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="F13" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G13" s="5" t="s">
+      <c r="F13" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G13" s="4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="14" spans="2:7">
-      <c r="B14" s="3" t="s">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B14" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E14" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F14" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G14" s="5" t="s">
+      <c r="E14" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G14" s="4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="15" spans="2:7">
-      <c r="B15" s="3" t="s">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B15" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D15" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E15" s="8" t="s">
+      <c r="D15" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="F15" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G15" s="5" t="s">
+      <c r="F15" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15" s="4" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="16" spans="2:7">
-      <c r="B16" s="3" t="s">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B16" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D16" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F16" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G16" s="5" t="s">
+      <c r="D16" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F16" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G16" s="4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="17" spans="2:7">
-      <c r="B17" s="3" t="s">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B17" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D17" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E17" s="8" t="s">
+      <c r="D17" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="F17" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G17" s="5" t="s">
+      <c r="F17" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G17" s="4" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="18" spans="2:7">
-      <c r="B18" s="3" t="s">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B18" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D18" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F18" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G18" s="5" t="s">
+      <c r="D18" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F18" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18" s="4" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="2:7">
-      <c r="B19" s="3" t="s">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B19" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D19" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F19" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G19" s="5" t="s">
+      <c r="D19" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F19" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="20" spans="2:7">
-      <c r="B20" s="3" t="s">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B20" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C20" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="D20" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F20" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G20" s="5" t="s">
+      <c r="D20" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F20" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" s="4" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="21" spans="2:7">
-      <c r="B21" s="3" t="s">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B21" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="D21" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F21" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G21" s="5" t="s">
+      <c r="D21" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F21" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="22" spans="2:7">
-      <c r="B22" s="3" t="s">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B22" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C22" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="D22" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F22" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G22" s="5" t="s">
+      <c r="D22" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F22" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="23" spans="2:7">
-      <c r="B23" s="3" t="s">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B23" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="D23" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F23" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G23" s="5" t="s">
+      <c r="D23" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F23" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" s="4" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="24" spans="2:7">
-      <c r="B24" s="3" t="s">
+    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B24" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D24" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F24" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G24" s="5" t="s">
+      <c r="D24" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F24" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" s="4" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="25" spans="2:7">
-      <c r="B25" s="3" t="s">
+    <row r="25" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B25" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="D25" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F25" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G25" s="5" t="s">
+      <c r="D25" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F25" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="26" spans="2:7">
-      <c r="B26" s="3" t="s">
+    <row r="26" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B26" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="C26" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="D26" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F26" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="5" t="s">
+      <c r="D26" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F26" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26" s="4" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="27" spans="2:7">
-      <c r="B27" s="3" t="s">
+    <row r="27" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B27" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="C27" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="D27" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F27" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G27" s="5" t="s">
+      <c r="D27" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F27" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G27" s="4" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="28" spans="2:7">
-      <c r="B28" s="3" t="s">
+    <row r="28" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B28" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D28" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F28" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G28" s="2" t="s">
+      <c r="D28" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F28" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G28" s="1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="29" spans="2:7">
-      <c r="B29" s="3" t="s">
+    <row r="29" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B29" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="D29" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F29" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G29" s="2" t="s">
+      <c r="D29" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F29" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G29" s="1" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="2:7">
-      <c r="B30" s="3" t="s">
+    <row r="30" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B30" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="D30" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F30" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G30" s="2" t="s">
+      <c r="D30" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F30" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G30" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="31" spans="2:7">
-      <c r="B31" s="3" t="s">
+    <row r="31" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B31" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="D31" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F31" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G31" s="2" t="s">
+      <c r="D31" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F31" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G31" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="32" spans="2:7">
-      <c r="B32" s="3" t="s">
+    <row r="32" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B32" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="D32" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F32" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G32" s="2" t="s">
+      <c r="D32" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F32" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G32" s="1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="33" spans="2:7">
-      <c r="B33" s="2" t="s">
+    <row r="33" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B33" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="D33" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F33" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G33" s="2" t="s">
+      <c r="D33" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F33" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G33" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="34" spans="2:7">
-      <c r="B34" s="2" t="s">
+    <row r="34" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B34" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D34" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F34" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G34" s="2" t="s">
+      <c r="D34" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F34" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G34" s="1" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="35" spans="2:7">
-      <c r="B35" s="2" t="s">
+    <row r="35" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B35" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="D35" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E35" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F35" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G35" s="2" t="s">
+      <c r="D35" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F35" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G35" s="1" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="36" spans="2:7">
-      <c r="B36" s="2" t="s">
+    <row r="36" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B36" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="D36" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F36" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G36" s="2" t="s">
+      <c r="D36" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F36" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G36" s="1" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="37" spans="2:7">
-      <c r="B37" s="2" t="s">
+    <row r="37" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B37" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D37" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E37" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F37" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G37" s="2" t="s">
+      <c r="D37" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F37" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G37" s="1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="38" spans="2:7">
-      <c r="B38" s="2" t="s">
+    <row r="38" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B38" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="D38" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E38" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F38" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G38" s="2" t="s">
+      <c r="D38" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F38" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G38" s="1" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="39" spans="2:7">
-      <c r="B39" s="2" t="s">
+    <row r="39" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B39" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="D39" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E39" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F39" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G39" s="2" t="s">
+      <c r="D39" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F39" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G39" s="1" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="40" spans="2:7">
-      <c r="B40" s="2" t="s">
+    <row r="40" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B40" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C40" s="10" t="s">
+      <c r="C40" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="D40" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E40" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F40" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G40" s="10" t="s">
+      <c r="D40" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F40" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G40" s="1" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="41" spans="2:7">
-      <c r="B41" s="2" t="s">
+    <row r="41" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B41" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C41" s="10" t="s">
+      <c r="C41" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="D41" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E41" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F41" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G41" s="10" t="s">
+      <c r="D41" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F41" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G41" s="1" t="s">
         <v>136</v>
       </c>
     </row>
+    <row r="42" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B42" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F42" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G42" s="9" t="s">
+        <v>138</v>
+      </c>
+    </row>
   </sheetData>
-  <printOptions>
-    <extLst>
-      <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1783587489" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
-      </ext>
-    </extLst>
-  </printOptions>
-  <pageMargins left="0.700000" right="0.700000" top="0.750000" bottom="0.750000" header="0.300000" footer="0.300000"/>
-  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="1"/>
-  <headerFooter>
-    <extLst>
-      <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1783587489" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1783587489" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1783587489" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1783587489" Id="1" type="0" value="0"/>
-      </ext>
-    </extLst>
-  </headerFooter>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" fitToWidth="0"/>
   <extLst>
     <ext uri="smNativeData">
       <pm:sheetPrefs xmlns:pm="smNativeData" day="1783587489" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">

--- a/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
@@ -1,34 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
+  <fileSharing readOnlyRecommended="0" userName="Lumino Game 03"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F16A6324-F4FB-40DA-8FFB-7E8994BFD58D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2280" yWindow="2200" windowWidth="30580" windowHeight="18680" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView activeTab="0" xWindow="240" yWindow="60" windowWidth="30580" windowHeight="18680" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:revision xmlns:pm="smNativeData" day="1783587489" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
-      <pm:docPrefs xmlns:pm="smNativeData" id="1783587489" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
-      <pm:compatibility xmlns:pm="smNativeData" id="1783587489" overlapCells="1"/>
-      <pm:defCurrency xmlns:pm="smNativeData" id="1783587489"/>
+      <pm:revision xmlns:pm="smNativeData" day="1783675043" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
+      <pm:docPrefs xmlns:pm="smNativeData" id="1783675043" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
+      <pm:compatibility xmlns:pm="smNativeData" id="1783675043" overlapCells="1"/>
+      <pm:defCurrency xmlns:pm="smNativeData" id="1783675043"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="143">
   <si>
     <t>##var</t>
   </si>
@@ -441,58 +436,101 @@
     <t>工厂处理游戏面板</t>
   </si>
   <si>
+    <t>PopRewardUI</t>
+  </si>
+  <si>
     <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/PopRewardUI/PopRewardUI.prefab</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>通用获得道具界面</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>PopRewardUI</t>
+  </si>
+  <si>
+    <t>FactoryProcessIntroPanel</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/FactoryUI/FactoryProcessIntroPanel.prefab</t>
+  </si>
+  <si>
+    <t>工厂处理介绍面板</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="8">
+    <numFmt numFmtId="5" formatCode="#,##0\ &quot;¥&quot;;\-#,##0\ &quot;¥&quot;"/>
+    <numFmt numFmtId="6" formatCode="#,##0\ &quot;¥&quot;;[Red]\-#,##0\ &quot;¥&quot;"/>
+    <numFmt numFmtId="7" formatCode="#,##0.00\ &quot;¥&quot;;\-#,##0.00\ &quot;¥&quot;"/>
+    <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;¥&quot;;[Red]\-#,##0.00\ &quot;¥&quot;"/>
+    <numFmt numFmtId="42" formatCode="_-* #,##0\ &quot;¥&quot;_-;\-* #,##0\ &quot;¥&quot;_-;_-* &quot;-&quot;\ &quot;¥&quot;_-;_-@_-"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0\ _¥_-;\-* #,##0\ _¥_-;_-* &quot;-&quot;\ _¥_-;_-@_-"/>
+    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;¥&quot;_-;\-* #,##0.00\ &quot;¥&quot;_-;_-* &quot;-&quot;??\ &quot;¥&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _¥_-;\-* #,##0.00\ _¥_-;_-* &quot;-&quot;??\ _¥_-;_-@_-"/>
+  </numFmts>
+  <fonts count="4">
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="等线"/>
       <charset val="134"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1783675043" ulstyle="none" kern="1">
+            <pm:latin face="等线" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1783675043" ulstyle="none" kern="1">
+            <pm:latin face="Arial" sz="200" lang="default"/>
+            <pm:cs face="Times New Roman" sz="200" lang="default"/>
+            <pm:ea face="SimSun" sz="200" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF1F2329"/>
       <name val="等线"/>
+      <charset val="134"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1783675043" ulstyle="none" kern="1">
+            <pm:latin face="等线" sz="200" lang="default"/>
+            <pm:cs face="Times New Roman" sz="200" lang="default"/>
+            <pm:ea face="SimSun" sz="200" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <color rgb="FF1F2329"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1783675043" fgClr="1F2329" ulstyle="none" kern="1">
+            <pm:latin face="等线" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -500,25 +538,61 @@
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFACB9CA"/>
         <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1783675043" type="1" fgLvl="100" fgClr="00ACB9CA" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF5B9BD5"/>
         <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1783675043" type="1" fgLvl="100" fgClr="005B9BD5" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1783675043" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783675043"/>
+        </ext>
+      </extLst>
     </border>
     <border>
       <left style="thin">
@@ -533,77 +607,125 @@
       <bottom style="thin">
         <color rgb="FFDEE0E3"/>
       </bottom>
-      <diagonal/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783675043">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+          </pm:border>
+        </ext>
+      </extLst>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783675043"/>
+        </ext>
+      </extLst>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783675043"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783675043"/>
+        </ext>
+      </extLst>
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="常规" xfId="0" builtinId="0" customBuiltin="1"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
+    <cellStyle name="常规 2" xfId="1"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
     <ext uri="smNativeData">
-      <pm:charStyles xmlns:pm="smNativeData" id="1783587489" count="1">
+      <pm:charStyles xmlns:pm="smNativeData" id="1783675043" count="1">
         <pm:charStyle name="普通" fontId="0" Id="1"/>
       </pm:charStyles>
-      <pm:colors xmlns:pm="smNativeData" id="1783587489" count="4">
+      <pm:colors xmlns:pm="smNativeData" id="1783675043" count="4">
         <pm:color name="颜色 24" rgb="1F2329"/>
         <pm:color name="颜色 25" rgb="ACB9CA"/>
         <pm:color name="颜色 26" rgb="5B9BD5"/>
@@ -869,877 +991,912 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G42"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <dimension ref="A1:G43"/>
+  <sheetFormatPr defaultRowHeight="13.45"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="28.58203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="100.08203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="25.1640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="23.6640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="17.6640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="24.1640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="8.6640625" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.6640625" style="1"/>
+    <col min="1" max="1" width="8.663793" customWidth="1" style="2"/>
+    <col min="2" max="2" width="28.577586" customWidth="1" style="2"/>
+    <col min="3" max="3" width="100.077586" customWidth="1" style="2"/>
+    <col min="4" max="4" width="25.163793" customWidth="1" style="2"/>
+    <col min="5" max="5" width="23.663793" customWidth="1" style="2"/>
+    <col min="6" max="6" width="17.663793" customWidth="1" style="2"/>
+    <col min="7" max="7" width="24.163793" customWidth="1" style="2"/>
+    <col min="8" max="16384" width="8.663793" customWidth="1" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:7">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:7">
+      <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:7">
+      <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B4" s="2" t="s">
+    <row r="4" spans="2:7">
+      <c r="B4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="4" t="b">
+      <c r="D4" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="2" t="s">
+    <row r="5" spans="2:7" ht="19.50" customHeight="1">
+      <c r="B5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="7" t="s">
+      <c r="D5" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="4" t="b">
+      <c r="F5" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B6" s="2" t="s">
+    <row r="6" spans="2:7">
+      <c r="B6" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="4" t="b">
+      <c r="D6" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B7" s="2" t="s">
+    <row r="7" spans="2:7">
+      <c r="B7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" s="4" t="b">
+      <c r="D7" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B8" s="2" t="s">
+    <row r="8" spans="2:7">
+      <c r="B8" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8" s="4" t="b">
+      <c r="D8" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B9" s="2" t="s">
+    <row r="9" spans="2:7">
+      <c r="B9" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="F9" s="4" t="b">
+      <c r="F9" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="5" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B10" s="2" t="s">
+    <row r="10" spans="2:7">
+      <c r="B10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="F10" s="4" t="b">
+      <c r="F10" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B11" s="2" t="s">
+    <row r="11" spans="2:7">
+      <c r="B11" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D11" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F11" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G11" s="4" t="s">
+      <c r="D11" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G11" s="5" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B12" s="2" t="s">
+    <row r="12" spans="2:7">
+      <c r="B12" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F12" s="4" t="b">
+      <c r="D12" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="5" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B13" s="2" t="s">
+    <row r="13" spans="2:7">
+      <c r="B13" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="F13" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G13" s="4" t="s">
+      <c r="F13" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G13" s="5" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B14" s="2" t="s">
+    <row r="14" spans="2:7">
+      <c r="B14" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E14" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F14" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G14" s="4" t="s">
+      <c r="E14" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G14" s="5" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B15" s="2" t="s">
+    <row r="15" spans="2:7">
+      <c r="B15" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D15" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E15" s="7" t="s">
+      <c r="D15" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="F15" s="4" t="b">
+      <c r="F15" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="5" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B16" s="2" t="s">
+    <row r="16" spans="2:7">
+      <c r="B16" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="D16" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F16" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G16" s="4" t="s">
+      <c r="D16" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F16" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G16" s="5" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B17" s="2" t="s">
+    <row r="17" spans="2:7">
+      <c r="B17" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="D17" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E17" s="7" t="s">
+      <c r="D17" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="F17" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G17" s="4" t="s">
+      <c r="F17" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G17" s="5" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B18" s="2" t="s">
+    <row r="18" spans="2:7">
+      <c r="B18" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="D18" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F18" s="4" t="b">
+      <c r="D18" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F18" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="G18" s="5" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B19" s="2" t="s">
+    <row r="19" spans="2:7">
+      <c r="B19" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="D19" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F19" s="4" t="b">
+      <c r="D19" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F19" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="G19" s="5" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B20" s="2" t="s">
+    <row r="20" spans="2:7">
+      <c r="B20" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="D20" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F20" s="4" t="b">
+      <c r="D20" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F20" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="G20" s="5" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B21" s="2" t="s">
+    <row r="21" spans="2:7">
+      <c r="B21" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="D21" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F21" s="4" t="b">
+      <c r="D21" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F21" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="G21" s="4" t="s">
+      <c r="G21" s="5" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B22" s="2" t="s">
+    <row r="22" spans="2:7">
+      <c r="B22" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="D22" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F22" s="4" t="b">
+      <c r="D22" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F22" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="G22" s="4" t="s">
+      <c r="G22" s="5" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B23" s="2" t="s">
+    <row r="23" spans="2:7">
+      <c r="B23" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="D23" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F23" s="4" t="b">
+      <c r="D23" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F23" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="G23" s="5" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B24" s="2" t="s">
+    <row r="24" spans="2:7">
+      <c r="B24" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="D24" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F24" s="4" t="b">
+      <c r="D24" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F24" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="G24" s="4" t="s">
+      <c r="G24" s="5" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B25" s="2" t="s">
+    <row r="25" spans="2:7">
+      <c r="B25" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="D25" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F25" s="4" t="b">
+      <c r="D25" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F25" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="G25" s="4" t="s">
+      <c r="G25" s="5" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B26" s="2" t="s">
+    <row r="26" spans="2:7">
+      <c r="B26" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C26" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="D26" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F26" s="4" t="b">
+      <c r="D26" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F26" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="G26" s="4" t="s">
+      <c r="G26" s="5" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B27" s="2" t="s">
+    <row r="27" spans="2:7">
+      <c r="B27" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="D27" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F27" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G27" s="4" t="s">
+      <c r="D27" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F27" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G27" s="5" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B28" s="2" t="s">
+    <row r="28" spans="2:7">
+      <c r="B28" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D28" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F28" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G28" s="1" t="s">
+      <c r="D28" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F28" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G28" s="2" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B29" s="2" t="s">
+    <row r="29" spans="2:7">
+      <c r="B29" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="D29" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F29" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G29" s="1" t="s">
+      <c r="D29" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F29" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G29" s="2" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B30" s="2" t="s">
+    <row r="30" spans="2:7">
+      <c r="B30" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D30" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F30" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G30" s="1" t="s">
+      <c r="D30" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F30" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G30" s="2" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B31" s="2" t="s">
+    <row r="31" spans="2:7">
+      <c r="B31" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="D31" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F31" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G31" s="1" t="s">
+      <c r="D31" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F31" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G31" s="2" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B32" s="2" t="s">
+    <row r="32" spans="2:7">
+      <c r="B32" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="D32" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F32" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G32" s="1" t="s">
+      <c r="D32" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F32" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G32" s="2" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B33" s="1" t="s">
+    <row r="33" spans="2:7">
+      <c r="B33" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="D33" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F33" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G33" s="1" t="s">
+      <c r="D33" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F33" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G33" s="2" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B34" s="1" t="s">
+    <row r="34" spans="2:7">
+      <c r="B34" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D34" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E34" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F34" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G34" s="1" t="s">
+      <c r="D34" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F34" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G34" s="2" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B35" s="1" t="s">
+    <row r="35" spans="2:7">
+      <c r="B35" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="D35" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F35" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G35" s="1" t="s">
+      <c r="D35" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F35" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G35" s="2" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B36" s="1" t="s">
+    <row r="36" spans="2:7">
+      <c r="B36" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="D36" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F36" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G36" s="1" t="s">
+      <c r="D36" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F36" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G36" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B37" s="1" t="s">
+    <row r="37" spans="2:7">
+      <c r="B37" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="D37" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F37" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G37" s="1" t="s">
+      <c r="D37" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F37" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G37" s="2" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="38" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B38" s="1" t="s">
+    <row r="38" spans="2:7">
+      <c r="B38" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="D38" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E38" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F38" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G38" s="1" t="s">
+      <c r="D38" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F38" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G38" s="2" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B39" s="1" t="s">
+    <row r="39" spans="2:7">
+      <c r="B39" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="D39" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E39" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F39" s="4" t="b">
+      <c r="D39" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F39" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="G39" s="1" t="s">
+      <c r="G39" s="2" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B40" s="1" t="s">
+    <row r="40" spans="2:7">
+      <c r="B40" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="D40" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E40" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F40" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G40" s="1" t="s">
+      <c r="D40" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F40" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G40" s="2" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B41" s="1" t="s">
+    <row r="41" spans="2:7">
+      <c r="B41" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="D41" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E41" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F41" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G41" s="1" t="s">
+      <c r="D41" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F41" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G41" s="2" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="42" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B42" s="1" t="s">
+    <row r="42" spans="2:7">
+      <c r="B42" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C42" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F42" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G42" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="C42" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E42" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F42" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G42" s="9" t="s">
-        <v>138</v>
+    </row>
+    <row r="43" spans="2:7">
+      <c r="B43" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F43" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>142</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" fitToWidth="0"/>
+  <printOptions>
+    <extLst>
+      <ext uri="smNativeData">
+        <pm:pageFlags xmlns:pm="smNativeData" id="1783675043" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+      </ext>
+    </extLst>
+  </printOptions>
+  <pageMargins left="0.700000" right="0.700000" top="0.750000" bottom="0.750000" header="0.300000" footer="0.300000"/>
+  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="1"/>
+  <headerFooter>
+    <extLst>
+      <ext uri="smNativeData">
+        <pm:header xmlns:pm="smNativeData" id="1783675043" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1783675043" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1783675043" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1783675043" Id="1" type="0" value="0"/>
+      </ext>
+    </extLst>
+  </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1783587489" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1783675043" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>

--- a/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
@@ -1,16 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
-  <fileSharing readOnlyRecommended="0" userName="Lumino Game 03"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22D82C67-18DF-46DB-B9D5-EC3E0D775B83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0" xWindow="240" yWindow="60" windowWidth="30580" windowHeight="18680" tabRatio="500"/>
+    <workbookView xWindow="4810" yWindow="2200" windowWidth="30580" windowHeight="18680" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext uri="smNativeData">
       <pm:revision xmlns:pm="smNativeData" day="1783675043" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
@@ -23,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="146">
   <si>
     <t>##var</t>
   </si>
@@ -452,85 +457,60 @@
   </si>
   <si>
     <t>工厂处理介绍面板</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/OnLineGameUI/OnLineGameUI.prefab</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>OnLineGameUI</t>
+  </si>
+  <si>
+    <t>线上玩法界面</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
-    <numFmt numFmtId="5" formatCode="#,##0\ &quot;¥&quot;;\-#,##0\ &quot;¥&quot;"/>
-    <numFmt numFmtId="6" formatCode="#,##0\ &quot;¥&quot;;[Red]\-#,##0\ &quot;¥&quot;"/>
-    <numFmt numFmtId="7" formatCode="#,##0.00\ &quot;¥&quot;;\-#,##0.00\ &quot;¥&quot;"/>
-    <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;¥&quot;;[Red]\-#,##0.00\ &quot;¥&quot;"/>
-    <numFmt numFmtId="42" formatCode="_-* #,##0\ &quot;¥&quot;_-;\-* #,##0\ &quot;¥&quot;_-;_-* &quot;-&quot;\ &quot;¥&quot;_-;_-@_-"/>
-    <numFmt numFmtId="41" formatCode="_-* #,##0\ _¥_-;\-* #,##0\ _¥_-;_-* &quot;-&quot;\ _¥_-;_-@_-"/>
-    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;¥&quot;_-;\-* #,##0.00\ &quot;¥&quot;_-;_-* &quot;-&quot;??\ &quot;¥&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _¥_-;\-* #,##0.00\ _¥_-;_-* &quot;-&quot;??\ _¥_-;_-@_-"/>
-  </numFmts>
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="等线"/>
       <charset val="134"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1783675043" ulstyle="none" kern="1">
-            <pm:latin face="等线" sz="220" lang="default"/>
-            <pm:cs face="Times New Roman" sz="220" lang="default"/>
-            <pm:ea face="SimSun" sz="220" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
-      <name val="Arial"/>
-      <family val="2"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
-      <sz val="10"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1783675043" ulstyle="none" kern="1">
-            <pm:latin face="Arial" sz="200" lang="default"/>
-            <pm:cs face="Times New Roman" sz="200" lang="default"/>
-            <pm:ea face="SimSun" sz="200" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
+      <name val="等线"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF1F2329"/>
       <name val="等线"/>
-      <charset val="134"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1783675043" ulstyle="none" kern="1">
-            <pm:latin face="等线" sz="200" lang="default"/>
-            <pm:cs face="Times New Roman" sz="200" lang="default"/>
-            <pm:ea face="SimSun" sz="200" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="等线"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
-      <color rgb="FF1F2329"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1783675043" fgClr="1F2329" ulstyle="none" kern="1">
-            <pm:latin face="等线" sz="220" lang="default"/>
-            <pm:cs face="Times New Roman" sz="220" lang="default"/>
-            <pm:ea face="SimSun" sz="220" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -538,61 +518,25 @@
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
-      <patternFill patternType="none"/>
-    </fill>
-    <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFACB9CA"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783675043" type="1" fgLvl="100" fgClr="00ACB9CA" bgLvl="0" bgClr="00FFFFFF"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF5B9BD5"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783675043" type="1" fgLvl="100" fgClr="005B9BD5" bgLvl="0" bgClr="00FFFFFF"/>
-          </ext>
-        </extLst>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783675043" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="4">
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783675043"/>
-        </ext>
-      </extLst>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -607,120 +551,72 @@
       <bottom style="thin">
         <color rgb="FFDEE0E3"/>
       </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783675043">
-            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-          </pm:border>
-        </ext>
-      </extLst>
+      <diagonal/>
     </border>
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783675043"/>
-        </ext>
-      </extLst>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783675043"/>
-        </ext>
-      </extLst>
-    </border>
-    <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783675043"/>
-        </ext>
-      </extLst>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
-    <cellStyle name="常规 2" xfId="1"/>
+    <cellStyle name="常规" xfId="0" builtinId="0" customBuiltin="1"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0"/>
   <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
     <ext uri="smNativeData">
       <pm:charStyles xmlns:pm="smNativeData" id="1783675043" count="1">
         <pm:charStyle name="普通" fontId="0" Id="1"/>
@@ -991,909 +887,914 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:G43"/>
-  <sheetFormatPr defaultRowHeight="13.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G44"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.663793" customWidth="1" style="2"/>
-    <col min="2" max="2" width="28.577586" customWidth="1" style="2"/>
-    <col min="3" max="3" width="100.077586" customWidth="1" style="2"/>
-    <col min="4" max="4" width="25.163793" customWidth="1" style="2"/>
-    <col min="5" max="5" width="23.663793" customWidth="1" style="2"/>
-    <col min="6" max="6" width="17.663793" customWidth="1" style="2"/>
-    <col min="7" max="7" width="24.163793" customWidth="1" style="2"/>
-    <col min="8" max="16384" width="8.663793" customWidth="1" style="2"/>
+    <col min="1" max="1" width="8.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="28.58203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="100.08203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="25.1640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="23.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="24.1640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="8.6640625" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="4" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="2:7">
-      <c r="B4" s="3" t="s">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G4" s="5" t="s">
+      <c r="D4" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="2:7" ht="19.50" customHeight="1">
-      <c r="B5" s="3" t="s">
+    <row r="5" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="8" t="s">
+      <c r="D5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G5" s="5" t="s">
+      <c r="F5" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="2:7">
-      <c r="B6" s="3" t="s">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G6" s="5" t="s">
+      <c r="D6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="2:7">
-      <c r="B7" s="3" t="s">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B7" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G7" s="5" t="s">
+      <c r="D7" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="2:7">
-      <c r="B8" s="3" t="s">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G8" s="5" t="s">
+      <c r="D8" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="2:7">
-      <c r="B9" s="3" t="s">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B9" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="F9" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G9" s="5" t="s">
+      <c r="F9" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="2:7">
-      <c r="B10" s="3" t="s">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B10" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="F10" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G10" s="5" t="s">
+      <c r="F10" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="2:7">
-      <c r="B11" s="3" t="s">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B11" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D11" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F11" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G11" s="5" t="s">
+      <c r="D11" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="2:7">
-      <c r="B12" s="3" t="s">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B12" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F12" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G12" s="5" t="s">
+      <c r="D12" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="13" spans="2:7">
-      <c r="B13" s="3" t="s">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B13" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="F13" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G13" s="5" t="s">
+      <c r="F13" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G13" s="4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="14" spans="2:7">
-      <c r="B14" s="3" t="s">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B14" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E14" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F14" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G14" s="5" t="s">
+      <c r="E14" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G14" s="4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="15" spans="2:7">
-      <c r="B15" s="3" t="s">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B15" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D15" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E15" s="8" t="s">
+      <c r="D15" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="F15" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G15" s="5" t="s">
+      <c r="F15" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15" s="4" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="16" spans="2:7">
-      <c r="B16" s="3" t="s">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B16" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D16" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F16" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G16" s="5" t="s">
+      <c r="D16" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F16" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G16" s="4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="17" spans="2:7">
-      <c r="B17" s="3" t="s">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B17" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D17" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E17" s="8" t="s">
+      <c r="D17" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="F17" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G17" s="5" t="s">
+      <c r="F17" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G17" s="4" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="18" spans="2:7">
-      <c r="B18" s="3" t="s">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B18" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D18" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F18" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G18" s="5" t="s">
+      <c r="D18" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F18" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18" s="4" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="2:7">
-      <c r="B19" s="3" t="s">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B19" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D19" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F19" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G19" s="5" t="s">
+      <c r="D19" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F19" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="20" spans="2:7">
-      <c r="B20" s="3" t="s">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B20" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C20" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="D20" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F20" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G20" s="5" t="s">
+      <c r="D20" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F20" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" s="4" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="21" spans="2:7">
-      <c r="B21" s="3" t="s">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B21" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="D21" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F21" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G21" s="5" t="s">
+      <c r="D21" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F21" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="22" spans="2:7">
-      <c r="B22" s="3" t="s">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B22" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C22" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="D22" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F22" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G22" s="5" t="s">
+      <c r="D22" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F22" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="23" spans="2:7">
-      <c r="B23" s="3" t="s">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B23" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="D23" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F23" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G23" s="5" t="s">
+      <c r="D23" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F23" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" s="4" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="24" spans="2:7">
-      <c r="B24" s="3" t="s">
+    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B24" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D24" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F24" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G24" s="5" t="s">
+      <c r="D24" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F24" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" s="4" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="25" spans="2:7">
-      <c r="B25" s="3" t="s">
+    <row r="25" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B25" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="D25" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F25" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G25" s="5" t="s">
+      <c r="D25" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F25" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="26" spans="2:7">
-      <c r="B26" s="3" t="s">
+    <row r="26" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B26" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="C26" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="D26" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F26" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="5" t="s">
+      <c r="D26" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F26" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26" s="4" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="27" spans="2:7">
-      <c r="B27" s="3" t="s">
+    <row r="27" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B27" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="C27" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="D27" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F27" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G27" s="5" t="s">
+      <c r="D27" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F27" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G27" s="4" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="28" spans="2:7">
-      <c r="B28" s="3" t="s">
+    <row r="28" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B28" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D28" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F28" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G28" s="2" t="s">
+      <c r="D28" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F28" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G28" s="1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="29" spans="2:7">
-      <c r="B29" s="3" t="s">
+    <row r="29" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B29" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="D29" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F29" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G29" s="2" t="s">
+      <c r="D29" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F29" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G29" s="1" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="2:7">
-      <c r="B30" s="3" t="s">
+    <row r="30" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B30" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="D30" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F30" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G30" s="2" t="s">
+      <c r="D30" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F30" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G30" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="31" spans="2:7">
-      <c r="B31" s="3" t="s">
+    <row r="31" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B31" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="D31" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F31" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G31" s="2" t="s">
+      <c r="D31" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F31" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G31" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="32" spans="2:7">
-      <c r="B32" s="3" t="s">
+    <row r="32" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B32" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="D32" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F32" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G32" s="2" t="s">
+      <c r="D32" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F32" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G32" s="1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="33" spans="2:7">
-      <c r="B33" s="2" t="s">
+    <row r="33" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B33" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="D33" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F33" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G33" s="2" t="s">
+      <c r="D33" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F33" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G33" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="34" spans="2:7">
-      <c r="B34" s="2" t="s">
+    <row r="34" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B34" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D34" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F34" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G34" s="2" t="s">
+      <c r="D34" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F34" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G34" s="1" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="35" spans="2:7">
-      <c r="B35" s="2" t="s">
+    <row r="35" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B35" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="D35" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E35" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F35" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G35" s="2" t="s">
+      <c r="D35" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F35" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G35" s="1" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="36" spans="2:7">
-      <c r="B36" s="2" t="s">
+    <row r="36" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B36" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="D36" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F36" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G36" s="2" t="s">
+      <c r="D36" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F36" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G36" s="1" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="37" spans="2:7">
-      <c r="B37" s="2" t="s">
+    <row r="37" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B37" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D37" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E37" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F37" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G37" s="2" t="s">
+      <c r="D37" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F37" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G37" s="1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="38" spans="2:7">
-      <c r="B38" s="2" t="s">
+    <row r="38" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B38" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="D38" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E38" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F38" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G38" s="2" t="s">
+      <c r="D38" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F38" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G38" s="1" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="39" spans="2:7">
-      <c r="B39" s="2" t="s">
+    <row r="39" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B39" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="D39" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E39" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F39" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G39" s="2" t="s">
+      <c r="D39" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F39" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G39" s="1" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="40" spans="2:7">
-      <c r="B40" s="2" t="s">
+    <row r="40" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B40" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="D40" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E40" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F40" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G40" s="2" t="s">
+      <c r="D40" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F40" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G40" s="1" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="41" spans="2:7">
-      <c r="B41" s="2" t="s">
+    <row r="41" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B41" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C41" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="D41" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E41" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F41" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G41" s="2" t="s">
+      <c r="D41" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F41" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G41" s="1" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="42" spans="2:7">
-      <c r="B42" s="2" t="s">
+    <row r="42" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B42" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C42" s="10" t="s">
+      <c r="C42" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="D42" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E42" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F42" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G42" s="10" t="s">
+      <c r="D42" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F42" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G42" s="1" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="43" spans="2:7">
-      <c r="B43" s="2" t="s">
+    <row r="43" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B43" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C43" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D43" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E43" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F43" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G43" s="2" t="s">
+      <c r="D43" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F43" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G43" s="1" t="s">
         <v>142</v>
       </c>
     </row>
+    <row r="44" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B44" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F44" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G44" s="9" t="s">
+        <v>145</v>
+      </c>
+    </row>
   </sheetData>
-  <printOptions>
-    <extLst>
-      <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1783675043" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
-      </ext>
-    </extLst>
-  </printOptions>
-  <pageMargins left="0.700000" right="0.700000" top="0.750000" bottom="0.750000" header="0.300000" footer="0.300000"/>
-  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="1"/>
-  <headerFooter>
-    <extLst>
-      <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1783675043" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1783675043" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1783675043" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1783675043" Id="1" type="0" value="0"/>
-      </ext>
-    </extLst>
-  </headerFooter>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" fitToWidth="0"/>
   <extLst>
     <ext uri="smNativeData">
       <pm:sheetPrefs xmlns:pm="smNativeData" day="1783675043" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">

--- a/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22D82C67-18DF-46DB-B9D5-EC3E0D775B83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E87D4CB2-4958-46CF-9C82-0B3C8F05E7F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4810" yWindow="2200" windowWidth="30580" windowHeight="18680" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3890" yWindow="1530" windowWidth="30580" windowHeight="18680" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="152">
   <si>
     <t>##var</t>
   </si>
@@ -412,15 +412,6 @@
   </si>
   <si>
     <t>工厂处理面板</t>
-  </si>
-  <si>
-    <t>TestPanel</t>
-  </si>
-  <si>
-    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/TestPanel/TestPanel.prefab</t>
-  </si>
-  <si>
-    <t>测试面板</t>
   </si>
   <si>
     <t>PopUnlockDollWindowsUI</t>
@@ -467,6 +458,40 @@
   </si>
   <si>
     <t>线上玩法界面</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>PopSelectedPictureUI</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/PopSelectedPictureUI/PopSelectedPictureUI.prefab</t>
+  </si>
+  <si>
+    <t>选择画稿图片</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>isMouseRightHide</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>bool</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>应用鼠标右键关闭</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>CommonUI</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Resources/XFramework/Prefab/CommonUI.prefab</t>
+  </si>
+  <si>
+    <t>主界面UI</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -474,7 +499,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -505,6 +530,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F2329"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
@@ -574,7 +606,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -601,6 +633,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -888,7 +926,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.6640625" style="1" customWidth="1"/>
@@ -896,13 +934,13 @@
     <col min="3" max="3" width="100.08203125" style="1" customWidth="1"/>
     <col min="4" max="4" width="25.1640625" style="1" customWidth="1"/>
     <col min="5" max="5" width="23.6640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="17.6640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="24.1640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="8.6640625" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.6640625" style="1"/>
+    <col min="6" max="7" width="17.6640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="24.1640625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -921,11 +959,14 @@
       <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -944,11 +985,14 @@
       <c r="F2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -967,827 +1011,976 @@
       <c r="F3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B4" s="2" t="s">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B4" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C5" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G4" s="4" t="s">
+      <c r="D5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="2" t="s">
+    <row r="6" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="7" t="s">
+      <c r="D6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G5" s="4" t="s">
+      <c r="F6" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B6" s="2" t="s">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B7" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C7" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G6" s="4" t="s">
+      <c r="D7" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B7" s="2" t="s">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C8" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G7" s="4" t="s">
+      <c r="D8" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B8" s="2" t="s">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B9" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C9" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G8" s="4" t="s">
+      <c r="D9" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B9" s="2" t="s">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B10" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C10" s="4" t="s">
         <v>38</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B10" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>41</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B11" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="F10" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G10" s="4" t="s">
+      <c r="F11" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H11" s="4" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B11" s="2" t="s">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B12" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C12" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D11" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F11" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G11" s="4" t="s">
+      <c r="D12" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H12" s="4" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B12" s="2" t="s">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B13" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C13" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F12" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G12" s="4" t="s">
+      <c r="D13" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B13" s="2" t="s">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B14" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C14" s="4" t="s">
         <v>51</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="F13" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B14" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>54</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="F14" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B15" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F15" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H15" s="4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B15" s="2" t="s">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B16" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C16" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D15" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E15" s="7" t="s">
+      <c r="D16" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="F15" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G15" s="4" t="s">
+      <c r="F16" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H16" s="4" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B16" s="2" t="s">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B17" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C17" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D16" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F16" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G16" s="4" t="s">
+      <c r="D17" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F17" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G17" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B17" s="2" t="s">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B18" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C18" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D17" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E17" s="7" t="s">
+      <c r="D18" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E18" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="F17" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G17" s="4" t="s">
+      <c r="F18" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G18" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H18" s="4" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B18" s="2" t="s">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B19" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C19" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D18" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F18" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G18" s="4" t="s">
+      <c r="D19" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F19" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H19" s="4" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B19" s="2" t="s">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B20" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C20" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D19" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F19" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G19" s="4" t="s">
+      <c r="D20" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F20" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" s="4" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B20" s="2" t="s">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B21" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C21" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="D20" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F20" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G20" s="4" t="s">
+      <c r="D21" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F21" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" s="4" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B21" s="2" t="s">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B22" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C22" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="D21" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F21" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G21" s="4" t="s">
+      <c r="D22" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F22" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H22" s="4" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B22" s="2" t="s">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B23" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C23" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="D22" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F22" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G22" s="4" t="s">
+      <c r="D23" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F23" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H23" s="4" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B23" s="2" t="s">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B24" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C24" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="D23" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F23" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G23" s="4" t="s">
+      <c r="D24" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F24" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H24" s="4" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B24" s="2" t="s">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B25" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C25" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D24" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F24" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G24" s="4" t="s">
+      <c r="D25" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F25" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H25" s="4" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B25" s="2" t="s">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B26" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C26" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="D25" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F25" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G25" s="4" t="s">
+      <c r="D26" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F26" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H26" s="4" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B26" s="2" t="s">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B27" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C27" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="D26" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F26" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="4" t="s">
+      <c r="D27" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F27" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G27" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H27" s="4" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B27" s="2" t="s">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B28" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C28" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="D27" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F27" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G27" s="4" t="s">
+      <c r="D28" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F28" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G28" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H28" s="4" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B28" s="2" t="s">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B29" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C29" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D28" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F28" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G28" s="1" t="s">
+      <c r="D29" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F29" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G29" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H29" s="1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B29" s="2" t="s">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B30" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C30" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="D29" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F29" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G29" s="1" t="s">
+      <c r="D30" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F30" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G30" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H30" s="1" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B30" s="2" t="s">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B31" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C31" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="D30" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F30" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G30" s="1" t="s">
+      <c r="D31" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F31" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G31" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H31" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B31" s="2" t="s">
+    <row r="32" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B32" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C32" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="D31" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F31" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G31" s="1" t="s">
+      <c r="D32" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F32" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G32" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H32" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B32" s="2" t="s">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B33" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C33" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="D32" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F32" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G32" s="1" t="s">
+      <c r="D33" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F33" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G33" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H33" s="1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B33" s="1" t="s">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B34" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C34" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="D33" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F33" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G33" s="1" t="s">
+      <c r="D34" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F34" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G34" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H34" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B34" s="1" t="s">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B35" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C35" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D34" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E34" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F34" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G34" s="1" t="s">
+      <c r="D35" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F35" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G35" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H35" s="1" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B35" s="1" t="s">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B36" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C36" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="D35" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F35" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G35" s="1" t="s">
+      <c r="D36" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F36" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G36" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H36" s="1" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B36" s="1" t="s">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B37" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C37" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="D36" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F36" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G36" s="1" t="s">
+      <c r="D37" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F37" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G37" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H37" s="1" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B37" s="1" t="s">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B38" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C38" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D37" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F37" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G37" s="1" t="s">
+      <c r="D38" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F38" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G38" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H38" s="1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="38" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B38" s="1" t="s">
+    <row r="39" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B39" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C39" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="D38" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E38" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F38" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G38" s="1" t="s">
+      <c r="D39" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F39" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G39" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H39" s="1" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B39" s="1" t="s">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B40" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C40" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="D39" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E39" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F39" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G39" s="1" t="s">
+      <c r="D40" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F40" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G40" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H40" s="1" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B40" s="1" t="s">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B41" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C41" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="D40" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E40" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F40" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G40" s="1" t="s">
+      <c r="D41" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F41" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G41" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H41" s="1" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B41" s="1" t="s">
+    <row r="42" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B42" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C42" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="D41" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E41" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F41" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G41" s="1" t="s">
+      <c r="D42" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F42" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G42" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H42" s="1" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="42" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B42" s="1" t="s">
+    <row r="43" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B43" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C43" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="D42" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E42" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F42" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G42" s="1" t="s">
+      <c r="D43" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F43" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G43" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H43" s="1" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="43" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B43" s="1" t="s">
+    <row r="44" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B44" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C44" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="C43" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E43" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F43" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G43" s="1" t="s">
+      <c r="D44" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F44" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G44" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H44" s="9" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B44" s="1" t="s">
+    <row r="45" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B45" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="C45" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C44" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E44" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F44" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G44" s="9" t="s">
+      <c r="D45" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F45" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G45" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H45" s="9" t="s">
         <v>145</v>
       </c>
     </row>

--- a/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
@@ -13,17 +13,17 @@
   <calcPr/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:revision xmlns:pm="smNativeData" day="1783675043" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
-      <pm:docPrefs xmlns:pm="smNativeData" id="1783675043" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
-      <pm:compatibility xmlns:pm="smNativeData" id="1783675043" overlapCells="1"/>
-      <pm:defCurrency xmlns:pm="smNativeData" id="1783675043"/>
+      <pm:revision xmlns:pm="smNativeData" day="1783925544" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
+      <pm:docPrefs xmlns:pm="smNativeData" id="1783925544" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
+      <pm:compatibility xmlns:pm="smNativeData" id="1783925544" overlapCells="1"/>
+      <pm:defCurrency xmlns:pm="smNativeData" id="1783925544"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="146">
   <si>
     <t>##var</t>
   </si>
@@ -452,6 +452,15 @@
   </si>
   <si>
     <t>工厂处理介绍面板</t>
+  </si>
+  <si>
+    <t>ShopHelpPanel</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/ShopUI/ShopHelpPanel.prefab</t>
+  </si>
+  <si>
+    <t>商店帮忙面板</t>
   </si>
 </sst>
 </file>
@@ -476,7 +485,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1783675043" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1783925544" ulstyle="none" kern="1">
             <pm:latin face="等线" sz="220" lang="default"/>
             <pm:cs face="Times New Roman" sz="220" lang="default"/>
             <pm:ea face="SimSun" sz="220" lang="default"/>
@@ -491,7 +500,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1783675043" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1783925544" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="200" lang="default"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -506,7 +515,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1783675043" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1783925544" ulstyle="none" kern="1">
             <pm:latin face="等线" sz="200" lang="default"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -521,7 +530,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1783675043" fgClr="1F2329" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1783925544" fgClr="1F2329" ulstyle="none" kern="1">
             <pm:latin face="等线" sz="220" lang="default"/>
             <pm:cs face="Times New Roman" sz="220" lang="default"/>
             <pm:ea face="SimSun" sz="220" lang="default"/>
@@ -546,7 +555,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783675043" type="1" fgLvl="100" fgClr="00ACB9CA" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1783925544" type="1" fgLvl="100" fgClr="00ACB9CA" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -557,7 +566,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783675043" type="1" fgLvl="100" fgClr="005B9BD5" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1783925544" type="1" fgLvl="100" fgClr="005B9BD5" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -568,7 +577,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783675043" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1783925544" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -590,7 +599,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783675043"/>
+          <pm:border xmlns:pm="smNativeData" id="1783925544"/>
         </ext>
       </extLst>
     </border>
@@ -609,7 +618,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783675043">
+          <pm:border xmlns:pm="smNativeData" id="1783925544">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
@@ -633,7 +642,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783675043"/>
+          <pm:border xmlns:pm="smNativeData" id="1783925544"/>
         </ext>
       </extLst>
     </border>
@@ -652,7 +661,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783675043"/>
+          <pm:border xmlns:pm="smNativeData" id="1783925544"/>
         </ext>
       </extLst>
     </border>
@@ -671,7 +680,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783675043"/>
+          <pm:border xmlns:pm="smNativeData" id="1783925544"/>
         </ext>
       </extLst>
     </border>
@@ -682,7 +691,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
@@ -711,9 +720,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
@@ -722,10 +728,10 @@
   <tableStyles count="0"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:charStyles xmlns:pm="smNativeData" id="1783675043" count="1">
+      <pm:charStyles xmlns:pm="smNativeData" id="1783925544" count="1">
         <pm:charStyle name="普通" fontId="0" Id="1"/>
       </pm:charStyles>
-      <pm:colors xmlns:pm="smNativeData" id="1783675043" count="4">
+      <pm:colors xmlns:pm="smNativeData" id="1783925544" count="4">
         <pm:color name="颜色 24" rgb="1F2329"/>
         <pm:color name="颜色 25" rgb="ACB9CA"/>
         <pm:color name="颜色 26" rgb="5B9BD5"/>
@@ -992,7 +998,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr defaultRowHeight="13.45"/>
   <cols>
     <col min="1" max="1" width="8.663793" customWidth="1" style="2"/>
@@ -1838,7 +1844,7 @@
       <c r="B42" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C42" s="10" t="s">
+      <c r="C42" s="2" t="s">
         <v>138</v>
       </c>
       <c r="D42" s="6" t="s">
@@ -1850,7 +1856,7 @@
       <c r="F42" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="G42" s="10" t="s">
+      <c r="G42" s="2" t="s">
         <v>139</v>
       </c>
     </row>
@@ -1872,13 +1878,33 @@
       </c>
       <c r="G43" s="2" t="s">
         <v>142</v>
+      </c>
+    </row>
+    <row r="44" spans="2:7">
+      <c r="B44" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F44" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>145</v>
       </c>
     </row>
   </sheetData>
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1783675043" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1783925544" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -1887,16 +1913,16 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1783675043" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1783675043" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1783675043" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1783675043" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1783925544" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1783925544" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1783925544" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1783925544" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1783675043" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1783925544" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>

--- a/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
@@ -13,10 +13,10 @@
   <calcPr/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:revision xmlns:pm="smNativeData" day="1784001298" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
-      <pm:docPrefs xmlns:pm="smNativeData" id="1784001298" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
-      <pm:compatibility xmlns:pm="smNativeData" id="1784001298" overlapCells="1"/>
-      <pm:defCurrency xmlns:pm="smNativeData" id="1784001298"/>
+      <pm:revision xmlns:pm="smNativeData" day="1784021498" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
+      <pm:docPrefs xmlns:pm="smNativeData" id="1784021498" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
+      <pm:compatibility xmlns:pm="smNativeData" id="1784021498" overlapCells="1"/>
+      <pm:defCurrency xmlns:pm="smNativeData" id="1784021498"/>
     </ext>
   </extLst>
 </workbook>
@@ -490,10 +490,10 @@
     <t>商店帮忙面板</t>
   </si>
   <si>
-    <t xml:space="preserve">ShopHelpEnterPanel </t>
-  </si>
-  <si>
-    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/SupermarketUI/ShopHelpEnterPanel .prefab</t>
+    <t>ShopHelpEnterPanel</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/SupermarketUI/ShopHelpEnterPanel.prefab</t>
   </si>
   <si>
     <t>商店帮忙进入面板</t>
@@ -521,7 +521,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784001298" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784021498" ulstyle="none" kern="1">
             <pm:latin face="等线" sz="220" lang="default"/>
             <pm:cs face="Times New Roman" sz="220" lang="default"/>
             <pm:ea face="SimSun" sz="220" lang="default"/>
@@ -536,7 +536,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784001298" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784021498" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="200" lang="default"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -551,7 +551,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784001298" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784021498" ulstyle="none" kern="1">
             <pm:latin face="等线" sz="200" lang="default"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -566,7 +566,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784001298" fgClr="1F2329" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784021498" fgClr="1F2329" ulstyle="none" kern="1">
             <pm:latin face="等线" sz="220" lang="default"/>
             <pm:cs face="Times New Roman" sz="220" lang="default"/>
             <pm:ea face="SimSun" sz="220" lang="default"/>
@@ -591,7 +591,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784001298" type="1" fgLvl="100" fgClr="00ACB9CA" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1784021498" type="1" fgLvl="100" fgClr="00ACB9CA" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -602,7 +602,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784001298" type="1" fgLvl="100" fgClr="005B9BD5" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1784021498" type="1" fgLvl="100" fgClr="005B9BD5" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -613,7 +613,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784001298" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1784021498" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -635,7 +635,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784001298"/>
+          <pm:border xmlns:pm="smNativeData" id="1784021498"/>
         </ext>
       </extLst>
     </border>
@@ -654,7 +654,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784001298">
+          <pm:border xmlns:pm="smNativeData" id="1784021498">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
@@ -678,7 +678,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784001298"/>
+          <pm:border xmlns:pm="smNativeData" id="1784021498"/>
         </ext>
       </extLst>
     </border>
@@ -697,7 +697,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784001298"/>
+          <pm:border xmlns:pm="smNativeData" id="1784021498"/>
         </ext>
       </extLst>
     </border>
@@ -716,7 +716,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784001298"/>
+          <pm:border xmlns:pm="smNativeData" id="1784021498"/>
         </ext>
       </extLst>
     </border>
@@ -764,10 +764,10 @@
   <tableStyles count="0"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:charStyles xmlns:pm="smNativeData" id="1784001298" count="1">
+      <pm:charStyles xmlns:pm="smNativeData" id="1784021498" count="1">
         <pm:charStyle name="普通" fontId="0" Id="1"/>
       </pm:charStyles>
-      <pm:colors xmlns:pm="smNativeData" id="1784001298" count="4">
+      <pm:colors xmlns:pm="smNativeData" id="1784021498" count="4">
         <pm:color name="颜色 24" rgb="1F2329"/>
         <pm:color name="颜色 25" rgb="ACB9CA"/>
         <pm:color name="颜色 26" rgb="5B9BD5"/>
@@ -2141,7 +2141,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1784001298" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1784021498" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -2150,16 +2150,16 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1784001298" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1784001298" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1784001298" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1784001298" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1784021498" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1784021498" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1784021498" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1784021498" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1784001298" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1784021498" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>

--- a/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
@@ -13,17 +13,17 @@
   <calcPr/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:revision xmlns:pm="smNativeData" day="1784021498" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
-      <pm:docPrefs xmlns:pm="smNativeData" id="1784021498" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
-      <pm:compatibility xmlns:pm="smNativeData" id="1784021498" overlapCells="1"/>
-      <pm:defCurrency xmlns:pm="smNativeData" id="1784021498"/>
+      <pm:revision xmlns:pm="smNativeData" day="1784087174" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
+      <pm:docPrefs xmlns:pm="smNativeData" id="1784087174" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
+      <pm:compatibility xmlns:pm="smNativeData" id="1784087174" overlapCells="1"/>
+      <pm:defCurrency xmlns:pm="smNativeData" id="1784087174"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="161">
   <si>
     <t>##var</t>
   </si>
@@ -497,6 +497,15 @@
   </si>
   <si>
     <t>商店帮忙进入面板</t>
+  </si>
+  <si>
+    <t>CookSettlePanel</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/MiniGame1KitchenUI/CookSettlePanel.prefab</t>
+  </si>
+  <si>
+    <t>炒菜结算面板</t>
   </si>
 </sst>
 </file>
@@ -521,7 +530,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784021498" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784087174" ulstyle="none" kern="1">
             <pm:latin face="等线" sz="220" lang="default"/>
             <pm:cs face="Times New Roman" sz="220" lang="default"/>
             <pm:ea face="SimSun" sz="220" lang="default"/>
@@ -536,7 +545,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784021498" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784087174" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="200" lang="default"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -551,7 +560,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784021498" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784087174" ulstyle="none" kern="1">
             <pm:latin face="等线" sz="200" lang="default"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -566,7 +575,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784021498" fgClr="1F2329" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784087174" fgClr="1F2329" ulstyle="none" kern="1">
             <pm:latin face="等线" sz="220" lang="default"/>
             <pm:cs face="Times New Roman" sz="220" lang="default"/>
             <pm:ea face="SimSun" sz="220" lang="default"/>
@@ -591,7 +600,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784021498" type="1" fgLvl="100" fgClr="00ACB9CA" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1784087174" type="1" fgLvl="100" fgClr="00ACB9CA" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -602,7 +611,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784021498" type="1" fgLvl="100" fgClr="005B9BD5" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1784087174" type="1" fgLvl="100" fgClr="005B9BD5" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -613,7 +622,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784021498" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1784087174" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -635,7 +644,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784021498"/>
+          <pm:border xmlns:pm="smNativeData" id="1784087174"/>
         </ext>
       </extLst>
     </border>
@@ -654,7 +663,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784021498">
+          <pm:border xmlns:pm="smNativeData" id="1784087174">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
@@ -678,7 +687,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784021498"/>
+          <pm:border xmlns:pm="smNativeData" id="1784087174"/>
         </ext>
       </extLst>
     </border>
@@ -697,7 +706,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784021498"/>
+          <pm:border xmlns:pm="smNativeData" id="1784087174"/>
         </ext>
       </extLst>
     </border>
@@ -716,7 +725,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784021498"/>
+          <pm:border xmlns:pm="smNativeData" id="1784087174"/>
         </ext>
       </extLst>
     </border>
@@ -764,10 +773,10 @@
   <tableStyles count="0"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:charStyles xmlns:pm="smNativeData" id="1784021498" count="1">
+      <pm:charStyles xmlns:pm="smNativeData" id="1784087174" count="1">
         <pm:charStyle name="普通" fontId="0" Id="1"/>
       </pm:charStyles>
-      <pm:colors xmlns:pm="smNativeData" id="1784021498" count="4">
+      <pm:colors xmlns:pm="smNativeData" id="1784087174" count="4">
         <pm:color name="颜色 24" rgb="1F2329"/>
         <pm:color name="颜色 25" rgb="ACB9CA"/>
         <pm:color name="颜色 26" rgb="5B9BD5"/>
@@ -1034,7 +1043,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr defaultRowHeight="13.45"/>
   <cols>
     <col min="1" max="1" width="8.663793" customWidth="1" style="2"/>
@@ -2137,11 +2146,34 @@
         <v>157</v>
       </c>
     </row>
+    <row r="48" spans="2:8">
+      <c r="B48" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F48" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G48" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1784021498" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1784087174" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -2150,16 +2182,16 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1784021498" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1784021498" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1784021498" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1784021498" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1784087174" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1784087174" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1784087174" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1784087174" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1784021498" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1784087174" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>

--- a/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
@@ -1,16 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
-  <fileSharing readOnlyRecommended="0" userName="Lumino Game 03"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83661BC1-4C85-4E39-87F1-15C904C3BA5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0" xWindow="240" yWindow="60" windowWidth="30580" windowHeight="18680" tabRatio="500"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext uri="smNativeData">
       <pm:revision xmlns:pm="smNativeData" day="1784087174" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
@@ -23,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="165">
   <si>
     <t>##var</t>
   </si>
@@ -506,85 +511,61 @@
   </si>
   <si>
     <t>炒菜结算面板</t>
+  </si>
+  <si>
+    <t>PopRewardPropertyUI</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/PopRewardPropertyUI/PopRewardPropertyUI.prefab</t>
+  </si>
+  <si>
+    <t>属性获得界面</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>UIPop</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
-    <numFmt numFmtId="5" formatCode="#,##0\ &quot;¥&quot;;\-#,##0\ &quot;¥&quot;"/>
-    <numFmt numFmtId="6" formatCode="#,##0\ &quot;¥&quot;;[Red]\-#,##0\ &quot;¥&quot;"/>
-    <numFmt numFmtId="7" formatCode="#,##0.00\ &quot;¥&quot;;\-#,##0.00\ &quot;¥&quot;"/>
-    <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;¥&quot;;[Red]\-#,##0.00\ &quot;¥&quot;"/>
-    <numFmt numFmtId="42" formatCode="_-* #,##0\ &quot;¥&quot;_-;\-* #,##0\ &quot;¥&quot;_-;_-* &quot;-&quot;\ &quot;¥&quot;_-;_-@_-"/>
-    <numFmt numFmtId="41" formatCode="_-* #,##0\ _¥_-;\-* #,##0\ _¥_-;_-* &quot;-&quot;\ _¥_-;_-@_-"/>
-    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;¥&quot;_-;\-* #,##0.00\ &quot;¥&quot;_-;_-* &quot;-&quot;??\ &quot;¥&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _¥_-;\-* #,##0.00\ _¥_-;_-* &quot;-&quot;??\ _¥_-;_-@_-"/>
-  </numFmts>
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="等线"/>
       <charset val="134"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784087174" ulstyle="none" kern="1">
-            <pm:latin face="等线" sz="220" lang="default"/>
-            <pm:cs face="Times New Roman" sz="220" lang="default"/>
-            <pm:ea face="SimSun" sz="220" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
-      <name val="Arial"/>
-      <family val="2"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
-      <sz val="10"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784087174" ulstyle="none" kern="1">
-            <pm:latin face="Arial" sz="200" lang="default"/>
-            <pm:cs face="Times New Roman" sz="200" lang="default"/>
-            <pm:ea face="SimSun" sz="200" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
+      <name val="等线"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF1F2329"/>
       <name val="等线"/>
-      <charset val="134"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784087174" ulstyle="none" kern="1">
-            <pm:latin face="等线" sz="200" lang="default"/>
-            <pm:cs face="Times New Roman" sz="200" lang="default"/>
-            <pm:ea face="SimSun" sz="200" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="等线"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
-      <color rgb="FF1F2329"/>
-      <sz val="11"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784087174" fgClr="1F2329" ulstyle="none" kern="1">
-            <pm:latin face="等线" sz="220" lang="default"/>
-            <pm:cs face="Times New Roman" sz="220" lang="default"/>
-            <pm:ea face="SimSun" sz="220" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -592,61 +573,25 @@
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
-      <patternFill patternType="none"/>
-    </fill>
-    <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFACB9CA"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784087174" type="1" fgLvl="100" fgClr="00ACB9CA" bgLvl="0" bgClr="00FFFFFF"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF5B9BD5"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784087174" type="1" fgLvl="100" fgClr="005B9BD5" bgLvl="0" bgClr="00FFFFFF"/>
-          </ext>
-        </extLst>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784087174" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="4">
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784087174"/>
-        </ext>
-      </extLst>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -661,117 +606,75 @@
       <bottom style="thin">
         <color rgb="FFDEE0E3"/>
       </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784087174">
-            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-          </pm:border>
-        </ext>
-      </extLst>
+      <diagonal/>
     </border>
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784087174"/>
-        </ext>
-      </extLst>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784087174"/>
-        </ext>
-      </extLst>
-    </border>
-    <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784087174"/>
-        </ext>
-      </extLst>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
-    <cellStyle name="常规 2" xfId="1"/>
+    <cellStyle name="常规" xfId="0" builtinId="0" customBuiltin="1"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0"/>
   <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
     <ext uri="smNativeData">
       <pm:charStyles xmlns:pm="smNativeData" id="1784087174" count="1">
         <pm:charStyle name="普通" fontId="0" Id="1"/>
@@ -1042,1153 +945,1161 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:H48"/>
-  <sheetFormatPr defaultRowHeight="13.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H49"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.663793" customWidth="1" style="2"/>
-    <col min="2" max="2" width="28.577586" customWidth="1" style="2"/>
-    <col min="3" max="3" width="100.077586" customWidth="1" style="2"/>
-    <col min="4" max="4" width="25.163793" customWidth="1" style="2"/>
-    <col min="5" max="5" width="23.663793" customWidth="1" style="2"/>
-    <col min="6" max="7" width="17.663793" customWidth="1" style="2"/>
-    <col min="8" max="8" width="24.163793" customWidth="1" style="2"/>
-    <col min="9" max="16384" width="8.663793" customWidth="1" style="2"/>
+    <col min="1" max="1" width="8.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="28.58203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="100.08203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="25.1640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="23.6640625" style="1" customWidth="1"/>
+    <col min="6" max="7" width="17.6640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="24.1640625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="4" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="2:8">
-      <c r="B4" s="3" t="s">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G4" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H4" s="2" t="s">
+      <c r="D4" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="2:8">
-      <c r="B5" s="3" t="s">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G5" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H5" s="5" t="s">
+      <c r="D5" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="19.50" customHeight="1">
-      <c r="B6" s="3" t="s">
+    <row r="6" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="8" t="s">
+      <c r="D6" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G6" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H6" s="5" t="s">
+      <c r="F6" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="2:8">
-      <c r="B7" s="3" t="s">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B7" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G7" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H7" s="5" t="s">
+      <c r="D7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="2:8">
-      <c r="B8" s="3" t="s">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G8" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H8" s="5" t="s">
+      <c r="D8" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" s="4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="2:8">
-      <c r="B9" s="3" t="s">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B9" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G9" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H9" s="5" t="s">
+      <c r="D9" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="2:8">
-      <c r="B10" s="3" t="s">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B10" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F10" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G10" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H10" s="5" t="s">
+      <c r="F10" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H10" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="2:8">
-      <c r="B11" s="3" t="s">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B11" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="F11" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G11" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H11" s="5" t="s">
+      <c r="F11" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H11" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="12" spans="2:8">
-      <c r="B12" s="3" t="s">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B12" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F12" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G12" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H12" s="5" t="s">
+      <c r="D12" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H12" s="4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="13" spans="2:8">
-      <c r="B13" s="3" t="s">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B13" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F13" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G13" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H13" s="5" t="s">
+      <c r="D13" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" s="4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="14" spans="2:8">
-      <c r="B14" s="3" t="s">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B14" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E14" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="F14" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G14" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H14" s="5" t="s">
+      <c r="F14" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G14" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" s="4" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="15" spans="2:8">
-      <c r="B15" s="3" t="s">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B15" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E15" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F15" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G15" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H15" s="5" t="s">
+      <c r="E15" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H15" s="4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="16" spans="2:8">
-      <c r="B16" s="3" t="s">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B16" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D16" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E16" s="8" t="s">
+      <c r="D16" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F16" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G16" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H16" s="5" t="s">
+      <c r="F16" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H16" s="4" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="17" spans="2:8">
-      <c r="B17" s="3" t="s">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B17" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D17" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F17" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G17" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H17" s="5" t="s">
+      <c r="D17" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G17" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="2:8">
-      <c r="B18" s="3" t="s">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B18" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D18" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E18" s="8" t="s">
+      <c r="D18" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F18" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G18" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H18" s="5" t="s">
+      <c r="F18" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G18" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H18" s="4" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="2:8">
-      <c r="B19" s="3" t="s">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B19" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D19" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F19" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G19" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H19" s="5" t="s">
+      <c r="D19" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F19" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H19" s="4" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="20" spans="2:8">
-      <c r="B20" s="3" t="s">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B20" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="D20" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F20" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G20" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H20" s="5" t="s">
+      <c r="D20" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F20" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" s="4" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="21" spans="2:8">
-      <c r="B21" s="3" t="s">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B21" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="D21" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F21" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G21" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H21" s="5" t="s">
+      <c r="D21" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" s="4" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="22" spans="2:8">
-      <c r="B22" s="3" t="s">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B22" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C22" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="D22" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F22" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G22" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H22" s="5" t="s">
+      <c r="D22" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F22" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H22" s="4" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="23" spans="2:8">
-      <c r="B23" s="3" t="s">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B23" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D23" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F23" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G23" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H23" s="5" t="s">
+      <c r="D23" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H23" s="4" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="24" spans="2:8">
-      <c r="B24" s="3" t="s">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B24" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="D24" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F24" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G24" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H24" s="5" t="s">
+      <c r="D24" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F24" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H24" s="4" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="25" spans="2:8">
-      <c r="B25" s="3" t="s">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B25" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="D25" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F25" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G25" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H25" s="5" t="s">
+      <c r="D25" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F25" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H25" s="4" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="26" spans="2:8">
-      <c r="B26" s="3" t="s">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B26" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="C26" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="D26" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F26" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H26" s="5" t="s">
+      <c r="D26" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F26" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H26" s="4" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="27" spans="2:8">
-      <c r="B27" s="3" t="s">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B27" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="C27" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="D27" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F27" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G27" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H27" s="5" t="s">
+      <c r="D27" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F27" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G27" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H27" s="4" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="28" spans="2:8">
-      <c r="B28" s="3" t="s">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B28" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C28" s="9" t="s">
+      <c r="C28" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="D28" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F28" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G28" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H28" s="5" t="s">
+      <c r="D28" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F28" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G28" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H28" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="29" spans="2:8">
-      <c r="B29" s="3" t="s">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B29" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="D29" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F29" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G29" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H29" s="2" t="s">
+      <c r="D29" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F29" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G29" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H29" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="30" spans="2:8">
-      <c r="B30" s="3" t="s">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B30" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="D30" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F30" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G30" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H30" s="2" t="s">
+      <c r="D30" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F30" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G30" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H30" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="31" spans="2:8">
-      <c r="B31" s="3" t="s">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B31" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="D31" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F31" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G31" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H31" s="2" t="s">
+      <c r="D31" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F31" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G31" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H31" s="1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="32" spans="2:8">
-      <c r="B32" s="3" t="s">
+    <row r="32" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B32" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="D32" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F32" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G32" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H32" s="2" t="s">
+      <c r="D32" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F32" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G32" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H32" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="33" spans="2:8">
-      <c r="B33" s="3" t="s">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B33" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D33" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F33" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G33" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H33" s="2" t="s">
+      <c r="D33" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F33" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G33" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H33" s="1" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="34" spans="2:8">
-      <c r="B34" s="2" t="s">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B34" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="D34" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F34" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G34" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H34" s="2" t="s">
+      <c r="D34" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F34" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G34" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H34" s="1" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="35" spans="2:8">
-      <c r="B35" s="2" t="s">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B35" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="D35" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E35" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F35" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G35" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H35" s="2" t="s">
+      <c r="D35" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F35" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G35" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H35" s="1" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="36" spans="2:8">
-      <c r="B36" s="2" t="s">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B36" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D36" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F36" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G36" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H36" s="2" t="s">
+      <c r="D36" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F36" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G36" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H36" s="1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="37" spans="2:8">
-      <c r="B37" s="2" t="s">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B37" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="D37" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E37" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F37" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G37" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H37" s="2" t="s">
+      <c r="D37" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F37" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G37" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H37" s="1" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="38" spans="2:8">
-      <c r="B38" s="2" t="s">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B38" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="D38" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E38" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F38" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G38" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H38" s="2" t="s">
+      <c r="D38" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F38" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G38" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H38" s="1" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="39" spans="2:8">
-      <c r="B39" s="2" t="s">
+    <row r="39" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B39" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="D39" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E39" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F39" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G39" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H39" s="2" t="s">
+      <c r="D39" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F39" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G39" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H39" s="1" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="40" spans="2:8">
-      <c r="B40" s="2" t="s">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B40" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="D40" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E40" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F40" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G40" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H40" s="2" t="s">
+      <c r="D40" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F40" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G40" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H40" s="1" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="41" spans="2:8">
-      <c r="B41" s="2" t="s">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B41" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C41" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="D41" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E41" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F41" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G41" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H41" s="2" t="s">
+      <c r="D41" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F41" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G41" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H41" s="1" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="42" spans="2:8">
-      <c r="B42" s="2" t="s">
+    <row r="42" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B42" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C42" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D42" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E42" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F42" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G42" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H42" s="2" t="s">
+      <c r="D42" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F42" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G42" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H42" s="1" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="43" spans="2:8">
-      <c r="B43" s="2" t="s">
+    <row r="43" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B43" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C43" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="D43" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E43" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F43" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G43" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H43" s="2" t="s">
+      <c r="D43" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F43" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G43" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H43" s="1" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="44" spans="2:8">
-      <c r="B44" s="2" t="s">
+    <row r="44" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B44" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="C44" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="D44" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E44" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F44" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G44" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H44" s="2" t="s">
+      <c r="D44" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F44" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G44" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H44" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="45" spans="2:8">
-      <c r="B45" s="2" t="s">
+    <row r="45" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B45" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C45" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="D45" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E45" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F45" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G45" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H45" s="2" t="s">
+      <c r="D45" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F45" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G45" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H45" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="46" spans="2:8">
-      <c r="B46" s="2" t="s">
+    <row r="46" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B46" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C46" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="D46" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E46" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F46" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G46" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H46" s="2" t="s">
+      <c r="D46" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F46" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G46" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H46" s="1" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="47" spans="2:8">
-      <c r="B47" s="2" t="s">
+    <row r="47" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B47" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C47" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="D47" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E47" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F47" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G47" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H47" s="2" t="s">
+      <c r="D47" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F47" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G47" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H47" s="1" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="48" spans="2:8">
-      <c r="B48" s="2" t="s">
+    <row r="48" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B48" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C48" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="D48" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E48" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F48" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G48" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H48" s="2" t="s">
+      <c r="D48" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F48" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G48" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H48" s="1" t="s">
         <v>160</v>
       </c>
     </row>
+    <row r="49" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B49" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E49" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="F49" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G49" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H49" s="9" t="s">
+        <v>163</v>
+      </c>
+    </row>
   </sheetData>
-  <printOptions>
-    <extLst>
-      <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1784087174" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
-      </ext>
-    </extLst>
-  </printOptions>
-  <pageMargins left="0.700000" right="0.700000" top="0.750000" bottom="0.750000" header="0.300000" footer="0.300000"/>
-  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="1"/>
-  <headerFooter>
-    <extLst>
-      <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1784087174" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1784087174" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1784087174" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1784087174" Id="1" type="0" value="0"/>
-      </ext>
-    </extLst>
-  </headerFooter>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" fitToWidth="0"/>
   <extLst>
     <ext uri="smNativeData">
       <pm:sheetPrefs xmlns:pm="smNativeData" day="1784087174" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">

--- a/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83661BC1-4C85-4E39-87F1-15C904C3BA5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{442C25B5-9CD8-42F7-9646-0737B4891E68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5220" yWindow="2100" windowWidth="30590" windowHeight="18380" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1193,7 +1193,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>45</v>

--- a/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{442C25B5-9CD8-42F7-9646-0737B4891E68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E34B395D-D908-46E3-BE55-B6036F302441}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5220" yWindow="2100" windowWidth="30590" windowHeight="18380" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5470" yWindow="480" windowWidth="30590" windowHeight="18380" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="174">
   <si>
     <t>##var</t>
   </si>
@@ -524,6 +524,36 @@
   </si>
   <si>
     <t>UIPop</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>BoothGameStartUI</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/BoothGameStartUI/Prefabs/BoothGameStartUI.prefab</t>
+  </si>
+  <si>
+    <t>会展准备界面</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>PopClothingSelectedUI</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/PopClothingSelectedUI/PopClothingSelectedUI.prefab</t>
+  </si>
+  <si>
+    <t>服装选择界面</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>PopMerchandiseSelectedUI</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/PopMerchandiseSelectedUI/PopMerchandiseSelectedUI.prefab</t>
+  </si>
+  <si>
+    <t>周边选择UI</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -946,7 +976,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.6640625" style="1" customWidth="1"/>
@@ -2096,6 +2126,75 @@
         <v>163</v>
       </c>
     </row>
+    <row r="50" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B50" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F50" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G50" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H50" s="9" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="51" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B51" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E51" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="F51" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G51" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H51" s="9" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="52" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B52" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E52" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="F52" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G52" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H52" s="9" t="s">
+        <v>173</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
@@ -1,34 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
+  <fileSharing readOnlyRecommended="0" userName="Lumino Game 03"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E34B395D-D908-46E3-BE55-B6036F302441}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5470" yWindow="480" windowWidth="30590" windowHeight="18380" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView activeTab="0" xWindow="240" yWindow="60" windowWidth="30590" windowHeight="18380" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:revision xmlns:pm="smNativeData" day="1784087174" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
-      <pm:docPrefs xmlns:pm="smNativeData" id="1784087174" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
-      <pm:compatibility xmlns:pm="smNativeData" id="1784087174" overlapCells="1"/>
-      <pm:defCurrency xmlns:pm="smNativeData" id="1784087174"/>
+      <pm:revision xmlns:pm="smNativeData" day="1784283445" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
+      <pm:docPrefs xmlns:pm="smNativeData" id="1784283445" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
+      <pm:compatibility xmlns:pm="smNativeData" id="1784283445" overlapCells="1"/>
+      <pm:defCurrency xmlns:pm="smNativeData" id="1784283445"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="180">
   <si>
     <t>##var</t>
   </si>
@@ -519,12 +514,10 @@
     <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/PopRewardPropertyUI/PopRewardPropertyUI.prefab</t>
   </si>
   <si>
+    <t>UIPop</t>
+  </si>
+  <si>
     <t>属性获得界面</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>UIPop</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>BoothGameStartUI</t>
@@ -534,7 +527,6 @@
   </si>
   <si>
     <t>会展准备界面</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>PopClothingSelectedUI</t>
@@ -544,7 +536,6 @@
   </si>
   <si>
     <t>服装选择界面</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>PopMerchandiseSelectedUI</t>
@@ -554,48 +545,133 @@
   </si>
   <si>
     <t>周边选择UI</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>FishGameEnterPanel</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/Fish/FishGameEnterPanel.prefab</t>
+  </si>
+  <si>
+    <t>钓鱼游戏进入面板</t>
+  </si>
+  <si>
+    <t>FishGamePanel</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/Fish/FishGamePanel.prefab</t>
+  </si>
+  <si>
+    <t>钓鱼游戏面板</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="8">
+    <numFmt numFmtId="5" formatCode="#,##0\ &quot;¥&quot;;\-#,##0\ &quot;¥&quot;"/>
+    <numFmt numFmtId="6" formatCode="#,##0\ &quot;¥&quot;;[Red]\-#,##0\ &quot;¥&quot;"/>
+    <numFmt numFmtId="7" formatCode="#,##0.00\ &quot;¥&quot;;\-#,##0.00\ &quot;¥&quot;"/>
+    <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;¥&quot;;[Red]\-#,##0.00\ &quot;¥&quot;"/>
+    <numFmt numFmtId="42" formatCode="_-* #,##0\ &quot;¥&quot;_-;\-* #,##0\ &quot;¥&quot;_-;_-* &quot;-&quot;\ &quot;¥&quot;_-;_-@_-"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0\ _¥_-;\-* #,##0\ _¥_-;_-* &quot;-&quot;\ _¥_-;_-@_-"/>
+    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;¥&quot;_-;\-* #,##0.00\ &quot;¥&quot;_-;_-* &quot;-&quot;??\ &quot;¥&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _¥_-;\-* #,##0.00\ _¥_-;_-* &quot;-&quot;??\ _¥_-;_-@_-"/>
+  </numFmts>
+  <fonts count="6">
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="等线"/>
       <charset val="134"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784283445" ulstyle="none" kern="1">
+            <pm:latin face="等线" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784283445" ulstyle="none" kern="1">
+            <pm:latin face="Arial" sz="200" lang="default"/>
+            <pm:cs face="Times New Roman" sz="200" lang="default"/>
+            <pm:ea face="SimSun" sz="200" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF1F2329"/>
       <name val="等线"/>
+      <charset val="134"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784283445" ulstyle="none" kern="1">
+            <pm:latin face="等线" sz="200" lang="default"/>
+            <pm:cs face="Times New Roman" sz="200" lang="default"/>
+            <pm:ea face="SimSun" sz="200" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <color rgb="FF1F2329"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784283445" fgClr="1F2329" ulstyle="none" kern="1">
+            <pm:latin face="等线" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="等线"/>
+      <name val="IÈ¿ß"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784283445" ulstyle="none" kern="1">
+            <pm:latin face="IÈ¿ß" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <b/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784283445" ulstyle="none" kern="1">
+            <pm:latin face="等线" sz="220" lang="default" weight="bold"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -603,25 +679,61 @@
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFACB9CA"/>
         <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784283445" type="1" fgLvl="100" fgClr="00ACB9CA" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF5B9BD5"/>
         <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784283445" type="1" fgLvl="100" fgClr="005B9BD5" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784283445" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784283445"/>
+        </ext>
+      </extLst>
     </border>
     <border>
       <left style="thin">
@@ -636,80 +748,128 @@
       <bottom style="thin">
         <color rgb="FFDEE0E3"/>
       </bottom>
-      <diagonal/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784283445">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+          </pm:border>
+        </ext>
+      </extLst>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784283445"/>
+        </ext>
+      </extLst>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784283445"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784283445"/>
+        </ext>
+      </extLst>
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="常规" xfId="0" builtinId="0" customBuiltin="1"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
+    <cellStyle name="常规 2" xfId="1"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
     <ext uri="smNativeData">
-      <pm:charStyles xmlns:pm="smNativeData" id="1784087174" count="1">
+      <pm:charStyles xmlns:pm="smNativeData" id="1784283445" count="1">
         <pm:charStyle name="普通" fontId="0" Id="1"/>
       </pm:charStyles>
-      <pm:colors xmlns:pm="smNativeData" id="1784087174" count="4">
+      <pm:colors xmlns:pm="smNativeData" id="1784283445" count="4">
         <pm:color name="颜色 24" rgb="1F2329"/>
         <pm:color name="颜色 25" rgb="ACB9CA"/>
         <pm:color name="颜色 26" rgb="5B9BD5"/>
@@ -975,1233 +1135,1294 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H52"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <dimension ref="A1:H54"/>
+  <sheetFormatPr defaultRowHeight="13.45"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="28.58203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="100.08203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="25.1640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="23.6640625" style="1" customWidth="1"/>
-    <col min="6" max="7" width="17.6640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="24.1640625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="8.6640625" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.6640625" style="1"/>
+    <col min="1" max="1" width="8.663793" customWidth="1" style="2"/>
+    <col min="2" max="2" width="28.577586" customWidth="1" style="2"/>
+    <col min="3" max="3" width="100.077586" customWidth="1" style="2"/>
+    <col min="4" max="4" width="25.163793" customWidth="1" style="2"/>
+    <col min="5" max="5" width="23.663793" customWidth="1" style="2"/>
+    <col min="6" max="7" width="17.663793" customWidth="1" style="2"/>
+    <col min="8" max="8" width="24.163793" customWidth="1" style="2"/>
+    <col min="9" max="16384" width="8.663793" customWidth="1" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
+    <row r="1" spans="1:8">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:8">
+      <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:8">
+      <c r="A3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B4" s="2" t="s">
+    <row r="4" spans="2:8">
+      <c r="B4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G4" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H4" s="1" t="s">
+      <c r="D4" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B5" s="2" t="s">
+    <row r="5" spans="2:8">
+      <c r="B5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G5" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H5" s="4" t="s">
+      <c r="D5" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="2" t="s">
+    <row r="6" spans="2:8" ht="19.50" customHeight="1">
+      <c r="B6" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="7" t="s">
+      <c r="D6" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G6" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H6" s="4" t="s">
+      <c r="F6" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B7" s="2" t="s">
+    <row r="7" spans="2:8">
+      <c r="B7" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G7" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H7" s="4" t="s">
+      <c r="D7" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B8" s="2" t="s">
+    <row r="8" spans="2:8">
+      <c r="B8" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G8" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H8" s="4" t="s">
+      <c r="D8" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" s="5" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B9" s="2" t="s">
+    <row r="9" spans="2:8">
+      <c r="B9" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G9" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H9" s="4" t="s">
+      <c r="D9" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" s="5" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B10" s="2" t="s">
+    <row r="10" spans="2:8">
+      <c r="B10" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="F10" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G10" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H10" s="4" t="s">
+      <c r="F10" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B11" s="2" t="s">
+    <row r="11" spans="2:8">
+      <c r="B11" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="F11" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G11" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H11" s="4" t="s">
+      <c r="F11" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H11" s="5" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B12" s="2" t="s">
+    <row r="12" spans="2:8">
+      <c r="B12" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F12" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G12" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H12" s="4" t="s">
+      <c r="D12" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H12" s="5" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B13" s="2" t="s">
+    <row r="13" spans="2:8">
+      <c r="B13" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D13" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F13" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G13" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H13" s="4" t="s">
+      <c r="D13" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" s="5" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B14" s="2" t="s">
+    <row r="14" spans="2:8">
+      <c r="B14" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="F14" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G14" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H14" s="4" t="s">
+      <c r="F14" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G14" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" s="5" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B15" s="2" t="s">
+    <row r="15" spans="2:8">
+      <c r="B15" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E15" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F15" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G15" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H15" s="4" t="s">
+      <c r="E15" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H15" s="5" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B16" s="2" t="s">
+    <row r="16" spans="2:8">
+      <c r="B16" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="D16" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E16" s="7" t="s">
+      <c r="D16" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F16" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G16" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H16" s="4" t="s">
+      <c r="F16" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H16" s="5" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B17" s="2" t="s">
+    <row r="17" spans="2:8">
+      <c r="B17" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="D17" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F17" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G17" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H17" s="4" t="s">
+      <c r="D17" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G17" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B18" s="2" t="s">
+    <row r="18" spans="2:8">
+      <c r="B18" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="D18" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E18" s="7" t="s">
+      <c r="D18" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F18" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G18" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H18" s="4" t="s">
+      <c r="F18" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G18" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H18" s="5" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B19" s="2" t="s">
+    <row r="19" spans="2:8">
+      <c r="B19" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="D19" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F19" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G19" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H19" s="4" t="s">
+      <c r="D19" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F19" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H19" s="5" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B20" s="2" t="s">
+    <row r="20" spans="2:8">
+      <c r="B20" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="D20" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F20" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G20" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H20" s="4" t="s">
+      <c r="D20" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F20" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" s="5" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B21" s="2" t="s">
+    <row r="21" spans="2:8">
+      <c r="B21" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="D21" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F21" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G21" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H21" s="4" t="s">
+      <c r="D21" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" s="5" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B22" s="2" t="s">
+    <row r="22" spans="2:8">
+      <c r="B22" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="D22" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F22" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G22" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H22" s="4" t="s">
+      <c r="D22" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F22" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H22" s="5" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B23" s="2" t="s">
+    <row r="23" spans="2:8">
+      <c r="B23" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="D23" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F23" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G23" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H23" s="4" t="s">
+      <c r="D23" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H23" s="5" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B24" s="2" t="s">
+    <row r="24" spans="2:8">
+      <c r="B24" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="D24" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F24" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G24" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H24" s="4" t="s">
+      <c r="D24" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F24" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H24" s="5" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B25" s="2" t="s">
+    <row r="25" spans="2:8">
+      <c r="B25" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="D25" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F25" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G25" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H25" s="4" t="s">
+      <c r="D25" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F25" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H25" s="5" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B26" s="2" t="s">
+    <row r="26" spans="2:8">
+      <c r="B26" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C26" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="D26" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F26" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H26" s="4" t="s">
+      <c r="D26" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F26" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H26" s="5" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B27" s="2" t="s">
+    <row r="27" spans="2:8">
+      <c r="B27" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="D27" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F27" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G27" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H27" s="4" t="s">
+      <c r="D27" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F27" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G27" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H27" s="5" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B28" s="2" t="s">
+    <row r="28" spans="2:8">
+      <c r="B28" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="C28" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="D28" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F28" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G28" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H28" s="4" t="s">
+      <c r="D28" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F28" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G28" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H28" s="5" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B29" s="2" t="s">
+    <row r="29" spans="2:8">
+      <c r="B29" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D29" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F29" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G29" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H29" s="1" t="s">
+      <c r="D29" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F29" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G29" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H29" s="2" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B30" s="2" t="s">
+    <row r="30" spans="2:8">
+      <c r="B30" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="D30" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F30" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G30" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H30" s="1" t="s">
+      <c r="D30" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F30" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G30" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H30" s="2" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B31" s="2" t="s">
+    <row r="31" spans="2:8">
+      <c r="B31" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="D31" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F31" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G31" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H31" s="1" t="s">
+      <c r="D31" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F31" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G31" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H31" s="2" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B32" s="2" t="s">
+    <row r="32" spans="2:8">
+      <c r="B32" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="D32" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F32" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G32" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H32" s="1" t="s">
+      <c r="D32" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F32" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G32" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H32" s="2" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B33" s="2" t="s">
+    <row r="33" spans="2:8">
+      <c r="B33" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D33" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F33" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G33" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H33" s="1" t="s">
+      <c r="D33" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F33" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G33" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H33" s="2" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B34" s="1" t="s">
+    <row r="34" spans="2:8">
+      <c r="B34" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="D34" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E34" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F34" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G34" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H34" s="1" t="s">
+      <c r="D34" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F34" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G34" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H34" s="2" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B35" s="1" t="s">
+    <row r="35" spans="2:8">
+      <c r="B35" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="D35" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F35" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G35" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H35" s="1" t="s">
+      <c r="D35" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F35" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G35" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H35" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B36" s="1" t="s">
+    <row r="36" spans="2:8">
+      <c r="B36" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="D36" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F36" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G36" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H36" s="1" t="s">
+      <c r="D36" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F36" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G36" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H36" s="2" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B37" s="1" t="s">
+    <row r="37" spans="2:8">
+      <c r="B37" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="D37" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F37" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G37" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H37" s="1" t="s">
+      <c r="D37" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F37" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G37" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H37" s="2" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B38" s="1" t="s">
+    <row r="38" spans="2:8">
+      <c r="B38" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="D38" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E38" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F38" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G38" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H38" s="1" t="s">
+      <c r="D38" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F38" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G38" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H38" s="2" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B39" s="1" t="s">
+    <row r="39" spans="2:8">
+      <c r="B39" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="D39" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E39" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F39" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G39" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H39" s="1" t="s">
+      <c r="D39" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F39" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G39" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H39" s="2" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B40" s="1" t="s">
+    <row r="40" spans="2:8">
+      <c r="B40" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="D40" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E40" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F40" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G40" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H40" s="1" t="s">
+      <c r="D40" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F40" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G40" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H40" s="2" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B41" s="1" t="s">
+    <row r="41" spans="2:8">
+      <c r="B41" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="D41" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E41" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F41" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G41" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H41" s="1" t="s">
+      <c r="D41" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F41" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G41" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H41" s="2" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B42" s="1" t="s">
+    <row r="42" spans="2:8">
+      <c r="B42" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C42" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="D42" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E42" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F42" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G42" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H42" s="1" t="s">
+      <c r="D42" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F42" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G42" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H42" s="2" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B43" s="1" t="s">
+    <row r="43" spans="2:8">
+      <c r="B43" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C43" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="D43" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E43" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F43" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G43" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H43" s="1" t="s">
+      <c r="D43" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F43" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G43" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H43" s="2" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B44" s="1" t="s">
+    <row r="44" spans="2:8">
+      <c r="B44" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C44" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="D44" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E44" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F44" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G44" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H44" s="1" t="s">
+      <c r="D44" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F44" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G44" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H44" s="2" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B45" s="1" t="s">
+    <row r="45" spans="2:8">
+      <c r="B45" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C45" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="D45" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E45" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F45" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G45" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H45" s="1" t="s">
+      <c r="D45" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F45" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G45" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H45" s="2" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B46" s="1" t="s">
+    <row r="46" spans="2:8">
+      <c r="B46" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C46" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="D46" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E46" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F46" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G46" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H46" s="1" t="s">
+      <c r="D46" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F46" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G46" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H46" s="2" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B47" s="1" t="s">
+    <row r="47" spans="2:8">
+      <c r="B47" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C47" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="D47" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E47" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F47" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G47" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H47" s="1" t="s">
+      <c r="D47" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F47" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G47" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H47" s="2" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B48" s="1" t="s">
+    <row r="48" spans="2:8">
+      <c r="B48" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="C48" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="D48" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E48" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F48" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G48" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H48" s="1" t="s">
+      <c r="D48" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F48" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G48" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H48" s="2" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="49" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B49" s="1" t="s">
+    <row r="49" spans="2:8">
+      <c r="B49" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C49" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="D49" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E49" s="10" t="s">
+      <c r="D49" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E49" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="F49" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G49" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H49" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="F49" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G49" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H49" s="9" t="s">
+    </row>
+    <row r="50" spans="2:8">
+      <c r="B50" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F50" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G50" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H50" s="10" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="51" spans="2:8">
+      <c r="B51" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E51" s="11" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="50" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B50" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E50" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F50" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G50" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H50" s="9" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="51" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B51" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D51" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E51" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="F51" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G51" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H51" s="9" t="s">
+      <c r="F51" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G51" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H51" s="10" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="52" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B52" s="1" t="s">
+    <row r="52" spans="2:8">
+      <c r="B52" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="C52" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="D52" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E52" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="F52" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G52" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H52" s="9" t="s">
+      <c r="D52" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E52" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="F52" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G52" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H52" s="10" t="s">
         <v>173</v>
       </c>
     </row>
+    <row r="53" spans="2:8">
+      <c r="B53" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D53" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E53" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="F53" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G53" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H53" s="10" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="54" spans="2:8">
+      <c r="B54" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E54" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="F54" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G54" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H54" s="10" t="s">
+        <v>179</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" fitToWidth="0"/>
+  <printOptions>
+    <extLst>
+      <ext uri="smNativeData">
+        <pm:pageFlags xmlns:pm="smNativeData" id="1784283445" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+      </ext>
+    </extLst>
+  </printOptions>
+  <pageMargins left="0.700000" right="0.700000" top="0.750000" bottom="0.750000" header="0.300000" footer="0.300000"/>
+  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="1"/>
+  <headerFooter>
+    <extLst>
+      <ext uri="smNativeData">
+        <pm:header xmlns:pm="smNativeData" id="1784283445" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1784283445" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1784283445" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1784283445" Id="1" type="0" value="0"/>
+      </ext>
+    </extLst>
+  </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1784087174" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1784283445" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>

--- a/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
@@ -1,16 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
-  <fileSharing readOnlyRecommended="0" userName="Lumino Game 03"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C7EF698-BDBC-46E0-BC5A-7D74A67050C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0" xWindow="240" yWindow="60" windowWidth="30590" windowHeight="18380" tabRatio="500"/>
+    <workbookView xWindow="5470" yWindow="480" windowWidth="30590" windowHeight="18380" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext uri="smNativeData">
       <pm:revision xmlns:pm="smNativeData" day="1784283445" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
@@ -23,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="183">
   <si>
     <t>##var</t>
   </si>
@@ -563,115 +568,54 @@
   </si>
   <si>
     <t>钓鱼游戏面板</t>
+  </si>
+  <si>
+    <t>ExhibitionGameUI</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/ExhibitionGameUI/ExhibitionGameUI.prefab</t>
+  </si>
+  <si>
+    <t>会展Game主UI</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
-    <numFmt numFmtId="5" formatCode="#,##0\ &quot;¥&quot;;\-#,##0\ &quot;¥&quot;"/>
-    <numFmt numFmtId="6" formatCode="#,##0\ &quot;¥&quot;;[Red]\-#,##0\ &quot;¥&quot;"/>
-    <numFmt numFmtId="7" formatCode="#,##0.00\ &quot;¥&quot;;\-#,##0.00\ &quot;¥&quot;"/>
-    <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;¥&quot;;[Red]\-#,##0.00\ &quot;¥&quot;"/>
-    <numFmt numFmtId="42" formatCode="_-* #,##0\ &quot;¥&quot;_-;\-* #,##0\ &quot;¥&quot;_-;_-* &quot;-&quot;\ &quot;¥&quot;_-;_-@_-"/>
-    <numFmt numFmtId="41" formatCode="_-* #,##0\ _¥_-;\-* #,##0\ _¥_-;_-* &quot;-&quot;\ _¥_-;_-@_-"/>
-    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;¥&quot;_-;\-* #,##0.00\ &quot;¥&quot;_-;_-* &quot;-&quot;??\ &quot;¥&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _¥_-;\-* #,##0.00\ _¥_-;_-* &quot;-&quot;??\ _¥_-;_-@_-"/>
-  </numFmts>
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="等线"/>
       <charset val="134"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784283445" ulstyle="none" kern="1">
-            <pm:latin face="等线" sz="220" lang="default"/>
-            <pm:cs face="Times New Roman" sz="220" lang="default"/>
-            <pm:ea face="SimSun" sz="220" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
-      <name val="Arial"/>
-      <family val="2"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
-      <sz val="10"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784283445" ulstyle="none" kern="1">
-            <pm:latin face="Arial" sz="200" lang="default"/>
-            <pm:cs face="Times New Roman" sz="200" lang="default"/>
-            <pm:ea face="SimSun" sz="200" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
+      <name val="等线"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF1F2329"/>
       <name val="等线"/>
-      <charset val="134"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784283445" ulstyle="none" kern="1">
-            <pm:latin face="等线" sz="200" lang="default"/>
-            <pm:cs face="Times New Roman" sz="200" lang="default"/>
-            <pm:ea face="SimSun" sz="200" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
-      <color rgb="FF1F2329"/>
-      <sz val="11"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784283445" fgClr="1F2329" ulstyle="none" kern="1">
-            <pm:latin face="等线" sz="220" lang="default"/>
-            <pm:cs face="Times New Roman" sz="220" lang="default"/>
-            <pm:ea face="SimSun" sz="220" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
-      <name val="IÈ¿ß"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784283445" ulstyle="none" kern="1">
-            <pm:latin face="IÈ¿ß" sz="220" lang="default"/>
-            <pm:cs face="Times New Roman" sz="220" lang="default"/>
-            <pm:ea face="SimSun" sz="220" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
-    </font>
-    <font>
+      <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
-      <b/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784283445" ulstyle="none" kern="1">
-            <pm:latin face="等线" sz="220" lang="default" weight="bold"/>
-            <pm:cs face="Times New Roman" sz="220" lang="default"/>
-            <pm:ea face="SimSun" sz="220" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -679,61 +623,25 @@
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
-      <patternFill patternType="none"/>
-    </fill>
-    <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFACB9CA"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784283445" type="1" fgLvl="100" fgClr="00ACB9CA" bgLvl="0" bgClr="00FFFFFF"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF5B9BD5"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784283445" type="1" fgLvl="100" fgClr="005B9BD5" bgLvl="0" bgClr="00FFFFFF"/>
-          </ext>
-        </extLst>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784283445" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="4">
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784283445"/>
-        </ext>
-      </extLst>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -748,123 +656,72 @@
       <bottom style="thin">
         <color rgb="FFDEE0E3"/>
       </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784283445">
-            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-          </pm:border>
-        </ext>
-      </extLst>
+      <diagonal/>
     </border>
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784283445"/>
-        </ext>
-      </extLst>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784283445"/>
-        </ext>
-      </extLst>
-    </border>
-    <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784283445"/>
-        </ext>
-      </extLst>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
-    <cellStyle name="常规 2" xfId="1"/>
+    <cellStyle name="常规" xfId="0" builtinId="0" customBuiltin="1"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0"/>
   <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
     <ext uri="smNativeData">
       <pm:charStyles xmlns:pm="smNativeData" id="1784283445" count="1">
         <pm:charStyle name="普通" fontId="0" Id="1"/>
@@ -1135,1291 +992,1299 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:H54"/>
-  <sheetFormatPr defaultRowHeight="13.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H55"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.663793" customWidth="1" style="2"/>
-    <col min="2" max="2" width="28.577586" customWidth="1" style="2"/>
-    <col min="3" max="3" width="100.077586" customWidth="1" style="2"/>
-    <col min="4" max="4" width="25.163793" customWidth="1" style="2"/>
-    <col min="5" max="5" width="23.663793" customWidth="1" style="2"/>
-    <col min="6" max="7" width="17.663793" customWidth="1" style="2"/>
-    <col min="8" max="8" width="24.163793" customWidth="1" style="2"/>
-    <col min="9" max="16384" width="8.663793" customWidth="1" style="2"/>
+    <col min="1" max="1" width="8.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="28.58203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="100.08203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="25.1640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="23.6640625" style="1" customWidth="1"/>
+    <col min="6" max="7" width="17.6640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="24.1640625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="4" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="2:8">
-      <c r="B4" s="3" t="s">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G4" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H4" s="2" t="s">
+      <c r="D4" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="2:8">
-      <c r="B5" s="3" t="s">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G5" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H5" s="5" t="s">
+      <c r="D5" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="19.50" customHeight="1">
-      <c r="B6" s="3" t="s">
+    <row r="6" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="8" t="s">
+      <c r="D6" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G6" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H6" s="5" t="s">
+      <c r="F6" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="2:8">
-      <c r="B7" s="3" t="s">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B7" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G7" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H7" s="5" t="s">
+      <c r="D7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="2:8">
-      <c r="B8" s="3" t="s">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G8" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H8" s="5" t="s">
+      <c r="D8" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" s="4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="2:8">
-      <c r="B9" s="3" t="s">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B9" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G9" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H9" s="5" t="s">
+      <c r="D9" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="2:8">
-      <c r="B10" s="3" t="s">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B10" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F10" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G10" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H10" s="5" t="s">
+      <c r="F10" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="2:8">
-      <c r="B11" s="3" t="s">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B11" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="F11" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G11" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H11" s="5" t="s">
+      <c r="F11" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H11" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="12" spans="2:8">
-      <c r="B12" s="3" t="s">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B12" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F12" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G12" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H12" s="5" t="s">
+      <c r="D12" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H12" s="4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="13" spans="2:8">
-      <c r="B13" s="3" t="s">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B13" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F13" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G13" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H13" s="5" t="s">
+      <c r="D13" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" s="4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="14" spans="2:8">
-      <c r="B14" s="3" t="s">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B14" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E14" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="F14" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G14" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H14" s="5" t="s">
+      <c r="F14" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G14" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" s="4" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="15" spans="2:8">
-      <c r="B15" s="3" t="s">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B15" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E15" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F15" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G15" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H15" s="5" t="s">
+      <c r="E15" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H15" s="4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="16" spans="2:8">
-      <c r="B16" s="3" t="s">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B16" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D16" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E16" s="8" t="s">
+      <c r="D16" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F16" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G16" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H16" s="5" t="s">
+      <c r="F16" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H16" s="4" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="17" spans="2:8">
-      <c r="B17" s="3" t="s">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B17" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D17" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F17" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G17" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H17" s="5" t="s">
+      <c r="D17" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G17" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="2:8">
-      <c r="B18" s="3" t="s">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B18" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D18" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E18" s="8" t="s">
+      <c r="D18" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F18" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G18" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H18" s="5" t="s">
+      <c r="F18" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G18" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H18" s="4" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="2:8">
-      <c r="B19" s="3" t="s">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B19" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D19" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F19" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G19" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H19" s="5" t="s">
+      <c r="D19" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F19" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H19" s="4" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="20" spans="2:8">
-      <c r="B20" s="3" t="s">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B20" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="D20" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F20" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G20" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H20" s="5" t="s">
+      <c r="D20" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F20" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" s="4" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="21" spans="2:8">
-      <c r="B21" s="3" t="s">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B21" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="D21" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F21" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G21" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H21" s="5" t="s">
+      <c r="D21" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" s="4" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="22" spans="2:8">
-      <c r="B22" s="3" t="s">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B22" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C22" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="D22" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F22" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G22" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H22" s="5" t="s">
+      <c r="D22" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F22" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H22" s="4" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="23" spans="2:8">
-      <c r="B23" s="3" t="s">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B23" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D23" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F23" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G23" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H23" s="5" t="s">
+      <c r="D23" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H23" s="4" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="24" spans="2:8">
-      <c r="B24" s="3" t="s">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B24" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="D24" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F24" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G24" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H24" s="5" t="s">
+      <c r="D24" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F24" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H24" s="4" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="25" spans="2:8">
-      <c r="B25" s="3" t="s">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B25" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="D25" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F25" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G25" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H25" s="5" t="s">
+      <c r="D25" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F25" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H25" s="4" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="26" spans="2:8">
-      <c r="B26" s="3" t="s">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B26" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="C26" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="D26" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F26" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H26" s="5" t="s">
+      <c r="D26" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F26" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H26" s="4" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="27" spans="2:8">
-      <c r="B27" s="3" t="s">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B27" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="C27" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="D27" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F27" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G27" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H27" s="5" t="s">
+      <c r="D27" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F27" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G27" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H27" s="4" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="28" spans="2:8">
-      <c r="B28" s="3" t="s">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B28" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C28" s="9" t="s">
+      <c r="C28" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="D28" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F28" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G28" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H28" s="5" t="s">
+      <c r="D28" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F28" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G28" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H28" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="29" spans="2:8">
-      <c r="B29" s="3" t="s">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B29" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="D29" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F29" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G29" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H29" s="2" t="s">
+      <c r="D29" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F29" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G29" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H29" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="30" spans="2:8">
-      <c r="B30" s="3" t="s">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B30" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="D30" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F30" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G30" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H30" s="2" t="s">
+      <c r="D30" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F30" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G30" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H30" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="31" spans="2:8">
-      <c r="B31" s="3" t="s">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B31" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="D31" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F31" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G31" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H31" s="2" t="s">
+      <c r="D31" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F31" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G31" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H31" s="1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="32" spans="2:8">
-      <c r="B32" s="3" t="s">
+    <row r="32" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B32" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="D32" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F32" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G32" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H32" s="2" t="s">
+      <c r="D32" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F32" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G32" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H32" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="33" spans="2:8">
-      <c r="B33" s="3" t="s">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B33" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D33" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F33" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G33" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H33" s="2" t="s">
+      <c r="D33" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F33" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G33" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H33" s="1" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="34" spans="2:8">
-      <c r="B34" s="2" t="s">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B34" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="D34" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F34" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G34" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H34" s="2" t="s">
+      <c r="D34" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F34" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G34" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H34" s="1" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="35" spans="2:8">
-      <c r="B35" s="2" t="s">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B35" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="D35" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E35" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F35" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G35" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H35" s="2" t="s">
+      <c r="D35" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F35" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G35" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H35" s="1" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="36" spans="2:8">
-      <c r="B36" s="2" t="s">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B36" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D36" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F36" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G36" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H36" s="2" t="s">
+      <c r="D36" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F36" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G36" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H36" s="1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="37" spans="2:8">
-      <c r="B37" s="2" t="s">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B37" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="D37" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E37" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F37" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G37" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H37" s="2" t="s">
+      <c r="D37" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F37" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G37" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H37" s="1" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="38" spans="2:8">
-      <c r="B38" s="2" t="s">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B38" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="D38" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E38" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F38" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G38" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H38" s="2" t="s">
+      <c r="D38" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F38" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G38" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H38" s="1" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="39" spans="2:8">
-      <c r="B39" s="2" t="s">
+    <row r="39" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B39" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="D39" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E39" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F39" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G39" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H39" s="2" t="s">
+      <c r="D39" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F39" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G39" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H39" s="1" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="40" spans="2:8">
-      <c r="B40" s="2" t="s">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B40" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="D40" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E40" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F40" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G40" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H40" s="2" t="s">
+      <c r="D40" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F40" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G40" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H40" s="1" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="41" spans="2:8">
-      <c r="B41" s="2" t="s">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B41" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C41" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="D41" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E41" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F41" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G41" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H41" s="2" t="s">
+      <c r="D41" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F41" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G41" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H41" s="1" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="42" spans="2:8">
-      <c r="B42" s="2" t="s">
+    <row r="42" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B42" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C42" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D42" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E42" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F42" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G42" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H42" s="2" t="s">
+      <c r="D42" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F42" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G42" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H42" s="1" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="43" spans="2:8">
-      <c r="B43" s="2" t="s">
+    <row r="43" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B43" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C43" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="D43" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E43" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F43" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G43" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H43" s="2" t="s">
+      <c r="D43" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F43" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G43" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H43" s="1" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="44" spans="2:8">
-      <c r="B44" s="2" t="s">
+    <row r="44" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B44" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="C44" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="D44" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E44" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F44" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G44" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H44" s="2" t="s">
+      <c r="D44" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F44" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G44" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H44" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="45" spans="2:8">
-      <c r="B45" s="2" t="s">
+    <row r="45" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B45" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C45" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="D45" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E45" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F45" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G45" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H45" s="2" t="s">
+      <c r="D45" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F45" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G45" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H45" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="46" spans="2:8">
-      <c r="B46" s="2" t="s">
+    <row r="46" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B46" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C46" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="D46" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E46" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F46" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G46" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H46" s="2" t="s">
+      <c r="D46" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F46" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G46" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H46" s="1" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="47" spans="2:8">
-      <c r="B47" s="2" t="s">
+    <row r="47" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B47" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C47" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="D47" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E47" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F47" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G47" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H47" s="2" t="s">
+      <c r="D47" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F47" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G47" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H47" s="1" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="48" spans="2:8">
-      <c r="B48" s="2" t="s">
+    <row r="48" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B48" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C48" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="D48" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E48" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F48" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G48" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H48" s="2" t="s">
+      <c r="D48" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F48" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G48" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H48" s="1" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="49" spans="2:8">
-      <c r="B49" s="2" t="s">
+    <row r="49" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B49" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C49" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="D49" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E49" s="11" t="s">
+      <c r="D49" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E49" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="F49" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G49" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H49" s="10" t="s">
+      <c r="F49" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G49" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H49" s="1" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="50" spans="2:8">
-      <c r="B50" s="2" t="s">
+    <row r="50" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B50" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C50" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D50" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E50" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F50" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G50" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H50" s="10" t="s">
+      <c r="D50" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F50" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G50" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H50" s="1" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="51" spans="2:8">
-      <c r="B51" s="2" t="s">
+    <row r="51" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B51" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="C51" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="D51" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E51" s="11" t="s">
+      <c r="D51" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E51" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="F51" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G51" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H51" s="10" t="s">
+      <c r="F51" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G51" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H51" s="1" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="52" spans="2:8">
-      <c r="B52" s="2" t="s">
+    <row r="52" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B52" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C52" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="D52" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E52" s="11" t="s">
+      <c r="D52" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E52" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="F52" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G52" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H52" s="10" t="s">
+      <c r="F52" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G52" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H52" s="1" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="53" spans="2:8">
-      <c r="B53" s="2" t="s">
+    <row r="53" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B53" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="C53" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="D53" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E53" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="F53" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G53" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H53" s="10" t="s">
+      <c r="D53" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F53" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G53" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H53" s="1" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="54" spans="2:8">
-      <c r="B54" s="2" t="s">
+    <row r="54" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B54" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C54" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D54" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E54" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="F54" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G54" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H54" s="10" t="s">
+      <c r="D54" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F54" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G54" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H54" s="1" t="s">
         <v>179</v>
       </c>
     </row>
+    <row r="55" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B55" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F55" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G55" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H55" s="9" t="s">
+        <v>182</v>
+      </c>
+    </row>
   </sheetData>
-  <printOptions>
-    <extLst>
-      <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1784283445" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
-      </ext>
-    </extLst>
-  </printOptions>
-  <pageMargins left="0.700000" right="0.700000" top="0.750000" bottom="0.750000" header="0.300000" footer="0.300000"/>
-  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="1"/>
-  <headerFooter>
-    <extLst>
-      <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1784283445" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1784283445" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1784283445" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1784283445" Id="1" type="0" value="0"/>
-      </ext>
-    </extLst>
-  </headerFooter>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" fitToWidth="0"/>
   <extLst>
     <ext uri="smNativeData">
       <pm:sheetPrefs xmlns:pm="smNativeData" day="1784283445" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">

--- a/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C7EF698-BDBC-46E0-BC5A-7D74A67050C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{315FEFCF-744A-40A4-BF66-DEBFAB7AC137}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5470" yWindow="480" windowWidth="30590" windowHeight="18380" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2275,7 +2275,7 @@
         <v>1</v>
       </c>
       <c r="G55" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H55" s="9" t="s">
         <v>182</v>

--- a/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
@@ -1,34 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
+  <fileSharing readOnlyRecommended="0" userName="Lumino Game 03"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{315FEFCF-744A-40A4-BF66-DEBFAB7AC137}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5470" yWindow="480" windowWidth="30590" windowHeight="18380" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView activeTab="0" xWindow="240" yWindow="60" windowWidth="30590" windowHeight="18380" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:revision xmlns:pm="smNativeData" day="1784283445" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
-      <pm:docPrefs xmlns:pm="smNativeData" id="1784283445" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
-      <pm:compatibility xmlns:pm="smNativeData" id="1784283445" overlapCells="1"/>
-      <pm:defCurrency xmlns:pm="smNativeData" id="1784283445"/>
+      <pm:revision xmlns:pm="smNativeData" day="1784530838" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
+      <pm:docPrefs xmlns:pm="smNativeData" id="1784530838" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
+      <pm:compatibility xmlns:pm="smNativeData" id="1784530838" overlapCells="1"/>
+      <pm:defCurrency xmlns:pm="smNativeData" id="1784530838"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="189">
   <si>
     <t>##var</t>
   </si>
@@ -577,45 +572,103 @@
   </si>
   <si>
     <t>会展Game主UI</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>FishGameWinPanel</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/Fish/FishGameWinPanel.prefab</t>
+  </si>
+  <si>
+    <t>钓鱼游戏胜利面板</t>
+  </si>
+  <si>
+    <t>FishGameLosePanel</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/Fish/FishGameLosePanel.prefab</t>
+  </si>
+  <si>
+    <t>钓鱼游戏失败面板</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="8">
+    <numFmt numFmtId="5" formatCode="#,##0\ &quot;¥&quot;;\-#,##0\ &quot;¥&quot;"/>
+    <numFmt numFmtId="6" formatCode="#,##0\ &quot;¥&quot;;[Red]\-#,##0\ &quot;¥&quot;"/>
+    <numFmt numFmtId="7" formatCode="#,##0.00\ &quot;¥&quot;;\-#,##0.00\ &quot;¥&quot;"/>
+    <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;¥&quot;;[Red]\-#,##0.00\ &quot;¥&quot;"/>
+    <numFmt numFmtId="42" formatCode="_-* #,##0\ &quot;¥&quot;_-;\-* #,##0\ &quot;¥&quot;_-;_-* &quot;-&quot;\ &quot;¥&quot;_-;_-@_-"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0\ _¥_-;\-* #,##0\ _¥_-;_-* &quot;-&quot;\ _¥_-;_-@_-"/>
+    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;¥&quot;_-;\-* #,##0.00\ &quot;¥&quot;_-;_-* &quot;-&quot;??\ &quot;¥&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _¥_-;\-* #,##0.00\ _¥_-;_-* &quot;-&quot;??\ _¥_-;_-@_-"/>
+  </numFmts>
+  <fonts count="4">
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="等线"/>
       <charset val="134"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784530838" ulstyle="none" kern="1">
+            <pm:latin face="等线" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784530838" ulstyle="none" kern="1">
+            <pm:latin face="Arial" sz="200" lang="default"/>
+            <pm:cs face="Times New Roman" sz="200" lang="default"/>
+            <pm:ea face="SimSun" sz="200" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF1F2329"/>
       <name val="等线"/>
+      <charset val="134"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784530838" ulstyle="none" kern="1">
+            <pm:latin face="等线" sz="200" lang="default"/>
+            <pm:cs face="Times New Roman" sz="200" lang="default"/>
+            <pm:ea face="SimSun" sz="200" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <color rgb="FF1F2329"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784530838" fgClr="1F2329" ulstyle="none" kern="1">
+            <pm:latin face="等线" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -623,25 +676,61 @@
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFACB9CA"/>
         <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784530838" type="1" fgLvl="100" fgClr="00ACB9CA" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF5B9BD5"/>
         <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784530838" type="1" fgLvl="100" fgClr="005B9BD5" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784530838" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784530838"/>
+        </ext>
+      </extLst>
     </border>
     <border>
       <left style="thin">
@@ -656,77 +745,125 @@
       <bottom style="thin">
         <color rgb="FFDEE0E3"/>
       </bottom>
-      <diagonal/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784530838">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+          </pm:border>
+        </ext>
+      </extLst>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784530838"/>
+        </ext>
+      </extLst>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784530838"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784530838"/>
+        </ext>
+      </extLst>
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="常规" xfId="0" builtinId="0" customBuiltin="1"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
+    <cellStyle name="常规 2" xfId="1"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
     <ext uri="smNativeData">
-      <pm:charStyles xmlns:pm="smNativeData" id="1784283445" count="1">
+      <pm:charStyles xmlns:pm="smNativeData" id="1784530838" count="1">
         <pm:charStyle name="普通" fontId="0" Id="1"/>
       </pm:charStyles>
-      <pm:colors xmlns:pm="smNativeData" id="1784283445" count="4">
+      <pm:colors xmlns:pm="smNativeData" id="1784530838" count="4">
         <pm:color name="颜色 24" rgb="1F2329"/>
         <pm:color name="颜色 25" rgb="ACB9CA"/>
         <pm:color name="颜色 26" rgb="5B9BD5"/>
@@ -992,1302 +1129,1363 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H55"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <dimension ref="A1:H57"/>
+  <sheetFormatPr defaultRowHeight="13.45"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="28.58203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="100.08203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="25.1640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="23.6640625" style="1" customWidth="1"/>
-    <col min="6" max="7" width="17.6640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="24.1640625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="8.6640625" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.6640625" style="1"/>
+    <col min="1" max="1" width="8.663793" customWidth="1" style="2"/>
+    <col min="2" max="2" width="28.577586" customWidth="1" style="2"/>
+    <col min="3" max="3" width="100.077586" customWidth="1" style="2"/>
+    <col min="4" max="4" width="25.163793" customWidth="1" style="2"/>
+    <col min="5" max="5" width="23.663793" customWidth="1" style="2"/>
+    <col min="6" max="7" width="17.663793" customWidth="1" style="2"/>
+    <col min="8" max="8" width="24.163793" customWidth="1" style="2"/>
+    <col min="9" max="16384" width="8.663793" customWidth="1" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
+    <row r="1" spans="1:8">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:8">
+      <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:8">
+      <c r="A3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B4" s="2" t="s">
+    <row r="4" spans="2:8">
+      <c r="B4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G4" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H4" s="1" t="s">
+      <c r="D4" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B5" s="2" t="s">
+    <row r="5" spans="2:8">
+      <c r="B5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G5" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H5" s="4" t="s">
+      <c r="D5" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="2" t="s">
+    <row r="6" spans="2:8" ht="19.50" customHeight="1">
+      <c r="B6" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="7" t="s">
+      <c r="D6" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G6" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H6" s="4" t="s">
+      <c r="F6" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B7" s="2" t="s">
+    <row r="7" spans="2:8">
+      <c r="B7" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G7" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H7" s="4" t="s">
+      <c r="D7" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B8" s="2" t="s">
+    <row r="8" spans="2:8">
+      <c r="B8" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G8" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H8" s="4" t="s">
+      <c r="D8" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" s="5" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B9" s="2" t="s">
+    <row r="9" spans="2:8">
+      <c r="B9" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G9" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H9" s="4" t="s">
+      <c r="D9" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" s="5" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B10" s="2" t="s">
+    <row r="10" spans="2:8">
+      <c r="B10" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="F10" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G10" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H10" s="4" t="s">
+      <c r="F10" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B11" s="2" t="s">
+    <row r="11" spans="2:8">
+      <c r="B11" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="F11" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G11" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H11" s="4" t="s">
+      <c r="F11" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H11" s="5" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B12" s="2" t="s">
+    <row r="12" spans="2:8">
+      <c r="B12" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F12" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G12" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H12" s="4" t="s">
+      <c r="D12" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H12" s="5" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B13" s="2" t="s">
+    <row r="13" spans="2:8">
+      <c r="B13" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D13" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F13" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G13" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H13" s="4" t="s">
+      <c r="D13" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" s="5" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B14" s="2" t="s">
+    <row r="14" spans="2:8">
+      <c r="B14" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="F14" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G14" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H14" s="4" t="s">
+      <c r="F14" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G14" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" s="5" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B15" s="2" t="s">
+    <row r="15" spans="2:8">
+      <c r="B15" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E15" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F15" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G15" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H15" s="4" t="s">
+      <c r="E15" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H15" s="5" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B16" s="2" t="s">
+    <row r="16" spans="2:8">
+      <c r="B16" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="D16" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E16" s="7" t="s">
+      <c r="D16" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F16" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G16" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H16" s="4" t="s">
+      <c r="F16" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H16" s="5" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B17" s="2" t="s">
+    <row r="17" spans="2:8">
+      <c r="B17" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="D17" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F17" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G17" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H17" s="4" t="s">
+      <c r="D17" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G17" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B18" s="2" t="s">
+    <row r="18" spans="2:8">
+      <c r="B18" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="D18" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E18" s="7" t="s">
+      <c r="D18" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F18" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G18" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H18" s="4" t="s">
+      <c r="F18" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G18" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H18" s="5" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B19" s="2" t="s">
+    <row r="19" spans="2:8">
+      <c r="B19" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="D19" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F19" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G19" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H19" s="4" t="s">
+      <c r="D19" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F19" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H19" s="5" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B20" s="2" t="s">
+    <row r="20" spans="2:8">
+      <c r="B20" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="D20" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F20" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G20" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H20" s="4" t="s">
+      <c r="D20" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F20" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" s="5" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B21" s="2" t="s">
+    <row r="21" spans="2:8">
+      <c r="B21" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="D21" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F21" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G21" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H21" s="4" t="s">
+      <c r="D21" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" s="5" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B22" s="2" t="s">
+    <row r="22" spans="2:8">
+      <c r="B22" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="D22" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F22" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G22" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H22" s="4" t="s">
+      <c r="D22" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F22" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H22" s="5" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B23" s="2" t="s">
+    <row r="23" spans="2:8">
+      <c r="B23" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="D23" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F23" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G23" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H23" s="4" t="s">
+      <c r="D23" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H23" s="5" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B24" s="2" t="s">
+    <row r="24" spans="2:8">
+      <c r="B24" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="D24" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F24" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G24" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H24" s="4" t="s">
+      <c r="D24" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F24" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H24" s="5" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B25" s="2" t="s">
+    <row r="25" spans="2:8">
+      <c r="B25" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="D25" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F25" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G25" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H25" s="4" t="s">
+      <c r="D25" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F25" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H25" s="5" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B26" s="2" t="s">
+    <row r="26" spans="2:8">
+      <c r="B26" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C26" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="D26" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F26" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H26" s="4" t="s">
+      <c r="D26" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F26" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H26" s="5" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B27" s="2" t="s">
+    <row r="27" spans="2:8">
+      <c r="B27" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="D27" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F27" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G27" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H27" s="4" t="s">
+      <c r="D27" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F27" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G27" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H27" s="5" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B28" s="2" t="s">
+    <row r="28" spans="2:8">
+      <c r="B28" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="C28" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="D28" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F28" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G28" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H28" s="4" t="s">
+      <c r="D28" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F28" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G28" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H28" s="5" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B29" s="2" t="s">
+    <row r="29" spans="2:8">
+      <c r="B29" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D29" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F29" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G29" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H29" s="1" t="s">
+      <c r="D29" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F29" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G29" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H29" s="2" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B30" s="2" t="s">
+    <row r="30" spans="2:8">
+      <c r="B30" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="D30" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F30" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G30" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H30" s="1" t="s">
+      <c r="D30" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F30" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G30" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H30" s="2" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B31" s="2" t="s">
+    <row r="31" spans="2:8">
+      <c r="B31" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="D31" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F31" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G31" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H31" s="1" t="s">
+      <c r="D31" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F31" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G31" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H31" s="2" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B32" s="2" t="s">
+    <row r="32" spans="2:8">
+      <c r="B32" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="D32" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F32" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G32" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H32" s="1" t="s">
+      <c r="D32" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F32" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G32" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H32" s="2" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B33" s="2" t="s">
+    <row r="33" spans="2:8">
+      <c r="B33" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D33" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F33" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G33" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H33" s="1" t="s">
+      <c r="D33" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F33" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G33" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H33" s="2" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B34" s="1" t="s">
+    <row r="34" spans="2:8">
+      <c r="B34" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="D34" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E34" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F34" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G34" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H34" s="1" t="s">
+      <c r="D34" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F34" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G34" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H34" s="2" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B35" s="1" t="s">
+    <row r="35" spans="2:8">
+      <c r="B35" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="D35" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F35" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G35" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H35" s="1" t="s">
+      <c r="D35" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F35" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G35" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H35" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B36" s="1" t="s">
+    <row r="36" spans="2:8">
+      <c r="B36" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="D36" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F36" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G36" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H36" s="1" t="s">
+      <c r="D36" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F36" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G36" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H36" s="2" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B37" s="1" t="s">
+    <row r="37" spans="2:8">
+      <c r="B37" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="D37" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F37" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G37" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H37" s="1" t="s">
+      <c r="D37" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F37" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G37" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H37" s="2" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B38" s="1" t="s">
+    <row r="38" spans="2:8">
+      <c r="B38" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="D38" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E38" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F38" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G38" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H38" s="1" t="s">
+      <c r="D38" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F38" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G38" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H38" s="2" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B39" s="1" t="s">
+    <row r="39" spans="2:8">
+      <c r="B39" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="D39" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E39" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F39" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G39" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H39" s="1" t="s">
+      <c r="D39" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F39" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G39" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H39" s="2" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B40" s="1" t="s">
+    <row r="40" spans="2:8">
+      <c r="B40" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="D40" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E40" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F40" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G40" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H40" s="1" t="s">
+      <c r="D40" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F40" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G40" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H40" s="2" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B41" s="1" t="s">
+    <row r="41" spans="2:8">
+      <c r="B41" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="D41" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E41" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F41" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G41" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H41" s="1" t="s">
+      <c r="D41" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F41" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G41" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H41" s="2" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B42" s="1" t="s">
+    <row r="42" spans="2:8">
+      <c r="B42" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C42" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="D42" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E42" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F42" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G42" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H42" s="1" t="s">
+      <c r="D42" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F42" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G42" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H42" s="2" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B43" s="1" t="s">
+    <row r="43" spans="2:8">
+      <c r="B43" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C43" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="D43" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E43" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F43" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G43" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H43" s="1" t="s">
+      <c r="D43" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F43" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G43" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H43" s="2" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B44" s="1" t="s">
+    <row r="44" spans="2:8">
+      <c r="B44" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C44" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="D44" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E44" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F44" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G44" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H44" s="1" t="s">
+      <c r="D44" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F44" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G44" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H44" s="2" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B45" s="1" t="s">
+    <row r="45" spans="2:8">
+      <c r="B45" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C45" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="D45" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E45" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F45" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G45" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H45" s="1" t="s">
+      <c r="D45" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F45" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G45" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H45" s="2" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B46" s="1" t="s">
+    <row r="46" spans="2:8">
+      <c r="B46" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C46" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="D46" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E46" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F46" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G46" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H46" s="1" t="s">
+      <c r="D46" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F46" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G46" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H46" s="2" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B47" s="1" t="s">
+    <row r="47" spans="2:8">
+      <c r="B47" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C47" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="D47" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E47" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F47" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G47" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H47" s="1" t="s">
+      <c r="D47" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F47" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G47" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H47" s="2" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B48" s="1" t="s">
+    <row r="48" spans="2:8">
+      <c r="B48" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="C48" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="D48" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E48" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F48" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G48" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H48" s="1" t="s">
+      <c r="D48" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F48" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G48" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H48" s="2" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="49" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B49" s="1" t="s">
+    <row r="49" spans="2:8">
+      <c r="B49" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C49" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="D49" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E49" s="7" t="s">
+      <c r="D49" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E49" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="F49" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G49" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H49" s="1" t="s">
+      <c r="F49" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G49" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H49" s="2" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="50" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B50" s="1" t="s">
+    <row r="50" spans="2:8">
+      <c r="B50" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="C50" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="D50" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E50" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F50" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G50" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H50" s="1" t="s">
+      <c r="D50" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F50" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G50" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H50" s="2" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="51" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B51" s="1" t="s">
+    <row r="51" spans="2:8">
+      <c r="B51" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="C51" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="D51" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E51" s="7" t="s">
+      <c r="D51" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E51" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="F51" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G51" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H51" s="1" t="s">
+      <c r="F51" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G51" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H51" s="2" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="52" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B52" s="1" t="s">
+    <row r="52" spans="2:8">
+      <c r="B52" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="C52" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="D52" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E52" s="7" t="s">
+      <c r="D52" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E52" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="F52" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G52" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H52" s="1" t="s">
+      <c r="F52" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G52" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H52" s="2" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="53" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B53" s="1" t="s">
+    <row r="53" spans="2:8">
+      <c r="B53" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="C53" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="D53" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E53" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F53" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G53" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H53" s="1" t="s">
+      <c r="D53" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F53" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G53" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H53" s="2" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="54" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B54" s="1" t="s">
+    <row r="54" spans="2:8">
+      <c r="B54" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="C54" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="D54" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E54" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F54" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G54" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H54" s="1" t="s">
+      <c r="D54" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F54" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G54" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H54" s="2" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="55" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B55" s="1" t="s">
+    <row r="55" spans="2:8">
+      <c r="B55" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="C55" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="D55" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E55" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F55" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G55" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H55" s="9" t="s">
+      <c r="D55" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F55" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G55" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H55" s="10" t="s">
         <v>182</v>
       </c>
     </row>
+    <row r="56" spans="2:8">
+      <c r="B56" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F56" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G56" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="57" spans="2:8">
+      <c r="B57" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F57" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G57" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H57" s="10" t="s">
+        <v>188</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" fitToWidth="0"/>
+  <printOptions>
+    <extLst>
+      <ext uri="smNativeData">
+        <pm:pageFlags xmlns:pm="smNativeData" id="1784530838" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+      </ext>
+    </extLst>
+  </printOptions>
+  <pageMargins left="0.700000" right="0.700000" top="0.750000" bottom="0.750000" header="0.300000" footer="0.300000"/>
+  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="1"/>
+  <headerFooter>
+    <extLst>
+      <ext uri="smNativeData">
+        <pm:header xmlns:pm="smNativeData" id="1784530838" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1784530838" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1784530838" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1784530838" Id="1" type="0" value="0"/>
+      </ext>
+    </extLst>
+  </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1784283445" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1784530838" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>

--- a/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
@@ -13,10 +13,10 @@
   <calcPr/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:revision xmlns:pm="smNativeData" day="1784530838" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
-      <pm:docPrefs xmlns:pm="smNativeData" id="1784530838" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
-      <pm:compatibility xmlns:pm="smNativeData" id="1784530838" overlapCells="1"/>
-      <pm:defCurrency xmlns:pm="smNativeData" id="1784530838"/>
+      <pm:revision xmlns:pm="smNativeData" day="1784600161" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
+      <pm:docPrefs xmlns:pm="smNativeData" id="1784600161" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
+      <pm:compatibility xmlns:pm="smNativeData" id="1784600161" overlapCells="1"/>
+      <pm:defCurrency xmlns:pm="smNativeData" id="1784600161"/>
     </ext>
   </extLst>
 </workbook>
@@ -614,7 +614,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784530838" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784600161" ulstyle="none" kern="1">
             <pm:latin face="等线" sz="220" lang="default"/>
             <pm:cs face="Times New Roman" sz="220" lang="default"/>
             <pm:ea face="SimSun" sz="220" lang="default"/>
@@ -629,7 +629,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784530838" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784600161" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="200" lang="default"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -644,7 +644,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784530838" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784600161" ulstyle="none" kern="1">
             <pm:latin face="等线" sz="200" lang="default"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -659,7 +659,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784530838" fgClr="1F2329" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784600161" fgClr="1F2329" ulstyle="none" kern="1">
             <pm:latin face="等线" sz="220" lang="default"/>
             <pm:cs face="Times New Roman" sz="220" lang="default"/>
             <pm:ea face="SimSun" sz="220" lang="default"/>
@@ -668,7 +668,7 @@
       </extLst>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -684,7 +684,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784530838" type="1" fgLvl="100" fgClr="00ACB9CA" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1784600161" type="1" fgLvl="100" fgClr="00ACB9CA" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -695,24 +695,13 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784530838" type="1" fgLvl="100" fgClr="005B9BD5" bgLvl="0" bgClr="00FFFFFF"/>
-          </ext>
-        </extLst>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784530838" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1784600161" type="1" fgLvl="100" fgClr="005B9BD5" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="4">
     <border>
       <left style="none">
         <color rgb="FF000000"/>
@@ -728,7 +717,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784530838"/>
+          <pm:border xmlns:pm="smNativeData" id="1784600161"/>
         </ext>
       </extLst>
     </border>
@@ -747,7 +736,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784530838">
+          <pm:border xmlns:pm="smNativeData" id="1784600161">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
@@ -771,7 +760,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784530838"/>
+          <pm:border xmlns:pm="smNativeData" id="1784600161"/>
         </ext>
       </extLst>
     </border>
@@ -790,26 +779,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784530838"/>
-        </ext>
-      </extLst>
-    </border>
-    <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784530838"/>
+          <pm:border xmlns:pm="smNativeData" id="1784600161"/>
         </ext>
       </extLst>
     </border>
@@ -820,7 +790,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
@@ -849,9 +819,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
@@ -860,10 +827,10 @@
   <tableStyles count="0"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:charStyles xmlns:pm="smNativeData" id="1784530838" count="1">
+      <pm:charStyles xmlns:pm="smNativeData" id="1784600161" count="1">
         <pm:charStyle name="普通" fontId="0" Id="1"/>
       </pm:charStyles>
-      <pm:colors xmlns:pm="smNativeData" id="1784530838" count="4">
+      <pm:colors xmlns:pm="smNativeData" id="1784600161" count="4">
         <pm:color name="颜色 24" rgb="1F2329"/>
         <pm:color name="颜色 25" rgb="ACB9CA"/>
         <pm:color name="颜色 26" rgb="5B9BD5"/>
@@ -2385,7 +2352,7 @@
         <v>25</v>
       </c>
       <c r="F54" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G54" s="5" t="b">
         <v>0</v>
@@ -2413,7 +2380,7 @@
       <c r="G55" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="H55" s="10" t="s">
+      <c r="H55" s="2" t="s">
         <v>182</v>
       </c>
     </row>
@@ -2459,7 +2426,7 @@
       <c r="G57" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="H57" s="10" t="s">
+      <c r="H57" s="2" t="s">
         <v>188</v>
       </c>
     </row>
@@ -2467,7 +2434,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1784530838" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1784600161" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -2476,16 +2443,16 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1784530838" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1784530838" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1784530838" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1784530838" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1784600161" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1784600161" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1784600161" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1784600161" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1784530838" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1784600161" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>

--- a/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
@@ -1,16 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
-  <fileSharing readOnlyRecommended="0" userName="Lumino Game 03"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{217C21D4-CA87-4D34-A3D6-5F2F1875505D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0" xWindow="240" yWindow="60" windowWidth="30590" windowHeight="18380" tabRatio="500"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext uri="smNativeData">
       <pm:revision xmlns:pm="smNativeData" day="1784600161" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
@@ -23,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="192">
   <si>
     <t>##var</t>
   </si>
@@ -590,85 +595,57 @@
   </si>
   <si>
     <t>钓鱼游戏失败面板</t>
+  </si>
+  <si>
+    <t>PopExhibitionSettlementUI</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/PopExhibitionSettlementUI/PopExhibitionSettlementUI.prefab</t>
+  </si>
+  <si>
+    <t>会展结算面版</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
-    <numFmt numFmtId="5" formatCode="#,##0\ &quot;¥&quot;;\-#,##0\ &quot;¥&quot;"/>
-    <numFmt numFmtId="6" formatCode="#,##0\ &quot;¥&quot;;[Red]\-#,##0\ &quot;¥&quot;"/>
-    <numFmt numFmtId="7" formatCode="#,##0.00\ &quot;¥&quot;;\-#,##0.00\ &quot;¥&quot;"/>
-    <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;¥&quot;;[Red]\-#,##0.00\ &quot;¥&quot;"/>
-    <numFmt numFmtId="42" formatCode="_-* #,##0\ &quot;¥&quot;_-;\-* #,##0\ &quot;¥&quot;_-;_-* &quot;-&quot;\ &quot;¥&quot;_-;_-@_-"/>
-    <numFmt numFmtId="41" formatCode="_-* #,##0\ _¥_-;\-* #,##0\ _¥_-;_-* &quot;-&quot;\ _¥_-;_-@_-"/>
-    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;¥&quot;_-;\-* #,##0.00\ &quot;¥&quot;_-;_-* &quot;-&quot;??\ &quot;¥&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _¥_-;\-* #,##0.00\ _¥_-;_-* &quot;-&quot;??\ _¥_-;_-@_-"/>
-  </numFmts>
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="等线"/>
       <charset val="134"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784600161" ulstyle="none" kern="1">
-            <pm:latin face="等线" sz="220" lang="default"/>
-            <pm:cs face="Times New Roman" sz="220" lang="default"/>
-            <pm:ea face="SimSun" sz="220" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
-      <name val="Arial"/>
-      <family val="2"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
-      <sz val="10"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784600161" ulstyle="none" kern="1">
-            <pm:latin face="Arial" sz="200" lang="default"/>
-            <pm:cs face="Times New Roman" sz="200" lang="default"/>
-            <pm:ea face="SimSun" sz="200" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
+      <name val="等线"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF1F2329"/>
       <name val="等线"/>
-      <charset val="134"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784600161" ulstyle="none" kern="1">
-            <pm:latin face="等线" sz="200" lang="default"/>
-            <pm:cs face="Times New Roman" sz="200" lang="default"/>
-            <pm:ea face="SimSun" sz="200" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="等线"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
-      <color rgb="FF1F2329"/>
-      <sz val="11"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784600161" fgClr="1F2329" ulstyle="none" kern="1">
-            <pm:latin face="等线" sz="220" lang="default"/>
-            <pm:cs face="Times New Roman" sz="220" lang="default"/>
-            <pm:ea face="SimSun" sz="220" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -676,50 +653,25 @@
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
-      <patternFill patternType="none"/>
-    </fill>
-    <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFACB9CA"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784600161" type="1" fgLvl="100" fgClr="00ACB9CA" bgLvl="0" bgClr="00FFFFFF"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF5B9BD5"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784600161" type="1" fgLvl="100" fgClr="005B9BD5" bgLvl="0" bgClr="00FFFFFF"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
   </fills>
   <borders count="4">
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784600161"/>
-        </ext>
-      </extLst>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -734,98 +686,72 @@
       <bottom style="thin">
         <color rgb="FFDEE0E3"/>
       </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784600161">
-            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-          </pm:border>
-        </ext>
-      </extLst>
+      <diagonal/>
     </border>
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784600161"/>
-        </ext>
-      </extLst>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784600161"/>
-        </ext>
-      </extLst>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
-    <cellStyle name="常规 2" xfId="1"/>
+    <cellStyle name="常规" xfId="0" builtinId="0" customBuiltin="1"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0"/>
   <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
     <ext uri="smNativeData">
       <pm:charStyles xmlns:pm="smNativeData" id="1784600161" count="1">
         <pm:charStyle name="普通" fontId="0" Id="1"/>
@@ -1096,1360 +1022,1368 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:H57"/>
-  <sheetFormatPr defaultRowHeight="13.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H58"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.663793" customWidth="1" style="2"/>
-    <col min="2" max="2" width="28.577586" customWidth="1" style="2"/>
-    <col min="3" max="3" width="100.077586" customWidth="1" style="2"/>
-    <col min="4" max="4" width="25.163793" customWidth="1" style="2"/>
-    <col min="5" max="5" width="23.663793" customWidth="1" style="2"/>
-    <col min="6" max="7" width="17.663793" customWidth="1" style="2"/>
-    <col min="8" max="8" width="24.163793" customWidth="1" style="2"/>
-    <col min="9" max="16384" width="8.663793" customWidth="1" style="2"/>
+    <col min="1" max="1" width="8.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="28.58203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="100.08203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="25.1640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="23.6640625" style="1" customWidth="1"/>
+    <col min="6" max="7" width="17.6640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="24.1640625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="4" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="2:8">
-      <c r="B4" s="3" t="s">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G4" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H4" s="2" t="s">
+      <c r="D4" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="2:8">
-      <c r="B5" s="3" t="s">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G5" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H5" s="5" t="s">
+      <c r="D5" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="19.50" customHeight="1">
-      <c r="B6" s="3" t="s">
+    <row r="6" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="8" t="s">
+      <c r="D6" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G6" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H6" s="5" t="s">
+      <c r="F6" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="2:8">
-      <c r="B7" s="3" t="s">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B7" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G7" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H7" s="5" t="s">
+      <c r="D7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="2:8">
-      <c r="B8" s="3" t="s">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G8" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H8" s="5" t="s">
+      <c r="D8" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" s="4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="2:8">
-      <c r="B9" s="3" t="s">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B9" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G9" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H9" s="5" t="s">
+      <c r="D9" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="2:8">
-      <c r="B10" s="3" t="s">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B10" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F10" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G10" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H10" s="5" t="s">
+      <c r="F10" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="2:8">
-      <c r="B11" s="3" t="s">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B11" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="F11" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G11" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H11" s="5" t="s">
+      <c r="F11" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H11" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="12" spans="2:8">
-      <c r="B12" s="3" t="s">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B12" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F12" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G12" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H12" s="5" t="s">
+      <c r="D12" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H12" s="4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="13" spans="2:8">
-      <c r="B13" s="3" t="s">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B13" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F13" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G13" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H13" s="5" t="s">
+      <c r="D13" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" s="4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="14" spans="2:8">
-      <c r="B14" s="3" t="s">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B14" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E14" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="F14" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G14" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H14" s="5" t="s">
+      <c r="F14" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G14" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" s="4" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="15" spans="2:8">
-      <c r="B15" s="3" t="s">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B15" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E15" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F15" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G15" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H15" s="5" t="s">
+      <c r="E15" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H15" s="4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="16" spans="2:8">
-      <c r="B16" s="3" t="s">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B16" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D16" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E16" s="8" t="s">
+      <c r="D16" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F16" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G16" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H16" s="5" t="s">
+      <c r="F16" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H16" s="4" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="17" spans="2:8">
-      <c r="B17" s="3" t="s">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B17" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D17" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F17" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G17" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H17" s="5" t="s">
+      <c r="D17" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G17" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="2:8">
-      <c r="B18" s="3" t="s">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B18" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D18" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E18" s="8" t="s">
+      <c r="D18" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F18" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G18" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H18" s="5" t="s">
+      <c r="F18" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G18" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H18" s="4" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="2:8">
-      <c r="B19" s="3" t="s">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B19" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D19" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F19" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G19" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H19" s="5" t="s">
+      <c r="D19" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F19" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H19" s="4" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="20" spans="2:8">
-      <c r="B20" s="3" t="s">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B20" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="D20" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F20" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G20" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H20" s="5" t="s">
+      <c r="D20" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F20" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" s="4" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="21" spans="2:8">
-      <c r="B21" s="3" t="s">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B21" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="D21" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F21" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G21" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H21" s="5" t="s">
+      <c r="D21" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" s="4" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="22" spans="2:8">
-      <c r="B22" s="3" t="s">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B22" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C22" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="D22" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F22" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G22" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H22" s="5" t="s">
+      <c r="D22" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F22" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H22" s="4" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="23" spans="2:8">
-      <c r="B23" s="3" t="s">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B23" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D23" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F23" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G23" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H23" s="5" t="s">
+      <c r="D23" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H23" s="4" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="24" spans="2:8">
-      <c r="B24" s="3" t="s">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B24" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="D24" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F24" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G24" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H24" s="5" t="s">
+      <c r="D24" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F24" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H24" s="4" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="25" spans="2:8">
-      <c r="B25" s="3" t="s">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B25" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="D25" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F25" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G25" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H25" s="5" t="s">
+      <c r="D25" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F25" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H25" s="4" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="26" spans="2:8">
-      <c r="B26" s="3" t="s">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B26" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="C26" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="D26" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F26" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H26" s="5" t="s">
+      <c r="D26" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F26" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H26" s="4" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="27" spans="2:8">
-      <c r="B27" s="3" t="s">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B27" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="C27" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="D27" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F27" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G27" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H27" s="5" t="s">
+      <c r="D27" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F27" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G27" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H27" s="4" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="28" spans="2:8">
-      <c r="B28" s="3" t="s">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B28" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C28" s="9" t="s">
+      <c r="C28" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="D28" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F28" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G28" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H28" s="5" t="s">
+      <c r="D28" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F28" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G28" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H28" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="29" spans="2:8">
-      <c r="B29" s="3" t="s">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B29" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="D29" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F29" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G29" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H29" s="2" t="s">
+      <c r="D29" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F29" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G29" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H29" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="30" spans="2:8">
-      <c r="B30" s="3" t="s">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B30" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="D30" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F30" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G30" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H30" s="2" t="s">
+      <c r="D30" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F30" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G30" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H30" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="31" spans="2:8">
-      <c r="B31" s="3" t="s">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B31" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="D31" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F31" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G31" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H31" s="2" t="s">
+      <c r="D31" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F31" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G31" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H31" s="1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="32" spans="2:8">
-      <c r="B32" s="3" t="s">
+    <row r="32" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B32" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="D32" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F32" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G32" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H32" s="2" t="s">
+      <c r="D32" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F32" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G32" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H32" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="33" spans="2:8">
-      <c r="B33" s="3" t="s">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B33" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D33" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F33" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G33" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H33" s="2" t="s">
+      <c r="D33" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F33" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G33" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H33" s="1" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="34" spans="2:8">
-      <c r="B34" s="2" t="s">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B34" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="D34" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F34" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G34" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H34" s="2" t="s">
+      <c r="D34" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F34" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G34" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H34" s="1" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="35" spans="2:8">
-      <c r="B35" s="2" t="s">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B35" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="D35" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E35" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F35" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G35" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H35" s="2" t="s">
+      <c r="D35" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F35" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G35" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H35" s="1" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="36" spans="2:8">
-      <c r="B36" s="2" t="s">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B36" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D36" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F36" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G36" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H36" s="2" t="s">
+      <c r="D36" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F36" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G36" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H36" s="1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="37" spans="2:8">
-      <c r="B37" s="2" t="s">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B37" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="D37" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E37" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F37" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G37" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H37" s="2" t="s">
+      <c r="D37" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F37" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G37" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H37" s="1" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="38" spans="2:8">
-      <c r="B38" s="2" t="s">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B38" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="D38" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E38" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F38" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G38" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H38" s="2" t="s">
+      <c r="D38" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F38" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G38" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H38" s="1" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="39" spans="2:8">
-      <c r="B39" s="2" t="s">
+    <row r="39" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B39" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="D39" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E39" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F39" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G39" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H39" s="2" t="s">
+      <c r="D39" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F39" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G39" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H39" s="1" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="40" spans="2:8">
-      <c r="B40" s="2" t="s">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B40" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="D40" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E40" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F40" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G40" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H40" s="2" t="s">
+      <c r="D40" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F40" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G40" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H40" s="1" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="41" spans="2:8">
-      <c r="B41" s="2" t="s">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B41" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C41" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="D41" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E41" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F41" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G41" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H41" s="2" t="s">
+      <c r="D41" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F41" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G41" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H41" s="1" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="42" spans="2:8">
-      <c r="B42" s="2" t="s">
+    <row r="42" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B42" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C42" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D42" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E42" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F42" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G42" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H42" s="2" t="s">
+      <c r="D42" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F42" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G42" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H42" s="1" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="43" spans="2:8">
-      <c r="B43" s="2" t="s">
+    <row r="43" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B43" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C43" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="D43" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E43" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F43" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G43" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H43" s="2" t="s">
+      <c r="D43" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F43" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G43" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H43" s="1" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="44" spans="2:8">
-      <c r="B44" s="2" t="s">
+    <row r="44" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B44" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="C44" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="D44" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E44" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F44" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G44" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H44" s="2" t="s">
+      <c r="D44" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F44" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G44" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H44" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="45" spans="2:8">
-      <c r="B45" s="2" t="s">
+    <row r="45" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B45" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C45" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="D45" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E45" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F45" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G45" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H45" s="2" t="s">
+      <c r="D45" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F45" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G45" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H45" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="46" spans="2:8">
-      <c r="B46" s="2" t="s">
+    <row r="46" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B46" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C46" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="D46" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E46" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F46" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G46" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H46" s="2" t="s">
+      <c r="D46" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F46" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G46" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H46" s="1" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="47" spans="2:8">
-      <c r="B47" s="2" t="s">
+    <row r="47" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B47" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C47" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="D47" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E47" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F47" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G47" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H47" s="2" t="s">
+      <c r="D47" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F47" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G47" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H47" s="1" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="48" spans="2:8">
-      <c r="B48" s="2" t="s">
+    <row r="48" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B48" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C48" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="D48" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E48" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F48" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G48" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H48" s="2" t="s">
+      <c r="D48" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F48" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G48" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H48" s="1" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="49" spans="2:8">
-      <c r="B49" s="2" t="s">
+    <row r="49" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B49" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C49" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="D49" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E49" s="8" t="s">
+      <c r="D49" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E49" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="F49" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G49" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H49" s="2" t="s">
+      <c r="F49" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G49" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H49" s="1" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="50" spans="2:8">
-      <c r="B50" s="2" t="s">
+    <row r="50" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B50" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C50" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D50" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E50" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F50" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G50" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H50" s="2" t="s">
+      <c r="D50" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F50" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G50" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H50" s="1" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="51" spans="2:8">
-      <c r="B51" s="2" t="s">
+    <row r="51" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B51" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="C51" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="D51" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E51" s="8" t="s">
+      <c r="D51" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E51" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="F51" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G51" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H51" s="2" t="s">
+      <c r="F51" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G51" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H51" s="1" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="52" spans="2:8">
-      <c r="B52" s="2" t="s">
+    <row r="52" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B52" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C52" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="D52" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E52" s="8" t="s">
+      <c r="D52" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E52" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="F52" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G52" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H52" s="2" t="s">
+      <c r="F52" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G52" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H52" s="1" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="53" spans="2:8">
-      <c r="B53" s="2" t="s">
+    <row r="53" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B53" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="C53" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="D53" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E53" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F53" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G53" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H53" s="2" t="s">
+      <c r="D53" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F53" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G53" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H53" s="1" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="54" spans="2:8">
-      <c r="B54" s="2" t="s">
+    <row r="54" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B54" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C54" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D54" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E54" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F54" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G54" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H54" s="2" t="s">
+      <c r="D54" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F54" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G54" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H54" s="1" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="55" spans="2:8">
-      <c r="B55" s="2" t="s">
+    <row r="55" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B55" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C55" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="D55" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E55" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F55" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G55" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H55" s="2" t="s">
+      <c r="D55" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F55" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G55" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H55" s="1" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="56" spans="2:8">
-      <c r="B56" s="2" t="s">
+    <row r="56" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B56" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="C56" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="D56" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E56" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F56" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G56" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H56" s="2" t="s">
+      <c r="D56" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E56" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F56" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G56" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H56" s="1" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="57" spans="2:8">
-      <c r="B57" s="2" t="s">
+    <row r="57" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B57" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="C57" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="D57" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E57" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F57" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G57" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H57" s="2" t="s">
+      <c r="D57" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E57" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F57" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G57" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H57" s="1" t="s">
         <v>188</v>
       </c>
     </row>
+    <row r="58" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B58" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E58" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F58" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G58" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H58" s="9" t="s">
+        <v>191</v>
+      </c>
+    </row>
   </sheetData>
-  <printOptions>
-    <extLst>
-      <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1784600161" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
-      </ext>
-    </extLst>
-  </printOptions>
-  <pageMargins left="0.700000" right="0.700000" top="0.750000" bottom="0.750000" header="0.300000" footer="0.300000"/>
-  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="1"/>
-  <headerFooter>
-    <extLst>
-      <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1784600161" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1784600161" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1784600161" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1784600161" Id="1" type="0" value="0"/>
-      </ext>
-    </extLst>
-  </headerFooter>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" fitToWidth="0"/>
   <extLst>
     <ext uri="smNativeData">
       <pm:sheetPrefs xmlns:pm="smNativeData" day="1784600161" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">

--- a/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{217C21D4-CA87-4D34-A3D6-5F2F1875505D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0905ADA-C423-46EB-9D00-A38CC1D40EFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2302,7 +2302,7 @@
         <v>25</v>
       </c>
       <c r="F55" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G55" s="4" t="b">
         <v>0</v>

--- a/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
@@ -13,17 +13,17 @@
   <calcPr/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:revision xmlns:pm="smNativeData" day="1784617663" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
-      <pm:docPrefs xmlns:pm="smNativeData" id="1784617663" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
-      <pm:compatibility xmlns:pm="smNativeData" id="1784617663" overlapCells="1"/>
-      <pm:defCurrency xmlns:pm="smNativeData" id="1784617663"/>
+      <pm:revision xmlns:pm="smNativeData" day="1784685760" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
+      <pm:docPrefs xmlns:pm="smNativeData" id="1784685760" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
+      <pm:compatibility xmlns:pm="smNativeData" id="1784685760" overlapCells="1"/>
+      <pm:defCurrency xmlns:pm="smNativeData" id="1784685760"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="195">
   <si>
     <t>##var</t>
   </si>
@@ -599,6 +599,15 @@
   </si>
   <si>
     <t>钓鱼图鉴面板</t>
+  </si>
+  <si>
+    <t>FishGameUnavailablePanel</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/Fish/FishGameUnavailablePanel.prefab</t>
+  </si>
+  <si>
+    <t>钓鱼老人离开后的提示面板</t>
   </si>
 </sst>
 </file>
@@ -623,7 +632,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784617663" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784685760" ulstyle="none" kern="1">
             <pm:latin face="等线" sz="220" lang="default"/>
             <pm:cs face="Times New Roman" sz="220" lang="default"/>
             <pm:ea face="SimSun" sz="220" lang="default"/>
@@ -638,7 +647,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784617663" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784685760" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="200" lang="default"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -653,7 +662,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784617663" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784685760" ulstyle="none" kern="1">
             <pm:latin face="等线" sz="200" lang="default"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -668,7 +677,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784617663" fgClr="1F2329" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784685760" fgClr="1F2329" ulstyle="none" kern="1">
             <pm:latin face="等线" sz="220" lang="default"/>
             <pm:cs face="Times New Roman" sz="220" lang="default"/>
             <pm:ea face="SimSun" sz="220" lang="default"/>
@@ -693,7 +702,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784617663" type="1" fgLvl="100" fgClr="00ACB9CA" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1784685760" type="1" fgLvl="100" fgClr="00ACB9CA" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -704,7 +713,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784617663" type="1" fgLvl="100" fgClr="005B9BD5" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1784685760" type="1" fgLvl="100" fgClr="005B9BD5" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -715,7 +724,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784617663" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1784685760" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -737,7 +746,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784617663"/>
+          <pm:border xmlns:pm="smNativeData" id="1784685760"/>
         </ext>
       </extLst>
     </border>
@@ -756,7 +765,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784617663">
+          <pm:border xmlns:pm="smNativeData" id="1784685760">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
@@ -780,7 +789,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784617663"/>
+          <pm:border xmlns:pm="smNativeData" id="1784685760"/>
         </ext>
       </extLst>
     </border>
@@ -799,7 +808,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784617663"/>
+          <pm:border xmlns:pm="smNativeData" id="1784685760"/>
         </ext>
       </extLst>
     </border>
@@ -818,7 +827,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784617663"/>
+          <pm:border xmlns:pm="smNativeData" id="1784685760"/>
         </ext>
       </extLst>
     </border>
@@ -866,10 +875,10 @@
   <tableStyles count="0"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:charStyles xmlns:pm="smNativeData" id="1784617663" count="1">
+      <pm:charStyles xmlns:pm="smNativeData" id="1784685760" count="1">
         <pm:charStyle name="普通" fontId="0" Id="1"/>
       </pm:charStyles>
-      <pm:colors xmlns:pm="smNativeData" id="1784617663" count="4">
+      <pm:colors xmlns:pm="smNativeData" id="1784685760" count="4">
         <pm:color name="颜色 24" rgb="1F2329"/>
         <pm:color name="颜色 25" rgb="ACB9CA"/>
         <pm:color name="颜色 26" rgb="5B9BD5"/>
@@ -1136,7 +1145,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:H58"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr defaultRowHeight="13.45"/>
   <cols>
     <col min="1" max="1" width="8.663793" customWidth="1" style="2"/>
@@ -2492,11 +2501,39 @@
         <v>191</v>
       </c>
     </row>
+    <row r="59" spans="2:8">
+      <c r="B59" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="D59" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E59" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F59" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G59" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="60" spans="8:8">
+      <c r="H60" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1784617663" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1784685760" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -2505,16 +2542,16 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1784617663" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1784617663" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1784617663" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1784617663" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1784685760" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1784685760" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1784685760" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1784685760" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1784617663" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1784685760" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>

--- a/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
@@ -13,17 +13,17 @@
   <calcPr/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:revision xmlns:pm="smNativeData" day="1784686762" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
-      <pm:docPrefs xmlns:pm="smNativeData" id="1784686762" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
-      <pm:compatibility xmlns:pm="smNativeData" id="1784686762" overlapCells="1"/>
-      <pm:defCurrency xmlns:pm="smNativeData" id="1784686762"/>
+      <pm:revision xmlns:pm="smNativeData" day="1784687484" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
+      <pm:docPrefs xmlns:pm="smNativeData" id="1784687484" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
+      <pm:compatibility xmlns:pm="smNativeData" id="1784687484" overlapCells="1"/>
+      <pm:defCurrency xmlns:pm="smNativeData" id="1784687484"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="198">
   <si>
     <t>##var</t>
   </si>
@@ -608,6 +608,15 @@
   </si>
   <si>
     <t>钓鱼老人离开后的提示面板</t>
+  </si>
+  <si>
+    <t>FishGalleryPanel</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/Fish/FishGalleryPanel.prefab</t>
+  </si>
+  <si>
+    <t>钓鱼图鉴面板</t>
   </si>
 </sst>
 </file>
@@ -624,7 +633,7 @@
     <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;¥&quot;_-;\-* #,##0.00\ &quot;¥&quot;_-;_-* &quot;-&quot;??\ &quot;¥&quot;_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _¥_-;\-* #,##0.00\ _¥_-;_-* &quot;-&quot;??\ _¥_-;_-@_-"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="4">
     <font>
       <name val="等线"/>
       <charset val="134"/>
@@ -632,7 +641,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784686762" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784687484" ulstyle="none" kern="1">
             <pm:latin face="等线" sz="220" lang="default"/>
             <pm:cs face="Times New Roman" sz="220" lang="default"/>
             <pm:ea face="SimSun" sz="220" lang="default"/>
@@ -647,7 +656,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784686762" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784687484" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="200" lang="default"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -662,7 +671,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784686762" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784687484" ulstyle="none" kern="1">
             <pm:latin face="等线" sz="200" lang="default"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -677,37 +686,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784686762" fgClr="1F2329" ulstyle="none" kern="1">
-            <pm:latin face="等线" sz="220" lang="default"/>
-            <pm:cs face="Times New Roman" sz="220" lang="default"/>
-            <pm:ea face="SimSun" sz="220" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="134"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784686762" fgClr="000000" ulstyle="none" kern="1">
-            <pm:latin face="等线" sz="220" lang="default"/>
-            <pm:cs face="Times New Roman" sz="220" lang="default"/>
-            <pm:ea face="SimSun" sz="220" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="134"/>
-      <color rgb="FF1F2329"/>
-      <sz val="11"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784686762" fgClr="1F2329" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784687484" fgClr="1F2329" ulstyle="none" kern="1">
             <pm:latin face="等线" sz="220" lang="default"/>
             <pm:cs face="Times New Roman" sz="220" lang="default"/>
             <pm:ea face="SimSun" sz="220" lang="default"/>
@@ -716,7 +695,7 @@
       </extLst>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -732,7 +711,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784686762" type="1" fgLvl="100" fgClr="00ACB9CA" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1784687484" type="1" fgLvl="100" fgClr="00ACB9CA" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -743,38 +722,24 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784686762" type="1" fgLvl="100" fgClr="005B9BD5" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1784687484" type="1" fgLvl="100" fgClr="005B9BD5" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFACB9CA"/>
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784686762" type="1" fgLvl="100" fgClr="00ACB9CA" bgLvl="100" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1784687484" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5B9BD5"/>
-        <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784686762" type="1" fgLvl="100" fgClr="005B9BD5" bgLvl="100" bgClr="00FFFFFF"/>
-          </ext>
-        </extLst>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="none"/>
-    </fill>
   </fills>
-  <borders count="7">
+  <borders count="5">
     <border>
       <left style="none">
         <color rgb="FF000000"/>
@@ -790,7 +755,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784686762"/>
+          <pm:border xmlns:pm="smNativeData" id="1784687484"/>
         </ext>
       </extLst>
     </border>
@@ -809,7 +774,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784686762">
+          <pm:border xmlns:pm="smNativeData" id="1784687484">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
@@ -833,7 +798,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784686762"/>
+          <pm:border xmlns:pm="smNativeData" id="1784687484"/>
         </ext>
       </extLst>
     </border>
@@ -852,69 +817,26 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784686762"/>
+          <pm:border xmlns:pm="smNativeData" id="1784687484"/>
         </ext>
       </extLst>
     </border>
     <border>
       <left style="none">
-        <color rgb="FF1F2329"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="none">
-        <color rgb="FF1F2329"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="none">
-        <color rgb="FF1F2329"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="none">
-        <color rgb="FF1F2329"/>
+        <color rgb="FF000000"/>
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784686762"/>
-        </ext>
-      </extLst>
-    </border>
-    <border>
-      <left style="none">
-        <color rgb="FF1F2329"/>
-      </left>
-      <right style="none">
-        <color rgb="FF1F2329"/>
-      </right>
-      <top style="none">
-        <color rgb="FF1F2329"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF1F2329"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784686762"/>
-        </ext>
-      </extLst>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFDEE0E3"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFDEE0E3"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFDEE0E3"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFDEE0E3"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784686762">
-            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-          </pm:border>
+          <pm:border xmlns:pm="smNativeData" id="1784687484"/>
         </ext>
       </extLst>
     </border>
@@ -925,7 +847,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
@@ -957,16 +879,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -977,10 +893,10 @@
   <tableStyles count="0"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:charStyles xmlns:pm="smNativeData" id="1784686762" count="1">
+      <pm:charStyles xmlns:pm="smNativeData" id="1784687484" count="1">
         <pm:charStyle name="普通" fontId="0" Id="1"/>
       </pm:charStyles>
-      <pm:colors xmlns:pm="smNativeData" id="1784686762" count="9">
+      <pm:colors xmlns:pm="smNativeData" id="1784687484" count="9">
         <pm:color name="颜色 24" rgb="1F2329"/>
         <pm:color name="颜色 25" rgb="ACB9CA"/>
         <pm:color name="颜色 26" rgb="5B9BD5"/>
@@ -1252,7 +1168,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr defaultRowHeight="13.45"/>
   <cols>
     <col min="1" max="1" width="8.663793" customWidth="1" style="2"/>
@@ -2604,38 +2520,61 @@
       <c r="G58" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="H58" s="10" t="s">
+      <c r="H58" s="2" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="59" spans="2:8">
-      <c r="B59" s="11" t="s">
+      <c r="B59" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="C59" s="11" t="s">
+      <c r="C59" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="D59" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="E59" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="F59" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="G59" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="H59" s="11" t="s">
+      <c r="D59" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E59" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="F59" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G59" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H59" s="10" t="s">
         <v>194</v>
+      </c>
+    </row>
+    <row r="60" spans="2:8">
+      <c r="B60" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="C60" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="D60" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E60" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="F60" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G60" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H60" s="10" t="s">
+        <v>197</v>
       </c>
     </row>
   </sheetData>
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1784686762" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1784687484" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -2644,16 +2583,16 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1784686762" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1784686762" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1784686762" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1784686762" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1784687484" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1784687484" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1784687484" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1784687484" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1784686762" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1784687484" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>

--- a/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
@@ -1,16 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
-  <fileSharing readOnlyRecommended="0" userName="Lumino Game 03"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54F9A960-79D8-4C2D-91FB-ED9A95749D54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0" xWindow="240" yWindow="60" windowWidth="38620" windowHeight="21100" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="2500" windowWidth="39220" windowHeight="18380" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext uri="smNativeData">
       <pm:revision xmlns:pm="smNativeData" day="1784687484" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
@@ -23,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="201">
   <si>
     <t>##var</t>
   </si>
@@ -617,85 +622,57 @@
   </si>
   <si>
     <t>钓鱼图鉴面板</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/GarmentMakingCommonUI/GarmentMakingCommonUI.prefab</t>
+  </si>
+  <si>
+    <t>服装制作主界面</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>GarmentMakingCommonUI</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
-    <numFmt numFmtId="5" formatCode="#,##0\ &quot;¥&quot;;\-#,##0\ &quot;¥&quot;"/>
-    <numFmt numFmtId="6" formatCode="#,##0\ &quot;¥&quot;;[Red]\-#,##0\ &quot;¥&quot;"/>
-    <numFmt numFmtId="7" formatCode="#,##0.00\ &quot;¥&quot;;\-#,##0.00\ &quot;¥&quot;"/>
-    <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;¥&quot;;[Red]\-#,##0.00\ &quot;¥&quot;"/>
-    <numFmt numFmtId="42" formatCode="_-* #,##0\ &quot;¥&quot;_-;\-* #,##0\ &quot;¥&quot;_-;_-* &quot;-&quot;\ &quot;¥&quot;_-;_-@_-"/>
-    <numFmt numFmtId="41" formatCode="_-* #,##0\ _¥_-;\-* #,##0\ _¥_-;_-* &quot;-&quot;\ _¥_-;_-@_-"/>
-    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;¥&quot;_-;\-* #,##0.00\ &quot;¥&quot;_-;_-* &quot;-&quot;??\ &quot;¥&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _¥_-;\-* #,##0.00\ _¥_-;_-* &quot;-&quot;??\ _¥_-;_-@_-"/>
-  </numFmts>
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="等线"/>
       <charset val="134"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784687484" ulstyle="none" kern="1">
-            <pm:latin face="等线" sz="220" lang="default"/>
-            <pm:cs face="Times New Roman" sz="220" lang="default"/>
-            <pm:ea face="SimSun" sz="220" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
-      <name val="Arial"/>
-      <family val="2"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
-      <sz val="10"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784687484" ulstyle="none" kern="1">
-            <pm:latin face="Arial" sz="200" lang="default"/>
-            <pm:cs face="Times New Roman" sz="200" lang="default"/>
-            <pm:ea face="SimSun" sz="200" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
+      <name val="等线"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF1F2329"/>
       <name val="等线"/>
-      <charset val="134"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784687484" ulstyle="none" kern="1">
-            <pm:latin face="等线" sz="200" lang="default"/>
-            <pm:cs face="Times New Roman" sz="200" lang="default"/>
-            <pm:ea face="SimSun" sz="200" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="等线"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
-      <color rgb="FF1F2329"/>
-      <sz val="11"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784687484" fgClr="1F2329" ulstyle="none" kern="1">
-            <pm:latin face="等线" sz="220" lang="default"/>
-            <pm:cs face="Times New Roman" sz="220" lang="default"/>
-            <pm:ea face="SimSun" sz="220" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -703,61 +680,25 @@
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
-      <patternFill patternType="none"/>
-    </fill>
-    <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFACB9CA"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784687484" type="1" fgLvl="100" fgClr="00ACB9CA" bgLvl="0" bgClr="00FFFFFF"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF5B9BD5"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784687484" type="1" fgLvl="100" fgClr="005B9BD5" bgLvl="0" bgClr="00FFFFFF"/>
-          </ext>
-        </extLst>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784687484" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="4">
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784687484"/>
-        </ext>
-      </extLst>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -772,126 +713,72 @@
       <bottom style="thin">
         <color rgb="FFDEE0E3"/>
       </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784687484">
-            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-          </pm:border>
-        </ext>
-      </extLst>
+      <diagonal/>
     </border>
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784687484"/>
-        </ext>
-      </extLst>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784687484"/>
-        </ext>
-      </extLst>
-    </border>
-    <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784687484"/>
-        </ext>
-      </extLst>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
-    <cellStyle name="常规 2" xfId="1"/>
+    <cellStyle name="常规" xfId="0" builtinId="0" customBuiltin="1"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0"/>
   <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
     <ext uri="smNativeData">
       <pm:charStyles xmlns:pm="smNativeData" id="1784687484" count="1">
         <pm:charStyle name="普通" fontId="0" Id="1"/>
@@ -1167,1429 +1054,1437 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:H60"/>
-  <sheetFormatPr defaultRowHeight="13.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H61"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.663793" customWidth="1" style="2"/>
-    <col min="2" max="2" width="28.577586" customWidth="1" style="2"/>
-    <col min="3" max="3" width="100.077586" customWidth="1" style="2"/>
-    <col min="4" max="4" width="25.163793" customWidth="1" style="2"/>
-    <col min="5" max="5" width="23.663793" customWidth="1" style="2"/>
-    <col min="6" max="7" width="17.663793" customWidth="1" style="2"/>
-    <col min="8" max="8" width="24.163793" customWidth="1" style="2"/>
-    <col min="9" max="16384" width="8.663793" customWidth="1" style="2"/>
+    <col min="1" max="1" width="8.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="28.58203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="100.08203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="25.1640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="23.6640625" style="1" customWidth="1"/>
+    <col min="6" max="7" width="17.6640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="24.1640625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="4" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="2:8">
-      <c r="B4" s="3" t="s">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G4" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H4" s="2" t="s">
+      <c r="D4" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="2:8">
-      <c r="B5" s="3" t="s">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G5" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H5" s="5" t="s">
+      <c r="D5" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="19.50" customHeight="1">
-      <c r="B6" s="3" t="s">
+    <row r="6" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="8" t="s">
+      <c r="D6" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G6" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H6" s="5" t="s">
+      <c r="F6" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="2:8">
-      <c r="B7" s="3" t="s">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B7" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G7" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H7" s="5" t="s">
+      <c r="D7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="2:8">
-      <c r="B8" s="3" t="s">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G8" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H8" s="5" t="s">
+      <c r="D8" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" s="4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="2:8">
-      <c r="B9" s="3" t="s">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B9" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G9" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H9" s="5" t="s">
+      <c r="D9" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="2:8">
-      <c r="B10" s="3" t="s">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B10" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F10" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G10" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H10" s="5" t="s">
+      <c r="F10" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="2:8">
-      <c r="B11" s="3" t="s">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B11" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="F11" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G11" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H11" s="5" t="s">
+      <c r="F11" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H11" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="12" spans="2:8">
-      <c r="B12" s="3" t="s">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B12" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F12" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G12" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H12" s="5" t="s">
+      <c r="D12" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H12" s="4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="13" spans="2:8">
-      <c r="B13" s="3" t="s">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B13" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F13" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G13" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H13" s="5" t="s">
+      <c r="D13" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" s="4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="14" spans="2:8">
-      <c r="B14" s="3" t="s">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B14" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E14" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="F14" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G14" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H14" s="5" t="s">
+      <c r="F14" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G14" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" s="4" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="15" spans="2:8">
-      <c r="B15" s="3" t="s">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B15" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E15" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F15" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G15" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H15" s="5" t="s">
+      <c r="E15" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H15" s="4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="16" spans="2:8">
-      <c r="B16" s="3" t="s">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B16" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D16" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E16" s="8" t="s">
+      <c r="D16" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F16" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G16" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H16" s="5" t="s">
+      <c r="F16" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H16" s="4" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="17" spans="2:8">
-      <c r="B17" s="3" t="s">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B17" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D17" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F17" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G17" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H17" s="5" t="s">
+      <c r="D17" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G17" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="2:8">
-      <c r="B18" s="3" t="s">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B18" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D18" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E18" s="8" t="s">
+      <c r="D18" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F18" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G18" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H18" s="5" t="s">
+      <c r="F18" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G18" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H18" s="4" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="2:8">
-      <c r="B19" s="3" t="s">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B19" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D19" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F19" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G19" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H19" s="5" t="s">
+      <c r="D19" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F19" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H19" s="4" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="20" spans="2:8">
-      <c r="B20" s="3" t="s">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B20" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="D20" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F20" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G20" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H20" s="5" t="s">
+      <c r="D20" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F20" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" s="4" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="21" spans="2:8">
-      <c r="B21" s="3" t="s">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B21" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="D21" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F21" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G21" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H21" s="5" t="s">
+      <c r="D21" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" s="4" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="22" spans="2:8">
-      <c r="B22" s="3" t="s">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B22" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C22" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="D22" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F22" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G22" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H22" s="5" t="s">
+      <c r="D22" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F22" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H22" s="4" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="23" spans="2:8">
-      <c r="B23" s="3" t="s">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B23" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D23" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F23" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G23" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H23" s="5" t="s">
+      <c r="D23" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H23" s="4" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="24" spans="2:8">
-      <c r="B24" s="3" t="s">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B24" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="D24" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F24" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G24" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H24" s="5" t="s">
+      <c r="D24" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F24" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H24" s="4" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="25" spans="2:8">
-      <c r="B25" s="3" t="s">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B25" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="D25" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F25" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G25" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H25" s="5" t="s">
+      <c r="D25" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F25" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H25" s="4" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="26" spans="2:8">
-      <c r="B26" s="3" t="s">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B26" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="C26" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="D26" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F26" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H26" s="5" t="s">
+      <c r="D26" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F26" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H26" s="4" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="27" spans="2:8">
-      <c r="B27" s="3" t="s">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B27" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="C27" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="D27" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F27" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G27" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H27" s="5" t="s">
+      <c r="D27" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F27" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G27" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H27" s="4" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="28" spans="2:8">
-      <c r="B28" s="3" t="s">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B28" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C28" s="9" t="s">
+      <c r="C28" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="D28" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F28" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G28" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H28" s="5" t="s">
+      <c r="D28" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F28" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G28" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H28" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="29" spans="2:8">
-      <c r="B29" s="3" t="s">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B29" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="D29" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F29" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G29" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H29" s="2" t="s">
+      <c r="D29" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F29" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G29" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H29" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="30" spans="2:8">
-      <c r="B30" s="3" t="s">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B30" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="D30" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F30" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G30" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H30" s="2" t="s">
+      <c r="D30" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F30" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G30" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H30" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="31" spans="2:8">
-      <c r="B31" s="3" t="s">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B31" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="D31" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F31" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G31" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H31" s="2" t="s">
+      <c r="D31" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F31" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G31" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H31" s="1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="32" spans="2:8">
-      <c r="B32" s="3" t="s">
+    <row r="32" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B32" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="D32" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F32" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G32" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H32" s="2" t="s">
+      <c r="D32" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F32" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G32" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H32" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="33" spans="2:8">
-      <c r="B33" s="3" t="s">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B33" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D33" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F33" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G33" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H33" s="2" t="s">
+      <c r="D33" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F33" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G33" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H33" s="1" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="34" spans="2:8">
-      <c r="B34" s="2" t="s">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B34" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="D34" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F34" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G34" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H34" s="2" t="s">
+      <c r="D34" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F34" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G34" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H34" s="1" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="35" spans="2:8">
-      <c r="B35" s="2" t="s">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B35" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="D35" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E35" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F35" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G35" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H35" s="2" t="s">
+      <c r="D35" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F35" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G35" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H35" s="1" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="36" spans="2:8">
-      <c r="B36" s="2" t="s">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B36" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D36" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F36" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G36" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H36" s="2" t="s">
+      <c r="D36" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F36" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G36" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H36" s="1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="37" spans="2:8">
-      <c r="B37" s="2" t="s">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B37" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="D37" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E37" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F37" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G37" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H37" s="2" t="s">
+      <c r="D37" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F37" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G37" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H37" s="1" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="38" spans="2:8">
-      <c r="B38" s="2" t="s">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B38" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="D38" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E38" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F38" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G38" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H38" s="2" t="s">
+      <c r="D38" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F38" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G38" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H38" s="1" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="39" spans="2:8">
-      <c r="B39" s="2" t="s">
+    <row r="39" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B39" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="D39" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E39" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F39" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G39" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H39" s="2" t="s">
+      <c r="D39" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F39" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G39" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H39" s="1" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="40" spans="2:8">
-      <c r="B40" s="2" t="s">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B40" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="D40" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E40" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F40" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G40" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H40" s="2" t="s">
+      <c r="D40" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F40" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G40" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H40" s="1" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="41" spans="2:8">
-      <c r="B41" s="2" t="s">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B41" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C41" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="D41" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E41" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F41" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G41" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H41" s="2" t="s">
+      <c r="D41" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F41" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G41" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H41" s="1" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="42" spans="2:8">
-      <c r="B42" s="2" t="s">
+    <row r="42" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B42" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C42" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D42" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E42" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F42" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G42" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H42" s="2" t="s">
+      <c r="D42" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F42" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G42" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H42" s="1" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="43" spans="2:8">
-      <c r="B43" s="2" t="s">
+    <row r="43" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B43" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C43" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="D43" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E43" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F43" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G43" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H43" s="2" t="s">
+      <c r="D43" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F43" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G43" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H43" s="1" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="44" spans="2:8">
-      <c r="B44" s="2" t="s">
+    <row r="44" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B44" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="C44" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="D44" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E44" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F44" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G44" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H44" s="2" t="s">
+      <c r="D44" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F44" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G44" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H44" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="45" spans="2:8">
-      <c r="B45" s="2" t="s">
+    <row r="45" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B45" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C45" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="D45" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E45" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F45" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G45" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H45" s="2" t="s">
+      <c r="D45" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F45" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G45" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H45" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="46" spans="2:8">
-      <c r="B46" s="2" t="s">
+    <row r="46" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B46" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C46" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="D46" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E46" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F46" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G46" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H46" s="2" t="s">
+      <c r="D46" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F46" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G46" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H46" s="1" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="47" spans="2:8">
-      <c r="B47" s="2" t="s">
+    <row r="47" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B47" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C47" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="D47" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E47" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F47" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G47" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H47" s="2" t="s">
+      <c r="D47" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F47" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G47" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H47" s="1" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="48" spans="2:8">
-      <c r="B48" s="2" t="s">
+    <row r="48" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B48" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C48" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="D48" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E48" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F48" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G48" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H48" s="2" t="s">
+      <c r="D48" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F48" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G48" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H48" s="1" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="49" spans="2:8">
-      <c r="B49" s="2" t="s">
+    <row r="49" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B49" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C49" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="D49" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E49" s="8" t="s">
+      <c r="D49" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E49" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="F49" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G49" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H49" s="2" t="s">
+      <c r="F49" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G49" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H49" s="1" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="50" spans="2:8">
-      <c r="B50" s="2" t="s">
+    <row r="50" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B50" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C50" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D50" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E50" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F50" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G50" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H50" s="2" t="s">
+      <c r="D50" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F50" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G50" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H50" s="1" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="51" spans="2:8">
-      <c r="B51" s="2" t="s">
+    <row r="51" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B51" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="C51" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="D51" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E51" s="8" t="s">
+      <c r="D51" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E51" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="F51" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G51" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H51" s="2" t="s">
+      <c r="F51" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G51" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H51" s="1" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="52" spans="2:8">
-      <c r="B52" s="2" t="s">
+    <row r="52" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B52" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C52" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="D52" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E52" s="8" t="s">
+      <c r="D52" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E52" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="F52" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G52" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H52" s="2" t="s">
+      <c r="F52" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G52" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H52" s="1" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="53" spans="2:8">
-      <c r="B53" s="2" t="s">
+    <row r="53" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B53" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="C53" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="D53" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E53" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F53" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G53" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H53" s="2" t="s">
+      <c r="D53" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F53" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G53" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H53" s="1" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="54" spans="2:8">
-      <c r="B54" s="2" t="s">
+    <row r="54" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B54" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C54" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D54" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E54" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F54" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G54" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H54" s="2" t="s">
+      <c r="D54" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F54" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G54" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H54" s="1" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="55" spans="2:8">
-      <c r="B55" s="2" t="s">
+    <row r="55" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B55" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C55" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="D55" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E55" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F55" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G55" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H55" s="2" t="s">
+      <c r="D55" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F55" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G55" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H55" s="1" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="56" spans="2:8">
-      <c r="B56" s="2" t="s">
+    <row r="56" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B56" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="C56" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="D56" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E56" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F56" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G56" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H56" s="2" t="s">
+      <c r="D56" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E56" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F56" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G56" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H56" s="1" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="57" spans="2:8">
-      <c r="B57" s="2" t="s">
+    <row r="57" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B57" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="C57" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="D57" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E57" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F57" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G57" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H57" s="2" t="s">
+      <c r="D57" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E57" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F57" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G57" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H57" s="1" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="58" spans="2:8">
-      <c r="B58" s="2" t="s">
+    <row r="58" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B58" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="C58" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="D58" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E58" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F58" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G58" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H58" s="2" t="s">
+      <c r="D58" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E58" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F58" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G58" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H58" s="1" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="59" spans="2:8">
-      <c r="B59" s="10" t="s">
+    <row r="59" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B59" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="C59" s="10" t="s">
+      <c r="C59" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="D59" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="E59" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="F59" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G59" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H59" s="10" t="s">
+      <c r="D59" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E59" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F59" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G59" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H59" s="1" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="60" spans="2:8">
-      <c r="B60" s="10" t="s">
+    <row r="60" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B60" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="C60" s="10" t="s">
+      <c r="C60" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="D60" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="E60" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="F60" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G60" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H60" s="10" t="s">
+      <c r="D60" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E60" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F60" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G60" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H60" s="1" t="s">
         <v>197</v>
       </c>
     </row>
+    <row r="61" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B61" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E61" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F61" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G61" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H61" s="9" t="s">
+        <v>199</v>
+      </c>
+    </row>
   </sheetData>
-  <printOptions>
-    <extLst>
-      <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1784687484" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
-      </ext>
-    </extLst>
-  </printOptions>
-  <pageMargins left="0.700000" right="0.700000" top="0.750000" bottom="0.750000" header="0.300000" footer="0.300000"/>
-  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="1"/>
-  <headerFooter>
-    <extLst>
-      <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1784687484" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1784687484" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1784687484" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1784687484" Id="1" type="0" value="0"/>
-      </ext>
-    </extLst>
-  </headerFooter>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" fitToWidth="0"/>
   <extLst>
     <ext uri="smNativeData">
       <pm:sheetPrefs xmlns:pm="smNativeData" day="1784687484" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">

--- a/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54F9A960-79D8-4C2D-91FB-ED9A95749D54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA9B60F5-56D1-4E48-A391-FE01AAB6321A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="2500" windowWidth="39220" windowHeight="18380" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="204">
   <si>
     <t>##var</t>
   </si>
@@ -632,6 +632,16 @@
   </si>
   <si>
     <t>GarmentMakingCommonUI</t>
+  </si>
+  <si>
+    <t>GarmentMakingUI</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/GarmentMakingUI/GarmentMakingUI.prefab</t>
+  </si>
+  <si>
+    <t>服装制作界面</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1055,7 +1065,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H62"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.6640625" style="1" customWidth="1"/>
@@ -2481,6 +2491,29 @@
         <v>199</v>
       </c>
     </row>
+    <row r="62" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B62" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E62" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F62" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G62" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H62" s="9" t="s">
+        <v>203</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA9B60F5-56D1-4E48-A391-FE01AAB6321A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BB153D7-13C6-41E2-9A67-85D48983CC5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2500" windowWidth="39220" windowHeight="18380" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3130" yWindow="1270" windowWidth="26660" windowHeight="18380" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="207">
   <si>
     <t>##var</t>
   </si>
@@ -641,6 +641,18 @@
   </si>
   <si>
     <t>服装制作界面</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>打板游戏界面</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ClothingPatternMakingUI</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/ClothinPatternMakingUI/ClothingPatternMakingUI.prefab</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1065,7 +1077,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.6640625" style="1" customWidth="1"/>
@@ -2514,6 +2526,29 @@
         <v>203</v>
       </c>
     </row>
+    <row r="63" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B63" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="C63" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E63" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F63" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G63" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H63" s="9" t="s">
+        <v>204</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BB153D7-13C6-41E2-9A67-85D48983CC5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBE05495-D863-48EF-8690-9F6891A46E36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3130" yWindow="1270" windowWidth="26660" windowHeight="18380" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="210">
   <si>
     <t>##var</t>
   </si>
@@ -653,6 +653,16 @@
   </si>
   <si>
     <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/ClothinPatternMakingUI/ClothingPatternMakingUI.prefab</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/PopCompleteWindow/PopCompleteWindow.prefab</t>
+  </si>
+  <si>
+    <t>PopCompleteWindow</t>
+  </si>
+  <si>
+    <t>通用完成界面</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1077,7 +1087,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H63"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.6640625" style="1" customWidth="1"/>
@@ -2549,6 +2559,29 @@
         <v>204</v>
       </c>
     </row>
+    <row r="64" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B64" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E64" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F64" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G64" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H64" s="9" t="s">
+        <v>209</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBE05495-D863-48EF-8690-9F6891A46E36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6595997-8038-4A6B-A72F-2F702C0F5DE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3130" yWindow="1270" windowWidth="26660" windowHeight="18380" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="213">
   <si>
     <t>##var</t>
   </si>
@@ -664,6 +664,16 @@
   <si>
     <t>通用完成界面</t>
     <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>PopFailWindows</t>
+  </si>
+  <si>
+    <t>通用失败界面</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/PopFailWindows/PopFailWindows.prefab</t>
   </si>
 </sst>
 </file>
@@ -1087,7 +1097,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:H65"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.6640625" style="1" customWidth="1"/>
@@ -2582,6 +2592,29 @@
         <v>209</v>
       </c>
     </row>
+    <row r="65" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B65" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E65" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F65" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G65" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H65" s="9" t="s">
+        <v>211</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6595997-8038-4A6B-A72F-2F702C0F5DE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDF6DFEA-75D8-44A5-89A5-BF340EF58C3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3130" yWindow="1270" windowWidth="26660" windowHeight="18380" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3520" yWindow="1160" windowWidth="31320" windowHeight="18380" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="216">
   <si>
     <t>##var</t>
   </si>
@@ -674,6 +674,16 @@
   </si>
   <si>
     <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/PopFailWindows/PopFailWindows.prefab</t>
+  </si>
+  <si>
+    <t>SewingMachineUI</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/SewingMachineUI/SewingMachineUI.prefab</t>
+  </si>
+  <si>
+    <t>熨斗小游戏</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1097,7 +1107,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H65"/>
+  <dimension ref="A1:H66"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.6640625" style="1" customWidth="1"/>
@@ -2615,6 +2625,29 @@
         <v>211</v>
       </c>
     </row>
+    <row r="66" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B66" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E66" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F66" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G66" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H66" s="9" t="s">
+        <v>215</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
@@ -1,34 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
+  <fileSharing readOnlyRecommended="0" userName="Lumino Game 03"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDF6DFEA-75D8-44A5-89A5-BF340EF58C3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3520" yWindow="1160" windowWidth="31320" windowHeight="18380" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView activeTab="0" xWindow="240" yWindow="60" windowWidth="31320" windowHeight="18380" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:revision xmlns:pm="smNativeData" day="1784687484" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
-      <pm:docPrefs xmlns:pm="smNativeData" id="1784687484" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
-      <pm:compatibility xmlns:pm="smNativeData" id="1784687484" overlapCells="1"/>
-      <pm:defCurrency xmlns:pm="smNativeData" id="1784687484"/>
+      <pm:revision xmlns:pm="smNativeData" day="1785202857" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
+      <pm:docPrefs xmlns:pm="smNativeData" id="1785202857" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
+      <pm:compatibility xmlns:pm="smNativeData" id="1785202857" overlapCells="1"/>
+      <pm:defCurrency xmlns:pm="smNativeData" id="1785202857"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="219">
   <si>
     <t>##var</t>
   </si>
@@ -624,14 +619,13 @@
     <t>钓鱼图鉴面板</t>
   </si>
   <si>
+    <t>GarmentMakingCommonUI</t>
+  </si>
+  <si>
     <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/GarmentMakingCommonUI/GarmentMakingCommonUI.prefab</t>
   </si>
   <si>
     <t>服装制作主界面</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>GarmentMakingCommonUI</t>
   </si>
   <si>
     <t>GarmentMakingUI</t>
@@ -641,39 +635,33 @@
   </si>
   <si>
     <t>服装制作界面</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ClothingPatternMakingUI</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/ClothinPatternMakingUI/ClothingPatternMakingUI.prefab</t>
   </si>
   <si>
     <t>打板游戏界面</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>ClothingPatternMakingUI</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/ClothinPatternMakingUI/ClothingPatternMakingUI.prefab</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>PopCompleteWindow</t>
   </si>
   <si>
     <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/PopCompleteWindow/PopCompleteWindow.prefab</t>
   </si>
   <si>
-    <t>PopCompleteWindow</t>
-  </si>
-  <si>
     <t>通用完成界面</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>PopFailWindows</t>
   </si>
   <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/PopFailWindows/PopFailWindows.prefab</t>
+  </si>
+  <si>
     <t>通用失败界面</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/PopFailWindows/PopFailWindows.prefab</t>
   </si>
   <si>
     <t>SewingMachineUI</t>
@@ -683,48 +671,94 @@
   </si>
   <si>
     <t>熨斗小游戏</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>MachiRoomGamePanel</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/MachiRoom/MachiRoomGamePanel.prefab</t>
+  </si>
+  <si>
+    <t>马吉房间游戏面板</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="8">
+    <numFmt numFmtId="5" formatCode="#,##0\ &quot;¥&quot;;\-#,##0\ &quot;¥&quot;"/>
+    <numFmt numFmtId="6" formatCode="#,##0\ &quot;¥&quot;;[Red]\-#,##0\ &quot;¥&quot;"/>
+    <numFmt numFmtId="7" formatCode="#,##0.00\ &quot;¥&quot;;\-#,##0.00\ &quot;¥&quot;"/>
+    <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;¥&quot;;[Red]\-#,##0.00\ &quot;¥&quot;"/>
+    <numFmt numFmtId="42" formatCode="_-* #,##0\ &quot;¥&quot;_-;\-* #,##0\ &quot;¥&quot;_-;_-* &quot;-&quot;\ &quot;¥&quot;_-;_-@_-"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0\ _¥_-;\-* #,##0\ _¥_-;_-* &quot;-&quot;\ _¥_-;_-@_-"/>
+    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;¥&quot;_-;\-* #,##0.00\ &quot;¥&quot;_-;_-* &quot;-&quot;??\ &quot;¥&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _¥_-;\-* #,##0.00\ _¥_-;_-* &quot;-&quot;??\ _¥_-;_-@_-"/>
+  </numFmts>
+  <fonts count="4">
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="等线"/>
       <charset val="134"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1785202857" ulstyle="none" kern="1">
+            <pm:latin face="等线" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1785202857" ulstyle="none" kern="1">
+            <pm:latin face="Arial" sz="200" lang="default"/>
+            <pm:cs face="Times New Roman" sz="200" lang="default"/>
+            <pm:ea face="SimSun" sz="200" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF1F2329"/>
       <name val="等线"/>
+      <charset val="134"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1785202857" ulstyle="none" kern="1">
+            <pm:latin face="等线" sz="200" lang="default"/>
+            <pm:cs face="Times New Roman" sz="200" lang="default"/>
+            <pm:ea face="SimSun" sz="200" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <color rgb="FF1F2329"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1785202857" fgClr="1F2329" ulstyle="none" kern="1">
+            <pm:latin face="等线" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -732,25 +766,61 @@
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFACB9CA"/>
         <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1785202857" type="1" fgLvl="100" fgClr="00ACB9CA" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF5B9BD5"/>
         <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1785202857" type="1" fgLvl="100" fgClr="005B9BD5" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1785202857" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1785202857"/>
+        </ext>
+      </extLst>
     </border>
     <border>
       <left style="thin">
@@ -765,86 +835,129 @@
       <bottom style="thin">
         <color rgb="FFDEE0E3"/>
       </bottom>
-      <diagonal/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1785202857">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+          </pm:border>
+        </ext>
+      </extLst>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1785202857"/>
+        </ext>
+      </extLst>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1785202857"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1785202857"/>
+        </ext>
+      </extLst>
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="常规" xfId="0" builtinId="0" customBuiltin="1"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
+    <cellStyle name="常规 2" xfId="1"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
     <ext uri="smNativeData">
-      <pm:charStyles xmlns:pm="smNativeData" id="1784687484" count="1">
+      <pm:charStyles xmlns:pm="smNativeData" id="1785202857" count="1">
         <pm:charStyle name="普通" fontId="0" Id="1"/>
       </pm:charStyles>
-      <pm:colors xmlns:pm="smNativeData" id="1784687484" count="9">
+      <pm:colors xmlns:pm="smNativeData" id="1785202857" count="4">
         <pm:color name="颜色 24" rgb="1F2329"/>
         <pm:color name="颜色 25" rgb="ACB9CA"/>
         <pm:color name="颜色 26" rgb="5B9BD5"/>
         <pm:color name="颜色 27" rgb="DEE0E3"/>
-        <pm:color name="黑色" rgb="000000"/>
-        <pm:color name="颜色 32" rgb="ACB9CA"/>
-        <pm:color name="颜色 50" rgb="5B9BD5"/>
-        <pm:color name="颜色 51" rgb="1F2329"/>
-        <pm:color name="颜色 52" rgb="DEE0E3"/>
       </pm:colors>
     </ext>
   </extLst>
@@ -1106,1555 +1219,1593 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H66"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <dimension ref="A1:H67"/>
+  <sheetFormatPr defaultRowHeight="13.45"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="28.58203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="100.08203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="25.1640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="23.6640625" style="1" customWidth="1"/>
-    <col min="6" max="7" width="17.6640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="24.1640625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="8.6640625" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.6640625" style="1"/>
+    <col min="1" max="1" width="8.663793" customWidth="1" style="2"/>
+    <col min="2" max="2" width="28.577586" customWidth="1" style="2"/>
+    <col min="3" max="3" width="100.077586" customWidth="1" style="2"/>
+    <col min="4" max="4" width="25.163793" customWidth="1" style="2"/>
+    <col min="5" max="5" width="23.663793" customWidth="1" style="2"/>
+    <col min="6" max="7" width="17.663793" customWidth="1" style="2"/>
+    <col min="8" max="8" width="24.163793" customWidth="1" style="2"/>
+    <col min="9" max="16384" width="8.663793" customWidth="1" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
+    <row r="1" spans="1:8">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:8">
+      <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:8">
+      <c r="A3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B4" s="2" t="s">
+    <row r="4" spans="2:8">
+      <c r="B4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G4" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H4" s="1" t="s">
+      <c r="D4" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B5" s="2" t="s">
+    <row r="5" spans="2:8">
+      <c r="B5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G5" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H5" s="4" t="s">
+      <c r="D5" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="2" t="s">
+    <row r="6" spans="2:8" ht="19.50" customHeight="1">
+      <c r="B6" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="7" t="s">
+      <c r="D6" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G6" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H6" s="4" t="s">
+      <c r="F6" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B7" s="2" t="s">
+    <row r="7" spans="2:8">
+      <c r="B7" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G7" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H7" s="4" t="s">
+      <c r="D7" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B8" s="2" t="s">
+    <row r="8" spans="2:8">
+      <c r="B8" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G8" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H8" s="4" t="s">
+      <c r="D8" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" s="5" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B9" s="2" t="s">
+    <row r="9" spans="2:8">
+      <c r="B9" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G9" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H9" s="4" t="s">
+      <c r="D9" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" s="5" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B10" s="2" t="s">
+    <row r="10" spans="2:8">
+      <c r="B10" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="F10" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G10" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H10" s="4" t="s">
+      <c r="F10" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B11" s="2" t="s">
+    <row r="11" spans="2:8">
+      <c r="B11" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="F11" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G11" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H11" s="4" t="s">
+      <c r="F11" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H11" s="5" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B12" s="2" t="s">
+    <row r="12" spans="2:8">
+      <c r="B12" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F12" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G12" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H12" s="4" t="s">
+      <c r="D12" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H12" s="5" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B13" s="2" t="s">
+    <row r="13" spans="2:8">
+      <c r="B13" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D13" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F13" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G13" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H13" s="4" t="s">
+      <c r="D13" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" s="5" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B14" s="2" t="s">
+    <row r="14" spans="2:8">
+      <c r="B14" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="F14" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G14" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H14" s="4" t="s">
+      <c r="F14" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G14" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" s="5" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B15" s="2" t="s">
+    <row r="15" spans="2:8">
+      <c r="B15" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E15" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F15" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G15" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H15" s="4" t="s">
+      <c r="E15" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H15" s="5" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B16" s="2" t="s">
+    <row r="16" spans="2:8">
+      <c r="B16" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="D16" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E16" s="7" t="s">
+      <c r="D16" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F16" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G16" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H16" s="4" t="s">
+      <c r="F16" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H16" s="5" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B17" s="2" t="s">
+    <row r="17" spans="2:8">
+      <c r="B17" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="D17" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F17" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G17" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H17" s="4" t="s">
+      <c r="D17" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G17" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B18" s="2" t="s">
+    <row r="18" spans="2:8">
+      <c r="B18" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="D18" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E18" s="7" t="s">
+      <c r="D18" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F18" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G18" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H18" s="4" t="s">
+      <c r="F18" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G18" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H18" s="5" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B19" s="2" t="s">
+    <row r="19" spans="2:8">
+      <c r="B19" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="D19" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F19" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G19" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H19" s="4" t="s">
+      <c r="D19" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F19" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H19" s="5" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B20" s="2" t="s">
+    <row r="20" spans="2:8">
+      <c r="B20" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="D20" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F20" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G20" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H20" s="4" t="s">
+      <c r="D20" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F20" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" s="5" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B21" s="2" t="s">
+    <row r="21" spans="2:8">
+      <c r="B21" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="D21" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F21" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G21" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H21" s="4" t="s">
+      <c r="D21" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" s="5" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B22" s="2" t="s">
+    <row r="22" spans="2:8">
+      <c r="B22" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="D22" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F22" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G22" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H22" s="4" t="s">
+      <c r="D22" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F22" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H22" s="5" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B23" s="2" t="s">
+    <row r="23" spans="2:8">
+      <c r="B23" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="D23" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F23" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G23" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H23" s="4" t="s">
+      <c r="D23" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H23" s="5" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B24" s="2" t="s">
+    <row r="24" spans="2:8">
+      <c r="B24" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="D24" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F24" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G24" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H24" s="4" t="s">
+      <c r="D24" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F24" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H24" s="5" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B25" s="2" t="s">
+    <row r="25" spans="2:8">
+      <c r="B25" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="D25" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F25" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G25" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H25" s="4" t="s">
+      <c r="D25" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F25" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H25" s="5" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B26" s="2" t="s">
+    <row r="26" spans="2:8">
+      <c r="B26" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C26" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="D26" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F26" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H26" s="4" t="s">
+      <c r="D26" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F26" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H26" s="5" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B27" s="2" t="s">
+    <row r="27" spans="2:8">
+      <c r="B27" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="D27" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F27" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G27" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H27" s="4" t="s">
+      <c r="D27" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F27" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G27" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H27" s="5" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B28" s="2" t="s">
+    <row r="28" spans="2:8">
+      <c r="B28" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="C28" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="D28" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F28" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G28" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H28" s="4" t="s">
+      <c r="D28" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F28" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G28" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H28" s="5" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B29" s="2" t="s">
+    <row r="29" spans="2:8">
+      <c r="B29" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D29" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F29" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G29" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H29" s="1" t="s">
+      <c r="D29" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F29" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G29" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H29" s="2" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B30" s="2" t="s">
+    <row r="30" spans="2:8">
+      <c r="B30" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="D30" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F30" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G30" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H30" s="1" t="s">
+      <c r="D30" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F30" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G30" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H30" s="2" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B31" s="2" t="s">
+    <row r="31" spans="2:8">
+      <c r="B31" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="D31" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F31" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G31" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H31" s="1" t="s">
+      <c r="D31" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F31" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G31" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H31" s="2" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B32" s="2" t="s">
+    <row r="32" spans="2:8">
+      <c r="B32" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="D32" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F32" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G32" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H32" s="1" t="s">
+      <c r="D32" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F32" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G32" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H32" s="2" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B33" s="2" t="s">
+    <row r="33" spans="2:8">
+      <c r="B33" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D33" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F33" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G33" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H33" s="1" t="s">
+      <c r="D33" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F33" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G33" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H33" s="2" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B34" s="1" t="s">
+    <row r="34" spans="2:8">
+      <c r="B34" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="D34" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E34" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F34" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G34" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H34" s="1" t="s">
+      <c r="D34" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F34" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G34" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H34" s="2" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B35" s="1" t="s">
+    <row r="35" spans="2:8">
+      <c r="B35" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="D35" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F35" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G35" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H35" s="1" t="s">
+      <c r="D35" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F35" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G35" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H35" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B36" s="1" t="s">
+    <row r="36" spans="2:8">
+      <c r="B36" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="D36" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F36" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G36" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H36" s="1" t="s">
+      <c r="D36" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F36" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G36" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H36" s="2" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B37" s="1" t="s">
+    <row r="37" spans="2:8">
+      <c r="B37" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="D37" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F37" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G37" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H37" s="1" t="s">
+      <c r="D37" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F37" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G37" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H37" s="2" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B38" s="1" t="s">
+    <row r="38" spans="2:8">
+      <c r="B38" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="D38" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E38" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F38" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G38" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H38" s="1" t="s">
+      <c r="D38" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F38" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G38" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H38" s="2" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B39" s="1" t="s">
+    <row r="39" spans="2:8">
+      <c r="B39" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="D39" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E39" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F39" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G39" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H39" s="1" t="s">
+      <c r="D39" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F39" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G39" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H39" s="2" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B40" s="1" t="s">
+    <row r="40" spans="2:8">
+      <c r="B40" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="D40" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E40" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F40" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G40" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H40" s="1" t="s">
+      <c r="D40" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F40" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G40" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H40" s="2" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B41" s="1" t="s">
+    <row r="41" spans="2:8">
+      <c r="B41" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="D41" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E41" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F41" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G41" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H41" s="1" t="s">
+      <c r="D41" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F41" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G41" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H41" s="2" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B42" s="1" t="s">
+    <row r="42" spans="2:8">
+      <c r="B42" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C42" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="D42" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E42" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F42" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G42" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H42" s="1" t="s">
+      <c r="D42" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F42" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G42" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H42" s="2" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B43" s="1" t="s">
+    <row r="43" spans="2:8">
+      <c r="B43" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C43" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="D43" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E43" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F43" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G43" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H43" s="1" t="s">
+      <c r="D43" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F43" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G43" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H43" s="2" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B44" s="1" t="s">
+    <row r="44" spans="2:8">
+      <c r="B44" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C44" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="D44" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E44" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F44" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G44" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H44" s="1" t="s">
+      <c r="D44" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F44" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G44" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H44" s="2" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B45" s="1" t="s">
+    <row r="45" spans="2:8">
+      <c r="B45" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C45" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="D45" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E45" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F45" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G45" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H45" s="1" t="s">
+      <c r="D45" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F45" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G45" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H45" s="2" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B46" s="1" t="s">
+    <row r="46" spans="2:8">
+      <c r="B46" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C46" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="D46" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E46" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F46" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G46" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H46" s="1" t="s">
+      <c r="D46" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F46" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G46" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H46" s="2" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B47" s="1" t="s">
+    <row r="47" spans="2:8">
+      <c r="B47" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C47" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="D47" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E47" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F47" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G47" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H47" s="1" t="s">
+      <c r="D47" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F47" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G47" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H47" s="2" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B48" s="1" t="s">
+    <row r="48" spans="2:8">
+      <c r="B48" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="C48" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="D48" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E48" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F48" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G48" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H48" s="1" t="s">
+      <c r="D48" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F48" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G48" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H48" s="2" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="49" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B49" s="1" t="s">
+    <row r="49" spans="2:8">
+      <c r="B49" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C49" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="D49" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E49" s="7" t="s">
+      <c r="D49" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E49" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="F49" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G49" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H49" s="1" t="s">
+      <c r="F49" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G49" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H49" s="2" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="50" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B50" s="1" t="s">
+    <row r="50" spans="2:8">
+      <c r="B50" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="C50" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="D50" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E50" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F50" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G50" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H50" s="1" t="s">
+      <c r="D50" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F50" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G50" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H50" s="2" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="51" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B51" s="1" t="s">
+    <row r="51" spans="2:8">
+      <c r="B51" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="C51" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="D51" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E51" s="7" t="s">
+      <c r="D51" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E51" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="F51" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G51" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H51" s="1" t="s">
+      <c r="F51" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G51" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H51" s="2" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="52" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B52" s="1" t="s">
+    <row r="52" spans="2:8">
+      <c r="B52" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="C52" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="D52" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E52" s="7" t="s">
+      <c r="D52" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E52" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="F52" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G52" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H52" s="1" t="s">
+      <c r="F52" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G52" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H52" s="2" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="53" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B53" s="1" t="s">
+    <row r="53" spans="2:8">
+      <c r="B53" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="C53" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="D53" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E53" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F53" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G53" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H53" s="1" t="s">
+      <c r="D53" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F53" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G53" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H53" s="2" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="54" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B54" s="1" t="s">
+    <row r="54" spans="2:8">
+      <c r="B54" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="C54" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="D54" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E54" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F54" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G54" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H54" s="1" t="s">
+      <c r="D54" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F54" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G54" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H54" s="2" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="55" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B55" s="1" t="s">
+    <row r="55" spans="2:8">
+      <c r="B55" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="C55" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="D55" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E55" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F55" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G55" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H55" s="1" t="s">
+      <c r="D55" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F55" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G55" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H55" s="2" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="56" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B56" s="1" t="s">
+    <row r="56" spans="2:8">
+      <c r="B56" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="C56" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="D56" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E56" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F56" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G56" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H56" s="1" t="s">
+      <c r="D56" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F56" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G56" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H56" s="2" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="57" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B57" s="1" t="s">
+    <row r="57" spans="2:8">
+      <c r="B57" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="C57" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="D57" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E57" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F57" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G57" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H57" s="1" t="s">
+      <c r="D57" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F57" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G57" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H57" s="2" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="58" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B58" s="1" t="s">
+    <row r="58" spans="2:8">
+      <c r="B58" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="C58" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="D58" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E58" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F58" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G58" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H58" s="1" t="s">
+      <c r="D58" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F58" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G58" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H58" s="2" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="59" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B59" s="1" t="s">
+    <row r="59" spans="2:8">
+      <c r="B59" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="C59" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="D59" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E59" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F59" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G59" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H59" s="1" t="s">
+      <c r="D59" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E59" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F59" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G59" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H59" s="2" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="60" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B60" s="1" t="s">
+    <row r="60" spans="2:8">
+      <c r="B60" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="C60" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="D60" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E60" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F60" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G60" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H60" s="1" t="s">
+      <c r="D60" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E60" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F60" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G60" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H60" s="2" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="61" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B61" s="1" t="s">
+    <row r="61" spans="2:8">
+      <c r="B61" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D61" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E61" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F61" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G61" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H61" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="C61" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="D61" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E61" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F61" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G61" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H61" s="9" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="62" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B62" s="1" t="s">
+    </row>
+    <row r="62" spans="2:8">
+      <c r="B62" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="C62" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="D62" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E62" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F62" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G62" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H62" s="9" t="s">
+      <c r="D62" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E62" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F62" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G62" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H62" s="10" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="63" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B63" s="9" t="s">
+    <row r="63" spans="2:8">
+      <c r="B63" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="C63" s="10" t="s">
         <v>205</v>
       </c>
-      <c r="C63" s="9" t="s">
+      <c r="D63" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E63" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F63" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G63" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H63" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="D63" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E63" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F63" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G63" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H63" s="9" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="64" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B64" s="1" t="s">
+    </row>
+    <row r="64" spans="2:8">
+      <c r="B64" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C64" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="C64" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="D64" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E64" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F64" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G64" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H64" s="9" t="s">
+      <c r="D64" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E64" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F64" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G64" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H64" s="10" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="65" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B65" s="1" t="s">
+    <row r="65" spans="2:8">
+      <c r="B65" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="C65" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D65" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E65" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F65" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G65" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H65" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="D65" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E65" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F65" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G65" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H65" s="9" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="66" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B66" s="1" t="s">
+    </row>
+    <row r="66" spans="2:8">
+      <c r="B66" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="C66" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="D66" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E66" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F66" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G66" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H66" s="9" t="s">
+      <c r="D66" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E66" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F66" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G66" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H66" s="10" t="s">
         <v>215</v>
       </c>
     </row>
+    <row r="67" spans="2:8">
+      <c r="B67" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D67" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E67" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F67" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G67" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H67" s="10" t="s">
+        <v>218</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" fitToWidth="0"/>
+  <printOptions>
+    <extLst>
+      <ext uri="smNativeData">
+        <pm:pageFlags xmlns:pm="smNativeData" id="1785202857" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+      </ext>
+    </extLst>
+  </printOptions>
+  <pageMargins left="0.700000" right="0.700000" top="0.750000" bottom="0.750000" header="0.300000" footer="0.300000"/>
+  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="1"/>
+  <headerFooter>
+    <extLst>
+      <ext uri="smNativeData">
+        <pm:header xmlns:pm="smNativeData" id="1785202857" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1785202857" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1785202857" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1785202857" Id="1" type="0" value="0"/>
+      </ext>
+    </extLst>
+  </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1784687484" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1785202857" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>

--- a/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
@@ -1,16 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
-  <fileSharing readOnlyRecommended="0" userName="Lumino Game 03"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0823E4D-08CD-4437-8E98-7226310CE2EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0" xWindow="240" yWindow="60" windowWidth="31320" windowHeight="18380" tabRatio="500"/>
+    <workbookView xWindow="3520" yWindow="1160" windowWidth="31320" windowHeight="18380" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext uri="smNativeData">
       <pm:revision xmlns:pm="smNativeData" day="1785202857" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
@@ -23,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="222">
   <si>
     <t>##var</t>
   </si>
@@ -680,85 +685,57 @@
   </si>
   <si>
     <t>马吉房间游戏面板</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/PuzzleUI/Prefabs/PuzzleUI.prefab</t>
+  </si>
+  <si>
+    <t>PuzzleUI</t>
+  </si>
+  <si>
+    <t>拼图小游戏</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
-    <numFmt numFmtId="5" formatCode="#,##0\ &quot;¥&quot;;\-#,##0\ &quot;¥&quot;"/>
-    <numFmt numFmtId="6" formatCode="#,##0\ &quot;¥&quot;;[Red]\-#,##0\ &quot;¥&quot;"/>
-    <numFmt numFmtId="7" formatCode="#,##0.00\ &quot;¥&quot;;\-#,##0.00\ &quot;¥&quot;"/>
-    <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;¥&quot;;[Red]\-#,##0.00\ &quot;¥&quot;"/>
-    <numFmt numFmtId="42" formatCode="_-* #,##0\ &quot;¥&quot;_-;\-* #,##0\ &quot;¥&quot;_-;_-* &quot;-&quot;\ &quot;¥&quot;_-;_-@_-"/>
-    <numFmt numFmtId="41" formatCode="_-* #,##0\ _¥_-;\-* #,##0\ _¥_-;_-* &quot;-&quot;\ _¥_-;_-@_-"/>
-    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;¥&quot;_-;\-* #,##0.00\ &quot;¥&quot;_-;_-* &quot;-&quot;??\ &quot;¥&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _¥_-;\-* #,##0.00\ _¥_-;_-* &quot;-&quot;??\ _¥_-;_-@_-"/>
-  </numFmts>
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="等线"/>
       <charset val="134"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1785202857" ulstyle="none" kern="1">
-            <pm:latin face="等线" sz="220" lang="default"/>
-            <pm:cs face="Times New Roman" sz="220" lang="default"/>
-            <pm:ea face="SimSun" sz="220" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
-      <name val="Arial"/>
-      <family val="2"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
-      <sz val="10"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1785202857" ulstyle="none" kern="1">
-            <pm:latin face="Arial" sz="200" lang="default"/>
-            <pm:cs face="Times New Roman" sz="200" lang="default"/>
-            <pm:ea face="SimSun" sz="200" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
+      <name val="等线"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF1F2329"/>
       <name val="等线"/>
-      <charset val="134"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1785202857" ulstyle="none" kern="1">
-            <pm:latin face="等线" sz="200" lang="default"/>
-            <pm:cs face="Times New Roman" sz="200" lang="default"/>
-            <pm:ea face="SimSun" sz="200" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="等线"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
-      <color rgb="FF1F2329"/>
-      <sz val="11"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1785202857" fgClr="1F2329" ulstyle="none" kern="1">
-            <pm:latin face="等线" sz="220" lang="default"/>
-            <pm:cs face="Times New Roman" sz="220" lang="default"/>
-            <pm:ea face="SimSun" sz="220" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -766,61 +743,25 @@
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
-      <patternFill patternType="none"/>
-    </fill>
-    <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFACB9CA"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1785202857" type="1" fgLvl="100" fgClr="00ACB9CA" bgLvl="0" bgClr="00FFFFFF"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF5B9BD5"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1785202857" type="1" fgLvl="100" fgClr="005B9BD5" bgLvl="0" bgClr="00FFFFFF"/>
-          </ext>
-        </extLst>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1785202857" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="4">
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1785202857"/>
-        </ext>
-      </extLst>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -835,120 +776,72 @@
       <bottom style="thin">
         <color rgb="FFDEE0E3"/>
       </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1785202857">
-            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-          </pm:border>
-        </ext>
-      </extLst>
+      <diagonal/>
     </border>
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1785202857"/>
-        </ext>
-      </extLst>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1785202857"/>
-        </ext>
-      </extLst>
-    </border>
-    <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1785202857"/>
-        </ext>
-      </extLst>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
-    <cellStyle name="常规 2" xfId="1"/>
+    <cellStyle name="常规" xfId="0" builtinId="0" customBuiltin="1"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0"/>
   <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
     <ext uri="smNativeData">
       <pm:charStyles xmlns:pm="smNativeData" id="1785202857" count="1">
         <pm:charStyle name="普通" fontId="0" Id="1"/>
@@ -1219,1590 +1112,1598 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:H67"/>
-  <sheetFormatPr defaultRowHeight="13.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H68"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.663793" customWidth="1" style="2"/>
-    <col min="2" max="2" width="28.577586" customWidth="1" style="2"/>
-    <col min="3" max="3" width="100.077586" customWidth="1" style="2"/>
-    <col min="4" max="4" width="25.163793" customWidth="1" style="2"/>
-    <col min="5" max="5" width="23.663793" customWidth="1" style="2"/>
-    <col min="6" max="7" width="17.663793" customWidth="1" style="2"/>
-    <col min="8" max="8" width="24.163793" customWidth="1" style="2"/>
-    <col min="9" max="16384" width="8.663793" customWidth="1" style="2"/>
+    <col min="1" max="1" width="8.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="28.58203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="100.08203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="25.1640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="23.6640625" style="1" customWidth="1"/>
+    <col min="6" max="7" width="17.6640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="24.1640625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="4" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="2:8">
-      <c r="B4" s="3" t="s">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G4" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H4" s="2" t="s">
+      <c r="D4" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="2:8">
-      <c r="B5" s="3" t="s">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G5" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H5" s="5" t="s">
+      <c r="D5" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="19.50" customHeight="1">
-      <c r="B6" s="3" t="s">
+    <row r="6" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="8" t="s">
+      <c r="D6" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G6" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H6" s="5" t="s">
+      <c r="F6" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="2:8">
-      <c r="B7" s="3" t="s">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B7" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G7" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H7" s="5" t="s">
+      <c r="D7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="2:8">
-      <c r="B8" s="3" t="s">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G8" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H8" s="5" t="s">
+      <c r="D8" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" s="4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="2:8">
-      <c r="B9" s="3" t="s">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B9" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G9" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H9" s="5" t="s">
+      <c r="D9" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="2:8">
-      <c r="B10" s="3" t="s">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B10" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F10" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G10" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H10" s="5" t="s">
+      <c r="F10" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="2:8">
-      <c r="B11" s="3" t="s">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B11" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="F11" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G11" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H11" s="5" t="s">
+      <c r="F11" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H11" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="12" spans="2:8">
-      <c r="B12" s="3" t="s">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B12" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F12" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G12" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H12" s="5" t="s">
+      <c r="D12" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H12" s="4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="13" spans="2:8">
-      <c r="B13" s="3" t="s">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B13" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F13" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G13" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H13" s="5" t="s">
+      <c r="D13" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" s="4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="14" spans="2:8">
-      <c r="B14" s="3" t="s">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B14" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E14" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="F14" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G14" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H14" s="5" t="s">
+      <c r="F14" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G14" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" s="4" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="15" spans="2:8">
-      <c r="B15" s="3" t="s">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B15" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E15" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F15" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G15" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H15" s="5" t="s">
+      <c r="E15" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H15" s="4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="16" spans="2:8">
-      <c r="B16" s="3" t="s">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B16" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D16" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E16" s="8" t="s">
+      <c r="D16" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F16" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G16" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H16" s="5" t="s">
+      <c r="F16" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H16" s="4" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="17" spans="2:8">
-      <c r="B17" s="3" t="s">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B17" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D17" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F17" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G17" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H17" s="5" t="s">
+      <c r="D17" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G17" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="2:8">
-      <c r="B18" s="3" t="s">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B18" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D18" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E18" s="8" t="s">
+      <c r="D18" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F18" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G18" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H18" s="5" t="s">
+      <c r="F18" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G18" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H18" s="4" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="2:8">
-      <c r="B19" s="3" t="s">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B19" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D19" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F19" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G19" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H19" s="5" t="s">
+      <c r="D19" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F19" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H19" s="4" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="20" spans="2:8">
-      <c r="B20" s="3" t="s">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B20" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="D20" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F20" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G20" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H20" s="5" t="s">
+      <c r="D20" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F20" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" s="4" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="21" spans="2:8">
-      <c r="B21" s="3" t="s">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B21" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="D21" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F21" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G21" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H21" s="5" t="s">
+      <c r="D21" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" s="4" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="22" spans="2:8">
-      <c r="B22" s="3" t="s">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B22" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C22" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="D22" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F22" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G22" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H22" s="5" t="s">
+      <c r="D22" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F22" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H22" s="4" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="23" spans="2:8">
-      <c r="B23" s="3" t="s">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B23" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D23" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F23" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G23" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H23" s="5" t="s">
+      <c r="D23" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H23" s="4" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="24" spans="2:8">
-      <c r="B24" s="3" t="s">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B24" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="D24" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F24" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G24" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H24" s="5" t="s">
+      <c r="D24" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F24" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H24" s="4" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="25" spans="2:8">
-      <c r="B25" s="3" t="s">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B25" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="D25" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F25" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G25" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H25" s="5" t="s">
+      <c r="D25" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F25" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H25" s="4" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="26" spans="2:8">
-      <c r="B26" s="3" t="s">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B26" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="C26" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="D26" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F26" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H26" s="5" t="s">
+      <c r="D26" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F26" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H26" s="4" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="27" spans="2:8">
-      <c r="B27" s="3" t="s">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B27" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="C27" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="D27" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F27" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G27" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H27" s="5" t="s">
+      <c r="D27" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F27" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G27" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H27" s="4" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="28" spans="2:8">
-      <c r="B28" s="3" t="s">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B28" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C28" s="9" t="s">
+      <c r="C28" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="D28" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F28" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G28" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H28" s="5" t="s">
+      <c r="D28" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F28" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G28" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H28" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="29" spans="2:8">
-      <c r="B29" s="3" t="s">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B29" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="D29" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F29" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G29" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H29" s="2" t="s">
+      <c r="D29" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F29" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G29" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H29" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="30" spans="2:8">
-      <c r="B30" s="3" t="s">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B30" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="D30" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F30" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G30" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H30" s="2" t="s">
+      <c r="D30" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F30" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G30" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H30" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="31" spans="2:8">
-      <c r="B31" s="3" t="s">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B31" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="D31" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F31" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G31" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H31" s="2" t="s">
+      <c r="D31" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F31" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G31" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H31" s="1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="32" spans="2:8">
-      <c r="B32" s="3" t="s">
+    <row r="32" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B32" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="D32" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F32" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G32" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H32" s="2" t="s">
+      <c r="D32" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F32" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G32" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H32" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="33" spans="2:8">
-      <c r="B33" s="3" t="s">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B33" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D33" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F33" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G33" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H33" s="2" t="s">
+      <c r="D33" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F33" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G33" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H33" s="1" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="34" spans="2:8">
-      <c r="B34" s="2" t="s">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B34" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="D34" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F34" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G34" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H34" s="2" t="s">
+      <c r="D34" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F34" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G34" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H34" s="1" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="35" spans="2:8">
-      <c r="B35" s="2" t="s">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B35" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="D35" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E35" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F35" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G35" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H35" s="2" t="s">
+      <c r="D35" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F35" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G35" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H35" s="1" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="36" spans="2:8">
-      <c r="B36" s="2" t="s">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B36" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D36" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F36" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G36" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H36" s="2" t="s">
+      <c r="D36" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F36" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G36" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H36" s="1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="37" spans="2:8">
-      <c r="B37" s="2" t="s">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B37" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="D37" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E37" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F37" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G37" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H37" s="2" t="s">
+      <c r="D37" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F37" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G37" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H37" s="1" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="38" spans="2:8">
-      <c r="B38" s="2" t="s">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B38" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="D38" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E38" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F38" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G38" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H38" s="2" t="s">
+      <c r="D38" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F38" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G38" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H38" s="1" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="39" spans="2:8">
-      <c r="B39" s="2" t="s">
+    <row r="39" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B39" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="D39" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E39" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F39" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G39" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H39" s="2" t="s">
+      <c r="D39" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F39" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G39" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H39" s="1" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="40" spans="2:8">
-      <c r="B40" s="2" t="s">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B40" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="D40" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E40" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F40" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G40" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H40" s="2" t="s">
+      <c r="D40" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F40" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G40" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H40" s="1" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="41" spans="2:8">
-      <c r="B41" s="2" t="s">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B41" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C41" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="D41" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E41" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F41" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G41" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H41" s="2" t="s">
+      <c r="D41" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F41" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G41" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H41" s="1" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="42" spans="2:8">
-      <c r="B42" s="2" t="s">
+    <row r="42" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B42" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C42" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D42" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E42" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F42" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G42" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H42" s="2" t="s">
+      <c r="D42" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F42" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G42" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H42" s="1" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="43" spans="2:8">
-      <c r="B43" s="2" t="s">
+    <row r="43" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B43" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C43" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="D43" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E43" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F43" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G43" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H43" s="2" t="s">
+      <c r="D43" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F43" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G43" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H43" s="1" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="44" spans="2:8">
-      <c r="B44" s="2" t="s">
+    <row r="44" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B44" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="C44" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="D44" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E44" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F44" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G44" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H44" s="2" t="s">
+      <c r="D44" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F44" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G44" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H44" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="45" spans="2:8">
-      <c r="B45" s="2" t="s">
+    <row r="45" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B45" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C45" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="D45" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E45" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F45" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G45" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H45" s="2" t="s">
+      <c r="D45" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F45" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G45" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H45" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="46" spans="2:8">
-      <c r="B46" s="2" t="s">
+    <row r="46" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B46" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C46" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="D46" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E46" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F46" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G46" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H46" s="2" t="s">
+      <c r="D46" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F46" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G46" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H46" s="1" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="47" spans="2:8">
-      <c r="B47" s="2" t="s">
+    <row r="47" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B47" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C47" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="D47" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E47" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F47" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G47" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H47" s="2" t="s">
+      <c r="D47" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F47" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G47" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H47" s="1" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="48" spans="2:8">
-      <c r="B48" s="2" t="s">
+    <row r="48" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B48" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C48" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="D48" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E48" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F48" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G48" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H48" s="2" t="s">
+      <c r="D48" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F48" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G48" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H48" s="1" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="49" spans="2:8">
-      <c r="B49" s="2" t="s">
+    <row r="49" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B49" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C49" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="D49" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E49" s="8" t="s">
+      <c r="D49" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E49" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="F49" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G49" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H49" s="2" t="s">
+      <c r="F49" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G49" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H49" s="1" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="50" spans="2:8">
-      <c r="B50" s="2" t="s">
+    <row r="50" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B50" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C50" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D50" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E50" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F50" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G50" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H50" s="2" t="s">
+      <c r="D50" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F50" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G50" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H50" s="1" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="51" spans="2:8">
-      <c r="B51" s="2" t="s">
+    <row r="51" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B51" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="C51" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="D51" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E51" s="8" t="s">
+      <c r="D51" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E51" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="F51" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G51" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H51" s="2" t="s">
+      <c r="F51" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G51" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H51" s="1" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="52" spans="2:8">
-      <c r="B52" s="2" t="s">
+    <row r="52" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B52" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C52" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="D52" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E52" s="8" t="s">
+      <c r="D52" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E52" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="F52" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G52" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H52" s="2" t="s">
+      <c r="F52" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G52" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H52" s="1" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="53" spans="2:8">
-      <c r="B53" s="2" t="s">
+    <row r="53" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B53" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="C53" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="D53" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E53" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F53" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G53" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H53" s="2" t="s">
+      <c r="D53" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F53" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G53" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H53" s="1" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="54" spans="2:8">
-      <c r="B54" s="2" t="s">
+    <row r="54" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B54" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C54" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D54" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E54" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F54" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G54" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H54" s="2" t="s">
+      <c r="D54" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F54" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G54" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H54" s="1" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="55" spans="2:8">
-      <c r="B55" s="2" t="s">
+    <row r="55" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B55" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C55" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="D55" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E55" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F55" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G55" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H55" s="2" t="s">
+      <c r="D55" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F55" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G55" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H55" s="1" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="56" spans="2:8">
-      <c r="B56" s="2" t="s">
+    <row r="56" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B56" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="C56" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="D56" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E56" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F56" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G56" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H56" s="2" t="s">
+      <c r="D56" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E56" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F56" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G56" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H56" s="1" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="57" spans="2:8">
-      <c r="B57" s="2" t="s">
+    <row r="57" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B57" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="C57" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="D57" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E57" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F57" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G57" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H57" s="2" t="s">
+      <c r="D57" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E57" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F57" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G57" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H57" s="1" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="58" spans="2:8">
-      <c r="B58" s="2" t="s">
+    <row r="58" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B58" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="C58" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="D58" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E58" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F58" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G58" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H58" s="2" t="s">
+      <c r="D58" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E58" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F58" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G58" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H58" s="1" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="59" spans="2:8">
-      <c r="B59" s="2" t="s">
+    <row r="59" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B59" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="C59" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="D59" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E59" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F59" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G59" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H59" s="2" t="s">
+      <c r="D59" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E59" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F59" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G59" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H59" s="1" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="60" spans="2:8">
-      <c r="B60" s="2" t="s">
+    <row r="60" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B60" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="C60" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="D60" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E60" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F60" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G60" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H60" s="2" t="s">
+      <c r="D60" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E60" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F60" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G60" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H60" s="1" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="61" spans="2:8">
-      <c r="B61" s="2" t="s">
+    <row r="61" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B61" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="C61" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="D61" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E61" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F61" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G61" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H61" s="10" t="s">
+      <c r="D61" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E61" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F61" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G61" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H61" s="1" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="62" spans="2:8">
-      <c r="B62" s="2" t="s">
+    <row r="62" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B62" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="C62" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="D62" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E62" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F62" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G62" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H62" s="10" t="s">
+      <c r="D62" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E62" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F62" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G62" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H62" s="1" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="63" spans="2:8">
-      <c r="B63" s="10" t="s">
+    <row r="63" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B63" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="C63" s="10" t="s">
+      <c r="C63" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="D63" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E63" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F63" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G63" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H63" s="10" t="s">
+      <c r="D63" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E63" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F63" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G63" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H63" s="1" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="64" spans="2:8">
-      <c r="B64" s="2" t="s">
+    <row r="64" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B64" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="C64" s="2" t="s">
+      <c r="C64" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="D64" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E64" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F64" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G64" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H64" s="10" t="s">
+      <c r="D64" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E64" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F64" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G64" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H64" s="1" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="65" spans="2:8">
-      <c r="B65" s="2" t="s">
+    <row r="65" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B65" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C65" s="2" t="s">
+      <c r="C65" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="D65" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E65" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F65" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G65" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H65" s="10" t="s">
+      <c r="D65" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E65" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F65" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G65" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H65" s="1" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="66" spans="2:8">
-      <c r="B66" s="2" t="s">
+    <row r="66" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B66" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="C66" s="2" t="s">
+      <c r="C66" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="D66" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E66" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F66" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G66" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H66" s="10" t="s">
+      <c r="D66" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E66" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F66" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G66" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H66" s="1" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="67" spans="2:8">
-      <c r="B67" s="2" t="s">
+    <row r="67" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B67" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="C67" s="2" t="s">
+      <c r="C67" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="D67" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E67" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F67" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G67" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H67" s="10" t="s">
+      <c r="D67" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E67" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F67" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G67" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H67" s="1" t="s">
         <v>218</v>
       </c>
     </row>
+    <row r="68" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B68" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="D68" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E68" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F68" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G68" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H68" s="9" t="s">
+        <v>221</v>
+      </c>
+    </row>
   </sheetData>
-  <printOptions>
-    <extLst>
-      <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1785202857" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
-      </ext>
-    </extLst>
-  </printOptions>
-  <pageMargins left="0.700000" right="0.700000" top="0.750000" bottom="0.750000" header="0.300000" footer="0.300000"/>
-  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="1"/>
-  <headerFooter>
-    <extLst>
-      <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1785202857" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1785202857" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1785202857" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1785202857" Id="1" type="0" value="0"/>
-      </ext>
-    </extLst>
-  </headerFooter>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" fitToWidth="0"/>
   <extLst>
     <ext uri="smNativeData">
       <pm:sheetPrefs xmlns:pm="smNativeData" day="1785202857" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">

--- a/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
@@ -1,27 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
+  <fileSharing readOnlyRecommended="0" userName="Lumino Game 03"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0823E4D-08CD-4437-8E98-7226310CE2EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3520" yWindow="1160" windowWidth="31320" windowHeight="18380" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView activeTab="0" xWindow="240" yWindow="60" windowWidth="31320" windowHeight="18380" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:revision xmlns:pm="smNativeData" day="1785202857" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
-      <pm:docPrefs xmlns:pm="smNativeData" id="1785202857" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
-      <pm:compatibility xmlns:pm="smNativeData" id="1785202857" overlapCells="1"/>
-      <pm:defCurrency xmlns:pm="smNativeData" id="1785202857"/>
+      <pm:revision xmlns:pm="smNativeData" day="1785223317" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
+      <pm:docPrefs xmlns:pm="smNativeData" id="1785223317" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
+      <pm:compatibility xmlns:pm="smNativeData" id="1785223317" overlapCells="1"/>
+      <pm:defCurrency xmlns:pm="smNativeData" id="1785223317"/>
     </ext>
   </extLst>
 </workbook>
@@ -687,55 +682,92 @@
     <t>马吉房间游戏面板</t>
   </si>
   <si>
+    <t>PuzzleUI</t>
+  </si>
+  <si>
     <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/PuzzleUI/Prefabs/PuzzleUI.prefab</t>
   </si>
   <si>
-    <t>PuzzleUI</t>
-  </si>
-  <si>
     <t>拼图小游戏</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="8">
+    <numFmt numFmtId="5" formatCode="#,##0\ &quot;¥&quot;;\-#,##0\ &quot;¥&quot;"/>
+    <numFmt numFmtId="6" formatCode="#,##0\ &quot;¥&quot;;[Red]\-#,##0\ &quot;¥&quot;"/>
+    <numFmt numFmtId="7" formatCode="#,##0.00\ &quot;¥&quot;;\-#,##0.00\ &quot;¥&quot;"/>
+    <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;¥&quot;;[Red]\-#,##0.00\ &quot;¥&quot;"/>
+    <numFmt numFmtId="42" formatCode="_-* #,##0\ &quot;¥&quot;_-;\-* #,##0\ &quot;¥&quot;_-;_-* &quot;-&quot;\ &quot;¥&quot;_-;_-@_-"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0\ _¥_-;\-* #,##0\ _¥_-;_-* &quot;-&quot;\ _¥_-;_-@_-"/>
+    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;¥&quot;_-;\-* #,##0.00\ &quot;¥&quot;_-;_-* &quot;-&quot;??\ &quot;¥&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _¥_-;\-* #,##0.00\ _¥_-;_-* &quot;-&quot;??\ _¥_-;_-@_-"/>
+  </numFmts>
+  <fonts count="4">
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="等线"/>
       <charset val="134"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1785223317" ulstyle="none" kern="1">
+            <pm:latin face="等线" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1785223317" ulstyle="none" kern="1">
+            <pm:latin face="Arial" sz="200" lang="default"/>
+            <pm:cs face="Times New Roman" sz="200" lang="default"/>
+            <pm:ea face="SimSun" sz="200" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF1F2329"/>
       <name val="等线"/>
+      <charset val="134"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1785223317" ulstyle="none" kern="1">
+            <pm:latin face="等线" sz="200" lang="default"/>
+            <pm:cs face="Times New Roman" sz="200" lang="default"/>
+            <pm:ea face="SimSun" sz="200" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <color rgb="FF1F2329"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1785223317" fgClr="1F2329" ulstyle="none" kern="1">
+            <pm:latin face="等线" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -743,25 +775,50 @@
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFACB9CA"/>
         <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1785223317" type="1" fgLvl="100" fgClr="00ACB9CA" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF5B9BD5"/>
         <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1785223317" type="1" fgLvl="100" fgClr="005B9BD5" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
   </fills>
   <borders count="4">
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1785223317"/>
+        </ext>
+      </extLst>
     </border>
     <border>
       <left style="thin">
@@ -776,77 +833,106 @@
       <bottom style="thin">
         <color rgb="FFDEE0E3"/>
       </bottom>
-      <diagonal/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1785223317">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+          </pm:border>
+        </ext>
+      </extLst>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1785223317"/>
+        </ext>
+      </extLst>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1785223317"/>
+        </ext>
+      </extLst>
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="常规" xfId="0" builtinId="0" customBuiltin="1"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
+    <cellStyle name="常规 2" xfId="1"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
     <ext uri="smNativeData">
-      <pm:charStyles xmlns:pm="smNativeData" id="1785202857" count="1">
+      <pm:charStyles xmlns:pm="smNativeData" id="1785223317" count="1">
         <pm:charStyle name="普通" fontId="0" Id="1"/>
       </pm:charStyles>
-      <pm:colors xmlns:pm="smNativeData" id="1785202857" count="4">
+      <pm:colors xmlns:pm="smNativeData" id="1785223317" count="4">
         <pm:color name="颜色 24" rgb="1F2329"/>
         <pm:color name="颜色 25" rgb="ACB9CA"/>
         <pm:color name="颜色 26" rgb="5B9BD5"/>
@@ -1112,1601 +1198,1616 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <dimension ref="A1:H68"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.45"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="28.58203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="100.08203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="25.1640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="23.6640625" style="1" customWidth="1"/>
-    <col min="6" max="7" width="17.6640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="24.1640625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="8.6640625" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.6640625" style="1"/>
+    <col min="1" max="1" width="8.663793" customWidth="1" style="2"/>
+    <col min="2" max="2" width="28.577586" customWidth="1" style="2"/>
+    <col min="3" max="3" width="100.077586" customWidth="1" style="2"/>
+    <col min="4" max="4" width="25.163793" customWidth="1" style="2"/>
+    <col min="5" max="5" width="23.663793" customWidth="1" style="2"/>
+    <col min="6" max="7" width="17.663793" customWidth="1" style="2"/>
+    <col min="8" max="8" width="24.163793" customWidth="1" style="2"/>
+    <col min="9" max="16384" width="8.663793" customWidth="1" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
+    <row r="1" spans="1:8">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:8">
+      <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:8">
+      <c r="A3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B4" s="2" t="s">
+    <row r="4" spans="2:8">
+      <c r="B4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G4" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H4" s="1" t="s">
+      <c r="D4" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B5" s="2" t="s">
+    <row r="5" spans="2:8">
+      <c r="B5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G5" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H5" s="4" t="s">
+      <c r="D5" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="2" t="s">
+    <row r="6" spans="2:8" ht="19.50" customHeight="1">
+      <c r="B6" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="7" t="s">
+      <c r="D6" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G6" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H6" s="4" t="s">
+      <c r="F6" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B7" s="2" t="s">
+    <row r="7" spans="2:8">
+      <c r="B7" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G7" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H7" s="4" t="s">
+      <c r="D7" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B8" s="2" t="s">
+    <row r="8" spans="2:8">
+      <c r="B8" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G8" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H8" s="4" t="s">
+      <c r="D8" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" s="5" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B9" s="2" t="s">
+    <row r="9" spans="2:8">
+      <c r="B9" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G9" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H9" s="4" t="s">
+      <c r="D9" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" s="5" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B10" s="2" t="s">
+    <row r="10" spans="2:8">
+      <c r="B10" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="F10" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G10" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H10" s="4" t="s">
+      <c r="F10" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B11" s="2" t="s">
+    <row r="11" spans="2:8">
+      <c r="B11" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="F11" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G11" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H11" s="4" t="s">
+      <c r="F11" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H11" s="5" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B12" s="2" t="s">
+    <row r="12" spans="2:8">
+      <c r="B12" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F12" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G12" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H12" s="4" t="s">
+      <c r="D12" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H12" s="5" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B13" s="2" t="s">
+    <row r="13" spans="2:8">
+      <c r="B13" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D13" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F13" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G13" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H13" s="4" t="s">
+      <c r="D13" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" s="5" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B14" s="2" t="s">
+    <row r="14" spans="2:8">
+      <c r="B14" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="F14" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G14" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H14" s="4" t="s">
+      <c r="F14" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G14" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" s="5" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B15" s="2" t="s">
+    <row r="15" spans="2:8">
+      <c r="B15" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E15" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F15" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G15" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H15" s="4" t="s">
+      <c r="E15" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H15" s="5" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B16" s="2" t="s">
+    <row r="16" spans="2:8">
+      <c r="B16" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="D16" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E16" s="7" t="s">
+      <c r="D16" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F16" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G16" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H16" s="4" t="s">
+      <c r="F16" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H16" s="5" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B17" s="2" t="s">
+    <row r="17" spans="2:8">
+      <c r="B17" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="D17" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F17" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G17" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H17" s="4" t="s">
+      <c r="D17" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G17" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B18" s="2" t="s">
+    <row r="18" spans="2:8">
+      <c r="B18" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="D18" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E18" s="7" t="s">
+      <c r="D18" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F18" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G18" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H18" s="4" t="s">
+      <c r="F18" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G18" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H18" s="5" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B19" s="2" t="s">
+    <row r="19" spans="2:8">
+      <c r="B19" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="D19" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F19" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G19" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H19" s="4" t="s">
+      <c r="D19" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F19" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H19" s="5" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B20" s="2" t="s">
+    <row r="20" spans="2:8">
+      <c r="B20" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="D20" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F20" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G20" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H20" s="4" t="s">
+      <c r="D20" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F20" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" s="5" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B21" s="2" t="s">
+    <row r="21" spans="2:8">
+      <c r="B21" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="D21" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F21" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G21" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H21" s="4" t="s">
+      <c r="D21" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" s="5" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B22" s="2" t="s">
+    <row r="22" spans="2:8">
+      <c r="B22" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="D22" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F22" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G22" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H22" s="4" t="s">
+      <c r="D22" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F22" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H22" s="5" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B23" s="2" t="s">
+    <row r="23" spans="2:8">
+      <c r="B23" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="D23" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F23" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G23" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H23" s="4" t="s">
+      <c r="D23" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H23" s="5" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B24" s="2" t="s">
+    <row r="24" spans="2:8">
+      <c r="B24" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="D24" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F24" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G24" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H24" s="4" t="s">
+      <c r="D24" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F24" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H24" s="5" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B25" s="2" t="s">
+    <row r="25" spans="2:8">
+      <c r="B25" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="D25" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F25" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G25" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H25" s="4" t="s">
+      <c r="D25" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F25" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H25" s="5" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B26" s="2" t="s">
+    <row r="26" spans="2:8">
+      <c r="B26" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C26" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="D26" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F26" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H26" s="4" t="s">
+      <c r="D26" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F26" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H26" s="5" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B27" s="2" t="s">
+    <row r="27" spans="2:8">
+      <c r="B27" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="D27" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F27" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G27" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H27" s="4" t="s">
+      <c r="D27" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F27" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G27" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H27" s="5" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B28" s="2" t="s">
+    <row r="28" spans="2:8">
+      <c r="B28" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="C28" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="D28" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F28" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G28" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H28" s="4" t="s">
+      <c r="D28" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F28" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G28" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H28" s="5" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B29" s="2" t="s">
+    <row r="29" spans="2:8">
+      <c r="B29" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D29" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F29" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G29" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H29" s="1" t="s">
+      <c r="D29" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F29" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G29" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H29" s="2" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B30" s="2" t="s">
+    <row r="30" spans="2:8">
+      <c r="B30" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="D30" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F30" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G30" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H30" s="1" t="s">
+      <c r="D30" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F30" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G30" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H30" s="2" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B31" s="2" t="s">
+    <row r="31" spans="2:8">
+      <c r="B31" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="D31" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F31" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G31" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H31" s="1" t="s">
+      <c r="D31" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F31" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G31" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H31" s="2" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B32" s="2" t="s">
+    <row r="32" spans="2:8">
+      <c r="B32" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="D32" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F32" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G32" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H32" s="1" t="s">
+      <c r="D32" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F32" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G32" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H32" s="2" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B33" s="2" t="s">
+    <row r="33" spans="2:8">
+      <c r="B33" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D33" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F33" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G33" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H33" s="1" t="s">
+      <c r="D33" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F33" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G33" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H33" s="2" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B34" s="1" t="s">
+    <row r="34" spans="2:8">
+      <c r="B34" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="D34" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E34" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F34" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G34" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H34" s="1" t="s">
+      <c r="D34" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F34" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G34" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H34" s="2" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B35" s="1" t="s">
+    <row r="35" spans="2:8">
+      <c r="B35" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="D35" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F35" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G35" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H35" s="1" t="s">
+      <c r="D35" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F35" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G35" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H35" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B36" s="1" t="s">
+    <row r="36" spans="2:8">
+      <c r="B36" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="D36" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F36" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G36" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H36" s="1" t="s">
+      <c r="D36" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F36" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G36" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H36" s="2" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B37" s="1" t="s">
+    <row r="37" spans="2:8">
+      <c r="B37" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="D37" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F37" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G37" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H37" s="1" t="s">
+      <c r="D37" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F37" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G37" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H37" s="2" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B38" s="1" t="s">
+    <row r="38" spans="2:8">
+      <c r="B38" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="D38" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E38" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F38" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G38" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H38" s="1" t="s">
+      <c r="D38" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F38" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G38" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H38" s="2" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B39" s="1" t="s">
+    <row r="39" spans="2:8">
+      <c r="B39" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="D39" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E39" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F39" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G39" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H39" s="1" t="s">
+      <c r="D39" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F39" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G39" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H39" s="2" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B40" s="1" t="s">
+    <row r="40" spans="2:8">
+      <c r="B40" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="D40" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E40" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F40" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G40" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H40" s="1" t="s">
+      <c r="D40" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F40" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G40" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H40" s="2" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B41" s="1" t="s">
+    <row r="41" spans="2:8">
+      <c r="B41" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="D41" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E41" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F41" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G41" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H41" s="1" t="s">
+      <c r="D41" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F41" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G41" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H41" s="2" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B42" s="1" t="s">
+    <row r="42" spans="2:8">
+      <c r="B42" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C42" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="D42" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E42" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F42" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G42" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H42" s="1" t="s">
+      <c r="D42" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F42" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G42" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H42" s="2" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B43" s="1" t="s">
+    <row r="43" spans="2:8">
+      <c r="B43" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C43" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="D43" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E43" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F43" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G43" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H43" s="1" t="s">
+      <c r="D43" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F43" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G43" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H43" s="2" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B44" s="1" t="s">
+    <row r="44" spans="2:8">
+      <c r="B44" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C44" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="D44" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E44" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F44" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G44" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H44" s="1" t="s">
+      <c r="D44" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F44" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G44" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H44" s="2" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B45" s="1" t="s">
+    <row r="45" spans="2:8">
+      <c r="B45" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C45" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="D45" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E45" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F45" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G45" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H45" s="1" t="s">
+      <c r="D45" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F45" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G45" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H45" s="2" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B46" s="1" t="s">
+    <row r="46" spans="2:8">
+      <c r="B46" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C46" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="D46" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E46" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F46" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G46" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H46" s="1" t="s">
+      <c r="D46" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F46" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G46" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H46" s="2" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B47" s="1" t="s">
+    <row r="47" spans="2:8">
+      <c r="B47" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C47" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="D47" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E47" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F47" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G47" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H47" s="1" t="s">
+      <c r="D47" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F47" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G47" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H47" s="2" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B48" s="1" t="s">
+    <row r="48" spans="2:8">
+      <c r="B48" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="C48" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="D48" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E48" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F48" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G48" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H48" s="1" t="s">
+      <c r="D48" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F48" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G48" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H48" s="2" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="49" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B49" s="1" t="s">
+    <row r="49" spans="2:8">
+      <c r="B49" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C49" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="D49" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E49" s="7" t="s">
+      <c r="D49" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E49" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="F49" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G49" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H49" s="1" t="s">
+      <c r="F49" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G49" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H49" s="2" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="50" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B50" s="1" t="s">
+    <row r="50" spans="2:8">
+      <c r="B50" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="C50" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="D50" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E50" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F50" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G50" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H50" s="1" t="s">
+      <c r="D50" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F50" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G50" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H50" s="2" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="51" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B51" s="1" t="s">
+    <row r="51" spans="2:8">
+      <c r="B51" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="C51" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="D51" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E51" s="7" t="s">
+      <c r="D51" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E51" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="F51" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G51" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H51" s="1" t="s">
+      <c r="F51" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G51" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H51" s="2" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="52" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B52" s="1" t="s">
+    <row r="52" spans="2:8">
+      <c r="B52" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="C52" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="D52" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E52" s="7" t="s">
+      <c r="D52" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E52" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="F52" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G52" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H52" s="1" t="s">
+      <c r="F52" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G52" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H52" s="2" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="53" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B53" s="1" t="s">
+    <row r="53" spans="2:8">
+      <c r="B53" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="C53" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="D53" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E53" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F53" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G53" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H53" s="1" t="s">
+      <c r="D53" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F53" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G53" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H53" s="2" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="54" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B54" s="1" t="s">
+    <row r="54" spans="2:8">
+      <c r="B54" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="C54" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="D54" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E54" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F54" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G54" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H54" s="1" t="s">
+      <c r="D54" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F54" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G54" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H54" s="2" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="55" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B55" s="1" t="s">
+    <row r="55" spans="2:8">
+      <c r="B55" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="C55" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="D55" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E55" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F55" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G55" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H55" s="1" t="s">
+      <c r="D55" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F55" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G55" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H55" s="2" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="56" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B56" s="1" t="s">
+    <row r="56" spans="2:8">
+      <c r="B56" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="C56" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="D56" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E56" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F56" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G56" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H56" s="1" t="s">
+      <c r="D56" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F56" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G56" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H56" s="2" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="57" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B57" s="1" t="s">
+    <row r="57" spans="2:8">
+      <c r="B57" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="C57" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="D57" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E57" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F57" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G57" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H57" s="1" t="s">
+      <c r="D57" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F57" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G57" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H57" s="2" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="58" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B58" s="1" t="s">
+    <row r="58" spans="2:8">
+      <c r="B58" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="C58" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="D58" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E58" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F58" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G58" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H58" s="1" t="s">
+      <c r="D58" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F58" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G58" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H58" s="2" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="59" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B59" s="1" t="s">
+    <row r="59" spans="2:8">
+      <c r="B59" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="C59" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="D59" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E59" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F59" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G59" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H59" s="1" t="s">
+      <c r="D59" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E59" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F59" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G59" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H59" s="2" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="60" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B60" s="1" t="s">
+    <row r="60" spans="2:8">
+      <c r="B60" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="C60" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="D60" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E60" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F60" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G60" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H60" s="1" t="s">
+      <c r="D60" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E60" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F60" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G60" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H60" s="2" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="61" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B61" s="1" t="s">
+    <row r="61" spans="2:8">
+      <c r="B61" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="C61" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="D61" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E61" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F61" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G61" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H61" s="1" t="s">
+      <c r="D61" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E61" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F61" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G61" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H61" s="2" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="62" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B62" s="1" t="s">
+    <row r="62" spans="2:8">
+      <c r="B62" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="C62" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="D62" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E62" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F62" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G62" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H62" s="1" t="s">
+      <c r="D62" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E62" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F62" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G62" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H62" s="2" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="63" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B63" s="1" t="s">
+    <row r="63" spans="2:8">
+      <c r="B63" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="C63" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="D63" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E63" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F63" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G63" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H63" s="1" t="s">
+      <c r="D63" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E63" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F63" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G63" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H63" s="2" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="64" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B64" s="1" t="s">
+    <row r="64" spans="2:8">
+      <c r="B64" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="C64" s="1" t="s">
+      <c r="C64" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="D64" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E64" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F64" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G64" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H64" s="1" t="s">
+      <c r="D64" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E64" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F64" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G64" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H64" s="2" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="65" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B65" s="1" t="s">
+    <row r="65" spans="2:8">
+      <c r="B65" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="C65" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="D65" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E65" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F65" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G65" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H65" s="1" t="s">
+      <c r="D65" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E65" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F65" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G65" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H65" s="2" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="66" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B66" s="1" t="s">
+    <row r="66" spans="2:8">
+      <c r="B66" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="C66" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="D66" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E66" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F66" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G66" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H66" s="1" t="s">
+      <c r="D66" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E66" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F66" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G66" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H66" s="2" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="67" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B67" s="1" t="s">
+    <row r="67" spans="2:8">
+      <c r="B67" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="C67" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="D67" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E67" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F67" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G67" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H67" s="1" t="s">
+      <c r="D67" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E67" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F67" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G67" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H67" s="2" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="68" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B68" s="1" t="s">
+    <row r="68" spans="2:8">
+      <c r="B68" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C68" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="C68" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="D68" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E68" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F68" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G68" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H68" s="9" t="s">
+      <c r="D68" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E68" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F68" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G68" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H68" s="10" t="s">
         <v>221</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" fitToWidth="0"/>
+  <printOptions>
+    <extLst>
+      <ext uri="smNativeData">
+        <pm:pageFlags xmlns:pm="smNativeData" id="1785223317" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+      </ext>
+    </extLst>
+  </printOptions>
+  <pageMargins left="0.700000" right="0.700000" top="0.750000" bottom="0.750000" header="0.300000" footer="0.300000"/>
+  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="1"/>
+  <headerFooter>
+    <extLst>
+      <ext uri="smNativeData">
+        <pm:header xmlns:pm="smNativeData" id="1785223317" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1785223317" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1785223317" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1785223317" Id="1" type="0" value="0"/>
+      </ext>
+    </extLst>
+  </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1785202857" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1785223317" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>

--- a/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
@@ -1,16 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
-  <fileSharing readOnlyRecommended="0" userName="Lumino Game 03"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA8EC97F-97C2-4F4C-AA5A-1B1D3432CC63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0" xWindow="240" yWindow="60" windowWidth="31320" windowHeight="18380" tabRatio="500"/>
+    <workbookView xWindow="5050" yWindow="2500" windowWidth="31320" windowHeight="18380" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext uri="smNativeData">
       <pm:revision xmlns:pm="smNativeData" day="1785223317" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
@@ -23,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="225">
   <si>
     <t>##var</t>
   </si>
@@ -689,85 +694,57 @@
   </si>
   <si>
     <t>拼图小游戏</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/MedicinalSolutionUI/Prefabs/MedicinalSolutionUI.prefab</t>
+  </si>
+  <si>
+    <t>MedicinalSolutionUI</t>
+  </si>
+  <si>
+    <t>滴胶固化玩法</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
-    <numFmt numFmtId="5" formatCode="#,##0\ &quot;¥&quot;;\-#,##0\ &quot;¥&quot;"/>
-    <numFmt numFmtId="6" formatCode="#,##0\ &quot;¥&quot;;[Red]\-#,##0\ &quot;¥&quot;"/>
-    <numFmt numFmtId="7" formatCode="#,##0.00\ &quot;¥&quot;;\-#,##0.00\ &quot;¥&quot;"/>
-    <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;¥&quot;;[Red]\-#,##0.00\ &quot;¥&quot;"/>
-    <numFmt numFmtId="42" formatCode="_-* #,##0\ &quot;¥&quot;_-;\-* #,##0\ &quot;¥&quot;_-;_-* &quot;-&quot;\ &quot;¥&quot;_-;_-@_-"/>
-    <numFmt numFmtId="41" formatCode="_-* #,##0\ _¥_-;\-* #,##0\ _¥_-;_-* &quot;-&quot;\ _¥_-;_-@_-"/>
-    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;¥&quot;_-;\-* #,##0.00\ &quot;¥&quot;_-;_-* &quot;-&quot;??\ &quot;¥&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _¥_-;\-* #,##0.00\ _¥_-;_-* &quot;-&quot;??\ _¥_-;_-@_-"/>
-  </numFmts>
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="等线"/>
       <charset val="134"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1785223317" ulstyle="none" kern="1">
-            <pm:latin face="等线" sz="220" lang="default"/>
-            <pm:cs face="Times New Roman" sz="220" lang="default"/>
-            <pm:ea face="SimSun" sz="220" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
-      <name val="Arial"/>
-      <family val="2"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
-      <sz val="10"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1785223317" ulstyle="none" kern="1">
-            <pm:latin face="Arial" sz="200" lang="default"/>
-            <pm:cs face="Times New Roman" sz="200" lang="default"/>
-            <pm:ea face="SimSun" sz="200" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
+      <name val="等线"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF1F2329"/>
       <name val="等线"/>
-      <charset val="134"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1785223317" ulstyle="none" kern="1">
-            <pm:latin face="等线" sz="200" lang="default"/>
-            <pm:cs face="Times New Roman" sz="200" lang="default"/>
-            <pm:ea face="SimSun" sz="200" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="等线"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
-      <color rgb="FF1F2329"/>
-      <sz val="11"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1785223317" fgClr="1F2329" ulstyle="none" kern="1">
-            <pm:latin face="等线" sz="220" lang="default"/>
-            <pm:cs face="Times New Roman" sz="220" lang="default"/>
-            <pm:ea face="SimSun" sz="220" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -775,50 +752,25 @@
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
-      <patternFill patternType="none"/>
-    </fill>
-    <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFACB9CA"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1785223317" type="1" fgLvl="100" fgClr="00ACB9CA" bgLvl="0" bgClr="00FFFFFF"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF5B9BD5"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1785223317" type="1" fgLvl="100" fgClr="005B9BD5" bgLvl="0" bgClr="00FFFFFF"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
   </fills>
   <borders count="4">
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1785223317"/>
-        </ext>
-      </extLst>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -833,101 +785,72 @@
       <bottom style="thin">
         <color rgb="FFDEE0E3"/>
       </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1785223317">
-            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-          </pm:border>
-        </ext>
-      </extLst>
+      <diagonal/>
     </border>
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1785223317"/>
-        </ext>
-      </extLst>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1785223317"/>
-        </ext>
-      </extLst>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
-    <cellStyle name="常规 2" xfId="1"/>
+    <cellStyle name="常规" xfId="0" builtinId="0" customBuiltin="1"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0"/>
   <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
     <ext uri="smNativeData">
       <pm:charStyles xmlns:pm="smNativeData" id="1785223317" count="1">
         <pm:charStyle name="普通" fontId="0" Id="1"/>
@@ -1198,1613 +1121,1621 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:H68"/>
-  <sheetFormatPr defaultRowHeight="13.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H69"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.663793" customWidth="1" style="2"/>
-    <col min="2" max="2" width="28.577586" customWidth="1" style="2"/>
-    <col min="3" max="3" width="100.077586" customWidth="1" style="2"/>
-    <col min="4" max="4" width="25.163793" customWidth="1" style="2"/>
-    <col min="5" max="5" width="23.663793" customWidth="1" style="2"/>
-    <col min="6" max="7" width="17.663793" customWidth="1" style="2"/>
-    <col min="8" max="8" width="24.163793" customWidth="1" style="2"/>
-    <col min="9" max="16384" width="8.663793" customWidth="1" style="2"/>
+    <col min="1" max="1" width="8.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="28.58203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="100.08203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="25.1640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="23.6640625" style="1" customWidth="1"/>
+    <col min="6" max="7" width="17.6640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="24.1640625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="4" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="2:8">
-      <c r="B4" s="3" t="s">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G4" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H4" s="2" t="s">
+      <c r="D4" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="2:8">
-      <c r="B5" s="3" t="s">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G5" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H5" s="5" t="s">
+      <c r="D5" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="19.50" customHeight="1">
-      <c r="B6" s="3" t="s">
+    <row r="6" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="8" t="s">
+      <c r="D6" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G6" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H6" s="5" t="s">
+      <c r="F6" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="2:8">
-      <c r="B7" s="3" t="s">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B7" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G7" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H7" s="5" t="s">
+      <c r="D7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="2:8">
-      <c r="B8" s="3" t="s">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G8" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H8" s="5" t="s">
+      <c r="D8" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" s="4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="2:8">
-      <c r="B9" s="3" t="s">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B9" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G9" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H9" s="5" t="s">
+      <c r="D9" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="2:8">
-      <c r="B10" s="3" t="s">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B10" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F10" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G10" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H10" s="5" t="s">
+      <c r="F10" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="2:8">
-      <c r="B11" s="3" t="s">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B11" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="F11" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G11" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H11" s="5" t="s">
+      <c r="F11" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H11" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="12" spans="2:8">
-      <c r="B12" s="3" t="s">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B12" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F12" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G12" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H12" s="5" t="s">
+      <c r="D12" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H12" s="4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="13" spans="2:8">
-      <c r="B13" s="3" t="s">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B13" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F13" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G13" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H13" s="5" t="s">
+      <c r="D13" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" s="4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="14" spans="2:8">
-      <c r="B14" s="3" t="s">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B14" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E14" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="F14" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G14" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H14" s="5" t="s">
+      <c r="F14" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G14" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" s="4" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="15" spans="2:8">
-      <c r="B15" s="3" t="s">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B15" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E15" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F15" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G15" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H15" s="5" t="s">
+      <c r="E15" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H15" s="4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="16" spans="2:8">
-      <c r="B16" s="3" t="s">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B16" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D16" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E16" s="8" t="s">
+      <c r="D16" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F16" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G16" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H16" s="5" t="s">
+      <c r="F16" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H16" s="4" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="17" spans="2:8">
-      <c r="B17" s="3" t="s">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B17" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D17" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F17" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G17" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H17" s="5" t="s">
+      <c r="D17" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G17" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="2:8">
-      <c r="B18" s="3" t="s">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B18" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D18" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E18" s="8" t="s">
+      <c r="D18" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F18" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G18" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H18" s="5" t="s">
+      <c r="F18" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G18" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H18" s="4" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="2:8">
-      <c r="B19" s="3" t="s">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B19" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D19" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F19" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G19" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H19" s="5" t="s">
+      <c r="D19" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F19" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H19" s="4" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="20" spans="2:8">
-      <c r="B20" s="3" t="s">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B20" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="D20" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F20" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G20" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H20" s="5" t="s">
+      <c r="D20" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F20" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" s="4" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="21" spans="2:8">
-      <c r="B21" s="3" t="s">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B21" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="D21" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F21" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G21" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H21" s="5" t="s">
+      <c r="D21" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" s="4" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="22" spans="2:8">
-      <c r="B22" s="3" t="s">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B22" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C22" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="D22" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F22" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G22" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H22" s="5" t="s">
+      <c r="D22" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F22" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H22" s="4" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="23" spans="2:8">
-      <c r="B23" s="3" t="s">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B23" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D23" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F23" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G23" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H23" s="5" t="s">
+      <c r="D23" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H23" s="4" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="24" spans="2:8">
-      <c r="B24" s="3" t="s">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B24" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="D24" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F24" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G24" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H24" s="5" t="s">
+      <c r="D24" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F24" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H24" s="4" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="25" spans="2:8">
-      <c r="B25" s="3" t="s">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B25" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="D25" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F25" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G25" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H25" s="5" t="s">
+      <c r="D25" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F25" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H25" s="4" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="26" spans="2:8">
-      <c r="B26" s="3" t="s">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B26" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="C26" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="D26" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F26" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H26" s="5" t="s">
+      <c r="D26" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F26" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H26" s="4" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="27" spans="2:8">
-      <c r="B27" s="3" t="s">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B27" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="C27" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="D27" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F27" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G27" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H27" s="5" t="s">
+      <c r="D27" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F27" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G27" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H27" s="4" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="28" spans="2:8">
-      <c r="B28" s="3" t="s">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B28" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C28" s="9" t="s">
+      <c r="C28" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="D28" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F28" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G28" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H28" s="5" t="s">
+      <c r="D28" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F28" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G28" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H28" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="29" spans="2:8">
-      <c r="B29" s="3" t="s">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B29" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="D29" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F29" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G29" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H29" s="2" t="s">
+      <c r="D29" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F29" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G29" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H29" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="30" spans="2:8">
-      <c r="B30" s="3" t="s">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B30" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="D30" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F30" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G30" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H30" s="2" t="s">
+      <c r="D30" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F30" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G30" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H30" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="31" spans="2:8">
-      <c r="B31" s="3" t="s">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B31" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="D31" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F31" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G31" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H31" s="2" t="s">
+      <c r="D31" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F31" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G31" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H31" s="1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="32" spans="2:8">
-      <c r="B32" s="3" t="s">
+    <row r="32" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B32" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="D32" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F32" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G32" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H32" s="2" t="s">
+      <c r="D32" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F32" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G32" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H32" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="33" spans="2:8">
-      <c r="B33" s="3" t="s">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B33" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D33" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F33" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G33" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H33" s="2" t="s">
+      <c r="D33" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F33" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G33" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H33" s="1" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="34" spans="2:8">
-      <c r="B34" s="2" t="s">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B34" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="D34" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F34" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G34" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H34" s="2" t="s">
+      <c r="D34" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F34" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G34" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H34" s="1" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="35" spans="2:8">
-      <c r="B35" s="2" t="s">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B35" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="D35" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E35" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F35" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G35" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H35" s="2" t="s">
+      <c r="D35" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F35" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G35" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H35" s="1" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="36" spans="2:8">
-      <c r="B36" s="2" t="s">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B36" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D36" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F36" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G36" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H36" s="2" t="s">
+      <c r="D36" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F36" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G36" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H36" s="1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="37" spans="2:8">
-      <c r="B37" s="2" t="s">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B37" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="D37" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E37" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F37" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G37" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H37" s="2" t="s">
+      <c r="D37" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F37" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G37" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H37" s="1" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="38" spans="2:8">
-      <c r="B38" s="2" t="s">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B38" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="D38" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E38" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F38" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G38" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H38" s="2" t="s">
+      <c r="D38" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F38" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G38" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H38" s="1" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="39" spans="2:8">
-      <c r="B39" s="2" t="s">
+    <row r="39" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B39" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="D39" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E39" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F39" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G39" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H39" s="2" t="s">
+      <c r="D39" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F39" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G39" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H39" s="1" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="40" spans="2:8">
-      <c r="B40" s="2" t="s">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B40" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="D40" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E40" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F40" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G40" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H40" s="2" t="s">
+      <c r="D40" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F40" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G40" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H40" s="1" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="41" spans="2:8">
-      <c r="B41" s="2" t="s">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B41" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C41" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="D41" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E41" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F41" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G41" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H41" s="2" t="s">
+      <c r="D41" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F41" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G41" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H41" s="1" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="42" spans="2:8">
-      <c r="B42" s="2" t="s">
+    <row r="42" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B42" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C42" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D42" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E42" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F42" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G42" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H42" s="2" t="s">
+      <c r="D42" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F42" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G42" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H42" s="1" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="43" spans="2:8">
-      <c r="B43" s="2" t="s">
+    <row r="43" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B43" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C43" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="D43" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E43" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F43" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G43" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H43" s="2" t="s">
+      <c r="D43" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F43" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G43" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H43" s="1" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="44" spans="2:8">
-      <c r="B44" s="2" t="s">
+    <row r="44" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B44" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="C44" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="D44" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E44" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F44" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G44" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H44" s="2" t="s">
+      <c r="D44" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F44" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G44" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H44" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="45" spans="2:8">
-      <c r="B45" s="2" t="s">
+    <row r="45" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B45" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C45" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="D45" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E45" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F45" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G45" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H45" s="2" t="s">
+      <c r="D45" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F45" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G45" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H45" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="46" spans="2:8">
-      <c r="B46" s="2" t="s">
+    <row r="46" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B46" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C46" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="D46" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E46" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F46" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G46" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H46" s="2" t="s">
+      <c r="D46" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F46" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G46" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H46" s="1" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="47" spans="2:8">
-      <c r="B47" s="2" t="s">
+    <row r="47" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B47" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C47" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="D47" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E47" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F47" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G47" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H47" s="2" t="s">
+      <c r="D47" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F47" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G47" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H47" s="1" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="48" spans="2:8">
-      <c r="B48" s="2" t="s">
+    <row r="48" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B48" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C48" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="D48" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E48" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F48" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G48" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H48" s="2" t="s">
+      <c r="D48" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F48" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G48" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H48" s="1" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="49" spans="2:8">
-      <c r="B49" s="2" t="s">
+    <row r="49" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B49" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C49" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="D49" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E49" s="8" t="s">
+      <c r="D49" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E49" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="F49" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G49" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H49" s="2" t="s">
+      <c r="F49" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G49" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H49" s="1" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="50" spans="2:8">
-      <c r="B50" s="2" t="s">
+    <row r="50" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B50" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C50" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D50" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E50" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F50" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G50" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H50" s="2" t="s">
+      <c r="D50" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F50" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G50" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H50" s="1" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="51" spans="2:8">
-      <c r="B51" s="2" t="s">
+    <row r="51" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B51" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="C51" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="D51" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E51" s="8" t="s">
+      <c r="D51" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E51" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="F51" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G51" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H51" s="2" t="s">
+      <c r="F51" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G51" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H51" s="1" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="52" spans="2:8">
-      <c r="B52" s="2" t="s">
+    <row r="52" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B52" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C52" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="D52" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E52" s="8" t="s">
+      <c r="D52" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E52" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="F52" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G52" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H52" s="2" t="s">
+      <c r="F52" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G52" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H52" s="1" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="53" spans="2:8">
-      <c r="B53" s="2" t="s">
+    <row r="53" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B53" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="C53" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="D53" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E53" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F53" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G53" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H53" s="2" t="s">
+      <c r="D53" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F53" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G53" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H53" s="1" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="54" spans="2:8">
-      <c r="B54" s="2" t="s">
+    <row r="54" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B54" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C54" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D54" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E54" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F54" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G54" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H54" s="2" t="s">
+      <c r="D54" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F54" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G54" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H54" s="1" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="55" spans="2:8">
-      <c r="B55" s="2" t="s">
+    <row r="55" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B55" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C55" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="D55" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E55" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F55" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G55" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H55" s="2" t="s">
+      <c r="D55" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F55" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G55" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H55" s="1" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="56" spans="2:8">
-      <c r="B56" s="2" t="s">
+    <row r="56" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B56" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="C56" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="D56" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E56" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F56" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G56" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H56" s="2" t="s">
+      <c r="D56" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E56" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F56" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G56" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H56" s="1" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="57" spans="2:8">
-      <c r="B57" s="2" t="s">
+    <row r="57" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B57" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="C57" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="D57" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E57" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F57" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G57" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H57" s="2" t="s">
+      <c r="D57" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E57" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F57" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G57" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H57" s="1" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="58" spans="2:8">
-      <c r="B58" s="2" t="s">
+    <row r="58" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B58" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="C58" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="D58" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E58" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F58" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G58" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H58" s="2" t="s">
+      <c r="D58" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E58" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F58" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G58" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H58" s="1" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="59" spans="2:8">
-      <c r="B59" s="2" t="s">
+    <row r="59" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B59" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="C59" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="D59" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E59" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F59" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G59" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H59" s="2" t="s">
+      <c r="D59" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E59" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F59" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G59" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H59" s="1" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="60" spans="2:8">
-      <c r="B60" s="2" t="s">
+    <row r="60" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B60" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="C60" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="D60" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E60" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F60" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G60" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H60" s="2" t="s">
+      <c r="D60" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E60" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F60" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G60" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H60" s="1" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="61" spans="2:8">
-      <c r="B61" s="2" t="s">
+    <row r="61" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B61" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="C61" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="D61" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E61" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F61" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G61" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H61" s="2" t="s">
+      <c r="D61" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E61" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F61" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G61" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H61" s="1" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="62" spans="2:8">
-      <c r="B62" s="2" t="s">
+    <row r="62" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B62" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="C62" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="D62" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E62" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F62" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G62" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H62" s="2" t="s">
+      <c r="D62" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E62" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F62" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G62" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H62" s="1" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="63" spans="2:8">
-      <c r="B63" s="2" t="s">
+    <row r="63" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B63" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="C63" s="2" t="s">
+      <c r="C63" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="D63" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E63" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F63" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G63" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H63" s="2" t="s">
+      <c r="D63" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E63" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F63" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G63" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H63" s="1" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="64" spans="2:8">
-      <c r="B64" s="2" t="s">
+    <row r="64" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B64" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="C64" s="2" t="s">
+      <c r="C64" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="D64" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E64" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F64" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G64" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H64" s="2" t="s">
+      <c r="D64" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E64" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F64" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G64" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H64" s="1" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="65" spans="2:8">
-      <c r="B65" s="2" t="s">
+    <row r="65" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B65" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C65" s="2" t="s">
+      <c r="C65" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="D65" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E65" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F65" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G65" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H65" s="2" t="s">
+      <c r="D65" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E65" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F65" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G65" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H65" s="1" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="66" spans="2:8">
-      <c r="B66" s="2" t="s">
+    <row r="66" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B66" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="C66" s="2" t="s">
+      <c r="C66" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="D66" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E66" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F66" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G66" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H66" s="2" t="s">
+      <c r="D66" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E66" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F66" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G66" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H66" s="1" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="67" spans="2:8">
-      <c r="B67" s="2" t="s">
+    <row r="67" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B67" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="C67" s="2" t="s">
+      <c r="C67" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="D67" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E67" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F67" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G67" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H67" s="2" t="s">
+      <c r="D67" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E67" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F67" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G67" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H67" s="1" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="68" spans="2:8">
-      <c r="B68" s="2" t="s">
+    <row r="68" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B68" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="C68" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="D68" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E68" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F68" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G68" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H68" s="10" t="s">
+      <c r="D68" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E68" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F68" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G68" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H68" s="1" t="s">
         <v>221</v>
       </c>
     </row>
+    <row r="69" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B69" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="D69" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E69" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F69" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G69" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H69" s="9" t="s">
+        <v>224</v>
+      </c>
+    </row>
   </sheetData>
-  <printOptions>
-    <extLst>
-      <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1785223317" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
-      </ext>
-    </extLst>
-  </printOptions>
-  <pageMargins left="0.700000" right="0.700000" top="0.750000" bottom="0.750000" header="0.300000" footer="0.300000"/>
-  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="1"/>
-  <headerFooter>
-    <extLst>
-      <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1785223317" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1785223317" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1785223317" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1785223317" Id="1" type="0" value="0"/>
-      </ext>
-    </extLst>
-  </headerFooter>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" fitToWidth="0"/>
   <extLst>
     <ext uri="smNativeData">
       <pm:sheetPrefs xmlns:pm="smNativeData" day="1785223317" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">

--- a/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA8EC97F-97C2-4F4C-AA5A-1B1D3432CC63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5486BF9-3A2D-48EE-A630-11EECA62CBF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5050" yWindow="2500" windowWidth="31320" windowHeight="18380" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\Project\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA8EC97F-97C2-4F4C-AA5A-1B1D3432CC63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8E89F0E-C138-4A63-A608-7E4796840398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5050" yWindow="2500" windowWidth="31320" windowHeight="18380" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7930" yWindow="5960" windowWidth="28800" windowHeight="14360" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="230">
   <si>
     <t>##var</t>
   </si>
@@ -703,6 +703,26 @@
   </si>
   <si>
     <t>滴胶固化玩法</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>DressMakingSprayPaintGamePanel</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/DressMaking/DressMakingSprayPaintGamePanel.prefab</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>UIDown</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>UIPanel</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>服装制作-喷漆小游戏</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -721,20 +741,24 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF1F2329"/>
       <name val="等线"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="等线"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1122,7 +1146,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H69"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.6640625" style="1" customWidth="1"/>
@@ -2732,6 +2756,29 @@
         <v>224</v>
       </c>
     </row>
+    <row r="70" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B70" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="D70" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="E70" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="F70" s="4">
+        <v>1</v>
+      </c>
+      <c r="G70" s="4">
+        <v>0</v>
+      </c>
+      <c r="H70" s="9" t="s">
+        <v>229</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
@@ -1,16 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
-  <fileSharing readOnlyRecommended="0" userName="Lumino Game 03"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86D291EA-2B20-4255-9E59-6663190D86A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0" xWindow="240" yWindow="60" windowWidth="31320" windowHeight="18380" tabRatio="500"/>
+    <workbookView xWindow="4600" yWindow="2330" windowWidth="31320" windowHeight="18380" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext uri="smNativeData">
       <pm:revision xmlns:pm="smNativeData" day="1785315983" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
@@ -23,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="231">
   <si>
     <t>##var</t>
   </si>
@@ -707,85 +712,67 @@
   </si>
   <si>
     <t>服装制作喷漆小游戏</t>
+  </si>
+  <si>
+    <t>GemSmartSlicerUI</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/GemSmartSlicerUI/GemSmartSlicerUI.prefab</t>
+  </si>
+  <si>
+    <t>宝石切割小游戏</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
-    <numFmt numFmtId="5" formatCode="#,##0\ &quot;¥&quot;;\-#,##0\ &quot;¥&quot;"/>
-    <numFmt numFmtId="6" formatCode="#,##0\ &quot;¥&quot;;[Red]\-#,##0\ &quot;¥&quot;"/>
-    <numFmt numFmtId="7" formatCode="#,##0.00\ &quot;¥&quot;;\-#,##0.00\ &quot;¥&quot;"/>
-    <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;¥&quot;;[Red]\-#,##0.00\ &quot;¥&quot;"/>
-    <numFmt numFmtId="42" formatCode="_-* #,##0\ &quot;¥&quot;_-;\-* #,##0\ &quot;¥&quot;_-;_-* &quot;-&quot;\ &quot;¥&quot;_-;_-@_-"/>
-    <numFmt numFmtId="41" formatCode="_-* #,##0\ _¥_-;\-* #,##0\ _¥_-;_-* &quot;-&quot;\ _¥_-;_-@_-"/>
-    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;¥&quot;_-;\-* #,##0.00\ &quot;¥&quot;_-;_-* &quot;-&quot;??\ &quot;¥&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _¥_-;\-* #,##0.00\ _¥_-;_-* &quot;-&quot;??\ _¥_-;_-@_-"/>
-  </numFmts>
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="等线"/>
       <charset val="134"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1785315983" ulstyle="none" kern="1">
-            <pm:latin face="等线" sz="220" lang="default"/>
-            <pm:cs face="Times New Roman" sz="220" lang="default"/>
-            <pm:ea face="SimSun" sz="220" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
-      <name val="Arial"/>
-      <family val="2"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
-      <sz val="10"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1785315983" ulstyle="none" kern="1">
-            <pm:latin face="Arial" sz="200" lang="default"/>
-            <pm:cs face="Times New Roman" sz="200" lang="default"/>
-            <pm:ea face="SimSun" sz="200" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
+      <name val="等线"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF1F2329"/>
       <name val="等线"/>
-      <charset val="134"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1785315983" ulstyle="none" kern="1">
-            <pm:latin face="等线" sz="200" lang="default"/>
-            <pm:cs face="Times New Roman" sz="200" lang="default"/>
-            <pm:ea face="SimSun" sz="200" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="等线"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
-      <color rgb="FF1F2329"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1785315983" fgClr="1F2329" ulstyle="none" kern="1">
-            <pm:latin face="等线" sz="220" lang="default"/>
-            <pm:cs face="Times New Roman" sz="220" lang="default"/>
-            <pm:ea face="SimSun" sz="220" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -793,61 +780,25 @@
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
-      <patternFill patternType="none"/>
-    </fill>
-    <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFACB9CA"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1785315983" type="1" fgLvl="100" fgClr="00ACB9CA" bgLvl="0" bgClr="00FFFFFF"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF5B9BD5"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1785315983" type="1" fgLvl="100" fgClr="005B9BD5" bgLvl="0" bgClr="00FFFFFF"/>
-          </ext>
-        </extLst>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1785315983" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="4">
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1785315983"/>
-        </ext>
-      </extLst>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -862,120 +813,75 @@
       <bottom style="thin">
         <color rgb="FFDEE0E3"/>
       </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1785315983">
-            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-          </pm:border>
-        </ext>
-      </extLst>
+      <diagonal/>
     </border>
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1785315983"/>
-        </ext>
-      </extLst>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1785315983"/>
-        </ext>
-      </extLst>
-    </border>
-    <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1785315983"/>
-        </ext>
-      </extLst>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
-    <cellStyle name="常规 2" xfId="1"/>
+    <cellStyle name="常规" xfId="0" builtinId="0" customBuiltin="1"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0"/>
   <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
     <ext uri="smNativeData">
       <pm:charStyles xmlns:pm="smNativeData" id="1785315983" count="1">
         <pm:charStyle name="普通" fontId="0" Id="1"/>
@@ -1246,1659 +1152,1667 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:H70"/>
-  <sheetFormatPr defaultRowHeight="13.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H71"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.663793" customWidth="1" style="2"/>
-    <col min="2" max="2" width="28.577586" customWidth="1" style="2"/>
-    <col min="3" max="3" width="100.077586" customWidth="1" style="2"/>
-    <col min="4" max="4" width="25.163793" customWidth="1" style="2"/>
-    <col min="5" max="5" width="23.663793" customWidth="1" style="2"/>
-    <col min="6" max="7" width="17.663793" customWidth="1" style="2"/>
-    <col min="8" max="8" width="24.163793" customWidth="1" style="2"/>
-    <col min="9" max="16384" width="8.663793" customWidth="1" style="2"/>
+    <col min="1" max="1" width="8.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="28.58203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="100.08203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="25.1640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="23.6640625" style="1" customWidth="1"/>
+    <col min="6" max="7" width="17.6640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="24.1640625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="4" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="2:8">
-      <c r="B4" s="3" t="s">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G4" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H4" s="2" t="s">
+      <c r="D4" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="2:8">
-      <c r="B5" s="3" t="s">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G5" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H5" s="5" t="s">
+      <c r="D5" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="19.50" customHeight="1">
-      <c r="B6" s="3" t="s">
+    <row r="6" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="8" t="s">
+      <c r="D6" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G6" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H6" s="5" t="s">
+      <c r="F6" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="2:8">
-      <c r="B7" s="3" t="s">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B7" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G7" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H7" s="5" t="s">
+      <c r="D7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="2:8">
-      <c r="B8" s="3" t="s">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G8" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H8" s="5" t="s">
+      <c r="D8" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" s="4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="2:8">
-      <c r="B9" s="3" t="s">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B9" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G9" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H9" s="5" t="s">
+      <c r="D9" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="2:8">
-      <c r="B10" s="3" t="s">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B10" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F10" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G10" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H10" s="5" t="s">
+      <c r="F10" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="2:8">
-      <c r="B11" s="3" t="s">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B11" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="F11" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G11" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H11" s="5" t="s">
+      <c r="F11" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H11" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="12" spans="2:8">
-      <c r="B12" s="3" t="s">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B12" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F12" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G12" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H12" s="5" t="s">
+      <c r="D12" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H12" s="4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="13" spans="2:8">
-      <c r="B13" s="3" t="s">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B13" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F13" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G13" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H13" s="5" t="s">
+      <c r="D13" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" s="4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="14" spans="2:8">
-      <c r="B14" s="3" t="s">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B14" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E14" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="F14" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G14" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H14" s="5" t="s">
+      <c r="F14" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G14" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" s="4" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="15" spans="2:8">
-      <c r="B15" s="3" t="s">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B15" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E15" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F15" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G15" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H15" s="5" t="s">
+      <c r="E15" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H15" s="4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="16" spans="2:8">
-      <c r="B16" s="3" t="s">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B16" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D16" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E16" s="8" t="s">
+      <c r="D16" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F16" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G16" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H16" s="5" t="s">
+      <c r="F16" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H16" s="4" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="17" spans="2:8">
-      <c r="B17" s="3" t="s">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B17" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D17" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F17" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G17" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H17" s="5" t="s">
+      <c r="D17" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G17" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="2:8">
-      <c r="B18" s="3" t="s">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B18" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D18" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E18" s="8" t="s">
+      <c r="D18" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F18" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G18" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H18" s="5" t="s">
+      <c r="F18" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G18" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H18" s="4" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="2:8">
-      <c r="B19" s="3" t="s">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B19" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D19" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F19" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G19" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H19" s="5" t="s">
+      <c r="D19" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F19" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H19" s="4" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="20" spans="2:8">
-      <c r="B20" s="3" t="s">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B20" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="D20" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F20" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G20" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H20" s="5" t="s">
+      <c r="D20" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F20" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" s="4" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="21" spans="2:8">
-      <c r="B21" s="3" t="s">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B21" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="D21" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F21" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G21" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H21" s="5" t="s">
+      <c r="D21" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" s="4" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="22" spans="2:8">
-      <c r="B22" s="3" t="s">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B22" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C22" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="D22" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F22" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G22" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H22" s="5" t="s">
+      <c r="D22" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F22" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H22" s="4" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="23" spans="2:8">
-      <c r="B23" s="3" t="s">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B23" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D23" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F23" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G23" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H23" s="5" t="s">
+      <c r="D23" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H23" s="4" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="24" spans="2:8">
-      <c r="B24" s="3" t="s">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B24" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="D24" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F24" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G24" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H24" s="5" t="s">
+      <c r="D24" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F24" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H24" s="4" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="25" spans="2:8">
-      <c r="B25" s="3" t="s">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B25" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="D25" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F25" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G25" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H25" s="5" t="s">
+      <c r="D25" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F25" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H25" s="4" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="26" spans="2:8">
-      <c r="B26" s="3" t="s">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B26" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="C26" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="D26" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F26" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H26" s="5" t="s">
+      <c r="D26" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F26" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H26" s="4" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="27" spans="2:8">
-      <c r="B27" s="3" t="s">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B27" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="C27" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="D27" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F27" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G27" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H27" s="5" t="s">
+      <c r="D27" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F27" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G27" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H27" s="4" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="28" spans="2:8">
-      <c r="B28" s="3" t="s">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B28" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C28" s="9" t="s">
+      <c r="C28" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="D28" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F28" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G28" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H28" s="5" t="s">
+      <c r="D28" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F28" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G28" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H28" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="29" spans="2:8">
-      <c r="B29" s="3" t="s">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B29" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="D29" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F29" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G29" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H29" s="2" t="s">
+      <c r="D29" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F29" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G29" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H29" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="30" spans="2:8">
-      <c r="B30" s="3" t="s">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B30" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="D30" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F30" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G30" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H30" s="2" t="s">
+      <c r="D30" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F30" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G30" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H30" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="31" spans="2:8">
-      <c r="B31" s="3" t="s">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B31" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="D31" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F31" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G31" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H31" s="2" t="s">
+      <c r="D31" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F31" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G31" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H31" s="1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="32" spans="2:8">
-      <c r="B32" s="3" t="s">
+    <row r="32" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B32" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="D32" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F32" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G32" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H32" s="2" t="s">
+      <c r="D32" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F32" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G32" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H32" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="33" spans="2:8">
-      <c r="B33" s="3" t="s">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B33" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D33" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F33" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G33" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H33" s="2" t="s">
+      <c r="D33" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F33" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G33" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H33" s="1" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="34" spans="2:8">
-      <c r="B34" s="2" t="s">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B34" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="D34" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F34" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G34" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H34" s="2" t="s">
+      <c r="D34" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F34" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G34" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H34" s="1" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="35" spans="2:8">
-      <c r="B35" s="2" t="s">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B35" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="D35" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E35" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F35" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G35" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H35" s="2" t="s">
+      <c r="D35" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F35" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G35" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H35" s="1" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="36" spans="2:8">
-      <c r="B36" s="2" t="s">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B36" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D36" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F36" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G36" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H36" s="2" t="s">
+      <c r="D36" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F36" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G36" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H36" s="1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="37" spans="2:8">
-      <c r="B37" s="2" t="s">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B37" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="D37" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E37" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F37" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G37" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H37" s="2" t="s">
+      <c r="D37" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F37" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G37" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H37" s="1" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="38" spans="2:8">
-      <c r="B38" s="2" t="s">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B38" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="D38" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E38" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F38" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G38" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H38" s="2" t="s">
+      <c r="D38" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F38" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G38" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H38" s="1" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="39" spans="2:8">
-      <c r="B39" s="2" t="s">
+    <row r="39" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B39" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="D39" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E39" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F39" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G39" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H39" s="2" t="s">
+      <c r="D39" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F39" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G39" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H39" s="1" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="40" spans="2:8">
-      <c r="B40" s="2" t="s">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B40" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="D40" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E40" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F40" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G40" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H40" s="2" t="s">
+      <c r="D40" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F40" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G40" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H40" s="1" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="41" spans="2:8">
-      <c r="B41" s="2" t="s">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B41" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C41" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="D41" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E41" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F41" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G41" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H41" s="2" t="s">
+      <c r="D41" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F41" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G41" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H41" s="1" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="42" spans="2:8">
-      <c r="B42" s="2" t="s">
+    <row r="42" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B42" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C42" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D42" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E42" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F42" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G42" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H42" s="2" t="s">
+      <c r="D42" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F42" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G42" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H42" s="1" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="43" spans="2:8">
-      <c r="B43" s="2" t="s">
+    <row r="43" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B43" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C43" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="D43" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E43" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F43" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G43" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H43" s="2" t="s">
+      <c r="D43" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F43" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G43" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H43" s="1" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="44" spans="2:8">
-      <c r="B44" s="2" t="s">
+    <row r="44" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B44" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="C44" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="D44" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E44" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F44" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G44" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H44" s="2" t="s">
+      <c r="D44" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F44" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G44" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H44" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="45" spans="2:8">
-      <c r="B45" s="2" t="s">
+    <row r="45" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B45" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C45" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="D45" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E45" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F45" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G45" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H45" s="2" t="s">
+      <c r="D45" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F45" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G45" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H45" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="46" spans="2:8">
-      <c r="B46" s="2" t="s">
+    <row r="46" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B46" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C46" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="D46" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E46" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F46" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G46" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H46" s="2" t="s">
+      <c r="D46" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F46" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G46" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H46" s="1" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="47" spans="2:8">
-      <c r="B47" s="2" t="s">
+    <row r="47" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B47" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C47" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="D47" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E47" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F47" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G47" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H47" s="2" t="s">
+      <c r="D47" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F47" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G47" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H47" s="1" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="48" spans="2:8">
-      <c r="B48" s="2" t="s">
+    <row r="48" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B48" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C48" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="D48" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E48" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F48" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G48" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H48" s="2" t="s">
+      <c r="D48" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F48" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G48" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H48" s="1" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="49" spans="2:8">
-      <c r="B49" s="2" t="s">
+    <row r="49" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B49" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C49" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="D49" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E49" s="8" t="s">
+      <c r="D49" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E49" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="F49" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G49" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H49" s="2" t="s">
+      <c r="F49" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G49" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H49" s="1" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="50" spans="2:8">
-      <c r="B50" s="2" t="s">
+    <row r="50" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B50" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C50" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D50" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E50" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F50" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G50" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H50" s="2" t="s">
+      <c r="D50" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F50" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G50" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H50" s="1" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="51" spans="2:8">
-      <c r="B51" s="2" t="s">
+    <row r="51" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B51" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="C51" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="D51" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E51" s="8" t="s">
+      <c r="D51" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E51" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="F51" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G51" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H51" s="2" t="s">
+      <c r="F51" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G51" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H51" s="1" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="52" spans="2:8">
-      <c r="B52" s="2" t="s">
+    <row r="52" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B52" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C52" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="D52" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E52" s="8" t="s">
+      <c r="D52" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E52" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="F52" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G52" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H52" s="2" t="s">
+      <c r="F52" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G52" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H52" s="1" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="53" spans="2:8">
-      <c r="B53" s="2" t="s">
+    <row r="53" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B53" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="C53" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="D53" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E53" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F53" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G53" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H53" s="2" t="s">
+      <c r="D53" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F53" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G53" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H53" s="1" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="54" spans="2:8">
-      <c r="B54" s="2" t="s">
+    <row r="54" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B54" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C54" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D54" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E54" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F54" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G54" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H54" s="2" t="s">
+      <c r="D54" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F54" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G54" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H54" s="1" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="55" spans="2:8">
-      <c r="B55" s="2" t="s">
+    <row r="55" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B55" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C55" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="D55" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E55" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F55" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G55" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H55" s="2" t="s">
+      <c r="D55" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F55" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G55" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H55" s="1" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="56" spans="2:8">
-      <c r="B56" s="2" t="s">
+    <row r="56" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B56" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="C56" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="D56" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E56" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F56" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G56" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H56" s="2" t="s">
+      <c r="D56" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E56" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F56" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G56" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H56" s="1" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="57" spans="2:8">
-      <c r="B57" s="2" t="s">
+    <row r="57" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B57" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="C57" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="D57" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E57" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F57" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G57" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H57" s="2" t="s">
+      <c r="D57" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E57" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F57" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G57" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H57" s="1" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="58" spans="2:8">
-      <c r="B58" s="2" t="s">
+    <row r="58" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B58" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="C58" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="D58" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E58" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F58" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G58" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H58" s="2" t="s">
+      <c r="D58" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E58" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F58" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G58" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H58" s="1" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="59" spans="2:8">
-      <c r="B59" s="2" t="s">
+    <row r="59" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B59" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="C59" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="D59" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E59" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F59" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G59" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H59" s="2" t="s">
+      <c r="D59" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E59" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F59" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G59" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H59" s="1" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="60" spans="2:8">
-      <c r="B60" s="2" t="s">
+    <row r="60" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B60" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="C60" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="D60" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E60" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F60" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G60" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H60" s="2" t="s">
+      <c r="D60" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E60" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F60" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G60" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H60" s="1" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="61" spans="2:8">
-      <c r="B61" s="2" t="s">
+    <row r="61" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B61" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="C61" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="D61" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E61" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F61" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G61" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H61" s="2" t="s">
+      <c r="D61" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E61" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F61" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G61" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H61" s="1" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="62" spans="2:8">
-      <c r="B62" s="2" t="s">
+    <row r="62" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B62" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="C62" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="D62" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E62" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F62" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G62" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H62" s="2" t="s">
+      <c r="D62" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E62" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F62" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G62" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H62" s="1" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="63" spans="2:8">
-      <c r="B63" s="2" t="s">
+    <row r="63" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B63" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="C63" s="2" t="s">
+      <c r="C63" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="D63" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E63" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F63" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G63" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H63" s="2" t="s">
+      <c r="D63" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E63" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F63" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G63" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H63" s="1" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="64" spans="2:8">
-      <c r="B64" s="2" t="s">
+    <row r="64" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B64" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="C64" s="2" t="s">
+      <c r="C64" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="D64" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E64" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F64" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G64" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H64" s="2" t="s">
+      <c r="D64" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E64" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F64" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G64" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H64" s="1" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="65" spans="2:8">
-      <c r="B65" s="2" t="s">
+    <row r="65" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B65" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C65" s="2" t="s">
+      <c r="C65" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="D65" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E65" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F65" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G65" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H65" s="2" t="s">
+      <c r="D65" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E65" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F65" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G65" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H65" s="1" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="66" spans="2:8">
-      <c r="B66" s="2" t="s">
+    <row r="66" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B66" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="C66" s="2" t="s">
+      <c r="C66" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="D66" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E66" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F66" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G66" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H66" s="2" t="s">
+      <c r="D66" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E66" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F66" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G66" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H66" s="1" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="67" spans="2:8">
-      <c r="B67" s="2" t="s">
+    <row r="67" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B67" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="C67" s="2" t="s">
+      <c r="C67" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="D67" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E67" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F67" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G67" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H67" s="2" t="s">
+      <c r="D67" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E67" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F67" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G67" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H67" s="1" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="68" spans="2:8">
-      <c r="B68" s="2" t="s">
+    <row r="68" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B68" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="C68" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="D68" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E68" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F68" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G68" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H68" s="2" t="s">
+      <c r="D68" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E68" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F68" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G68" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H68" s="1" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="69" spans="2:8">
-      <c r="B69" s="2" t="s">
+    <row r="69" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B69" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="C69" s="2" t="s">
+      <c r="C69" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="D69" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E69" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F69" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G69" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H69" s="10" t="s">
+      <c r="D69" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E69" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F69" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G69" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H69" s="1" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="70" spans="2:8">
-      <c r="B70" s="2" t="s">
+    <row r="70" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B70" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="C70" s="2" t="s">
+      <c r="C70" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="D70" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F70" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" s="2" t="s">
+      <c r="D70" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F70" s="1">
+        <v>1</v>
+      </c>
+      <c r="G70" s="1">
+        <v>0</v>
+      </c>
+      <c r="H70" s="1" t="s">
         <v>227</v>
       </c>
     </row>
+    <row r="71" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B71" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C71" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F71" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G71" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H71" s="10" t="s">
+        <v>230</v>
+      </c>
+    </row>
   </sheetData>
-  <printOptions>
-    <extLst>
-      <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1785315983" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
-      </ext>
-    </extLst>
-  </printOptions>
-  <pageMargins left="0.700000" right="0.700000" top="0.750000" bottom="0.750000" header="0.300000" footer="0.300000"/>
-  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="1"/>
-  <headerFooter>
-    <extLst>
-      <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1785315983" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1785315983" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1785315983" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1785315983" Id="1" type="0" value="0"/>
-      </ext>
-    </extLst>
-  </headerFooter>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" fitToWidth="0"/>
   <extLst>
     <ext uri="smNativeData">
       <pm:sheetPrefs xmlns:pm="smNativeData" day="1785315983" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">

--- a/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{667CE561-578A-4B4B-824A-6F3CD98DF76F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29435D31-B3D7-4AA6-8259-81F8A3E33875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4600" yWindow="2330" windowWidth="31320" windowHeight="18380" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="2500" windowWidth="37150" windowHeight="18380" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="231">
   <si>
     <t>##var</t>
   </si>
@@ -715,6 +715,16 @@
   </si>
   <si>
     <t>UITop</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>RacingCarSewingMachinesUI</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/RacingCarSewingMachinesUI/RacingCarSewingMachinesUI.prefab</t>
+  </si>
+  <si>
+    <t>如龙赛车小游戏</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -1144,7 +1154,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.6640625" style="1" customWidth="1"/>
@@ -2586,6 +2596,26 @@
         <v>224</v>
       </c>
     </row>
+    <row r="72" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B72" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E72" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F72" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G72" s="9" t="s">
+        <v>230</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
@@ -1,16 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
-  <fileSharing readOnlyRecommended="0" userName="Lumino Game 03"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C40B2B0D-AF6D-413C-8031-49C0CA4132F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0" xWindow="240" yWindow="60" windowWidth="37150" windowHeight="18380" tabRatio="500"/>
+    <workbookView xWindow="510" yWindow="4380" windowWidth="37150" windowHeight="18380" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext uri="smNativeData">
       <pm:revision xmlns:pm="smNativeData" day="1785722958" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
@@ -23,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="237">
   <si>
     <t>##var</t>
   </si>
@@ -725,101 +730,63 @@
   </si>
   <si>
     <t>服装制作刺绣填色小游戏</t>
+  </si>
+  <si>
+    <t>UpperBodyUI</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/UpperBodyUI/Prefabs/UpperBodyUI.prefab</t>
+  </si>
+  <si>
+    <t>服装上身小游戏</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
-    <numFmt numFmtId="5" formatCode="#,##0\ &quot;¥&quot;;\-#,##0\ &quot;¥&quot;"/>
-    <numFmt numFmtId="6" formatCode="#,##0\ &quot;¥&quot;;[Red]\-#,##0\ &quot;¥&quot;"/>
-    <numFmt numFmtId="7" formatCode="#,##0.00\ &quot;¥&quot;;\-#,##0.00\ &quot;¥&quot;"/>
-    <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;¥&quot;;[Red]\-#,##0.00\ &quot;¥&quot;"/>
-    <numFmt numFmtId="42" formatCode="_-* #,##0\ &quot;¥&quot;_-;\-* #,##0\ &quot;¥&quot;_-;_-* &quot;-&quot;\ &quot;¥&quot;_-;_-@_-"/>
-    <numFmt numFmtId="41" formatCode="_-* #,##0\ _¥_-;\-* #,##0\ _¥_-;_-* &quot;-&quot;\ _¥_-;_-@_-"/>
-    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;¥&quot;_-;\-* #,##0.00\ &quot;¥&quot;_-;_-* &quot;-&quot;??\ &quot;¥&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _¥_-;\-* #,##0.00\ _¥_-;_-* &quot;-&quot;??\ _¥_-;_-@_-"/>
-  </numFmts>
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="等线"/>
       <charset val="134"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1785722958" ulstyle="none" kern="1">
-            <pm:latin face="等线" sz="220" lang="default"/>
-            <pm:cs face="Times New Roman" sz="220" lang="default"/>
-            <pm:ea face="SimSun" sz="220" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
-      <name val="Arial"/>
-      <family val="2"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
-      <sz val="10"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1785722958" ulstyle="none" kern="1">
-            <pm:latin face="Arial" sz="200" lang="default"/>
-            <pm:cs face="Times New Roman" sz="200" lang="default"/>
-            <pm:ea face="SimSun" sz="200" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
+      <name val="等线"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF1F2329"/>
       <name val="等线"/>
-      <charset val="134"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1785722958" ulstyle="none" kern="1">
-            <pm:latin face="等线" sz="200" lang="default"/>
-            <pm:cs face="Times New Roman" sz="200" lang="default"/>
-            <pm:ea face="SimSun" sz="200" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="等线"/>
-      <charset val="134"/>
-      <color rgb="FF1F2329"/>
-      <sz val="11"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1785722958" fgClr="1F2329" ulstyle="none" kern="1">
-            <pm:latin face="等线" sz="220" lang="default"/>
-            <pm:cs face="Times New Roman" sz="220" lang="default"/>
-            <pm:ea face="SimSun" sz="220" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="等线"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
-      <b/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1785722958" ulstyle="none" kern="1">
-            <pm:latin face="等线" sz="220" lang="default" weight="bold"/>
-            <pm:cs face="Times New Roman" sz="220" lang="default" weight="bold"/>
-            <pm:ea face="SimSun" sz="220" lang="default" weight="bold"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -827,39 +794,19 @@
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
-      <patternFill patternType="none"/>
-    </fill>
-    <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF5B9BD5"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1785722958" type="1" fgLvl="100" fgClr="005B9BD5" bgLvl="0" bgClr="00FFFFFF"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
   </fills>
   <borders count="3">
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1785722958"/>
-        </ext>
-      </extLst>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -874,85 +821,65 @@
       <bottom style="thin">
         <color rgb="FFDEE0E3"/>
       </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1785722958">
-            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-          </pm:border>
-        </ext>
-      </extLst>
+      <diagonal/>
     </border>
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1785722958"/>
-        </ext>
-      </extLst>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
-    <cellStyle name="常规 2" xfId="1"/>
+    <cellStyle name="常规" xfId="0" builtinId="0" customBuiltin="1"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0"/>
   <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
     <ext uri="smNativeData">
       <pm:charStyles xmlns:pm="smNativeData" id="1785722958" count="1">
         <pm:charStyle name="普通" fontId="0" Id="1"/>
@@ -1222,1508 +1149,1513 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:G73"/>
-  <sheetFormatPr defaultRowHeight="13.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G74"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.663793" customWidth="1" style="2"/>
-    <col min="2" max="2" width="28.577586" customWidth="1" style="2"/>
-    <col min="3" max="3" width="100.077586" customWidth="1" style="2"/>
-    <col min="4" max="4" width="23.663793" customWidth="1" style="2"/>
-    <col min="5" max="6" width="17.663793" customWidth="1" style="2"/>
-    <col min="7" max="7" width="24.163793" customWidth="1" style="2"/>
-    <col min="8" max="16384" width="8.663793" customWidth="1" style="2"/>
+    <col min="1" max="1" width="8.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="28.58203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="100.08203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="23.6640625" style="1" customWidth="1"/>
+    <col min="5" max="6" width="17.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="24.1640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="8.6640625" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="4" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="2:7">
-      <c r="B4" s="3" t="s">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F4" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G4" s="2" t="s">
+      <c r="D4" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="2:7">
-      <c r="B5" s="3" t="s">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F5" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G5" s="5" t="s">
+      <c r="D5" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="2:7" ht="19.50" customHeight="1">
-      <c r="B6" s="3" t="s">
+    <row r="6" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F6" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G6" s="5" t="s">
+      <c r="E6" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="2:7">
-      <c r="B7" s="3" t="s">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B7" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F7" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G7" s="5" t="s">
+      <c r="D7" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="2:7">
-      <c r="B8" s="3" t="s">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F8" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G8" s="5" t="s">
+      <c r="D8" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F8" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" s="4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="2:7">
-      <c r="B9" s="3" t="s">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B9" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F9" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G9" s="5" t="s">
+      <c r="D9" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F9" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" s="4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="2:7">
-      <c r="B10" s="3" t="s">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B10" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E10" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F10" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G10" s="5" t="s">
+      <c r="E10" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F10" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="2:7">
-      <c r="B11" s="3" t="s">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B11" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="E11" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F11" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G11" s="5" t="s">
+      <c r="E11" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F11" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="2:7">
-      <c r="B12" s="3" t="s">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B12" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E12" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F12" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G12" s="5" t="s">
+      <c r="D12" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F12" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="13" spans="2:7">
-      <c r="B13" s="3" t="s">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B13" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D13" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E13" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F13" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G13" s="5" t="s">
+      <c r="D13" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F13" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G13" s="4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="14" spans="2:7">
-      <c r="B14" s="3" t="s">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B14" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E14" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F14" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G14" s="5" t="s">
+      <c r="E14" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F14" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G14" s="4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="15" spans="2:7">
-      <c r="B15" s="3" t="s">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B15" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D15" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E15" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F15" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G15" s="5" t="s">
+      <c r="D15" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F15" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15" s="4" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="16" spans="2:7">
-      <c r="B16" s="3" t="s">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B16" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E16" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F16" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G16" s="5" t="s">
+      <c r="E16" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F16" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G16" s="4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="17" spans="2:7">
-      <c r="B17" s="3" t="s">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B17" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D17" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E17" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F17" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G17" s="5" t="s">
+      <c r="D17" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F17" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17" s="4" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="18" spans="2:7">
-      <c r="B18" s="3" t="s">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B18" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="D18" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E18" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F18" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G18" s="5" t="s">
+      <c r="E18" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F18" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G18" s="4" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="2:7">
-      <c r="B19" s="3" t="s">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B19" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D19" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E19" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F19" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G19" s="5" t="s">
+      <c r="D19" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E19" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F19" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="20" spans="2:7">
-      <c r="B20" s="3" t="s">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B20" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D20" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E20" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F20" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G20" s="5" t="s">
+      <c r="D20" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E20" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F20" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" s="4" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="21" spans="2:7">
-      <c r="B21" s="3" t="s">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B21" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="D21" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E21" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F21" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G21" s="5" t="s">
+      <c r="D21" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E21" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F21" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="22" spans="2:7">
-      <c r="B22" s="3" t="s">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B22" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="D22" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E22" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F22" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G22" s="5" t="s">
+      <c r="D22" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E22" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F22" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="23" spans="2:7">
-      <c r="B23" s="3" t="s">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B23" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="D23" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E23" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F23" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G23" s="5" t="s">
+      <c r="D23" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E23" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F23" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" s="4" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="24" spans="2:7">
-      <c r="B24" s="3" t="s">
+    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B24" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="D24" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E24" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F24" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G24" s="5" t="s">
+      <c r="D24" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E24" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F24" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" s="4" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="25" spans="2:7">
-      <c r="B25" s="3" t="s">
+    <row r="25" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B25" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="D25" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E25" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F25" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G25" s="5" t="s">
+      <c r="D25" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E25" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F25" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="26" spans="2:7">
-      <c r="B26" s="3" t="s">
+    <row r="26" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B26" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C26" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="D26" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E26" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F26" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="5" t="s">
+      <c r="D26" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E26" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F26" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26" s="4" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="27" spans="2:7">
-      <c r="B27" s="3" t="s">
+    <row r="27" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B27" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="D27" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E27" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F27" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G27" s="5" t="s">
+      <c r="D27" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E27" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F27" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G27" s="4" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="28" spans="2:7">
-      <c r="B28" s="3" t="s">
+    <row r="28" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B28" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="C28" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="D28" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E28" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F28" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G28" s="5" t="s">
+      <c r="D28" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E28" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F28" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G28" s="4" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="29" spans="2:7">
-      <c r="B29" s="3" t="s">
+    <row r="29" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B29" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="D29" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E29" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F29" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G29" s="2" t="s">
+      <c r="D29" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E29" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F29" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G29" s="1" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="2:7">
-      <c r="B30" s="3" t="s">
+    <row r="30" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B30" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="D30" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E30" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F30" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G30" s="2" t="s">
+      <c r="D30" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E30" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F30" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G30" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="31" spans="2:7">
-      <c r="B31" s="3" t="s">
+    <row r="31" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B31" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="D31" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E31" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F31" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G31" s="2" t="s">
+      <c r="D31" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E31" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F31" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G31" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="32" spans="2:7">
-      <c r="B32" s="3" t="s">
+    <row r="32" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B32" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="D32" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E32" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F32" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G32" s="2" t="s">
+      <c r="D32" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E32" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F32" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G32" s="1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="33" spans="2:7">
-      <c r="B33" s="3" t="s">
+    <row r="33" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B33" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="D33" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E33" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F33" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G33" s="2" t="s">
+      <c r="D33" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E33" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F33" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G33" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="34" spans="2:7">
-      <c r="B34" s="2" t="s">
+    <row r="34" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B34" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D34" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E34" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F34" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G34" s="2" t="s">
+      <c r="D34" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E34" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F34" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G34" s="1" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="35" spans="2:7">
-      <c r="B35" s="2" t="s">
+    <row r="35" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B35" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="D35" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E35" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F35" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G35" s="2" t="s">
+      <c r="D35" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E35" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F35" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G35" s="1" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="36" spans="2:7">
-      <c r="B36" s="2" t="s">
+    <row r="36" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B36" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="D36" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E36" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F36" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G36" s="2" t="s">
+      <c r="D36" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E36" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F36" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G36" s="1" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="37" spans="2:7">
-      <c r="B37" s="2" t="s">
+    <row r="37" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B37" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D37" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E37" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F37" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G37" s="2" t="s">
+      <c r="D37" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E37" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F37" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G37" s="1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="38" spans="2:7">
-      <c r="B38" s="2" t="s">
+    <row r="38" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B38" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="D38" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E38" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F38" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G38" s="2" t="s">
+      <c r="D38" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E38" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F38" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G38" s="1" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="39" spans="2:7">
-      <c r="B39" s="2" t="s">
+    <row r="39" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B39" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="D39" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E39" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F39" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G39" s="2" t="s">
+      <c r="D39" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E39" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F39" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G39" s="1" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="40" spans="2:7">
-      <c r="B40" s="2" t="s">
+    <row r="40" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B40" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="D40" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E40" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F40" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G40" s="2" t="s">
+      <c r="D40" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E40" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F40" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G40" s="1" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="41" spans="2:7">
-      <c r="B41" s="2" t="s">
+    <row r="41" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B41" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C41" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="D41" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E41" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F41" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G41" s="2" t="s">
+      <c r="D41" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E41" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F41" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G41" s="1" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="42" spans="2:7">
-      <c r="B42" s="2" t="s">
+    <row r="42" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B42" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C42" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="D42" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E42" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F42" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G42" s="2" t="s">
+      <c r="D42" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E42" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F42" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G42" s="1" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="43" spans="2:7">
-      <c r="B43" s="2" t="s">
+    <row r="43" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B43" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C43" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D43" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E43" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F43" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G43" s="2" t="s">
+      <c r="D43" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E43" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F43" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G43" s="1" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="44" spans="2:7">
-      <c r="B44" s="2" t="s">
+    <row r="44" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B44" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="C44" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="D44" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E44" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F44" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G44" s="2" t="s">
+      <c r="D44" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E44" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F44" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G44" s="1" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="45" spans="2:7">
-      <c r="B45" s="2" t="s">
+    <row r="45" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B45" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C45" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="D45" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E45" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F45" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G45" s="2" t="s">
+      <c r="D45" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E45" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F45" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G45" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="46" spans="2:7">
-      <c r="B46" s="2" t="s">
+    <row r="46" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B46" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C46" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="D46" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E46" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F46" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G46" s="2" t="s">
+      <c r="D46" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E46" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F46" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G46" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="47" spans="2:7">
-      <c r="B47" s="2" t="s">
+    <row r="47" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B47" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C47" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="D47" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E47" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F47" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G47" s="2" t="s">
+      <c r="D47" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E47" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F47" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G47" s="1" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="48" spans="2:7">
-      <c r="B48" s="2" t="s">
+    <row r="48" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B48" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C48" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="D48" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E48" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F48" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G48" s="2" t="s">
+      <c r="D48" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E48" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F48" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G48" s="1" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="49" spans="2:7">
-      <c r="B49" s="2" t="s">
+    <row r="49" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B49" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C49" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="D49" s="7" t="s">
+      <c r="D49" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="E49" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F49" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G49" s="2" t="s">
+      <c r="E49" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F49" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G49" s="1" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="50" spans="2:7">
-      <c r="B50" s="2" t="s">
+    <row r="50" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B50" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C50" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="D50" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E50" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F50" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G50" s="2" t="s">
+      <c r="D50" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E50" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F50" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G50" s="1" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="51" spans="2:7">
-      <c r="B51" s="2" t="s">
+    <row r="51" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B51" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="C51" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D51" s="7" t="s">
+      <c r="D51" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="E51" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F51" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G51" s="2" t="s">
+      <c r="E51" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F51" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G51" s="1" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="52" spans="2:7">
-      <c r="B52" s="2" t="s">
+    <row r="52" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B52" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C52" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="D52" s="7" t="s">
+      <c r="D52" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="E52" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F52" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G52" s="2" t="s">
+      <c r="E52" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F52" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G52" s="1" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="53" spans="2:7">
-      <c r="B53" s="2" t="s">
+    <row r="53" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B53" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="C53" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="D53" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E53" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F53" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G53" s="2" t="s">
+      <c r="D53" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E53" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F53" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G53" s="1" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="54" spans="2:7">
-      <c r="B54" s="2" t="s">
+    <row r="54" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B54" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C54" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="D54" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E54" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F54" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G54" s="2" t="s">
+      <c r="D54" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E54" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F54" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G54" s="1" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="55" spans="2:7">
-      <c r="B55" s="2" t="s">
+    <row r="55" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B55" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C55" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D55" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E55" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F55" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G55" s="2" t="s">
+      <c r="D55" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E55" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F55" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G55" s="1" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="56" spans="2:7">
-      <c r="B56" s="2" t="s">
+    <row r="56" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B56" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="C56" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="D56" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E56" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F56" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G56" s="2" t="s">
+      <c r="D56" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E56" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F56" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G56" s="1" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="57" spans="2:7">
-      <c r="B57" s="2" t="s">
+    <row r="57" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B57" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="C57" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="D57" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E57" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F57" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G57" s="2" t="s">
+      <c r="D57" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E57" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F57" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G57" s="1" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="58" spans="2:7">
-      <c r="B58" s="2" t="s">
+    <row r="58" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B58" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="C58" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="D58" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E58" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F58" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G58" s="2" t="s">
+      <c r="D58" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E58" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F58" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G58" s="1" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="59" spans="2:7">
-      <c r="B59" s="2" t="s">
+    <row r="59" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B59" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="C59" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="D59" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E59" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F59" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G59" s="2" t="s">
+      <c r="D59" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E59" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F59" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G59" s="1" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="60" spans="2:7">
-      <c r="B60" s="2" t="s">
+    <row r="60" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B60" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="C60" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="D60" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E60" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F60" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G60" s="2" t="s">
+      <c r="D60" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E60" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F60" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G60" s="1" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="61" spans="2:7">
-      <c r="B61" s="2" t="s">
+    <row r="61" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B61" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="C61" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="D61" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E61" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F61" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G61" s="2" t="s">
+      <c r="D61" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E61" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F61" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G61" s="1" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="62" spans="2:7">
-      <c r="B62" s="2" t="s">
+    <row r="62" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B62" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="C62" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="D62" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E62" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F62" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G62" s="2" t="s">
+      <c r="D62" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E62" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F62" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G62" s="1" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="63" spans="2:7">
-      <c r="B63" s="2" t="s">
+    <row r="63" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B63" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="C63" s="2" t="s">
+      <c r="C63" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="D63" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E63" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F63" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G63" s="2" t="s">
+      <c r="D63" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E63" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F63" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G63" s="1" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="64" spans="2:7">
-      <c r="B64" s="2" t="s">
+    <row r="64" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B64" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="C64" s="2" t="s">
+      <c r="C64" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="D64" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E64" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F64" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G64" s="2" t="s">
+      <c r="D64" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E64" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F64" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G64" s="1" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="65" spans="2:7">
-      <c r="B65" s="2" t="s">
+    <row r="65" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B65" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="C65" s="2" t="s">
+      <c r="C65" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="D65" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E65" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F65" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G65" s="2" t="s">
+      <c r="D65" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E65" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F65" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G65" s="1" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="66" spans="2:7">
-      <c r="B66" s="2" t="s">
+    <row r="66" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B66" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C66" s="2" t="s">
+      <c r="C66" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="D66" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E66" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F66" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G66" s="2" t="s">
+      <c r="D66" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E66" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F66" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G66" s="1" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="67" spans="2:7">
-      <c r="B67" s="2" t="s">
+    <row r="67" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B67" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="C67" s="2" t="s">
+      <c r="C67" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="D67" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E67" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F67" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G67" s="2" t="s">
+      <c r="D67" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E67" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F67" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G67" s="1" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="68" spans="2:7">
-      <c r="B68" s="2" t="s">
+    <row r="68" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B68" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="C68" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="D68" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E68" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F68" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G68" s="2" t="s">
+      <c r="D68" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E68" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F68" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G68" s="1" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="69" spans="2:7">
-      <c r="B69" s="2" t="s">
+    <row r="69" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B69" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="C69" s="2" t="s">
+      <c r="C69" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="D69" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E69" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F69" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G69" s="2" t="s">
+      <c r="D69" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E69" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F69" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G69" s="1" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="70" spans="2:7">
-      <c r="B70" s="2" t="s">
+    <row r="70" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B70" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="C70" s="2" t="s">
+      <c r="C70" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="D70" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E70" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G70" s="2" t="s">
+      <c r="D70" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E70" s="1">
+        <v>1</v>
+      </c>
+      <c r="F70" s="1">
+        <v>0</v>
+      </c>
+      <c r="G70" s="1" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="71" spans="2:7">
-      <c r="B71" s="2" t="s">
+    <row r="71" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B71" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="C71" s="9" t="s">
+      <c r="C71" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="D71" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E71" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F71" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G71" s="10" t="s">
+      <c r="D71" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E71" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F71" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G71" s="1" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="72" spans="2:7">
-      <c r="B72" s="2" t="s">
+    <row r="72" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B72" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="C72" s="2" t="s">
+      <c r="C72" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="D72" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E72" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F72" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G72" s="10" t="s">
+      <c r="D72" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E72" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F72" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G72" s="1" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="73" spans="2:7">
-      <c r="B73" s="2" t="s">
+    <row r="73" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B73" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="C73" s="2" t="s">
+      <c r="C73" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="D73" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E73" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F73" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G73" s="2" t="s">
+      <c r="D73" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E73" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F73" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G73" s="1" t="s">
         <v>233</v>
       </c>
     </row>
+    <row r="74" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B74" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E74" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F74" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G74" s="9" t="s">
+        <v>236</v>
+      </c>
+    </row>
   </sheetData>
-  <printOptions>
-    <extLst>
-      <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1785722958" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
-      </ext>
-    </extLst>
-  </printOptions>
-  <pageMargins left="0.700000" right="0.700000" top="0.750000" bottom="0.750000" header="0.300000" footer="0.300000"/>
-  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="1"/>
-  <headerFooter>
-    <extLst>
-      <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1785722958" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1785722958" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1785722958" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1785722958" Id="1" type="0" value="0"/>
-      </ext>
-    </extLst>
-  </headerFooter>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" fitToWidth="0"/>
   <extLst>
     <ext uri="smNativeData">
       <pm:sheetPrefs xmlns:pm="smNativeData" day="1785722958" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">

--- a/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
@@ -1,34 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
+  <fileSharing readOnlyRecommended="0" userName="Lumino Game 03"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C40B2B0D-AF6D-413C-8031-49C0CA4132F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="510" yWindow="4380" windowWidth="37150" windowHeight="18380" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView activeTab="0" xWindow="240" yWindow="60" windowWidth="37150" windowHeight="18380" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:revision xmlns:pm="smNativeData" day="1785722958" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
-      <pm:docPrefs xmlns:pm="smNativeData" id="1785722958" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
-      <pm:compatibility xmlns:pm="smNativeData" id="1785722958" overlapCells="1"/>
-      <pm:defCurrency xmlns:pm="smNativeData" id="1785722958"/>
+      <pm:revision xmlns:pm="smNativeData" day="1785834872" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
+      <pm:docPrefs xmlns:pm="smNativeData" id="1785834872" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
+      <pm:compatibility xmlns:pm="smNativeData" id="1785834872" overlapCells="1"/>
+      <pm:defCurrency xmlns:pm="smNativeData" id="1785834872"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="240">
   <si>
     <t>##var</t>
   </si>
@@ -739,54 +734,110 @@
   </si>
   <si>
     <t>服装上身小游戏</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>GiftGivingPanel</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/Gift/GiftGivingPanel.prefab</t>
+  </si>
+  <si>
+    <t>礼物赠送面板</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="8">
+    <numFmt numFmtId="5" formatCode="#,##0\ &quot;¥&quot;;\-#,##0\ &quot;¥&quot;"/>
+    <numFmt numFmtId="6" formatCode="#,##0\ &quot;¥&quot;;[Red]\-#,##0\ &quot;¥&quot;"/>
+    <numFmt numFmtId="7" formatCode="#,##0.00\ &quot;¥&quot;;\-#,##0.00\ &quot;¥&quot;"/>
+    <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;¥&quot;;[Red]\-#,##0.00\ &quot;¥&quot;"/>
+    <numFmt numFmtId="42" formatCode="_-* #,##0\ &quot;¥&quot;_-;\-* #,##0\ &quot;¥&quot;_-;_-* &quot;-&quot;\ &quot;¥&quot;_-;_-@_-"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0\ _¥_-;\-* #,##0\ _¥_-;_-* &quot;-&quot;\ _¥_-;_-@_-"/>
+    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;¥&quot;_-;\-* #,##0.00\ &quot;¥&quot;_-;_-* &quot;-&quot;??\ &quot;¥&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _¥_-;\-* #,##0.00\ _¥_-;_-* &quot;-&quot;??\ _¥_-;_-@_-"/>
+  </numFmts>
+  <fonts count="5">
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="等线"/>
       <charset val="134"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1785834872" ulstyle="none" kern="1">
+            <pm:latin face="等线" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1785834872" ulstyle="none" kern="1">
+            <pm:latin face="Arial" sz="200" lang="default"/>
+            <pm:cs face="Times New Roman" sz="200" lang="default"/>
+            <pm:ea face="SimSun" sz="200" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF1F2329"/>
       <name val="等线"/>
+      <charset val="134"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1785834872" ulstyle="none" kern="1">
+            <pm:latin face="等线" sz="200" lang="default"/>
+            <pm:cs face="Times New Roman" sz="200" lang="default"/>
+            <pm:ea face="SimSun" sz="200" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
-      <b/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <color rgb="FF1F2329"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1785834872" fgClr="1F2329" ulstyle="none" kern="1">
+            <pm:latin face="等线" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <b/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1785834872" ulstyle="none" kern="1">
+            <pm:latin face="等线" sz="220" lang="default" weight="bold"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default" weight="bold"/>
+            <pm:ea face="SimSun" sz="220" lang="default" weight="bold"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -794,19 +845,50 @@
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF5B9BD5"/>
         <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1785834872" type="1" fgLvl="100" fgClr="005B9BD5" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1785834872" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1785834872"/>
+        </ext>
+      </extLst>
     </border>
     <border>
       <left style="thin">
@@ -821,70 +903,106 @@
       <bottom style="thin">
         <color rgb="FFDEE0E3"/>
       </bottom>
-      <diagonal/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1785834872">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+          </pm:border>
+        </ext>
+      </extLst>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1785834872"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1785834872"/>
+        </ext>
+      </extLst>
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="常规" xfId="0" builtinId="0" customBuiltin="1"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
+    <cellStyle name="常规 2" xfId="1"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
     <ext uri="smNativeData">
-      <pm:charStyles xmlns:pm="smNativeData" id="1785722958" count="1">
+      <pm:charStyles xmlns:pm="smNativeData" id="1785834872" count="1">
         <pm:charStyle name="普通" fontId="0" Id="1"/>
       </pm:charStyles>
-      <pm:colors xmlns:pm="smNativeData" id="1785722958" count="3">
+      <pm:colors xmlns:pm="smNativeData" id="1785834872" count="3">
         <pm:color name="颜色 24" rgb="1F2329"/>
         <pm:color name="颜色 25" rgb="5B9BD5"/>
         <pm:color name="颜色 26" rgb="DEE0E3"/>
@@ -1149,1516 +1267,1551 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G74"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <dimension ref="A1:G75"/>
+  <sheetFormatPr defaultRowHeight="13.45"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="28.58203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="100.08203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="23.6640625" style="1" customWidth="1"/>
-    <col min="5" max="6" width="17.6640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="24.1640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="8.6640625" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.6640625" style="1"/>
+    <col min="1" max="1" width="8.663793" customWidth="1" style="2"/>
+    <col min="2" max="2" width="28.577586" customWidth="1" style="2"/>
+    <col min="3" max="3" width="100.077586" customWidth="1" style="2"/>
+    <col min="4" max="4" width="23.663793" customWidth="1" style="2"/>
+    <col min="5" max="6" width="17.663793" customWidth="1" style="2"/>
+    <col min="7" max="7" width="24.163793" customWidth="1" style="2"/>
+    <col min="8" max="16384" width="8.663793" customWidth="1" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
+    <row r="1" spans="1:7">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:7">
+      <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:7">
+      <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B4" s="2" t="s">
+    <row r="4" spans="2:7">
+      <c r="B4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F4" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G4" s="1" t="s">
+      <c r="D4" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B5" s="2" t="s">
+    <row r="5" spans="2:7">
+      <c r="B5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F5" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G5" s="4" t="s">
+      <c r="D5" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="2" t="s">
+    <row r="6" spans="2:7" ht="19.50" customHeight="1">
+      <c r="B6" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F6" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G6" s="4" t="s">
+      <c r="E6" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B7" s="2" t="s">
+    <row r="7" spans="2:7">
+      <c r="B7" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F7" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G7" s="4" t="s">
+      <c r="D7" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B8" s="2" t="s">
+    <row r="8" spans="2:7">
+      <c r="B8" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F8" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G8" s="4" t="s">
+      <c r="D8" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" s="5" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B9" s="2" t="s">
+    <row r="9" spans="2:7">
+      <c r="B9" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F9" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G9" s="4" t="s">
+      <c r="D9" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" s="5" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B10" s="2" t="s">
+    <row r="10" spans="2:7">
+      <c r="B10" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="E10" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F10" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G10" s="4" t="s">
+      <c r="E10" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B11" s="2" t="s">
+    <row r="11" spans="2:7">
+      <c r="B11" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="E11" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F11" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G11" s="4" t="s">
+      <c r="E11" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G11" s="5" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B12" s="2" t="s">
+    <row r="12" spans="2:7">
+      <c r="B12" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E12" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F12" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G12" s="4" t="s">
+      <c r="D12" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F12" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12" s="5" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B13" s="2" t="s">
+    <row r="13" spans="2:7">
+      <c r="B13" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E13" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F13" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G13" s="4" t="s">
+      <c r="D13" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G13" s="5" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B14" s="2" t="s">
+    <row r="14" spans="2:7">
+      <c r="B14" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E14" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F14" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G14" s="4" t="s">
+      <c r="E14" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F14" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G14" s="5" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B15" s="2" t="s">
+    <row r="15" spans="2:7">
+      <c r="B15" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D15" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E15" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F15" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G15" s="4" t="s">
+      <c r="D15" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F15" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15" s="5" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B16" s="2" t="s">
+    <row r="16" spans="2:7">
+      <c r="B16" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E16" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F16" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G16" s="4" t="s">
+      <c r="E16" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G16" s="5" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B17" s="2" t="s">
+    <row r="17" spans="2:7">
+      <c r="B17" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="D17" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E17" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F17" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G17" s="4" t="s">
+      <c r="D17" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F17" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17" s="5" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B18" s="2" t="s">
+    <row r="18" spans="2:7">
+      <c r="B18" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E18" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F18" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G18" s="4" t="s">
+      <c r="E18" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F18" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G18" s="5" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B19" s="2" t="s">
+    <row r="19" spans="2:7">
+      <c r="B19" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="D19" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E19" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F19" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G19" s="4" t="s">
+      <c r="D19" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E19" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F19" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" s="5" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B20" s="2" t="s">
+    <row r="20" spans="2:7">
+      <c r="B20" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="D20" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E20" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F20" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G20" s="4" t="s">
+      <c r="D20" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E20" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F20" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" s="5" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B21" s="2" t="s">
+    <row r="21" spans="2:7">
+      <c r="B21" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="D21" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E21" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F21" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G21" s="4" t="s">
+      <c r="D21" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E21" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F21" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" s="5" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B22" s="2" t="s">
+    <row r="22" spans="2:7">
+      <c r="B22" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="D22" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E22" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F22" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G22" s="4" t="s">
+      <c r="D22" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E22" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F22" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" s="5" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B23" s="2" t="s">
+    <row r="23" spans="2:7">
+      <c r="B23" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C23" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="D23" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E23" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F23" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G23" s="4" t="s">
+      <c r="D23" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E23" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F23" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" s="5" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B24" s="2" t="s">
+    <row r="24" spans="2:7">
+      <c r="B24" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C24" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D24" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E24" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F24" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G24" s="4" t="s">
+      <c r="D24" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E24" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F24" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" s="5" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B25" s="2" t="s">
+    <row r="25" spans="2:7">
+      <c r="B25" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C25" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="D25" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E25" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F25" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G25" s="4" t="s">
+      <c r="D25" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E25" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F25" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" s="5" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B26" s="2" t="s">
+    <row r="26" spans="2:7">
+      <c r="B26" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="C26" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="D26" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E26" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F26" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="4" t="s">
+      <c r="D26" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E26" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F26" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26" s="5" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B27" s="2" t="s">
+    <row r="27" spans="2:7">
+      <c r="B27" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C27" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="D27" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E27" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F27" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G27" s="4" t="s">
+      <c r="D27" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E27" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F27" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G27" s="5" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B28" s="2" t="s">
+    <row r="28" spans="2:7">
+      <c r="B28" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="C28" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="D28" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E28" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F28" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G28" s="4" t="s">
+      <c r="D28" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E28" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F28" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G28" s="5" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B29" s="2" t="s">
+    <row r="29" spans="2:7">
+      <c r="B29" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="D29" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E29" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F29" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G29" s="1" t="s">
+      <c r="D29" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E29" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F29" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G29" s="2" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B30" s="2" t="s">
+    <row r="30" spans="2:7">
+      <c r="B30" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D30" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E30" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F30" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G30" s="1" t="s">
+      <c r="D30" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E30" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F30" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G30" s="2" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B31" s="2" t="s">
+    <row r="31" spans="2:7">
+      <c r="B31" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="D31" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E31" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F31" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G31" s="1" t="s">
+      <c r="D31" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E31" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F31" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G31" s="2" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B32" s="2" t="s">
+    <row r="32" spans="2:7">
+      <c r="B32" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="D32" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E32" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F32" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G32" s="1" t="s">
+      <c r="D32" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E32" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F32" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G32" s="2" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B33" s="2" t="s">
+    <row r="33" spans="2:7">
+      <c r="B33" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="D33" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E33" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F33" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G33" s="1" t="s">
+      <c r="D33" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E33" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F33" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G33" s="2" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B34" s="1" t="s">
+    <row r="34" spans="2:7">
+      <c r="B34" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D34" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E34" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F34" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G34" s="1" t="s">
+      <c r="D34" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E34" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F34" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G34" s="2" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B35" s="1" t="s">
+    <row r="35" spans="2:7">
+      <c r="B35" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="D35" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E35" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F35" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G35" s="1" t="s">
+      <c r="D35" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E35" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F35" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G35" s="2" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B36" s="1" t="s">
+    <row r="36" spans="2:7">
+      <c r="B36" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="D36" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E36" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F36" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G36" s="1" t="s">
+      <c r="D36" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E36" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F36" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G36" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B37" s="1" t="s">
+    <row r="37" spans="2:7">
+      <c r="B37" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="D37" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E37" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F37" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G37" s="1" t="s">
+      <c r="D37" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E37" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F37" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G37" s="2" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="38" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B38" s="1" t="s">
+    <row r="38" spans="2:7">
+      <c r="B38" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="D38" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E38" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F38" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G38" s="1" t="s">
+      <c r="D38" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E38" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F38" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G38" s="2" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B39" s="1" t="s">
+    <row r="39" spans="2:7">
+      <c r="B39" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="D39" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E39" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F39" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G39" s="1" t="s">
+      <c r="D39" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E39" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F39" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G39" s="2" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B40" s="1" t="s">
+    <row r="40" spans="2:7">
+      <c r="B40" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="D40" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E40" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F40" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G40" s="1" t="s">
+      <c r="D40" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E40" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F40" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G40" s="2" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B41" s="1" t="s">
+    <row r="41" spans="2:7">
+      <c r="B41" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="D41" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E41" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F41" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G41" s="1" t="s">
+      <c r="D41" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E41" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F41" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G41" s="2" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="42" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B42" s="1" t="s">
+    <row r="42" spans="2:7">
+      <c r="B42" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C42" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="D42" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E42" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F42" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G42" s="1" t="s">
+      <c r="D42" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E42" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F42" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G42" s="2" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="43" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B43" s="1" t="s">
+    <row r="43" spans="2:7">
+      <c r="B43" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C43" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="D43" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E43" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F43" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G43" s="1" t="s">
+      <c r="D43" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E43" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F43" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G43" s="2" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B44" s="1" t="s">
+    <row r="44" spans="2:7">
+      <c r="B44" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C44" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="D44" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E44" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F44" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G44" s="1" t="s">
+      <c r="D44" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E44" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F44" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G44" s="2" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="45" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B45" s="1" t="s">
+    <row r="45" spans="2:7">
+      <c r="B45" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C45" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="D45" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E45" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F45" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G45" s="1" t="s">
+      <c r="D45" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E45" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F45" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G45" s="2" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="46" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B46" s="1" t="s">
+    <row r="46" spans="2:7">
+      <c r="B46" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C46" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="D46" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E46" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F46" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G46" s="1" t="s">
+      <c r="D46" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E46" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F46" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G46" s="2" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="47" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B47" s="1" t="s">
+    <row r="47" spans="2:7">
+      <c r="B47" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C47" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="D47" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E47" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F47" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G47" s="1" t="s">
+      <c r="D47" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E47" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F47" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G47" s="2" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="48" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B48" s="1" t="s">
+    <row r="48" spans="2:7">
+      <c r="B48" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="C48" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="D48" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E48" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F48" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G48" s="1" t="s">
+      <c r="D48" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E48" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F48" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G48" s="2" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="49" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B49" s="1" t="s">
+    <row r="49" spans="2:7">
+      <c r="B49" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C49" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="D49" s="6" t="s">
+      <c r="D49" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="E49" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F49" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G49" s="1" t="s">
+      <c r="E49" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F49" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G49" s="2" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="50" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B50" s="1" t="s">
+    <row r="50" spans="2:7">
+      <c r="B50" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="C50" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="D50" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E50" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F50" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G50" s="1" t="s">
+      <c r="D50" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E50" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F50" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G50" s="2" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="51" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B51" s="1" t="s">
+    <row r="51" spans="2:7">
+      <c r="B51" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="C51" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="D51" s="6" t="s">
+      <c r="D51" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="E51" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F51" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G51" s="1" t="s">
+      <c r="E51" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F51" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G51" s="2" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="52" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B52" s="1" t="s">
+    <row r="52" spans="2:7">
+      <c r="B52" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="C52" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="D52" s="6" t="s">
+      <c r="D52" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="E52" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F52" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G52" s="1" t="s">
+      <c r="E52" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F52" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G52" s="2" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="53" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B53" s="1" t="s">
+    <row r="53" spans="2:7">
+      <c r="B53" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="C53" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="D53" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E53" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F53" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G53" s="1" t="s">
+      <c r="D53" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E53" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F53" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G53" s="2" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="54" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B54" s="1" t="s">
+    <row r="54" spans="2:7">
+      <c r="B54" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="C54" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="D54" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E54" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F54" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G54" s="1" t="s">
+      <c r="D54" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E54" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F54" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G54" s="2" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="55" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B55" s="1" t="s">
+    <row r="55" spans="2:7">
+      <c r="B55" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="C55" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="D55" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E55" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F55" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G55" s="1" t="s">
+      <c r="D55" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E55" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F55" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G55" s="2" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="56" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B56" s="1" t="s">
+    <row r="56" spans="2:7">
+      <c r="B56" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="C56" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="D56" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E56" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F56" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G56" s="1" t="s">
+      <c r="D56" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E56" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F56" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G56" s="2" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="57" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B57" s="1" t="s">
+    <row r="57" spans="2:7">
+      <c r="B57" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="C57" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="D57" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E57" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F57" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G57" s="1" t="s">
+      <c r="D57" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E57" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F57" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G57" s="2" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="58" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B58" s="1" t="s">
+    <row r="58" spans="2:7">
+      <c r="B58" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="C58" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="D58" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E58" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F58" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G58" s="1" t="s">
+      <c r="D58" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E58" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F58" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G58" s="2" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="59" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B59" s="1" t="s">
+    <row r="59" spans="2:7">
+      <c r="B59" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="C59" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="D59" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E59" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F59" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G59" s="1" t="s">
+      <c r="D59" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E59" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F59" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G59" s="2" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="60" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B60" s="1" t="s">
+    <row r="60" spans="2:7">
+      <c r="B60" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="C60" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="D60" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E60" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F60" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G60" s="1" t="s">
+      <c r="D60" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E60" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F60" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G60" s="2" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="61" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B61" s="1" t="s">
+    <row r="61" spans="2:7">
+      <c r="B61" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="C61" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="D61" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E61" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F61" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G61" s="1" t="s">
+      <c r="D61" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E61" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F61" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G61" s="2" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="62" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B62" s="1" t="s">
+    <row r="62" spans="2:7">
+      <c r="B62" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="C62" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="D62" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E62" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F62" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G62" s="1" t="s">
+      <c r="D62" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E62" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F62" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G62" s="2" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="63" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B63" s="1" t="s">
+    <row r="63" spans="2:7">
+      <c r="B63" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="C63" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="D63" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E63" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F63" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G63" s="1" t="s">
+      <c r="D63" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E63" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F63" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G63" s="2" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="64" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B64" s="1" t="s">
+    <row r="64" spans="2:7">
+      <c r="B64" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="C64" s="1" t="s">
+      <c r="C64" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="D64" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E64" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F64" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G64" s="1" t="s">
+      <c r="D64" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E64" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F64" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G64" s="2" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="65" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B65" s="1" t="s">
+    <row r="65" spans="2:7">
+      <c r="B65" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="C65" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="D65" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E65" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F65" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G65" s="1" t="s">
+      <c r="D65" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E65" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F65" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G65" s="2" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="66" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B66" s="1" t="s">
+    <row r="66" spans="2:7">
+      <c r="B66" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="C66" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="D66" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E66" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F66" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G66" s="1" t="s">
+      <c r="D66" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E66" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F66" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G66" s="2" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="67" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B67" s="1" t="s">
+    <row r="67" spans="2:7">
+      <c r="B67" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="C67" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="D67" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E67" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F67" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G67" s="1" t="s">
+      <c r="D67" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E67" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F67" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G67" s="2" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="68" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B68" s="1" t="s">
+    <row r="68" spans="2:7">
+      <c r="B68" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="C68" s="1" t="s">
+      <c r="C68" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="D68" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E68" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F68" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G68" s="1" t="s">
+      <c r="D68" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E68" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F68" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G68" s="2" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="69" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B69" s="1" t="s">
+    <row r="69" spans="2:7">
+      <c r="B69" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="C69" s="1" t="s">
+      <c r="C69" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="D69" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E69" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F69" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G69" s="1" t="s">
+      <c r="D69" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E69" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F69" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G69" s="2" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="70" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B70" s="1" t="s">
+    <row r="70" spans="2:7">
+      <c r="B70" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="C70" s="1" t="s">
+      <c r="C70" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="D70" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E70" s="1">
-        <v>1</v>
-      </c>
-      <c r="F70" s="1">
-        <v>0</v>
-      </c>
-      <c r="G70" s="1" t="s">
+      <c r="D70" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" s="2" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="71" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B71" s="1" t="s">
+    <row r="71" spans="2:7">
+      <c r="B71" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="C71" s="8" t="s">
+      <c r="C71" s="9" t="s">
         <v>226</v>
       </c>
-      <c r="D71" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E71" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F71" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G71" s="1" t="s">
+      <c r="D71" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E71" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F71" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G71" s="2" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="72" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B72" s="1" t="s">
+    <row r="72" spans="2:7">
+      <c r="B72" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="C72" s="1" t="s">
+      <c r="C72" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="D72" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E72" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F72" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G72" s="1" t="s">
+      <c r="D72" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E72" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F72" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G72" s="2" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="73" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B73" s="1" t="s">
+    <row r="73" spans="2:7">
+      <c r="B73" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C73" s="1" t="s">
+      <c r="C73" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="D73" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E73" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="F73" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G73" s="1" t="s">
+      <c r="D73" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E73" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F73" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G73" s="2" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="74" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B74" s="1" t="s">
+    <row r="74" spans="2:7">
+      <c r="B74" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="C74" s="1" t="s">
+      <c r="C74" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="D74" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E74" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="F74" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G74" s="9" t="s">
+      <c r="D74" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E74" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F74" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G74" s="10" t="s">
         <v>236</v>
       </c>
     </row>
+    <row r="75" spans="2:7">
+      <c r="B75" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E75" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F75" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G75" s="10" t="s">
+        <v>239</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" fitToWidth="0"/>
+  <printOptions>
+    <extLst>
+      <ext uri="smNativeData">
+        <pm:pageFlags xmlns:pm="smNativeData" id="1785834872" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+      </ext>
+    </extLst>
+  </printOptions>
+  <pageMargins left="0.700000" right="0.700000" top="0.750000" bottom="0.750000" header="0.300000" footer="0.300000"/>
+  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="1"/>
+  <headerFooter>
+    <extLst>
+      <ext uri="smNativeData">
+        <pm:header xmlns:pm="smNativeData" id="1785834872" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1785834872" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1785834872" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1785834872" Id="1" type="0" value="0"/>
+      </ext>
+    </extLst>
+  </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1785722958" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1785834872" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>

--- a/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
@@ -1,16 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
-  <fileSharing readOnlyRecommended="0" userName="Lumino Game 03"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CDE2F04-A4D0-4C0A-8898-C3E886078447}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0" xWindow="240" yWindow="60" windowWidth="37150" windowHeight="18380" tabRatio="500"/>
+    <workbookView xWindow="5160" yWindow="1290" windowWidth="37160" windowHeight="18570" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext uri="smNativeData">
       <pm:revision xmlns:pm="smNativeData" day="1785834872" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
@@ -23,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="242">
   <si>
     <t>##var</t>
   </si>
@@ -743,101 +748,54 @@
   </si>
   <si>
     <t>礼物赠送面板</t>
+  </si>
+  <si>
+    <t>DramaRuntimeUI</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/DramaRuntimeUI/DramaRuntimeUI.prefab</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
-    <numFmt numFmtId="5" formatCode="#,##0\ &quot;¥&quot;;\-#,##0\ &quot;¥&quot;"/>
-    <numFmt numFmtId="6" formatCode="#,##0\ &quot;¥&quot;;[Red]\-#,##0\ &quot;¥&quot;"/>
-    <numFmt numFmtId="7" formatCode="#,##0.00\ &quot;¥&quot;;\-#,##0.00\ &quot;¥&quot;"/>
-    <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;¥&quot;;[Red]\-#,##0.00\ &quot;¥&quot;"/>
-    <numFmt numFmtId="42" formatCode="_-* #,##0\ &quot;¥&quot;_-;\-* #,##0\ &quot;¥&quot;_-;_-* &quot;-&quot;\ &quot;¥&quot;_-;_-@_-"/>
-    <numFmt numFmtId="41" formatCode="_-* #,##0\ _¥_-;\-* #,##0\ _¥_-;_-* &quot;-&quot;\ _¥_-;_-@_-"/>
-    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;¥&quot;_-;\-* #,##0.00\ &quot;¥&quot;_-;_-* &quot;-&quot;??\ &quot;¥&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _¥_-;\-* #,##0.00\ _¥_-;_-* &quot;-&quot;??\ _¥_-;_-@_-"/>
-  </numFmts>
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="等线"/>
       <charset val="134"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1785834872" ulstyle="none" kern="1">
-            <pm:latin face="等线" sz="220" lang="default"/>
-            <pm:cs face="Times New Roman" sz="220" lang="default"/>
-            <pm:ea face="SimSun" sz="220" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
-      <name val="Arial"/>
-      <family val="2"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
-      <sz val="10"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1785834872" ulstyle="none" kern="1">
-            <pm:latin face="Arial" sz="200" lang="default"/>
-            <pm:cs face="Times New Roman" sz="200" lang="default"/>
-            <pm:ea face="SimSun" sz="200" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
+      <name val="等线"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF1F2329"/>
       <name val="等线"/>
-      <charset val="134"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1785834872" ulstyle="none" kern="1">
-            <pm:latin face="等线" sz="200" lang="default"/>
-            <pm:cs face="Times New Roman" sz="200" lang="default"/>
-            <pm:ea face="SimSun" sz="200" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="等线"/>
-      <charset val="134"/>
-      <color rgb="FF1F2329"/>
-      <sz val="11"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1785834872" fgClr="1F2329" ulstyle="none" kern="1">
-            <pm:latin face="等线" sz="220" lang="default"/>
-            <pm:cs face="Times New Roman" sz="220" lang="default"/>
-            <pm:ea face="SimSun" sz="220" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="等线"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
-      <b/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1785834872" ulstyle="none" kern="1">
-            <pm:latin face="等线" sz="220" lang="default" weight="bold"/>
-            <pm:cs face="Times New Roman" sz="220" lang="default" weight="bold"/>
-            <pm:ea face="SimSun" sz="220" lang="default" weight="bold"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -845,50 +803,19 @@
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
-      <patternFill patternType="none"/>
-    </fill>
-    <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF5B9BD5"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1785834872" type="1" fgLvl="100" fgClr="005B9BD5" bgLvl="0" bgClr="00FFFFFF"/>
-          </ext>
-        </extLst>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1785834872" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1785834872"/>
-        </ext>
-      </extLst>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -903,101 +830,62 @@
       <bottom style="thin">
         <color rgb="FFDEE0E3"/>
       </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1785834872">
-            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-          </pm:border>
-        </ext>
-      </extLst>
+      <diagonal/>
     </border>
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1785834872"/>
-        </ext>
-      </extLst>
-    </border>
-    <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1785834872"/>
-        </ext>
-      </extLst>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
-    <cellStyle name="常规 2" xfId="1"/>
+    <cellStyle name="常规" xfId="0" builtinId="0" customBuiltin="1"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0"/>
   <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
     <ext uri="smNativeData">
       <pm:charStyles xmlns:pm="smNativeData" id="1785834872" count="1">
         <pm:charStyle name="普通" fontId="0" Id="1"/>
@@ -1267,1548 +1155,1553 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:G75"/>
-  <sheetFormatPr defaultRowHeight="13.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G76"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.663793" customWidth="1" style="2"/>
-    <col min="2" max="2" width="28.577586" customWidth="1" style="2"/>
-    <col min="3" max="3" width="100.077586" customWidth="1" style="2"/>
-    <col min="4" max="4" width="23.663793" customWidth="1" style="2"/>
-    <col min="5" max="6" width="17.663793" customWidth="1" style="2"/>
-    <col min="7" max="7" width="24.163793" customWidth="1" style="2"/>
-    <col min="8" max="16384" width="8.663793" customWidth="1" style="2"/>
+    <col min="1" max="1" width="8.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="28.58203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="100.08203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="23.6640625" style="1" customWidth="1"/>
+    <col min="5" max="6" width="17.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="24.1640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="8.6640625" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="4" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="2:7">
-      <c r="B4" s="3" t="s">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F4" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G4" s="2" t="s">
+      <c r="D4" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="2:7">
-      <c r="B5" s="3" t="s">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F5" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G5" s="5" t="s">
+      <c r="D5" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="2:7" ht="19.50" customHeight="1">
-      <c r="B6" s="3" t="s">
+    <row r="6" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F6" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G6" s="5" t="s">
+      <c r="E6" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="2:7">
-      <c r="B7" s="3" t="s">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B7" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F7" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G7" s="5" t="s">
+      <c r="D7" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="2:7">
-      <c r="B8" s="3" t="s">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F8" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G8" s="5" t="s">
+      <c r="D8" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F8" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" s="4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="2:7">
-      <c r="B9" s="3" t="s">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B9" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F9" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G9" s="5" t="s">
+      <c r="D9" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F9" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" s="4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="2:7">
-      <c r="B10" s="3" t="s">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B10" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E10" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F10" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G10" s="5" t="s">
+      <c r="E10" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F10" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="2:7">
-      <c r="B11" s="3" t="s">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B11" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="E11" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F11" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G11" s="5" t="s">
+      <c r="E11" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F11" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="2:7">
-      <c r="B12" s="3" t="s">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B12" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E12" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F12" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G12" s="5" t="s">
+      <c r="D12" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F12" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="13" spans="2:7">
-      <c r="B13" s="3" t="s">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B13" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D13" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E13" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F13" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G13" s="5" t="s">
+      <c r="D13" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F13" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G13" s="4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="14" spans="2:7">
-      <c r="B14" s="3" t="s">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B14" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E14" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F14" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G14" s="5" t="s">
+      <c r="E14" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F14" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G14" s="4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="15" spans="2:7">
-      <c r="B15" s="3" t="s">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B15" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D15" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E15" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F15" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G15" s="5" t="s">
+      <c r="D15" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F15" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15" s="4" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="16" spans="2:7">
-      <c r="B16" s="3" t="s">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B16" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E16" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F16" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G16" s="5" t="s">
+      <c r="E16" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F16" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G16" s="4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="17" spans="2:7">
-      <c r="B17" s="3" t="s">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B17" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D17" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E17" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F17" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G17" s="5" t="s">
+      <c r="D17" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F17" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17" s="4" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="18" spans="2:7">
-      <c r="B18" s="3" t="s">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B18" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E18" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F18" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G18" s="5" t="s">
+      <c r="E18" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F18" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G18" s="4" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="2:7">
-      <c r="B19" s="3" t="s">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B19" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D19" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E19" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F19" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G19" s="5" t="s">
+      <c r="D19" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E19" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F19" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="20" spans="2:7">
-      <c r="B20" s="3" t="s">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B20" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D20" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E20" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F20" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G20" s="5" t="s">
+      <c r="D20" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E20" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F20" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" s="4" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="21" spans="2:7">
-      <c r="B21" s="3" t="s">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B21" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="D21" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E21" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F21" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G21" s="5" t="s">
+      <c r="D21" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E21" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F21" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="22" spans="2:7">
-      <c r="B22" s="3" t="s">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B22" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="D22" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E22" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F22" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G22" s="5" t="s">
+      <c r="D22" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E22" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F22" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="23" spans="2:7">
-      <c r="B23" s="3" t="s">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B23" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="D23" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E23" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F23" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G23" s="5" t="s">
+      <c r="D23" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E23" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F23" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" s="4" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="24" spans="2:7">
-      <c r="B24" s="3" t="s">
+    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B24" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="D24" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E24" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F24" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G24" s="5" t="s">
+      <c r="D24" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E24" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F24" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" s="4" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="25" spans="2:7">
-      <c r="B25" s="3" t="s">
+    <row r="25" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B25" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="D25" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E25" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F25" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G25" s="5" t="s">
+      <c r="D25" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E25" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F25" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="26" spans="2:7">
-      <c r="B26" s="3" t="s">
+    <row r="26" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B26" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C26" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="D26" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E26" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F26" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="5" t="s">
+      <c r="D26" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E26" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F26" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26" s="4" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="27" spans="2:7">
-      <c r="B27" s="3" t="s">
+    <row r="27" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B27" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="D27" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E27" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F27" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G27" s="5" t="s">
+      <c r="D27" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E27" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F27" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G27" s="4" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="28" spans="2:7">
-      <c r="B28" s="3" t="s">
+    <row r="28" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B28" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="C28" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="D28" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E28" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F28" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G28" s="5" t="s">
+      <c r="D28" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E28" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F28" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G28" s="4" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="29" spans="2:7">
-      <c r="B29" s="3" t="s">
+    <row r="29" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B29" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="D29" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E29" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F29" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G29" s="2" t="s">
+      <c r="D29" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E29" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F29" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G29" s="1" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="2:7">
-      <c r="B30" s="3" t="s">
+    <row r="30" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B30" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="D30" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E30" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F30" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G30" s="2" t="s">
+      <c r="D30" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E30" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F30" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G30" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="31" spans="2:7">
-      <c r="B31" s="3" t="s">
+    <row r="31" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B31" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="D31" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E31" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F31" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G31" s="2" t="s">
+      <c r="D31" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E31" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F31" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G31" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="32" spans="2:7">
-      <c r="B32" s="3" t="s">
+    <row r="32" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B32" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="D32" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E32" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F32" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G32" s="2" t="s">
+      <c r="D32" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E32" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F32" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G32" s="1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="33" spans="2:7">
-      <c r="B33" s="3" t="s">
+    <row r="33" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B33" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="D33" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E33" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F33" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G33" s="2" t="s">
+      <c r="D33" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E33" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F33" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G33" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="34" spans="2:7">
-      <c r="B34" s="2" t="s">
+    <row r="34" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B34" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D34" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E34" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F34" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G34" s="2" t="s">
+      <c r="D34" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E34" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F34" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G34" s="1" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="35" spans="2:7">
-      <c r="B35" s="2" t="s">
+    <row r="35" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B35" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="D35" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E35" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F35" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G35" s="2" t="s">
+      <c r="D35" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E35" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F35" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G35" s="1" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="36" spans="2:7">
-      <c r="B36" s="2" t="s">
+    <row r="36" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B36" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="D36" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E36" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F36" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G36" s="2" t="s">
+      <c r="D36" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E36" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F36" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G36" s="1" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="37" spans="2:7">
-      <c r="B37" s="2" t="s">
+    <row r="37" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B37" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D37" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E37" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F37" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G37" s="2" t="s">
+      <c r="D37" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E37" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F37" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G37" s="1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="38" spans="2:7">
-      <c r="B38" s="2" t="s">
+    <row r="38" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B38" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="D38" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E38" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F38" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G38" s="2" t="s">
+      <c r="D38" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E38" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F38" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G38" s="1" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="39" spans="2:7">
-      <c r="B39" s="2" t="s">
+    <row r="39" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B39" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="D39" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E39" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F39" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G39" s="2" t="s">
+      <c r="D39" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E39" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F39" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G39" s="1" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="40" spans="2:7">
-      <c r="B40" s="2" t="s">
+    <row r="40" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B40" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="D40" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E40" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F40" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G40" s="2" t="s">
+      <c r="D40" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E40" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F40" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G40" s="1" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="41" spans="2:7">
-      <c r="B41" s="2" t="s">
+    <row r="41" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B41" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C41" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="D41" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E41" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F41" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G41" s="2" t="s">
+      <c r="D41" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E41" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F41" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G41" s="1" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="42" spans="2:7">
-      <c r="B42" s="2" t="s">
+    <row r="42" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B42" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C42" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="D42" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E42" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F42" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G42" s="2" t="s">
+      <c r="D42" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E42" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F42" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G42" s="1" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="43" spans="2:7">
-      <c r="B43" s="2" t="s">
+    <row r="43" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B43" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C43" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D43" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E43" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F43" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G43" s="2" t="s">
+      <c r="D43" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E43" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F43" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G43" s="1" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="44" spans="2:7">
-      <c r="B44" s="2" t="s">
+    <row r="44" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B44" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="C44" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="D44" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E44" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F44" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G44" s="2" t="s">
+      <c r="D44" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E44" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F44" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G44" s="1" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="45" spans="2:7">
-      <c r="B45" s="2" t="s">
+    <row r="45" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B45" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C45" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="D45" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E45" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F45" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G45" s="2" t="s">
+      <c r="D45" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E45" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F45" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G45" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="46" spans="2:7">
-      <c r="B46" s="2" t="s">
+    <row r="46" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B46" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C46" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="D46" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E46" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F46" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G46" s="2" t="s">
+      <c r="D46" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E46" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F46" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G46" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="47" spans="2:7">
-      <c r="B47" s="2" t="s">
+    <row r="47" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B47" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C47" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="D47" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E47" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F47" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G47" s="2" t="s">
+      <c r="D47" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E47" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F47" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G47" s="1" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="48" spans="2:7">
-      <c r="B48" s="2" t="s">
+    <row r="48" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B48" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C48" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="D48" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E48" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F48" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G48" s="2" t="s">
+      <c r="D48" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E48" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F48" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G48" s="1" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="49" spans="2:7">
-      <c r="B49" s="2" t="s">
+    <row r="49" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B49" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C49" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="D49" s="7" t="s">
+      <c r="D49" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="E49" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F49" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G49" s="2" t="s">
+      <c r="E49" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F49" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G49" s="1" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="50" spans="2:7">
-      <c r="B50" s="2" t="s">
+    <row r="50" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B50" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C50" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="D50" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E50" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F50" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G50" s="2" t="s">
+      <c r="D50" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E50" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F50" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G50" s="1" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="51" spans="2:7">
-      <c r="B51" s="2" t="s">
+    <row r="51" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B51" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="C51" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D51" s="7" t="s">
+      <c r="D51" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="E51" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F51" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G51" s="2" t="s">
+      <c r="E51" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F51" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G51" s="1" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="52" spans="2:7">
-      <c r="B52" s="2" t="s">
+    <row r="52" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B52" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C52" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="D52" s="7" t="s">
+      <c r="D52" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="E52" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F52" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G52" s="2" t="s">
+      <c r="E52" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F52" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G52" s="1" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="53" spans="2:7">
-      <c r="B53" s="2" t="s">
+    <row r="53" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B53" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="C53" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="D53" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E53" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F53" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G53" s="2" t="s">
+      <c r="D53" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E53" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F53" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G53" s="1" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="54" spans="2:7">
-      <c r="B54" s="2" t="s">
+    <row r="54" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B54" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C54" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="D54" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E54" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F54" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G54" s="2" t="s">
+      <c r="D54" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E54" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F54" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G54" s="1" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="55" spans="2:7">
-      <c r="B55" s="2" t="s">
+    <row r="55" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B55" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C55" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D55" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E55" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F55" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G55" s="2" t="s">
+      <c r="D55" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E55" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F55" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G55" s="1" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="56" spans="2:7">
-      <c r="B56" s="2" t="s">
+    <row r="56" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B56" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="C56" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="D56" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E56" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F56" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G56" s="2" t="s">
+      <c r="D56" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E56" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F56" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G56" s="1" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="57" spans="2:7">
-      <c r="B57" s="2" t="s">
+    <row r="57" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B57" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="C57" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="D57" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E57" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F57" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G57" s="2" t="s">
+      <c r="D57" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E57" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F57" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G57" s="1" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="58" spans="2:7">
-      <c r="B58" s="2" t="s">
+    <row r="58" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B58" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="C58" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="D58" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E58" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F58" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G58" s="2" t="s">
+      <c r="D58" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E58" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F58" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G58" s="1" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="59" spans="2:7">
-      <c r="B59" s="2" t="s">
+    <row r="59" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B59" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="C59" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="D59" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E59" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F59" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G59" s="2" t="s">
+      <c r="D59" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E59" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F59" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G59" s="1" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="60" spans="2:7">
-      <c r="B60" s="2" t="s">
+    <row r="60" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B60" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="C60" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="D60" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E60" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F60" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G60" s="2" t="s">
+      <c r="D60" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E60" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F60" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G60" s="1" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="61" spans="2:7">
-      <c r="B61" s="2" t="s">
+    <row r="61" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B61" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="C61" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="D61" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E61" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F61" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G61" s="2" t="s">
+      <c r="D61" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E61" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F61" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G61" s="1" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="62" spans="2:7">
-      <c r="B62" s="2" t="s">
+    <row r="62" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B62" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="C62" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="D62" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E62" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F62" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G62" s="2" t="s">
+      <c r="D62" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E62" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F62" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G62" s="1" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="63" spans="2:7">
-      <c r="B63" s="2" t="s">
+    <row r="63" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B63" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="C63" s="2" t="s">
+      <c r="C63" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="D63" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E63" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F63" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G63" s="2" t="s">
+      <c r="D63" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E63" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F63" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G63" s="1" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="64" spans="2:7">
-      <c r="B64" s="2" t="s">
+    <row r="64" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B64" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="C64" s="2" t="s">
+      <c r="C64" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="D64" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E64" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F64" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G64" s="2" t="s">
+      <c r="D64" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E64" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F64" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G64" s="1" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="65" spans="2:7">
-      <c r="B65" s="2" t="s">
+    <row r="65" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B65" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="C65" s="2" t="s">
+      <c r="C65" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="D65" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E65" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F65" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G65" s="2" t="s">
+      <c r="D65" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E65" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F65" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G65" s="1" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="66" spans="2:7">
-      <c r="B66" s="2" t="s">
+    <row r="66" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B66" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C66" s="2" t="s">
+      <c r="C66" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="D66" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E66" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F66" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G66" s="2" t="s">
+      <c r="D66" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E66" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F66" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G66" s="1" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="67" spans="2:7">
-      <c r="B67" s="2" t="s">
+    <row r="67" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B67" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="C67" s="2" t="s">
+      <c r="C67" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="D67" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E67" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F67" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G67" s="2" t="s">
+      <c r="D67" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E67" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F67" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G67" s="1" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="68" spans="2:7">
-      <c r="B68" s="2" t="s">
+    <row r="68" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B68" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="C68" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="D68" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E68" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F68" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G68" s="2" t="s">
+      <c r="D68" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E68" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F68" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G68" s="1" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="69" spans="2:7">
-      <c r="B69" s="2" t="s">
+    <row r="69" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B69" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="C69" s="2" t="s">
+      <c r="C69" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="D69" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E69" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F69" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G69" s="2" t="s">
+      <c r="D69" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E69" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F69" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G69" s="1" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="70" spans="2:7">
-      <c r="B70" s="2" t="s">
+    <row r="70" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B70" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="C70" s="2" t="s">
+      <c r="C70" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="D70" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E70" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G70" s="2" t="s">
+      <c r="D70" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E70" s="1">
+        <v>1</v>
+      </c>
+      <c r="F70" s="1">
+        <v>0</v>
+      </c>
+      <c r="G70" s="1" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="71" spans="2:7">
-      <c r="B71" s="2" t="s">
+    <row r="71" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B71" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="C71" s="9" t="s">
+      <c r="C71" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="D71" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E71" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F71" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G71" s="2" t="s">
+      <c r="D71" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E71" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F71" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G71" s="1" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="72" spans="2:7">
-      <c r="B72" s="2" t="s">
+    <row r="72" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B72" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="C72" s="2" t="s">
+      <c r="C72" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="D72" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E72" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F72" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G72" s="2" t="s">
+      <c r="D72" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E72" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F72" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G72" s="1" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="73" spans="2:7">
-      <c r="B73" s="2" t="s">
+    <row r="73" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B73" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="C73" s="2" t="s">
+      <c r="C73" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="D73" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E73" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F73" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G73" s="2" t="s">
+      <c r="D73" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E73" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F73" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G73" s="1" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="74" spans="2:7">
-      <c r="B74" s="2" t="s">
+    <row r="74" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B74" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="C74" s="2" t="s">
+      <c r="C74" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="D74" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E74" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F74" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G74" s="10" t="s">
+      <c r="D74" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E74" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F74" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G74" s="1" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="75" spans="2:7">
-      <c r="B75" s="2" t="s">
+    <row r="75" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B75" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="C75" s="2" t="s">
+      <c r="C75" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="D75" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E75" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F75" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G75" s="10" t="s">
+      <c r="D75" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E75" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F75" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G75" s="1" t="s">
         <v>239</v>
       </c>
     </row>
+    <row r="76" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B76" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E76" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F76" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
   </sheetData>
-  <printOptions>
-    <extLst>
-      <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1785834872" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
-      </ext>
-    </extLst>
-  </printOptions>
-  <pageMargins left="0.700000" right="0.700000" top="0.750000" bottom="0.750000" header="0.300000" footer="0.300000"/>
-  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="1"/>
-  <headerFooter>
-    <extLst>
-      <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1785834872" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1785834872" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1785834872" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1785834872" Id="1" type="0" value="0"/>
-      </ext>
-    </extLst>
-  </headerFooter>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" fitToWidth="0"/>
   <extLst>
     <ext uri="smNativeData">
       <pm:sheetPrefs xmlns:pm="smNativeData" day="1785834872" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">

--- a/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
@@ -1,16 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
-  <fileSharing readOnlyRecommended="0" userName="Lumino Game 03"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\Project\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28D23E21-A0DE-4950-8134-623FEF289FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0" xWindow="240" yWindow="60" windowWidth="37150" windowHeight="18380" tabRatio="500"/>
+    <workbookView xWindow="1520" yWindow="1520" windowWidth="28800" windowHeight="15370" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext uri="smNativeData">
       <pm:revision xmlns:pm="smNativeData" day="1785834872" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
@@ -23,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="244">
   <si>
     <t>##var</t>
   </si>
@@ -743,101 +748,63 @@
   </si>
   <si>
     <t>礼物赠送面板</t>
+  </si>
+  <si>
+    <t>QuestPanel</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/Quest/QuestPanel.prefab</t>
+  </si>
+  <si>
+    <t>True</t>
+  </si>
+  <si>
+    <t>任务面板</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
-    <numFmt numFmtId="5" formatCode="#,##0\ &quot;¥&quot;;\-#,##0\ &quot;¥&quot;"/>
-    <numFmt numFmtId="6" formatCode="#,##0\ &quot;¥&quot;;[Red]\-#,##0\ &quot;¥&quot;"/>
-    <numFmt numFmtId="7" formatCode="#,##0.00\ &quot;¥&quot;;\-#,##0.00\ &quot;¥&quot;"/>
-    <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;¥&quot;;[Red]\-#,##0.00\ &quot;¥&quot;"/>
-    <numFmt numFmtId="42" formatCode="_-* #,##0\ &quot;¥&quot;_-;\-* #,##0\ &quot;¥&quot;_-;_-* &quot;-&quot;\ &quot;¥&quot;_-;_-@_-"/>
-    <numFmt numFmtId="41" formatCode="_-* #,##0\ _¥_-;\-* #,##0\ _¥_-;_-* &quot;-&quot;\ _¥_-;_-@_-"/>
-    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;¥&quot;_-;\-* #,##0.00\ &quot;¥&quot;_-;_-* &quot;-&quot;??\ &quot;¥&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _¥_-;\-* #,##0.00\ _¥_-;_-* &quot;-&quot;??\ _¥_-;_-@_-"/>
-  </numFmts>
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="等线"/>
       <charset val="134"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1785834872" ulstyle="none" kern="1">
-            <pm:latin face="等线" sz="220" lang="default"/>
-            <pm:cs face="Times New Roman" sz="220" lang="default"/>
-            <pm:ea face="SimSun" sz="220" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
-      <name val="Arial"/>
-      <family val="2"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
-      <sz val="10"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1785834872" ulstyle="none" kern="1">
-            <pm:latin face="Arial" sz="200" lang="default"/>
-            <pm:cs face="Times New Roman" sz="200" lang="default"/>
-            <pm:ea face="SimSun" sz="200" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
+      <name val="等线"/>
+      <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF1F2329"/>
       <name val="等线"/>
       <charset val="134"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1785834872" ulstyle="none" kern="1">
-            <pm:latin face="等线" sz="200" lang="default"/>
-            <pm:cs face="Times New Roman" sz="200" lang="default"/>
-            <pm:ea face="SimSun" sz="200" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="等线"/>
       <charset val="134"/>
-      <color rgb="FF1F2329"/>
-      <sz val="11"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1785834872" fgClr="1F2329" ulstyle="none" kern="1">
-            <pm:latin face="等线" sz="220" lang="default"/>
-            <pm:cs face="Times New Roman" sz="220" lang="default"/>
-            <pm:ea face="SimSun" sz="220" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="等线"/>
       <charset val="134"/>
-      <b/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1785834872" ulstyle="none" kern="1">
-            <pm:latin face="等线" sz="220" lang="default" weight="bold"/>
-            <pm:cs face="Times New Roman" sz="220" lang="default" weight="bold"/>
-            <pm:ea face="SimSun" sz="220" lang="default" weight="bold"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <charset val="134"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -845,50 +812,19 @@
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
-      <patternFill patternType="none"/>
-    </fill>
-    <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF5B9BD5"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1785834872" type="1" fgLvl="100" fgClr="005B9BD5" bgLvl="0" bgClr="00FFFFFF"/>
-          </ext>
-        </extLst>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1785834872" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1785834872"/>
-        </ext>
-      </extLst>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -903,101 +839,65 @@
       <bottom style="thin">
         <color rgb="FFDEE0E3"/>
       </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1785834872">
-            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-          </pm:border>
-        </ext>
-      </extLst>
+      <diagonal/>
     </border>
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1785834872"/>
-        </ext>
-      </extLst>
-    </border>
-    <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1785834872"/>
-        </ext>
-      </extLst>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
-    <cellStyle name="常规 2" xfId="1"/>
+    <cellStyle name="常规" xfId="0" builtinId="0" customBuiltin="1"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0"/>
   <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
     <ext uri="smNativeData">
       <pm:charStyles xmlns:pm="smNativeData" id="1785834872" count="1">
         <pm:charStyle name="普通" fontId="0" Id="1"/>
@@ -1267,1548 +1167,1553 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:G75"/>
-  <sheetFormatPr defaultRowHeight="13.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G76"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.663793" customWidth="1" style="2"/>
-    <col min="2" max="2" width="28.577586" customWidth="1" style="2"/>
-    <col min="3" max="3" width="100.077586" customWidth="1" style="2"/>
-    <col min="4" max="4" width="23.663793" customWidth="1" style="2"/>
-    <col min="5" max="6" width="17.663793" customWidth="1" style="2"/>
-    <col min="7" max="7" width="24.163793" customWidth="1" style="2"/>
-    <col min="8" max="16384" width="8.663793" customWidth="1" style="2"/>
+    <col min="1" max="1" width="8.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="28.58203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="100.08203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="23.6640625" style="1" customWidth="1"/>
+    <col min="5" max="6" width="17.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="24.1640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="8.6640625" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="4" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="2:7">
-      <c r="B4" s="3" t="s">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F4" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G4" s="2" t="s">
+      <c r="D4" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="2:7">
-      <c r="B5" s="3" t="s">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F5" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G5" s="5" t="s">
+      <c r="D5" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="2:7" ht="19.50" customHeight="1">
-      <c r="B6" s="3" t="s">
+    <row r="6" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F6" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G6" s="5" t="s">
+      <c r="E6" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="2:7">
-      <c r="B7" s="3" t="s">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B7" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F7" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G7" s="5" t="s">
+      <c r="D7" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="2:7">
-      <c r="B8" s="3" t="s">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F8" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G8" s="5" t="s">
+      <c r="D8" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F8" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" s="4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="2:7">
-      <c r="B9" s="3" t="s">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B9" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F9" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G9" s="5" t="s">
+      <c r="D9" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F9" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" s="4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="2:7">
-      <c r="B10" s="3" t="s">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B10" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E10" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F10" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G10" s="5" t="s">
+      <c r="E10" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F10" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="2:7">
-      <c r="B11" s="3" t="s">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B11" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="E11" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F11" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G11" s="5" t="s">
+      <c r="E11" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F11" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="2:7">
-      <c r="B12" s="3" t="s">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B12" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E12" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F12" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G12" s="5" t="s">
+      <c r="D12" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F12" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="13" spans="2:7">
-      <c r="B13" s="3" t="s">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B13" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D13" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E13" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F13" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G13" s="5" t="s">
+      <c r="D13" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F13" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G13" s="4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="14" spans="2:7">
-      <c r="B14" s="3" t="s">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B14" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E14" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F14" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G14" s="5" t="s">
+      <c r="E14" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F14" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G14" s="4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="15" spans="2:7">
-      <c r="B15" s="3" t="s">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B15" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D15" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E15" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F15" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G15" s="5" t="s">
+      <c r="D15" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F15" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15" s="4" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="16" spans="2:7">
-      <c r="B16" s="3" t="s">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B16" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E16" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F16" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G16" s="5" t="s">
+      <c r="E16" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F16" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G16" s="4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="17" spans="2:7">
-      <c r="B17" s="3" t="s">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B17" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D17" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E17" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F17" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G17" s="5" t="s">
+      <c r="D17" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F17" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17" s="4" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="18" spans="2:7">
-      <c r="B18" s="3" t="s">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B18" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E18" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F18" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G18" s="5" t="s">
+      <c r="E18" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F18" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G18" s="4" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="2:7">
-      <c r="B19" s="3" t="s">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B19" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D19" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E19" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F19" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G19" s="5" t="s">
+      <c r="D19" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E19" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F19" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="20" spans="2:7">
-      <c r="B20" s="3" t="s">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B20" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D20" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E20" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F20" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G20" s="5" t="s">
+      <c r="D20" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E20" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F20" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" s="4" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="21" spans="2:7">
-      <c r="B21" s="3" t="s">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B21" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="D21" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E21" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F21" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G21" s="5" t="s">
+      <c r="D21" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E21" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F21" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="22" spans="2:7">
-      <c r="B22" s="3" t="s">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B22" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="D22" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E22" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F22" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G22" s="5" t="s">
+      <c r="D22" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E22" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F22" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="23" spans="2:7">
-      <c r="B23" s="3" t="s">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B23" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="D23" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E23" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F23" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G23" s="5" t="s">
+      <c r="D23" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E23" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F23" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" s="4" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="24" spans="2:7">
-      <c r="B24" s="3" t="s">
+    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B24" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="D24" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E24" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F24" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G24" s="5" t="s">
+      <c r="D24" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E24" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F24" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" s="4" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="25" spans="2:7">
-      <c r="B25" s="3" t="s">
+    <row r="25" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B25" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="D25" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E25" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F25" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G25" s="5" t="s">
+      <c r="D25" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E25" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F25" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="26" spans="2:7">
-      <c r="B26" s="3" t="s">
+    <row r="26" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B26" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C26" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="D26" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E26" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F26" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="5" t="s">
+      <c r="D26" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E26" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F26" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26" s="4" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="27" spans="2:7">
-      <c r="B27" s="3" t="s">
+    <row r="27" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B27" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="D27" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E27" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F27" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G27" s="5" t="s">
+      <c r="D27" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E27" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F27" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G27" s="4" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="28" spans="2:7">
-      <c r="B28" s="3" t="s">
+    <row r="28" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B28" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="C28" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="D28" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E28" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F28" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G28" s="5" t="s">
+      <c r="D28" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E28" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F28" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G28" s="4" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="29" spans="2:7">
-      <c r="B29" s="3" t="s">
+    <row r="29" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B29" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="D29" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E29" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F29" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G29" s="2" t="s">
+      <c r="D29" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E29" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F29" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G29" s="1" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="2:7">
-      <c r="B30" s="3" t="s">
+    <row r="30" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B30" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="D30" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E30" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F30" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G30" s="2" t="s">
+      <c r="D30" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E30" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F30" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G30" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="31" spans="2:7">
-      <c r="B31" s="3" t="s">
+    <row r="31" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B31" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="D31" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E31" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F31" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G31" s="2" t="s">
+      <c r="D31" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E31" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F31" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G31" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="32" spans="2:7">
-      <c r="B32" s="3" t="s">
+    <row r="32" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B32" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="D32" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E32" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F32" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G32" s="2" t="s">
+      <c r="D32" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E32" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F32" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G32" s="1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="33" spans="2:7">
-      <c r="B33" s="3" t="s">
+    <row r="33" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B33" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="D33" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E33" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F33" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G33" s="2" t="s">
+      <c r="D33" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E33" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F33" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G33" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="34" spans="2:7">
-      <c r="B34" s="2" t="s">
+    <row r="34" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B34" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D34" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E34" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F34" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G34" s="2" t="s">
+      <c r="D34" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E34" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F34" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G34" s="1" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="35" spans="2:7">
-      <c r="B35" s="2" t="s">
+    <row r="35" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B35" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="D35" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E35" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F35" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G35" s="2" t="s">
+      <c r="D35" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E35" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F35" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G35" s="1" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="36" spans="2:7">
-      <c r="B36" s="2" t="s">
+    <row r="36" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B36" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="D36" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E36" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F36" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G36" s="2" t="s">
+      <c r="D36" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E36" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F36" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G36" s="1" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="37" spans="2:7">
-      <c r="B37" s="2" t="s">
+    <row r="37" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B37" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D37" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E37" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F37" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G37" s="2" t="s">
+      <c r="D37" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E37" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F37" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G37" s="1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="38" spans="2:7">
-      <c r="B38" s="2" t="s">
+    <row r="38" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B38" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="D38" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E38" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F38" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G38" s="2" t="s">
+      <c r="D38" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E38" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F38" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G38" s="1" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="39" spans="2:7">
-      <c r="B39" s="2" t="s">
+    <row r="39" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B39" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="D39" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E39" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F39" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G39" s="2" t="s">
+      <c r="D39" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E39" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F39" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G39" s="1" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="40" spans="2:7">
-      <c r="B40" s="2" t="s">
+    <row r="40" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B40" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="D40" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E40" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F40" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G40" s="2" t="s">
+      <c r="D40" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E40" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F40" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G40" s="1" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="41" spans="2:7">
-      <c r="B41" s="2" t="s">
+    <row r="41" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B41" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C41" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="D41" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E41" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F41" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G41" s="2" t="s">
+      <c r="D41" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E41" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F41" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G41" s="1" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="42" spans="2:7">
-      <c r="B42" s="2" t="s">
+    <row r="42" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B42" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C42" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="D42" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E42" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F42" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G42" s="2" t="s">
+      <c r="D42" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E42" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F42" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G42" s="1" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="43" spans="2:7">
-      <c r="B43" s="2" t="s">
+    <row r="43" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B43" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C43" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D43" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E43" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F43" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G43" s="2" t="s">
+      <c r="D43" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E43" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F43" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G43" s="1" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="44" spans="2:7">
-      <c r="B44" s="2" t="s">
+    <row r="44" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B44" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="C44" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="D44" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E44" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F44" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G44" s="2" t="s">
+      <c r="D44" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E44" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F44" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G44" s="1" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="45" spans="2:7">
-      <c r="B45" s="2" t="s">
+    <row r="45" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B45" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C45" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="D45" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E45" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F45" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G45" s="2" t="s">
+      <c r="D45" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E45" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F45" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G45" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="46" spans="2:7">
-      <c r="B46" s="2" t="s">
+    <row r="46" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B46" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C46" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="D46" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E46" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F46" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G46" s="2" t="s">
+      <c r="D46" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E46" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F46" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G46" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="47" spans="2:7">
-      <c r="B47" s="2" t="s">
+    <row r="47" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B47" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C47" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="D47" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E47" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F47" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G47" s="2" t="s">
+      <c r="D47" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E47" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F47" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G47" s="1" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="48" spans="2:7">
-      <c r="B48" s="2" t="s">
+    <row r="48" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B48" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C48" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="D48" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E48" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F48" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G48" s="2" t="s">
+      <c r="D48" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E48" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F48" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G48" s="1" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="49" spans="2:7">
-      <c r="B49" s="2" t="s">
+    <row r="49" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B49" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C49" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="D49" s="7" t="s">
+      <c r="D49" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="E49" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F49" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G49" s="2" t="s">
+      <c r="E49" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F49" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G49" s="1" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="50" spans="2:7">
-      <c r="B50" s="2" t="s">
+    <row r="50" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B50" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C50" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="D50" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E50" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F50" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G50" s="2" t="s">
+      <c r="D50" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E50" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F50" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G50" s="1" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="51" spans="2:7">
-      <c r="B51" s="2" t="s">
+    <row r="51" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B51" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="C51" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D51" s="7" t="s">
+      <c r="D51" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="E51" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F51" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G51" s="2" t="s">
+      <c r="E51" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F51" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G51" s="1" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="52" spans="2:7">
-      <c r="B52" s="2" t="s">
+    <row r="52" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B52" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C52" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="D52" s="7" t="s">
+      <c r="D52" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="E52" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F52" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G52" s="2" t="s">
+      <c r="E52" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F52" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G52" s="1" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="53" spans="2:7">
-      <c r="B53" s="2" t="s">
+    <row r="53" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B53" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="C53" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="D53" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E53" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F53" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G53" s="2" t="s">
+      <c r="D53" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E53" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F53" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G53" s="1" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="54" spans="2:7">
-      <c r="B54" s="2" t="s">
+    <row r="54" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B54" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C54" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="D54" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E54" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F54" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G54" s="2" t="s">
+      <c r="D54" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E54" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F54" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G54" s="1" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="55" spans="2:7">
-      <c r="B55" s="2" t="s">
+    <row r="55" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B55" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C55" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D55" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E55" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F55" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G55" s="2" t="s">
+      <c r="D55" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E55" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F55" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G55" s="1" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="56" spans="2:7">
-      <c r="B56" s="2" t="s">
+    <row r="56" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B56" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="C56" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="D56" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E56" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F56" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G56" s="2" t="s">
+      <c r="D56" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E56" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F56" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G56" s="1" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="57" spans="2:7">
-      <c r="B57" s="2" t="s">
+    <row r="57" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B57" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="C57" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="D57" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E57" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F57" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G57" s="2" t="s">
+      <c r="D57" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E57" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F57" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G57" s="1" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="58" spans="2:7">
-      <c r="B58" s="2" t="s">
+    <row r="58" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B58" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="C58" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="D58" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E58" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F58" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G58" s="2" t="s">
+      <c r="D58" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E58" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F58" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G58" s="1" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="59" spans="2:7">
-      <c r="B59" s="2" t="s">
+    <row r="59" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B59" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="C59" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="D59" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E59" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F59" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G59" s="2" t="s">
+      <c r="D59" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E59" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F59" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G59" s="1" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="60" spans="2:7">
-      <c r="B60" s="2" t="s">
+    <row r="60" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B60" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="C60" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="D60" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E60" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F60" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G60" s="2" t="s">
+      <c r="D60" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E60" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F60" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G60" s="1" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="61" spans="2:7">
-      <c r="B61" s="2" t="s">
+    <row r="61" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B61" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="C61" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="D61" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E61" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F61" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G61" s="2" t="s">
+      <c r="D61" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E61" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F61" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G61" s="1" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="62" spans="2:7">
-      <c r="B62" s="2" t="s">
+    <row r="62" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B62" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="C62" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="D62" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E62" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F62" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G62" s="2" t="s">
+      <c r="D62" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E62" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F62" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G62" s="1" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="63" spans="2:7">
-      <c r="B63" s="2" t="s">
+    <row r="63" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B63" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="C63" s="2" t="s">
+      <c r="C63" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="D63" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E63" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F63" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G63" s="2" t="s">
+      <c r="D63" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E63" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F63" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G63" s="1" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="64" spans="2:7">
-      <c r="B64" s="2" t="s">
+    <row r="64" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B64" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="C64" s="2" t="s">
+      <c r="C64" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="D64" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E64" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F64" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G64" s="2" t="s">
+      <c r="D64" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E64" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F64" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G64" s="1" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="65" spans="2:7">
-      <c r="B65" s="2" t="s">
+    <row r="65" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B65" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="C65" s="2" t="s">
+      <c r="C65" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="D65" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E65" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F65" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G65" s="2" t="s">
+      <c r="D65" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E65" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F65" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G65" s="1" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="66" spans="2:7">
-      <c r="B66" s="2" t="s">
+    <row r="66" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B66" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C66" s="2" t="s">
+      <c r="C66" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="D66" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E66" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F66" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G66" s="2" t="s">
+      <c r="D66" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E66" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F66" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G66" s="1" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="67" spans="2:7">
-      <c r="B67" s="2" t="s">
+    <row r="67" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B67" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="C67" s="2" t="s">
+      <c r="C67" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="D67" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E67" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F67" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G67" s="2" t="s">
+      <c r="D67" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E67" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F67" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G67" s="1" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="68" spans="2:7">
-      <c r="B68" s="2" t="s">
+    <row r="68" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B68" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="C68" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="D68" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E68" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F68" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G68" s="2" t="s">
+      <c r="D68" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E68" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F68" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G68" s="1" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="69" spans="2:7">
-      <c r="B69" s="2" t="s">
+    <row r="69" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B69" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="C69" s="2" t="s">
+      <c r="C69" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="D69" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E69" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F69" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G69" s="2" t="s">
+      <c r="D69" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E69" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F69" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G69" s="1" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="70" spans="2:7">
-      <c r="B70" s="2" t="s">
+    <row r="70" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B70" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="C70" s="2" t="s">
+      <c r="C70" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="D70" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E70" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G70" s="2" t="s">
+      <c r="D70" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E70" s="1">
+        <v>1</v>
+      </c>
+      <c r="F70" s="1">
+        <v>0</v>
+      </c>
+      <c r="G70" s="1" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="71" spans="2:7">
-      <c r="B71" s="2" t="s">
+    <row r="71" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B71" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="C71" s="9" t="s">
+      <c r="C71" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="D71" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E71" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F71" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G71" s="2" t="s">
+      <c r="D71" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E71" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F71" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G71" s="1" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="72" spans="2:7">
-      <c r="B72" s="2" t="s">
+    <row r="72" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B72" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="C72" s="2" t="s">
+      <c r="C72" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="D72" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E72" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F72" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G72" s="2" t="s">
+      <c r="D72" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E72" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F72" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G72" s="1" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="73" spans="2:7">
-      <c r="B73" s="2" t="s">
+    <row r="73" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B73" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="C73" s="2" t="s">
+      <c r="C73" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="D73" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E73" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F73" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G73" s="2" t="s">
+      <c r="D73" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E73" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F73" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G73" s="1" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="74" spans="2:7">
-      <c r="B74" s="2" t="s">
+    <row r="74" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B74" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="C74" s="2" t="s">
+      <c r="C74" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="D74" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E74" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F74" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G74" s="10" t="s">
+      <c r="D74" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E74" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F74" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G74" s="1" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="75" spans="2:7">
-      <c r="B75" s="2" t="s">
+    <row r="75" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B75" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="C75" s="2" t="s">
+      <c r="C75" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="D75" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E75" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F75" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G75" s="10" t="s">
+      <c r="D75" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E75" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F75" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G75" s="1" t="s">
         <v>239</v>
       </c>
     </row>
+    <row r="76" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B76" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="C76" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="D76" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E76" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="F76" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="G76" s="9" t="s">
+        <v>243</v>
+      </c>
+    </row>
   </sheetData>
-  <printOptions>
-    <extLst>
-      <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1785834872" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
-      </ext>
-    </extLst>
-  </printOptions>
-  <pageMargins left="0.700000" right="0.700000" top="0.750000" bottom="0.750000" header="0.300000" footer="0.300000"/>
-  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="1"/>
-  <headerFooter>
-    <extLst>
-      <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1785834872" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1785834872" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1785834872" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1785834872" Id="1" type="0" value="0"/>
-      </ext>
-    </extLst>
-  </headerFooter>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" fitToWidth="0"/>
   <extLst>
     <ext uri="smNativeData">
       <pm:sheetPrefs xmlns:pm="smNativeData" day="1785834872" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">

--- a/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
@@ -1,34 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
+  <fileSharing readOnlyRecommended="0" userName="Lumino Game 03"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\Project\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3C615D7-F7F2-4DA2-8592-FBCB33D5ADC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1520" yWindow="1520" windowWidth="28800" windowHeight="15370" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView activeTab="0" xWindow="240" yWindow="60" windowWidth="28800" windowHeight="15370" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:revision xmlns:pm="smNativeData" day="1786418658" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
-      <pm:docPrefs xmlns:pm="smNativeData" id="1786418658" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
-      <pm:compatibility xmlns:pm="smNativeData" id="1786418658" overlapCells="1"/>
-      <pm:defCurrency xmlns:pm="smNativeData" id="1786418658"/>
+      <pm:revision xmlns:pm="smNativeData" day="1786600546" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
+      <pm:docPrefs xmlns:pm="smNativeData" id="1786600546" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
+      <pm:compatibility xmlns:pm="smNativeData" id="1786600546" overlapCells="1"/>
+      <pm:defCurrency xmlns:pm="smNativeData" id="1786600546"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="251">
   <si>
     <t>##var</t>
   </si>
@@ -763,6 +758,15 @@
   </si>
   <si>
     <t>任务面板</t>
+  </si>
+  <si>
+    <t>QuestAcceptPop</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/Quest/QuestAcceptPop.prefab</t>
+  </si>
+  <si>
+    <t>任务接受弹窗</t>
   </si>
   <si>
     <t>QuestRewardPop</t>
@@ -777,46 +781,97 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="9">
+    <numFmt numFmtId="5" formatCode="#,##0\ &quot;¥&quot;;\-#,##0\ &quot;¥&quot;"/>
+    <numFmt numFmtId="6" formatCode="#,##0\ &quot;¥&quot;;[Red]\-#,##0\ &quot;¥&quot;"/>
+    <numFmt numFmtId="7" formatCode="#,##0.00\ &quot;¥&quot;;\-#,##0.00\ &quot;¥&quot;"/>
+    <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;¥&quot;;[Red]\-#,##0.00\ &quot;¥&quot;"/>
+    <numFmt numFmtId="42" formatCode="_-* #,##0\ &quot;¥&quot;_-;\-* #,##0\ &quot;¥&quot;_-;_-* &quot;-&quot;\ &quot;¥&quot;_-;_-@_-"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0\ _¥_-;\-* #,##0\ _¥_-;_-* &quot;-&quot;\ _¥_-;_-@_-"/>
+    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;¥&quot;_-;\-* #,##0.00\ &quot;¥&quot;_-;_-* &quot;-&quot;??\ &quot;¥&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _¥_-;\-* #,##0.00\ _¥_-;_-* &quot;-&quot;??\ _¥_-;_-@_-"/>
+    <numFmt numFmtId="49" formatCode="@"/>
+  </numFmts>
+  <fonts count="5">
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="等线"/>
       <charset val="134"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1786600546" ulstyle="none" kern="1">
+            <pm:latin face="等线" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1786600546" ulstyle="none" kern="1">
+            <pm:latin face="Arial" sz="200" lang="default"/>
+            <pm:cs face="Times New Roman" sz="200" lang="default"/>
+            <pm:ea face="SimSun" sz="200" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="134"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1786600546" ulstyle="none" kern="1">
+            <pm:latin face="等线" sz="200" lang="default"/>
+            <pm:cs face="Times New Roman" sz="200" lang="default"/>
+            <pm:ea face="SimSun" sz="200" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF1F2329"/>
       <name val="等线"/>
       <charset val="134"/>
+      <color rgb="FF1F2329"/>
+      <sz val="11"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1786600546" fgClr="1F2329" ulstyle="none" kern="1">
+            <pm:latin face="等线" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="等线"/>
       <charset val="134"/>
-    </font>
-    <font>
+      <b/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <charset val="134"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1786600546" ulstyle="none" kern="1">
+            <pm:latin face="等线" sz="220" lang="default" weight="bold"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default" weight="bold"/>
+            <pm:ea face="SimSun" sz="220" lang="default" weight="bold"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -824,19 +879,50 @@
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF5B9BD5"/>
         <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1786600546" type="1" fgLvl="100" fgClr="005B9BD5" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1786600546" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1786600546"/>
+        </ext>
+      </extLst>
     </border>
     <border>
       <left style="thin">
@@ -851,49 +937,92 @@
       <bottom style="thin">
         <color rgb="FFDEE0E3"/>
       </bottom>
-      <diagonal/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1786600546">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+          </pm:border>
+        </ext>
+      </extLst>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1786600546"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1786600546"/>
+        </ext>
+      </extLst>
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -901,29 +1030,19 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="常规" xfId="0" builtinId="0" customBuiltin="1"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
+    <cellStyle name="常规 2" xfId="1"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
     <ext uri="smNativeData">
-      <pm:charStyles xmlns:pm="smNativeData" id="1786418658" count="1">
+      <pm:charStyles xmlns:pm="smNativeData" id="1786600546" count="1">
         <pm:charStyle name="普通" fontId="0" Id="1"/>
       </pm:charStyles>
-      <pm:colors xmlns:pm="smNativeData" id="1786418658" count="6">
+      <pm:colors xmlns:pm="smNativeData" id="1786600546" count="3">
         <pm:color name="颜色 24" rgb="1F2329"/>
         <pm:color name="颜色 25" rgb="5B9BD5"/>
         <pm:color name="颜色 26" rgb="DEE0E3"/>
-        <pm:color name="黑色" rgb="000000"/>
-        <pm:color name="颜色 32" rgb="1F2329"/>
-        <pm:color name="颜色 50" rgb="DEE0E3"/>
       </pm:colors>
     </ext>
   </extLst>
@@ -1185,1597 +1304,1631 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <dimension ref="A1:G79"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.45"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="28.58203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="100.08203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="23.6640625" style="1" customWidth="1"/>
-    <col min="5" max="6" width="17.6640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="24.1640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="8.6640625" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.6640625" style="1"/>
+    <col min="1" max="1" width="8.663793" customWidth="1" style="2"/>
+    <col min="2" max="2" width="28.577586" customWidth="1" style="2"/>
+    <col min="3" max="3" width="100.077586" customWidth="1" style="2"/>
+    <col min="4" max="4" width="23.663793" customWidth="1" style="2"/>
+    <col min="5" max="6" width="17.663793" customWidth="1" style="2"/>
+    <col min="7" max="7" width="24.163793" customWidth="1" style="2"/>
+    <col min="8" max="16384" width="8.663793" customWidth="1" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
+    <row r="1" spans="1:7">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:7">
+      <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:7">
+      <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B4" s="2" t="s">
+    <row r="4" spans="2:7">
+      <c r="B4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F4" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G4" s="1" t="s">
+      <c r="D4" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B5" s="2" t="s">
+    <row r="5" spans="2:7">
+      <c r="B5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F5" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G5" s="4" t="s">
+      <c r="D5" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="2" t="s">
+    <row r="6" spans="2:7" ht="19.50" customHeight="1">
+      <c r="B6" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F6" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G6" s="4" t="s">
+      <c r="E6" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B7" s="2" t="s">
+    <row r="7" spans="2:7">
+      <c r="B7" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F7" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G7" s="4" t="s">
+      <c r="D7" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B8" s="2" t="s">
+    <row r="8" spans="2:7">
+      <c r="B8" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F8" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G8" s="4" t="s">
+      <c r="D8" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" s="5" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B9" s="2" t="s">
+    <row r="9" spans="2:7">
+      <c r="B9" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F9" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G9" s="4" t="s">
+      <c r="D9" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" s="5" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B10" s="2" t="s">
+    <row r="10" spans="2:7">
+      <c r="B10" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="E10" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F10" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G10" s="4" t="s">
+      <c r="E10" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B11" s="2" t="s">
+    <row r="11" spans="2:7">
+      <c r="B11" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="E11" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F11" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G11" s="4" t="s">
+      <c r="E11" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G11" s="5" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B12" s="2" t="s">
+    <row r="12" spans="2:7">
+      <c r="B12" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E12" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F12" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G12" s="4" t="s">
+      <c r="D12" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F12" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12" s="5" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B13" s="2" t="s">
+    <row r="13" spans="2:7">
+      <c r="B13" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E13" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F13" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G13" s="4" t="s">
+      <c r="D13" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G13" s="5" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B14" s="2" t="s">
+    <row r="14" spans="2:7">
+      <c r="B14" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E14" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F14" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G14" s="4" t="s">
+      <c r="E14" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F14" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G14" s="5" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B15" s="2" t="s">
+    <row r="15" spans="2:7">
+      <c r="B15" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D15" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E15" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F15" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G15" s="4" t="s">
+      <c r="D15" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F15" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15" s="5" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B16" s="2" t="s">
+    <row r="16" spans="2:7">
+      <c r="B16" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E16" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F16" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G16" s="4" t="s">
+      <c r="E16" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G16" s="5" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B17" s="2" t="s">
+    <row r="17" spans="2:7">
+      <c r="B17" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="D17" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E17" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F17" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G17" s="4" t="s">
+      <c r="D17" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F17" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17" s="5" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B18" s="2" t="s">
+    <row r="18" spans="2:7">
+      <c r="B18" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E18" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F18" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G18" s="4" t="s">
+      <c r="E18" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F18" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G18" s="5" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B19" s="2" t="s">
+    <row r="19" spans="2:7">
+      <c r="B19" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="D19" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E19" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F19" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G19" s="4" t="s">
+      <c r="D19" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E19" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F19" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" s="5" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B20" s="2" t="s">
+    <row r="20" spans="2:7">
+      <c r="B20" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="D20" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E20" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F20" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G20" s="4" t="s">
+      <c r="D20" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E20" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F20" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" s="5" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B21" s="2" t="s">
+    <row r="21" spans="2:7">
+      <c r="B21" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="D21" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E21" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F21" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G21" s="4" t="s">
+      <c r="D21" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E21" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F21" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" s="5" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B22" s="2" t="s">
+    <row r="22" spans="2:7">
+      <c r="B22" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="D22" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E22" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F22" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G22" s="4" t="s">
+      <c r="D22" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E22" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F22" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" s="5" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B23" s="2" t="s">
+    <row r="23" spans="2:7">
+      <c r="B23" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C23" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="D23" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E23" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F23" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G23" s="4" t="s">
+      <c r="D23" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E23" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F23" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" s="5" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B24" s="2" t="s">
+    <row r="24" spans="2:7">
+      <c r="B24" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C24" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D24" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E24" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F24" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G24" s="4" t="s">
+      <c r="D24" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E24" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F24" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" s="5" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B25" s="2" t="s">
+    <row r="25" spans="2:7">
+      <c r="B25" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C25" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="D25" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E25" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F25" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G25" s="4" t="s">
+      <c r="D25" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E25" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F25" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" s="5" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B26" s="2" t="s">
+    <row r="26" spans="2:7">
+      <c r="B26" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="C26" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="D26" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E26" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F26" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="4" t="s">
+      <c r="D26" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E26" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F26" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26" s="5" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B27" s="2" t="s">
+    <row r="27" spans="2:7">
+      <c r="B27" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C27" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="D27" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E27" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F27" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G27" s="4" t="s">
+      <c r="D27" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E27" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F27" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G27" s="5" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B28" s="2" t="s">
+    <row r="28" spans="2:7">
+      <c r="B28" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="C28" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="D28" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E28" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F28" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G28" s="4" t="s">
+      <c r="D28" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E28" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F28" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G28" s="5" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B29" s="2" t="s">
+    <row r="29" spans="2:7">
+      <c r="B29" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="D29" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E29" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F29" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G29" s="1" t="s">
+      <c r="D29" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E29" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F29" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G29" s="2" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B30" s="2" t="s">
+    <row r="30" spans="2:7">
+      <c r="B30" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D30" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E30" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F30" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G30" s="1" t="s">
+      <c r="D30" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E30" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F30" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G30" s="2" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B31" s="2" t="s">
+    <row r="31" spans="2:7">
+      <c r="B31" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="D31" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E31" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F31" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G31" s="1" t="s">
+      <c r="D31" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E31" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F31" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G31" s="2" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B32" s="2" t="s">
+    <row r="32" spans="2:7">
+      <c r="B32" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="D32" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E32" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F32" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G32" s="1" t="s">
+      <c r="D32" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E32" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F32" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G32" s="2" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B33" s="2" t="s">
+    <row r="33" spans="2:7">
+      <c r="B33" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="D33" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E33" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F33" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G33" s="1" t="s">
+      <c r="D33" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E33" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F33" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G33" s="2" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B34" s="1" t="s">
+    <row r="34" spans="2:7">
+      <c r="B34" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D34" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E34" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F34" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G34" s="1" t="s">
+      <c r="D34" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E34" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F34" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G34" s="2" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B35" s="1" t="s">
+    <row r="35" spans="2:7">
+      <c r="B35" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="D35" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E35" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F35" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G35" s="1" t="s">
+      <c r="D35" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E35" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F35" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G35" s="2" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B36" s="1" t="s">
+    <row r="36" spans="2:7">
+      <c r="B36" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="D36" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E36" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F36" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G36" s="1" t="s">
+      <c r="D36" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E36" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F36" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G36" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B37" s="1" t="s">
+    <row r="37" spans="2:7">
+      <c r="B37" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="D37" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E37" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F37" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G37" s="1" t="s">
+      <c r="D37" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E37" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F37" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G37" s="2" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="38" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B38" s="1" t="s">
+    <row r="38" spans="2:7">
+      <c r="B38" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="D38" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E38" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F38" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G38" s="1" t="s">
+      <c r="D38" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E38" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F38" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G38" s="2" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B39" s="1" t="s">
+    <row r="39" spans="2:7">
+      <c r="B39" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="D39" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E39" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F39" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G39" s="1" t="s">
+      <c r="D39" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E39" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F39" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G39" s="2" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B40" s="1" t="s">
+    <row r="40" spans="2:7">
+      <c r="B40" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="D40" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E40" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F40" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G40" s="1" t="s">
+      <c r="D40" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E40" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F40" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G40" s="2" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B41" s="1" t="s">
+    <row r="41" spans="2:7">
+      <c r="B41" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="D41" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E41" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F41" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G41" s="1" t="s">
+      <c r="D41" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E41" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F41" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G41" s="2" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="42" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B42" s="1" t="s">
+    <row r="42" spans="2:7">
+      <c r="B42" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C42" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="D42" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E42" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F42" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G42" s="1" t="s">
+      <c r="D42" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E42" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F42" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G42" s="2" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="43" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B43" s="1" t="s">
+    <row r="43" spans="2:7">
+      <c r="B43" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C43" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="D43" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E43" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F43" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G43" s="1" t="s">
+      <c r="D43" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E43" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F43" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G43" s="2" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B44" s="1" t="s">
+    <row r="44" spans="2:7">
+      <c r="B44" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C44" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="D44" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E44" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F44" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G44" s="1" t="s">
+      <c r="D44" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E44" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F44" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G44" s="2" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="45" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B45" s="1" t="s">
+    <row r="45" spans="2:7">
+      <c r="B45" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C45" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="D45" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E45" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F45" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G45" s="1" t="s">
+      <c r="D45" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E45" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F45" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G45" s="2" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="46" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B46" s="1" t="s">
+    <row r="46" spans="2:7">
+      <c r="B46" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C46" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="D46" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E46" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F46" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G46" s="1" t="s">
+      <c r="D46" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E46" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F46" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G46" s="2" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="47" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B47" s="1" t="s">
+    <row r="47" spans="2:7">
+      <c r="B47" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C47" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="D47" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E47" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F47" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G47" s="1" t="s">
+      <c r="D47" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E47" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F47" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G47" s="2" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="48" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B48" s="1" t="s">
+    <row r="48" spans="2:7">
+      <c r="B48" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="C48" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="D48" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E48" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F48" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G48" s="1" t="s">
+      <c r="D48" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E48" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F48" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G48" s="2" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="49" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B49" s="1" t="s">
+    <row r="49" spans="2:7">
+      <c r="B49" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C49" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="D49" s="6" t="s">
+      <c r="D49" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="E49" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F49" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G49" s="1" t="s">
+      <c r="E49" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F49" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G49" s="2" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="50" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B50" s="1" t="s">
+    <row r="50" spans="2:7">
+      <c r="B50" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="C50" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="D50" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E50" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F50" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G50" s="1" t="s">
+      <c r="D50" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E50" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F50" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G50" s="2" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="51" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B51" s="1" t="s">
+    <row r="51" spans="2:7">
+      <c r="B51" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="C51" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="D51" s="6" t="s">
+      <c r="D51" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="E51" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F51" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G51" s="1" t="s">
+      <c r="E51" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F51" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G51" s="2" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="52" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B52" s="1" t="s">
+    <row r="52" spans="2:7">
+      <c r="B52" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="C52" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="D52" s="6" t="s">
+      <c r="D52" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="E52" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F52" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G52" s="1" t="s">
+      <c r="E52" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F52" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G52" s="2" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="53" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B53" s="1" t="s">
+    <row r="53" spans="2:7">
+      <c r="B53" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="C53" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="D53" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E53" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F53" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G53" s="1" t="s">
+      <c r="D53" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E53" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F53" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G53" s="2" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="54" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B54" s="1" t="s">
+    <row r="54" spans="2:7">
+      <c r="B54" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="C54" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="D54" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E54" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F54" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G54" s="1" t="s">
+      <c r="D54" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E54" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F54" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G54" s="2" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="55" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B55" s="1" t="s">
+    <row r="55" spans="2:7">
+      <c r="B55" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="C55" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="D55" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E55" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F55" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G55" s="1" t="s">
+      <c r="D55" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E55" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F55" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G55" s="2" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="56" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B56" s="1" t="s">
+    <row r="56" spans="2:7">
+      <c r="B56" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="C56" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="D56" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E56" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F56" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G56" s="1" t="s">
+      <c r="D56" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E56" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F56" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G56" s="2" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="57" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B57" s="1" t="s">
+    <row r="57" spans="2:7">
+      <c r="B57" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="C57" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="D57" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E57" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F57" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G57" s="1" t="s">
+      <c r="D57" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E57" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F57" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G57" s="2" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="58" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B58" s="1" t="s">
+    <row r="58" spans="2:7">
+      <c r="B58" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="C58" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="D58" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E58" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F58" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G58" s="1" t="s">
+      <c r="D58" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E58" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F58" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G58" s="2" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="59" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B59" s="1" t="s">
+    <row r="59" spans="2:7">
+      <c r="B59" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="C59" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="D59" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E59" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F59" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G59" s="1" t="s">
+      <c r="D59" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E59" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F59" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G59" s="2" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="60" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B60" s="1" t="s">
+    <row r="60" spans="2:7">
+      <c r="B60" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="C60" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="D60" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E60" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F60" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G60" s="1" t="s">
+      <c r="D60" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E60" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F60" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G60" s="2" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="61" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B61" s="1" t="s">
+    <row r="61" spans="2:7">
+      <c r="B61" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="C61" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="D61" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E61" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F61" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G61" s="1" t="s">
+      <c r="D61" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E61" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F61" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G61" s="2" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="62" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B62" s="1" t="s">
+    <row r="62" spans="2:7">
+      <c r="B62" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="C62" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="D62" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E62" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F62" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G62" s="1" t="s">
+      <c r="D62" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E62" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F62" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G62" s="2" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="63" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B63" s="1" t="s">
+    <row r="63" spans="2:7">
+      <c r="B63" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="C63" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="D63" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E63" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F63" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G63" s="1" t="s">
+      <c r="D63" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E63" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F63" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G63" s="2" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="64" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B64" s="1" t="s">
+    <row r="64" spans="2:7">
+      <c r="B64" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="C64" s="1" t="s">
+      <c r="C64" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="D64" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E64" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F64" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G64" s="1" t="s">
+      <c r="D64" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E64" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F64" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G64" s="2" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="65" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B65" s="1" t="s">
+    <row r="65" spans="2:7">
+      <c r="B65" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="C65" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="D65" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E65" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F65" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G65" s="1" t="s">
+      <c r="D65" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E65" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F65" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G65" s="2" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="66" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B66" s="1" t="s">
+    <row r="66" spans="2:7">
+      <c r="B66" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="C66" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="D66" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E66" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F66" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G66" s="1" t="s">
+      <c r="D66" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E66" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F66" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G66" s="2" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="67" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B67" s="1" t="s">
+    <row r="67" spans="2:7">
+      <c r="B67" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="C67" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="D67" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E67" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F67" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G67" s="1" t="s">
+      <c r="D67" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E67" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F67" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G67" s="2" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="68" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B68" s="1" t="s">
+    <row r="68" spans="2:7">
+      <c r="B68" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="C68" s="1" t="s">
+      <c r="C68" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="D68" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E68" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F68" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G68" s="1" t="s">
+      <c r="D68" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E68" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F68" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G68" s="2" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="69" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B69" s="1" t="s">
+    <row r="69" spans="2:7">
+      <c r="B69" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="C69" s="1" t="s">
+      <c r="C69" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="D69" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E69" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F69" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G69" s="1" t="s">
+      <c r="D69" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E69" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F69" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G69" s="2" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="70" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B70" s="1" t="s">
+    <row r="70" spans="2:7">
+      <c r="B70" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="C70" s="1" t="s">
+      <c r="C70" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="D70" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E70" s="1">
-        <v>1</v>
-      </c>
-      <c r="F70" s="1">
-        <v>0</v>
-      </c>
-      <c r="G70" s="1" t="s">
+      <c r="D70" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" s="2" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="71" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B71" s="1" t="s">
+    <row r="71" spans="2:7">
+      <c r="B71" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="C71" s="8" t="s">
+      <c r="C71" s="9" t="s">
         <v>226</v>
       </c>
-      <c r="D71" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E71" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F71" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G71" s="1" t="s">
+      <c r="D71" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E71" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F71" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G71" s="2" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="72" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B72" s="1" t="s">
+    <row r="72" spans="2:7">
+      <c r="B72" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="C72" s="1" t="s">
+      <c r="C72" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="D72" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E72" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F72" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G72" s="1" t="s">
+      <c r="D72" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E72" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F72" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G72" s="2" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="73" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B73" s="1" t="s">
+    <row r="73" spans="2:7">
+      <c r="B73" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C73" s="1" t="s">
+      <c r="C73" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="D73" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E73" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="F73" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G73" s="1" t="s">
+      <c r="D73" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E73" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F73" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G73" s="2" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="74" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B74" s="1" t="s">
+    <row r="74" spans="2:7">
+      <c r="B74" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="C74" s="1" t="s">
+      <c r="C74" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="D74" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E74" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="F74" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G74" s="1" t="s">
+      <c r="D74" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E74" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F74" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G74" s="2" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="75" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B75" s="1" t="s">
+    <row r="75" spans="2:7">
+      <c r="B75" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="C75" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="D75" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E75" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="F75" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G75" s="1" t="s">
+      <c r="D75" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E75" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F75" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G75" s="2" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="76" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B76" s="1" t="s">
+    <row r="76" spans="2:7">
+      <c r="B76" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="C76" s="1" t="s">
+      <c r="C76" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="D76" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E76" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F76" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G76" s="1" t="s">
+      <c r="D76" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E76" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F76" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G76" s="2" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="77" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B77" s="9" t="s">
+    <row r="77" spans="2:7">
+      <c r="B77" s="10" t="s">
         <v>242</v>
       </c>
-      <c r="C77" s="9" t="s">
+      <c r="C77" s="10" t="s">
         <v>243</v>
       </c>
-      <c r="D77" s="9" t="s">
+      <c r="D77" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="E77" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F77" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G77" s="9" t="s">
+      <c r="E77" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F77" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G77" s="10" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="78" spans="2:7" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="79" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B79" s="10" t="s">
+    <row r="78" spans="2:7">
+      <c r="B78" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="C79" s="10" t="s">
+      <c r="C78" s="11" t="s">
         <v>246</v>
       </c>
-      <c r="D79" s="10" t="s">
+      <c r="D78" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="E79" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="F79" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G79" s="10" t="s">
+      <c r="E78" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F78" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G78" s="11" t="s">
         <v>247</v>
       </c>
     </row>
+    <row r="79" spans="2:7">
+      <c r="B79" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="C79" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="D79" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="E79" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F79" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G79" s="11" t="s">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" fitToWidth="0"/>
+  <printOptions>
+    <extLst>
+      <ext uri="smNativeData">
+        <pm:pageFlags xmlns:pm="smNativeData" id="1786600546" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+      </ext>
+    </extLst>
+  </printOptions>
+  <pageMargins left="0.700000" right="0.700000" top="0.750000" bottom="0.750000" header="0.300000" footer="0.300000"/>
+  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="1"/>
+  <headerFooter>
+    <extLst>
+      <ext uri="smNativeData">
+        <pm:header xmlns:pm="smNativeData" id="1786600546" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1786600546" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1786600546" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1786600546" Id="1" type="0" value="0"/>
+      </ext>
+    </extLst>
+  </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1786418658" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1786600546" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>

--- a/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFE2DBC7-042E-49E3-B36F-AB71ECFD5F56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C33EB465-0AF8-4A6C-8B2B-36BD493CF30A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4450" yWindow="2240" windowWidth="44100" windowHeight="18570" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="251">
   <si>
     <t>##var</t>
   </si>
@@ -769,6 +769,18 @@
   </si>
   <si>
     <t>任务奖励弹窗</t>
+  </si>
+  <si>
+    <t>TutorialUI</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/TutorialUI/TutorialUI.prefab</t>
+  </si>
+  <si>
+    <t>FALSE</t>
+  </si>
+  <si>
+    <t>新手引导遮罩UI</t>
   </si>
 </sst>
 </file>
@@ -1172,7 +1184,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.6640625" style="1" customWidth="1"/>
@@ -2754,6 +2766,26 @@
         <v>246</v>
       </c>
     </row>
+    <row r="79" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B79" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="C79" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="D79" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E79" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="F79" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="G79" s="9" t="s">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/UIPageData.xlsx
@@ -1,34 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C33EB465-0AF8-4A6C-8B2B-36BD493CF30A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4450" yWindow="2240" windowWidth="44100" windowHeight="18570" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="17680" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="smNativeData">
-      <pm:revision xmlns:pm="smNativeData" day="1786600546" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
-      <pm:docPrefs xmlns:pm="smNativeData" id="1786600546" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
-      <pm:compatibility xmlns:pm="smNativeData" id="1786600546" overlapCells="1"/>
-      <pm:defCurrency xmlns:pm="smNativeData" id="1786600546"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="249">
   <si>
     <t>##var</t>
   </si>
@@ -63,9 +67,6 @@
     <t>bool</t>
   </si>
   <si>
-    <t>bool</t>
-  </si>
-  <si>
     <t>##</t>
   </si>
   <si>
@@ -496,9 +497,6 @@
   </si>
   <si>
     <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/PopRewardPropertyUI/PopRewardPropertyUI.prefab</t>
-  </si>
-  <si>
-    <t>UIPop</t>
   </si>
   <si>
     <t>属性获得界面</t>
@@ -786,8 +784,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -798,29 +802,174 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF1F2329"/>
       <name val="等线"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
+      <color theme="1"/>
+      <name val="SimSun"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="等线"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="SimSun"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="SimSun"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="SimSun"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="SimSun"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -833,8 +982,194 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -858,16 +1193,251 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
-      <bottom/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -876,22 +1446,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -901,28 +1471,62 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="常规" xfId="0" builtinId="0" customBuiltin="1"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+  <cellStyles count="50">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 2" xfId="49"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-    <ext uri="smNativeData">
-      <pm:charStyles xmlns:pm="smNativeData" id="1786600546" count="1">
-        <pm:charStyle name="普通" fontId="0" Id="1"/>
-      </pm:charStyles>
-      <pm:colors xmlns:pm="smNativeData" id="1786600546" count="3">
-        <pm:color name="颜色 24" rgb="1F2329"/>
-        <pm:color name="颜色 25" rgb="5B9BD5"/>
-        <pm:color name="颜色 26" rgb="DEE0E3"/>
-      </pm:colors>
     </ext>
   </extLst>
 </styleSheet>
@@ -1152,9 +1756,6 @@
     <a:spDef>
       <a:spPr/>
       <a:bodyPr>
-        <a:prstTxWarp prst="textNoShape">
-          <a:avLst/>
-        </a:prstTxWarp>
         <a:noAutofit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -1178,26 +1779,26 @@
       </a:style>
     </a:spDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:G79"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="28.58203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="100.08203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="23.6640625" style="1" customWidth="1"/>
-    <col min="5" max="6" width="17.6640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="24.1640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="8.6640625" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.6640625" style="1"/>
+    <col min="1" max="1" width="8.66666666666667" style="1" customWidth="1"/>
+    <col min="2" max="2" width="28.5833333333333" style="1" customWidth="1"/>
+    <col min="3" max="3" width="100.083333333333" style="1" customWidth="1"/>
+    <col min="4" max="4" width="23.6666666666667" style="1" customWidth="1"/>
+    <col min="5" max="6" width="17.6666666666667" style="1" customWidth="1"/>
+    <col min="7" max="7" width="24.1666666666667" style="1" customWidth="1"/>
+    <col min="8" max="8" width="8.66666666666667" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.66666666666667" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1220,7 +1821,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -1237,1566 +1838,1558 @@
         <v>10</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="1" t="s">
+    </row>
+    <row r="4" spans="1:7">
+      <c r="B4" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F4" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G4" s="1" t="s">
+    </row>
+    <row r="5" spans="1:7">
+      <c r="B5" s="2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="D5" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F5" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G5" s="4" t="s">
+    </row>
+    <row r="6" ht="19.5" customHeight="1" spans="1:7">
+      <c r="B6" s="2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="D6" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="E6" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F6" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G6" s="4" t="s">
+    </row>
+    <row r="7" spans="1:7">
+      <c r="B7" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="D7" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F7" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G7" s="4" t="s">
+    </row>
+    <row r="8" spans="1:7">
+      <c r="B8" s="2" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="D8" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F8" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F8" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G8" s="4" t="s">
+    </row>
+    <row r="9" spans="1:7">
+      <c r="B9" s="2" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="D9" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F9" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F9" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G9" s="4" t="s">
+    </row>
+    <row r="10" spans="1:7">
+      <c r="B10" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="D10" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="E10" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F10" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E10" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F10" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G10" s="4" t="s">
+    </row>
+    <row r="11" spans="1:7">
+      <c r="B11" s="2" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="D11" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F11" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F11" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G11" s="4" t="s">
+    </row>
+    <row r="12" spans="1:7">
+      <c r="B12" s="2" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B12" s="2" t="s">
+      <c r="C12" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="D12" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F12" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E12" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F12" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G12" s="4" t="s">
+    </row>
+    <row r="13" spans="1:7">
+      <c r="B13" s="2" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B13" s="2" t="s">
+      <c r="C13" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="D13" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F13" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G13" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E13" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F13" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G13" s="4" t="s">
+    </row>
+    <row r="14" spans="1:7">
+      <c r="B14" s="2" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B14" s="2" t="s">
+      <c r="C14" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="D14" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F14" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G14" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D14" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E14" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F14" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G14" s="4" t="s">
+    </row>
+    <row r="15" spans="1:7">
+      <c r="B15" s="2" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B15" s="2" t="s">
+      <c r="C15" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="D15" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F15" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="D15" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E15" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F15" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G15" s="4" t="s">
+    </row>
+    <row r="16" spans="1:7">
+      <c r="B16" s="2" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B16" s="2" t="s">
+      <c r="C16" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="D16" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F16" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D16" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E16" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F16" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G16" s="4" t="s">
+    </row>
+    <row r="17" spans="2:7">
+      <c r="B17" s="2" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B17" s="2" t="s">
+      <c r="C17" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="D17" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F17" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G17" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="D17" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E17" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F17" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G17" s="4" t="s">
+    </row>
+    <row r="18" spans="2:7">
+      <c r="B18" s="2" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B18" s="2" t="s">
+      <c r="C18" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="D18" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F18" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D18" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E18" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F18" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G18" s="4" t="s">
+    </row>
+    <row r="19" spans="2:7">
+      <c r="B19" s="2" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B19" s="2" t="s">
+      <c r="C19" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="D19" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F19" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D19" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E19" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F19" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G19" s="4" t="s">
+    </row>
+    <row r="20" spans="2:7">
+      <c r="B20" s="2" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B20" s="2" t="s">
+      <c r="C20" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="D20" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F20" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="D20" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E20" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F20" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G20" s="4" t="s">
+    </row>
+    <row r="21" spans="2:7">
+      <c r="B21" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B21" s="2" t="s">
+      <c r="C21" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="D21" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E21" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F21" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D21" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E21" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F21" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G21" s="4" t="s">
+    </row>
+    <row r="22" spans="2:7">
+      <c r="B22" s="2" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B22" s="2" t="s">
+      <c r="C22" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="D22" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F22" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="D22" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E22" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F22" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G22" s="4" t="s">
+    </row>
+    <row r="23" spans="2:7">
+      <c r="B23" s="2" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B23" s="2" t="s">
+      <c r="C23" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="D23" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F23" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="D23" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E23" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F23" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G23" s="4" t="s">
+    </row>
+    <row r="24" spans="2:7">
+      <c r="B24" s="2" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B24" s="2" t="s">
+      <c r="C24" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="D24" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F24" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="D24" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E24" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F24" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G24" s="4" t="s">
+    </row>
+    <row r="25" spans="2:7">
+      <c r="B25" s="2" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B25" s="2" t="s">
+      <c r="C25" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="D25" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F25" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="D25" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E25" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F25" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G25" s="4" t="s">
+    </row>
+    <row r="26" spans="2:7">
+      <c r="B26" s="2" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B26" s="2" t="s">
+      <c r="C26" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="D26" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E26" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F26" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="D26" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E26" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F26" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="4" t="s">
+    </row>
+    <row r="27" spans="2:7">
+      <c r="B27" s="2" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B27" s="2" t="s">
+      <c r="C27" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="D27" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F27" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G27" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="D27" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E27" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F27" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G27" s="4" t="s">
+    </row>
+    <row r="28" spans="2:7">
+      <c r="B28" s="2" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B28" s="2" t="s">
+      <c r="C28" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="D28" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F28" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G28" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="D28" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E28" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F28" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G28" s="1" t="s">
+    </row>
+    <row r="29" spans="2:7">
+      <c r="B29" s="2" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B29" s="2" t="s">
+      <c r="C29" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="D29" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F29" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G29" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="D29" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E29" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F29" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G29" s="1" t="s">
+    </row>
+    <row r="30" spans="2:7">
+      <c r="B30" s="2" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B30" s="2" t="s">
+      <c r="C30" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="D30" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F30" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G30" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="D30" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E30" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F30" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G30" s="1" t="s">
+    </row>
+    <row r="31" spans="2:7">
+      <c r="B31" s="2" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B31" s="2" t="s">
+      <c r="C31" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="D31" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F31" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G31" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="D31" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E31" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F31" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G31" s="1" t="s">
+    </row>
+    <row r="32" spans="2:7">
+      <c r="B32" s="2" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B32" s="2" t="s">
+      <c r="C32" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="D32" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E32" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F32" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G32" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D32" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E32" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F32" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G32" s="1" t="s">
+    </row>
+    <row r="33" spans="2:7">
+      <c r="B33" s="1" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B33" s="1" t="s">
+      <c r="C33" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="D33" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F33" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G33" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="D33" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E33" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F33" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G33" s="1" t="s">
+    </row>
+    <row r="34" spans="2:7">
+      <c r="B34" s="1" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B34" s="1" t="s">
+      <c r="C34" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="D34" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E34" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F34" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G34" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D34" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E34" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F34" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G34" s="1" t="s">
+    </row>
+    <row r="35" spans="2:7">
+      <c r="B35" s="1" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B35" s="1" t="s">
+      <c r="C35" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="D35" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E35" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F35" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G35" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="D35" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E35" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F35" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G35" s="1" t="s">
+    </row>
+    <row r="36" spans="2:7">
+      <c r="B36" s="1" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B36" s="1" t="s">
+      <c r="C36" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="D36" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E36" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F36" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G36" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="D36" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E36" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F36" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G36" s="1" t="s">
+    </row>
+    <row r="37" spans="2:7">
+      <c r="B37" s="1" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B37" s="1" t="s">
+      <c r="C37" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="D37" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E37" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F37" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G37" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="D37" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E37" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F37" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G37" s="1" t="s">
+    </row>
+    <row r="38" spans="2:7">
+      <c r="B38" s="1" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="38" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B38" s="1" t="s">
+      <c r="C38" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="D38" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E38" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F38" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G38" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="D38" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E38" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F38" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G38" s="1" t="s">
+    </row>
+    <row r="39" spans="2:7">
+      <c r="B39" s="1" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B39" s="1" t="s">
+      <c r="C39" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="D39" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E39" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F39" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G39" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D39" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E39" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F39" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G39" s="1" t="s">
+    </row>
+    <row r="40" spans="2:7">
+      <c r="B40" s="1" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B40" s="1" t="s">
+      <c r="C40" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="D40" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E40" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F40" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G40" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="D40" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E40" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F40" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G40" s="1" t="s">
+    </row>
+    <row r="41" spans="2:7">
+      <c r="B41" s="1" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B41" s="1" t="s">
+      <c r="C41" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="D41" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E41" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F41" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G41" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="D41" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E41" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F41" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G41" s="1" t="s">
+    </row>
+    <row r="42" spans="2:7">
+      <c r="B42" s="1" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="42" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B42" s="1" t="s">
+      <c r="C42" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="D42" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E42" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F42" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G42" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="D42" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E42" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F42" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G42" s="1" t="s">
+    </row>
+    <row r="43" spans="2:7">
+      <c r="B43" s="1" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="43" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B43" s="1" t="s">
+      <c r="C43" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="D43" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E43" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F43" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G43" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="D43" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E43" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F43" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G43" s="1" t="s">
+    </row>
+    <row r="44" spans="2:7">
+      <c r="B44" s="1" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B44" s="1" t="s">
+      <c r="C44" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="D44" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E44" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F44" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G44" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D44" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E44" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F44" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G44" s="1" t="s">
+    </row>
+    <row r="45" spans="2:7">
+      <c r="B45" s="1" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="45" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B45" s="1" t="s">
+      <c r="C45" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="D45" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E45" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F45" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G45" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="D45" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E45" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F45" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G45" s="1" t="s">
+    </row>
+    <row r="46" spans="2:7">
+      <c r="B46" s="1" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="46" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B46" s="1" t="s">
+      <c r="C46" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="D46" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E46" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F46" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G46" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="D46" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E46" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F46" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G46" s="1" t="s">
+    </row>
+    <row r="47" spans="2:7">
+      <c r="B47" s="1" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="47" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B47" s="1" t="s">
+      <c r="C47" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="D47" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E47" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F47" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G47" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="D47" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E47" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F47" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G47" s="1" t="s">
+    </row>
+    <row r="48" spans="2:7">
+      <c r="B48" s="1" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="48" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B48" s="1" t="s">
+      <c r="C48" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="D48" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E48" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F48" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G48" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="D48" s="6" t="s">
+    </row>
+    <row r="49" spans="2:7">
+      <c r="B49" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="E48" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F48" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G48" s="1" t="s">
+      <c r="C49" s="1" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="49" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B49" s="1" t="s">
+      <c r="D49" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E49" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F49" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G49" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="C49" s="1" t="s">
+    </row>
+    <row r="50" spans="2:7">
+      <c r="B50" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="D49" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E49" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F49" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G49" s="1" t="s">
+      <c r="C50" s="1" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="50" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B50" s="1" t="s">
+      <c r="D50" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E50" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F50" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G50" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C50" s="1" t="s">
+    </row>
+    <row r="51" spans="2:7">
+      <c r="B51" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="D50" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="E50" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F50" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G50" s="1" t="s">
+      <c r="C51" s="1" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="51" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B51" s="1" t="s">
+      <c r="D51" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E51" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F51" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G51" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="C51" s="1" t="s">
+    </row>
+    <row r="52" spans="2:7">
+      <c r="B52" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="D51" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="E51" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F51" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G51" s="1" t="s">
+      <c r="C52" s="1" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="52" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B52" s="1" t="s">
+      <c r="D52" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E52" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F52" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G52" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="C52" s="1" t="s">
+    </row>
+    <row r="53" spans="2:7">
+      <c r="B53" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="D52" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E52" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F52" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G52" s="1" t="s">
+      <c r="C53" s="1" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="53" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B53" s="1" t="s">
+      <c r="D53" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E53" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F53" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G53" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="C53" s="1" t="s">
+    </row>
+    <row r="54" spans="2:7">
+      <c r="B54" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="D53" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E53" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F53" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G53" s="1" t="s">
+      <c r="C54" s="1" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="54" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B54" s="1" t="s">
+      <c r="D54" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E54" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F54" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G54" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="C54" s="1" t="s">
+    </row>
+    <row r="55" spans="2:7">
+      <c r="B55" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="D54" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E54" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F54" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G54" s="1" t="s">
+      <c r="C55" s="1" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="55" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B55" s="1" t="s">
+      <c r="D55" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E55" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F55" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G55" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="C55" s="1" t="s">
+    </row>
+    <row r="56" spans="2:7">
+      <c r="B56" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="D55" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E55" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F55" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G55" s="1" t="s">
+      <c r="C56" s="1" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="56" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B56" s="1" t="s">
+      <c r="D56" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E56" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F56" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G56" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="C56" s="1" t="s">
+    </row>
+    <row r="57" spans="2:7">
+      <c r="B57" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="D56" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E56" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F56" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G56" s="1" t="s">
+      <c r="C57" s="1" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="57" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B57" s="1" t="s">
+      <c r="D57" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E57" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F57" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G57" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="C57" s="1" t="s">
+    </row>
+    <row r="58" spans="2:7">
+      <c r="B58" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="D57" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E57" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F57" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G57" s="1" t="s">
+      <c r="C58" s="1" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="58" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B58" s="1" t="s">
+      <c r="D58" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E58" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F58" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G58" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="C58" s="1" t="s">
+    </row>
+    <row r="59" spans="2:7">
+      <c r="B59" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="D58" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E58" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F58" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G58" s="1" t="s">
+      <c r="C59" s="1" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="59" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B59" s="1" t="s">
+      <c r="D59" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E59" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F59" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G59" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="C59" s="1" t="s">
+    </row>
+    <row r="60" spans="2:7">
+      <c r="B60" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="D59" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E59" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F59" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G59" s="1" t="s">
+      <c r="C60" s="1" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="60" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B60" s="1" t="s">
+      <c r="D60" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E60" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F60" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G60" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="C60" s="1" t="s">
+    </row>
+    <row r="61" spans="2:7">
+      <c r="B61" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="D60" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E60" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F60" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G60" s="1" t="s">
+      <c r="C61" s="1" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="61" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B61" s="1" t="s">
+      <c r="D61" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E61" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F61" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G61" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="C61" s="1" t="s">
+    </row>
+    <row r="62" spans="2:7">
+      <c r="B62" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="D61" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E61" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F61" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G61" s="1" t="s">
+      <c r="C62" s="1" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="62" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B62" s="1" t="s">
+      <c r="D62" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E62" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F62" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G62" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="C62" s="1" t="s">
+    </row>
+    <row r="63" spans="2:7">
+      <c r="B63" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="D62" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E62" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F62" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G62" s="1" t="s">
+      <c r="C63" s="1" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="63" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B63" s="1" t="s">
+      <c r="D63" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E63" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F63" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G63" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="C63" s="1" t="s">
+    </row>
+    <row r="64" spans="2:7">
+      <c r="B64" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="D63" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E63" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F63" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G63" s="1" t="s">
+      <c r="C64" s="1" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="64" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B64" s="1" t="s">
+      <c r="D64" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E64" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F64" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G64" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="C64" s="1" t="s">
+    </row>
+    <row r="65" spans="2:7">
+      <c r="B65" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="D64" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E64" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F64" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G64" s="1" t="s">
+      <c r="C65" s="1" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="65" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B65" s="1" t="s">
+      <c r="D65" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E65" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F65" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G65" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="C65" s="1" t="s">
+    </row>
+    <row r="66" spans="2:7">
+      <c r="B66" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="D65" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E65" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F65" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G65" s="1" t="s">
+      <c r="C66" s="1" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="66" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B66" s="1" t="s">
+      <c r="D66" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E66" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F66" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G66" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="C66" s="1" t="s">
+    </row>
+    <row r="67" spans="2:7">
+      <c r="B67" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="D66" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E66" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F66" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G66" s="1" t="s">
+      <c r="C67" s="1" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="67" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B67" s="1" t="s">
+      <c r="D67" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E67" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F67" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G67" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="C67" s="1" t="s">
+    </row>
+    <row r="68" spans="2:7">
+      <c r="B68" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="D67" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E67" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F67" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G67" s="1" t="s">
+      <c r="C68" s="1" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="68" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B68" s="1" t="s">
+      <c r="D68" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E68" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F68" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G68" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C68" s="1" t="s">
+    </row>
+    <row r="69" spans="2:7">
+      <c r="B69" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="D68" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E68" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F68" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G68" s="1" t="s">
+      <c r="C69" s="1" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="69" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B69" s="1" t="s">
+      <c r="D69" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E69" s="1">
+        <v>1</v>
+      </c>
+      <c r="F69" s="1">
+        <v>0</v>
+      </c>
+      <c r="G69" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="C69" s="1" t="s">
+    </row>
+    <row r="70" spans="2:7">
+      <c r="B70" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="D69" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E69" s="1">
-        <v>1</v>
-      </c>
-      <c r="F69" s="1">
-        <v>0</v>
-      </c>
-      <c r="G69" s="1" t="s">
+      <c r="C70" s="8" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="70" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B70" s="1" t="s">
+      <c r="D70" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E70" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F70" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G70" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="C70" s="8" t="s">
+    </row>
+    <row r="71" spans="2:7">
+      <c r="B71" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="D70" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E70" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F70" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G70" s="1" t="s">
+      <c r="C71" s="1" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="71" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B71" s="1" t="s">
+      <c r="D71" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E71" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F71" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G71" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="C71" s="1" t="s">
+    </row>
+    <row r="72" spans="2:7">
+      <c r="B72" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="D71" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E71" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F71" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G71" s="1" t="s">
+      <c r="C72" s="1" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="72" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B72" s="1" t="s">
+      <c r="D72" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E72" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F72" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G72" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="C72" s="1" t="s">
+    </row>
+    <row r="73" spans="2:7">
+      <c r="B73" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="D72" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E72" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="F72" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G72" s="1" t="s">
+      <c r="C73" s="1" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="73" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B73" s="1" t="s">
+      <c r="D73" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E73" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F73" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G73" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="C73" s="1" t="s">
+    </row>
+    <row r="74" spans="2:7">
+      <c r="B74" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="D73" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E73" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="F73" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G73" s="1" t="s">
+      <c r="C74" s="1" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="74" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B74" s="1" t="s">
+      <c r="D74" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E74" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F74" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G74" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="C74" s="1" t="s">
+    </row>
+    <row r="75" spans="2:7">
+      <c r="B75" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="D74" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E74" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="F74" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G74" s="1" t="s">
+      <c r="C75" s="1" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="75" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B75" s="1" t="s">
+      <c r="D75" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E75" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F75" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="76" spans="2:7">
+      <c r="B76" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="C76" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="D75" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E75" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F75" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G75" s="1" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="76" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B76" s="9" t="s">
+      <c r="D76" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E76" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F76" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G76" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="C76" s="9" t="s">
+    </row>
+    <row r="77" spans="2:7">
+      <c r="B77" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="D76" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="E76" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F76" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G76" s="9" t="s">
+      <c r="C77" s="9" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="77" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B77" s="1" t="s">
+      <c r="D77" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E77" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F77" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G77" s="9" t="s">
         <v>241</v>
       </c>
-      <c r="C77" s="9" t="s">
+    </row>
+    <row r="78" spans="2:7">
+      <c r="B78" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="D77" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="E77" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F77" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G77" s="9" t="s">
+      <c r="C78" s="9" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="78" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B78" s="9" t="s">
+      <c r="D78" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E78" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F78" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G78" s="9" t="s">
         <v>244</v>
       </c>
-      <c r="C78" s="9" t="s">
+    </row>
+    <row r="79" spans="2:7">
+      <c r="B79" s="9" t="s">
         <v>245</v>
       </c>
-      <c r="D78" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="E78" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="F78" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G78" s="9" t="s">
+      <c r="C79" s="9" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="79" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B79" s="9" t="s">
+      <c r="D79" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E79" s="9" t="s">
         <v>247</v>
       </c>
-      <c r="C79" s="9" t="s">
+      <c r="F79" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="G79" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="D79" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="E79" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="F79" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="G79" s="9" t="s">
-        <v>250</v>
-      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" fitToWidth="0"/>
-  <extLst>
-    <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1786600546" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
-        <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
-        <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
-      </pm:sheetPrefs>
-    </ext>
-  </extLst>
+  <pageSetup paperSize="9" fitToWidth="0" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>